--- a/all_shops.xlsx
+++ b/all_shops.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1215"/>
+  <dimension ref="A1:J1216"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53338,7 +53338,7 @@
         </is>
       </c>
       <c r="B1156" t="n">
-        <v>3416</v>
+        <v>3420</v>
       </c>
       <c r="C1156" t="inlineStr">
         <is>
@@ -53347,78 +53347,26 @@
       </c>
       <c r="D1156" t="inlineStr">
         <is>
-          <t>вул Здолбунівська 15</t>
+          <t>вул Ушинського 10</t>
         </is>
       </c>
       <c r="E1156" t="inlineStr">
         <is>
-          <t>Київ</t>
+          <t>Одеса</t>
         </is>
       </c>
       <c r="F1156" t="inlineStr">
         <is>
-          <t>м. Київ</t>
+          <t>Odessa</t>
         </is>
       </c>
       <c r="G1156" t="n">
-        <v>50.4185123</v>
+        <v>46.4845584</v>
       </c>
       <c r="H1156" t="n">
-        <v>30.631541</v>
+        <v>30.7208259</v>
       </c>
       <c r="I1156" t="inlineStr">
-        <is>
-          <t>Пн: 09:30-20:00
-Вт: 09:30-20:00
-Ср: 09:30-20:00
-Чт: 09:30-20:00
-Пт: 09:30-20:00
-Сб: 09:30-20:00
-Нд: 09:30-20:00</t>
-        </is>
-      </c>
-      <c r="J1156" t="inlineStr">
-        <is>
-          <t>м. Київ</t>
-        </is>
-      </c>
-    </row>
-    <row r="1157">
-      <c r="A1157" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1157" t="n">
-        <v>3420</v>
-      </c>
-      <c r="C1157" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1157" t="inlineStr">
-        <is>
-          <t>вул Ушинського 10</t>
-        </is>
-      </c>
-      <c r="E1157" t="inlineStr">
-        <is>
-          <t>Одеса</t>
-        </is>
-      </c>
-      <c r="F1157" t="inlineStr">
-        <is>
-          <t>Odessa</t>
-        </is>
-      </c>
-      <c r="G1157" t="n">
-        <v>46.4845584</v>
-      </c>
-      <c r="H1157" t="n">
-        <v>30.7208259</v>
-      </c>
-      <c r="I1157" t="inlineStr">
         <is>
           <t>Пн: 09:00-18:00
 Вт: 09:00-18:00
@@ -53429,48 +53377,48 @@
 Нд: Вихідний</t>
         </is>
       </c>
-      <c r="J1157" t="inlineStr">
+      <c r="J1156" t="inlineStr">
         <is>
           <t>Odessa</t>
         </is>
       </c>
     </row>
-    <row r="1158">
-      <c r="A1158" t="inlineStr">
+    <row r="1157">
+      <c r="A1157" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1158" t="n">
+      <c r="B1157" t="n">
         <v>3421</v>
       </c>
-      <c r="C1158" t="inlineStr">
+      <c r="C1157" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1158" t="inlineStr">
+      <c r="D1157" t="inlineStr">
         <is>
           <t>вул Святоюріївська 10/2</t>
         </is>
       </c>
-      <c r="E1158" t="inlineStr">
+      <c r="E1157" t="inlineStr">
         <is>
           <t>Вишневе</t>
         </is>
       </c>
-      <c r="F1158" t="inlineStr">
+      <c r="F1157" t="inlineStr">
         <is>
           <t>Kiev</t>
         </is>
       </c>
-      <c r="G1158" t="n">
+      <c r="G1157" t="n">
         <v>50.3833741</v>
       </c>
-      <c r="H1158" t="n">
+      <c r="H1157" t="n">
         <v>30.3731464</v>
       </c>
-      <c r="I1158" t="inlineStr">
+      <c r="I1157" t="inlineStr">
         <is>
           <t>Пн: 09:00-19:00
 Вт: 09:00-19:00
@@ -53481,48 +53429,48 @@
 Нд: 09:00-19:00</t>
         </is>
       </c>
-      <c r="J1158" t="inlineStr">
+      <c r="J1157" t="inlineStr">
         <is>
           <t>Kiev</t>
         </is>
       </c>
     </row>
-    <row r="1159">
-      <c r="A1159" t="inlineStr">
+    <row r="1158">
+      <c r="A1158" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1159" t="n">
+      <c r="B1158" t="n">
         <v>3422</v>
       </c>
-      <c r="C1159" t="inlineStr">
+      <c r="C1158" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1159" t="inlineStr">
+      <c r="D1158" t="inlineStr">
         <is>
           <t>вул Європейська (Жовтнева) 31а</t>
         </is>
       </c>
-      <c r="E1159" t="inlineStr">
+      <c r="E1158" t="inlineStr">
         <is>
           <t>Вишневе</t>
         </is>
       </c>
-      <c r="F1159" t="inlineStr">
+      <c r="F1158" t="inlineStr">
         <is>
           <t>Kiev</t>
         </is>
       </c>
-      <c r="G1159" t="n">
+      <c r="G1158" t="n">
         <v>50.3919298</v>
       </c>
-      <c r="H1159" t="n">
+      <c r="H1158" t="n">
         <v>30.3759122</v>
       </c>
-      <c r="I1159" t="inlineStr">
+      <c r="I1158" t="inlineStr">
         <is>
           <t>Пн: 10:00-19:00
 Вт: 10:00-19:00
@@ -53533,48 +53481,48 @@
 Нд: 10:00-18:00</t>
         </is>
       </c>
-      <c r="J1159" t="inlineStr">
+      <c r="J1158" t="inlineStr">
         <is>
           <t>Kiev</t>
         </is>
       </c>
     </row>
-    <row r="1160">
-      <c r="A1160" t="inlineStr">
+    <row r="1159">
+      <c r="A1159" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1160" t="n">
+      <c r="B1159" t="n">
         <v>3424</v>
       </c>
-      <c r="C1160" t="inlineStr">
+      <c r="C1159" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1160" t="inlineStr">
+      <c r="D1159" t="inlineStr">
         <is>
           <t>просп Свободи 47</t>
         </is>
       </c>
-      <c r="E1160" t="inlineStr">
+      <c r="E1159" t="inlineStr">
         <is>
           <t>Кременчук</t>
         </is>
       </c>
-      <c r="F1160" t="inlineStr">
+      <c r="F1159" t="inlineStr">
         <is>
           <t>Полтавська</t>
         </is>
       </c>
-      <c r="G1160" t="n">
+      <c r="G1159" t="n">
         <v>49.0886626</v>
       </c>
-      <c r="H1160" t="n">
+      <c r="H1159" t="n">
         <v>33.4285175</v>
       </c>
-      <c r="I1160" t="inlineStr">
+      <c r="I1159" t="inlineStr">
         <is>
           <t>Пн: 09:00-19:00
 Вт: 09:00-19:00
@@ -53585,48 +53533,48 @@
 Нд: 09:00-17:00</t>
         </is>
       </c>
-      <c r="J1160" t="inlineStr">
+      <c r="J1159" t="inlineStr">
         <is>
           <t>Полтавська</t>
         </is>
       </c>
     </row>
-    <row r="1161">
-      <c r="A1161" t="inlineStr">
+    <row r="1160">
+      <c r="A1160" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1161" t="n">
+      <c r="B1160" t="n">
         <v>3428</v>
       </c>
-      <c r="C1161" t="inlineStr">
+      <c r="C1160" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1161" t="inlineStr">
+      <c r="D1160" t="inlineStr">
         <is>
           <t>пл Миру 11</t>
         </is>
       </c>
-      <c r="E1161" t="inlineStr">
+      <c r="E1160" t="inlineStr">
         <is>
           <t>Гадяч</t>
         </is>
       </c>
-      <c r="F1161" t="inlineStr">
+      <c r="F1160" t="inlineStr">
         <is>
           <t>Полтавська</t>
         </is>
       </c>
-      <c r="G1161" t="n">
+      <c r="G1160" t="n">
         <v>50.3739846</v>
       </c>
-      <c r="H1161" t="n">
+      <c r="H1160" t="n">
         <v>33.9836438</v>
       </c>
-      <c r="I1161" t="inlineStr">
+      <c r="I1160" t="inlineStr">
         <is>
           <t>Пн: 09:00-17:00
 Вт: 09:00-17:00
@@ -53637,48 +53585,48 @@
 Нд: 09:00-17:00</t>
         </is>
       </c>
-      <c r="J1161" t="inlineStr">
+      <c r="J1160" t="inlineStr">
         <is>
           <t>Полтавська</t>
         </is>
       </c>
     </row>
-    <row r="1162">
-      <c r="A1162" t="inlineStr">
+    <row r="1161">
+      <c r="A1161" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1162" t="n">
+      <c r="B1161" t="n">
         <v>3432</v>
       </c>
-      <c r="C1162" t="inlineStr">
+      <c r="C1161" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1162" t="inlineStr">
+      <c r="D1161" t="inlineStr">
         <is>
           <t>бул Шевченка 385</t>
         </is>
       </c>
-      <c r="E1162" t="inlineStr">
+      <c r="E1161" t="inlineStr">
         <is>
           <t>Черкаси</t>
         </is>
       </c>
-      <c r="F1162" t="inlineStr">
+      <c r="F1161" t="inlineStr">
         <is>
           <t>Черкаська</t>
         </is>
       </c>
-      <c r="G1162" t="n">
+      <c r="G1161" t="n">
         <v>49.424669</v>
       </c>
-      <c r="H1162" t="n">
+      <c r="H1161" t="n">
         <v>32.0953677</v>
       </c>
-      <c r="I1162" t="inlineStr">
+      <c r="I1161" t="inlineStr">
         <is>
           <t>Пн: 10:00-20:00
 Вт: 10:00-20:00
@@ -53689,48 +53637,48 @@
 Нд: 10:00-20:00</t>
         </is>
       </c>
-      <c r="J1162" t="inlineStr">
+      <c r="J1161" t="inlineStr">
         <is>
           <t>Черкаська</t>
         </is>
       </c>
     </row>
-    <row r="1163">
-      <c r="A1163" t="inlineStr">
+    <row r="1162">
+      <c r="A1162" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1163" t="n">
+      <c r="B1162" t="n">
         <v>3435</v>
       </c>
-      <c r="C1163" t="inlineStr">
+      <c r="C1162" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1163" t="inlineStr">
+      <c r="D1162" t="inlineStr">
         <is>
           <t>просп Науки 1/2</t>
         </is>
       </c>
-      <c r="E1163" t="inlineStr">
+      <c r="E1162" t="inlineStr">
         <is>
           <t>Київ</t>
         </is>
       </c>
-      <c r="F1163" t="inlineStr">
+      <c r="F1162" t="inlineStr">
         <is>
           <t>м. Київ</t>
         </is>
       </c>
-      <c r="G1163" t="n">
+      <c r="G1162" t="n">
         <v>50.4064898</v>
       </c>
-      <c r="H1163" t="n">
+      <c r="H1162" t="n">
         <v>30.519621</v>
       </c>
-      <c r="I1163" t="inlineStr">
+      <c r="I1162" t="inlineStr">
         <is>
           <t>Пн: 07:00-22:00
 Вт: 07:00-22:00
@@ -53741,48 +53689,48 @@
 Нд: 07:00-22:00</t>
         </is>
       </c>
-      <c r="J1163" t="inlineStr">
+      <c r="J1162" t="inlineStr">
         <is>
           <t>м. Київ</t>
         </is>
       </c>
     </row>
-    <row r="1164">
-      <c r="A1164" t="inlineStr">
+    <row r="1163">
+      <c r="A1163" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1164" t="n">
+      <c r="B1163" t="n">
         <v>3437</v>
       </c>
-      <c r="C1164" t="inlineStr">
+      <c r="C1163" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1164" t="inlineStr">
+      <c r="D1163" t="inlineStr">
         <is>
           <t>просп Богоявленський 338</t>
         </is>
       </c>
-      <c r="E1164" t="inlineStr">
+      <c r="E1163" t="inlineStr">
         <is>
           <t>Миколаїв (Миколаївська)</t>
         </is>
       </c>
-      <c r="F1164" t="inlineStr">
+      <c r="F1163" t="inlineStr">
         <is>
           <t>Миколаївська</t>
         </is>
       </c>
-      <c r="G1164" t="n">
+      <c r="G1163" t="n">
         <v>46.8557792</v>
       </c>
-      <c r="H1164" t="n">
+      <c r="H1163" t="n">
         <v>32.0141945</v>
       </c>
-      <c r="I1164" t="inlineStr">
+      <c r="I1163" t="inlineStr">
         <is>
           <t>Пн: 09:00-18:00
 Вт: 09:00-18:00
@@ -53793,48 +53741,48 @@
 Нд: 09:00-18:00</t>
         </is>
       </c>
-      <c r="J1164" t="inlineStr">
+      <c r="J1163" t="inlineStr">
         <is>
           <t>Миколаївська</t>
         </is>
       </c>
     </row>
-    <row r="1165">
-      <c r="A1165" t="inlineStr">
+    <row r="1164">
+      <c r="A1164" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1165" t="n">
+      <c r="B1164" t="n">
         <v>3441</v>
       </c>
-      <c r="C1165" t="inlineStr">
+      <c r="C1164" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1165" t="inlineStr">
+      <c r="D1164" t="inlineStr">
         <is>
           <t>вул Українська 71а</t>
         </is>
       </c>
-      <c r="E1165" t="inlineStr">
+      <c r="E1164" t="inlineStr">
         <is>
           <t>Путила</t>
         </is>
       </c>
-      <c r="F1165" t="inlineStr">
+      <c r="F1164" t="inlineStr">
         <is>
           <t>Чернівецька</t>
         </is>
       </c>
-      <c r="G1165" t="n">
+      <c r="G1164" t="n">
         <v>47.998305</v>
       </c>
-      <c r="H1165" t="n">
+      <c r="H1164" t="n">
         <v>25.0850933</v>
       </c>
-      <c r="I1165" t="inlineStr">
+      <c r="I1164" t="inlineStr">
         <is>
           <t>Пн: 09:00-18:00
 Вт: 09:00-18:00
@@ -53845,48 +53793,48 @@
 Нд: 10:00-16:00</t>
         </is>
       </c>
-      <c r="J1165" t="inlineStr">
+      <c r="J1164" t="inlineStr">
         <is>
           <t>Чернівецька</t>
         </is>
       </c>
     </row>
-    <row r="1166">
-      <c r="A1166" t="inlineStr">
+    <row r="1165">
+      <c r="A1165" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1166" t="n">
+      <c r="B1165" t="n">
         <v>3445</v>
       </c>
-      <c r="C1166" t="inlineStr">
+      <c r="C1165" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1166" t="inlineStr">
+      <c r="D1165" t="inlineStr">
         <is>
           <t>вул Шевченка 73</t>
         </is>
       </c>
-      <c r="E1166" t="inlineStr">
+      <c r="E1165" t="inlineStr">
         <is>
           <t>Снятин</t>
         </is>
       </c>
-      <c r="F1166" t="inlineStr">
+      <c r="F1165" t="inlineStr">
         <is>
           <t>Івано-Франківська</t>
         </is>
       </c>
-      <c r="G1166" t="n">
+      <c r="G1165" t="n">
         <v>48.4514483</v>
       </c>
-      <c r="H1166" t="n">
+      <c r="H1165" t="n">
         <v>25.5551122</v>
       </c>
-      <c r="I1166" t="inlineStr">
+      <c r="I1165" t="inlineStr">
         <is>
           <t>Пн: 09:00-18:00
 Вт: 09:00-18:00
@@ -53897,48 +53845,48 @@
 Нд: Вихідний</t>
         </is>
       </c>
-      <c r="J1166" t="inlineStr">
+      <c r="J1165" t="inlineStr">
         <is>
           <t>Івано-Франківська</t>
         </is>
       </c>
     </row>
-    <row r="1167">
-      <c r="A1167" t="inlineStr">
+    <row r="1166">
+      <c r="A1166" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1167" t="n">
+      <c r="B1166" t="n">
         <v>3454</v>
       </c>
-      <c r="C1167" t="inlineStr">
+      <c r="C1166" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1167" t="inlineStr">
+      <c r="D1166" t="inlineStr">
         <is>
           <t>вул Зелена 1а</t>
         </is>
       </c>
-      <c r="E1167" t="inlineStr">
+      <c r="E1166" t="inlineStr">
         <is>
           <t>Мостиська</t>
         </is>
       </c>
-      <c r="F1167" t="inlineStr">
+      <c r="F1166" t="inlineStr">
         <is>
           <t>Львівська</t>
         </is>
       </c>
-      <c r="G1167" t="n">
+      <c r="G1166" t="n">
         <v>49.7913487</v>
       </c>
-      <c r="H1167" t="n">
+      <c r="H1166" t="n">
         <v>23.1536667</v>
       </c>
-      <c r="I1167" t="inlineStr">
+      <c r="I1166" t="inlineStr">
         <is>
           <t>Пн: 09:00-19:00
 Вт: 09:00-19:00
@@ -53949,48 +53897,48 @@
 Нд: 10:00-17:00</t>
         </is>
       </c>
-      <c r="J1167" t="inlineStr">
+      <c r="J1166" t="inlineStr">
         <is>
           <t>Львівська</t>
         </is>
       </c>
     </row>
-    <row r="1168">
-      <c r="A1168" t="inlineStr">
+    <row r="1167">
+      <c r="A1167" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1168" t="n">
+      <c r="B1167" t="n">
         <v>3463</v>
       </c>
-      <c r="C1168" t="inlineStr">
+      <c r="C1167" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1168" t="inlineStr">
+      <c r="D1167" t="inlineStr">
         <is>
           <t>вул Грушевського 41А</t>
         </is>
       </c>
-      <c r="E1168" t="inlineStr">
+      <c r="E1167" t="inlineStr">
         <is>
           <t>Первомайськ</t>
         </is>
       </c>
-      <c r="F1168" t="inlineStr">
+      <c r="F1167" t="inlineStr">
         <is>
           <t>Миколаївська</t>
         </is>
       </c>
-      <c r="G1168" t="n">
+      <c r="G1167" t="n">
         <v>48.0425652</v>
       </c>
-      <c r="H1168" t="n">
+      <c r="H1167" t="n">
         <v>30.8444596</v>
       </c>
-      <c r="I1168" t="inlineStr">
+      <c r="I1167" t="inlineStr">
         <is>
           <t>Пн: 08:00-18:00
 Вт: 08:00-18:00
@@ -54001,48 +53949,48 @@
 Нд: 08:00-18:00</t>
         </is>
       </c>
-      <c r="J1168" t="inlineStr">
+      <c r="J1167" t="inlineStr">
         <is>
           <t>Миколаївська</t>
         </is>
       </c>
     </row>
-    <row r="1169">
-      <c r="A1169" t="inlineStr">
+    <row r="1168">
+      <c r="A1168" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1169" t="n">
+      <c r="B1168" t="n">
         <v>3464</v>
       </c>
-      <c r="C1169" t="inlineStr">
+      <c r="C1168" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1169" t="inlineStr">
+      <c r="D1168" t="inlineStr">
         <is>
           <t>вул Огієнка 41</t>
         </is>
       </c>
-      <c r="E1169" t="inlineStr">
+      <c r="E1168" t="inlineStr">
         <is>
           <t>Камянець-Подільский</t>
         </is>
       </c>
-      <c r="F1169" t="inlineStr">
+      <c r="F1168" t="inlineStr">
         <is>
           <t>Хмельницька</t>
         </is>
       </c>
-      <c r="G1169" t="n">
+      <c r="G1168" t="n">
         <v>48.681053</v>
       </c>
-      <c r="H1169" t="n">
+      <c r="H1168" t="n">
         <v>26.5871481</v>
       </c>
-      <c r="I1169" t="inlineStr">
+      <c r="I1168" t="inlineStr">
         <is>
           <t>Пн: 08:00-18:00
 Вт: 08:00-18:00
@@ -54053,48 +54001,48 @@
 Нд: 10:00-16:00</t>
         </is>
       </c>
-      <c r="J1169" t="inlineStr">
+      <c r="J1168" t="inlineStr">
         <is>
           <t>Хмельницька</t>
         </is>
       </c>
     </row>
-    <row r="1170">
-      <c r="A1170" t="inlineStr">
+    <row r="1169">
+      <c r="A1169" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1170" t="n">
+      <c r="B1169" t="n">
         <v>3465</v>
       </c>
-      <c r="C1170" t="inlineStr">
+      <c r="C1169" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1170" t="inlineStr">
+      <c r="D1169" t="inlineStr">
         <is>
           <t>вул Хмельницька 6</t>
         </is>
       </c>
-      <c r="E1170" t="inlineStr">
+      <c r="E1169" t="inlineStr">
         <is>
           <t>Ярмолинці</t>
         </is>
       </c>
-      <c r="F1170" t="inlineStr">
+      <c r="F1169" t="inlineStr">
         <is>
           <t>Хмельницька</t>
         </is>
       </c>
-      <c r="G1170" t="n">
+      <c r="G1169" t="n">
         <v>49.19112</v>
       </c>
-      <c r="H1170" t="n">
+      <c r="H1169" t="n">
         <v>26.83537</v>
       </c>
-      <c r="I1170" t="inlineStr">
+      <c r="I1169" t="inlineStr">
         <is>
           <t>Пн: 09:00-18:00
 Вт: 09:00-18:00
@@ -54105,48 +54053,48 @@
 Нд: Вихідний</t>
         </is>
       </c>
-      <c r="J1170" t="inlineStr">
+      <c r="J1169" t="inlineStr">
         <is>
           <t>Хмельницька</t>
         </is>
       </c>
     </row>
-    <row r="1171">
-      <c r="A1171" t="inlineStr">
+    <row r="1170">
+      <c r="A1170" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1171" t="n">
+      <c r="B1170" t="n">
         <v>3466</v>
       </c>
-      <c r="C1171" t="inlineStr">
+      <c r="C1170" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1171" t="inlineStr">
+      <c r="D1170" t="inlineStr">
         <is>
           <t>просп Берестейський (Перемоги) 86а</t>
         </is>
       </c>
-      <c r="E1171" t="inlineStr">
+      <c r="E1170" t="inlineStr">
         <is>
           <t>Київ</t>
         </is>
       </c>
-      <c r="F1171" t="inlineStr">
+      <c r="F1170" t="inlineStr">
         <is>
           <t>Kiev</t>
         </is>
       </c>
-      <c r="G1171" t="n">
+      <c r="G1170" t="n">
         <v>50.4588998</v>
       </c>
-      <c r="H1171" t="n">
+      <c r="H1170" t="n">
         <v>30.4041254</v>
       </c>
-      <c r="I1171" t="inlineStr">
+      <c r="I1170" t="inlineStr">
         <is>
           <t>Пн: 10:00-21:00
 Вт: 10:00-21:00
@@ -54157,48 +54105,48 @@
 Нд: 10:00-21:00</t>
         </is>
       </c>
-      <c r="J1171" t="inlineStr">
+      <c r="J1170" t="inlineStr">
         <is>
           <t>Kiev</t>
         </is>
       </c>
     </row>
-    <row r="1172">
-      <c r="A1172" t="inlineStr">
+    <row r="1171">
+      <c r="A1171" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1172" t="n">
+      <c r="B1171" t="n">
         <v>3467</v>
       </c>
-      <c r="C1172" t="inlineStr">
+      <c r="C1171" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1172" t="inlineStr">
+      <c r="D1171" t="inlineStr">
         <is>
           <t>вул Харківська 2/2</t>
         </is>
       </c>
-      <c r="E1172" t="inlineStr">
+      <c r="E1171" t="inlineStr">
         <is>
           <t>Суми</t>
         </is>
       </c>
-      <c r="F1172" t="inlineStr">
+      <c r="F1171" t="inlineStr">
         <is>
           <t>Сумська</t>
         </is>
       </c>
-      <c r="G1172" t="n">
+      <c r="G1171" t="n">
         <v>50.9041752</v>
       </c>
-      <c r="H1172" t="n">
+      <c r="H1171" t="n">
         <v>34.8048057</v>
       </c>
-      <c r="I1172" t="inlineStr">
+      <c r="I1171" t="inlineStr">
         <is>
           <t>Пн: 10:00-19:00
 Вт: 10:00-19:00
@@ -54209,48 +54157,48 @@
 Нд: 10:00-19:00</t>
         </is>
       </c>
-      <c r="J1172" t="inlineStr">
+      <c r="J1171" t="inlineStr">
         <is>
           <t>Сумська</t>
         </is>
       </c>
     </row>
-    <row r="1173">
-      <c r="A1173" t="inlineStr">
+    <row r="1172">
+      <c r="A1172" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1173" t="n">
+      <c r="B1172" t="n">
         <v>3470</v>
       </c>
-      <c r="C1173" t="inlineStr">
+      <c r="C1172" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1173" t="inlineStr">
+      <c r="D1172" t="inlineStr">
         <is>
           <t>вул  Хрещатик 13</t>
         </is>
       </c>
-      <c r="E1173" t="inlineStr">
+      <c r="E1172" t="inlineStr">
         <is>
           <t>Київ</t>
         </is>
       </c>
-      <c r="F1173" t="inlineStr">
+      <c r="F1172" t="inlineStr">
         <is>
           <t>м. Київ</t>
         </is>
       </c>
-      <c r="G1173" t="n">
+      <c r="G1172" t="n">
         <v>50.4487897</v>
       </c>
-      <c r="H1173" t="n">
+      <c r="H1172" t="n">
         <v>30.5233361</v>
       </c>
-      <c r="I1173" t="inlineStr">
+      <c r="I1172" t="inlineStr">
         <is>
           <t>Пн: 10:00-20:00
 Вт: 10:00-20:00
@@ -54261,48 +54209,48 @@
 Нд: 10:00-20:00</t>
         </is>
       </c>
-      <c r="J1173" t="inlineStr">
+      <c r="J1172" t="inlineStr">
         <is>
           <t>м. Київ</t>
         </is>
       </c>
     </row>
-    <row r="1174">
-      <c r="A1174" t="inlineStr">
+    <row r="1173">
+      <c r="A1173" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1174" t="n">
+      <c r="B1173" t="n">
         <v>3471</v>
       </c>
-      <c r="C1174" t="inlineStr">
+      <c r="C1173" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1174" t="inlineStr">
+      <c r="D1173" t="inlineStr">
         <is>
           <t>вул Університетська 45</t>
         </is>
       </c>
-      <c r="E1174" t="inlineStr">
+      <c r="E1173" t="inlineStr">
         <is>
           <t>Словянськ</t>
         </is>
       </c>
-      <c r="F1174" t="inlineStr">
+      <c r="F1173" t="inlineStr">
         <is>
           <t>Дніпропетровська</t>
         </is>
       </c>
-      <c r="G1174" t="n">
+      <c r="G1173" t="n">
         <v>48.0008788</v>
       </c>
-      <c r="H1174" t="n">
+      <c r="H1173" t="n">
         <v>33.4821954</v>
       </c>
-      <c r="I1174" t="inlineStr">
+      <c r="I1173" t="inlineStr">
         <is>
           <t>Пн: 10:00-17:00
 Вт: 10:00-17:00
@@ -54313,48 +54261,48 @@
 Нд: Вихідний</t>
         </is>
       </c>
-      <c r="J1174" t="inlineStr">
+      <c r="J1173" t="inlineStr">
         <is>
           <t>Дніпропетровська</t>
         </is>
       </c>
     </row>
-    <row r="1175">
-      <c r="A1175" t="inlineStr">
+    <row r="1174">
+      <c r="A1174" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1175" t="n">
+      <c r="B1174" t="n">
         <v>3472</v>
       </c>
-      <c r="C1175" t="inlineStr">
+      <c r="C1174" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1175" t="inlineStr">
+      <c r="D1174" t="inlineStr">
         <is>
           <t>вул Чернівецька 2Б</t>
         </is>
       </c>
-      <c r="E1175" t="inlineStr">
+      <c r="E1174" t="inlineStr">
         <is>
           <t>Сторожинець</t>
         </is>
       </c>
-      <c r="F1175" t="inlineStr">
+      <c r="F1174" t="inlineStr">
         <is>
           <t>Чернівецька</t>
         </is>
       </c>
-      <c r="G1175" t="n">
+      <c r="G1174" t="n">
         <v>48.1604917</v>
       </c>
-      <c r="H1175" t="n">
+      <c r="H1174" t="n">
         <v>25.721244</v>
       </c>
-      <c r="I1175" t="inlineStr">
+      <c r="I1174" t="inlineStr">
         <is>
           <t>Пн: 09:00-18:00
 Вт: 09:00-18:00
@@ -54365,48 +54313,48 @@
 Нд: Вихідний</t>
         </is>
       </c>
-      <c r="J1175" t="inlineStr">
+      <c r="J1174" t="inlineStr">
         <is>
           <t>Чернівецька</t>
         </is>
       </c>
     </row>
-    <row r="1176">
-      <c r="A1176" t="inlineStr">
+    <row r="1175">
+      <c r="A1175" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1176" t="n">
+      <c r="B1175" t="n">
         <v>3474</v>
       </c>
-      <c r="C1176" t="inlineStr">
+      <c r="C1175" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1176" t="inlineStr">
+      <c r="D1175" t="inlineStr">
         <is>
           <t>вул Нескорених (Героїв Праці) 13</t>
         </is>
       </c>
-      <c r="E1176" t="inlineStr">
+      <c r="E1175" t="inlineStr">
         <is>
           <t>Харків</t>
         </is>
       </c>
-      <c r="F1176" t="inlineStr">
+      <c r="F1175" t="inlineStr">
         <is>
           <t>Харківська</t>
         </is>
       </c>
-      <c r="G1176" t="n">
+      <c r="G1175" t="n">
         <v>50.0254117</v>
       </c>
-      <c r="H1176" t="n">
+      <c r="H1175" t="n">
         <v>36.3369339</v>
       </c>
-      <c r="I1176" t="inlineStr">
+      <c r="I1175" t="inlineStr">
         <is>
           <t>Пн: 09:00-18:00
 Вт: 09:00-18:00
@@ -54417,48 +54365,48 @@
 Нд: 09:00-17:00</t>
         </is>
       </c>
-      <c r="J1176" t="inlineStr">
+      <c r="J1175" t="inlineStr">
         <is>
           <t>Харківська</t>
         </is>
       </c>
     </row>
-    <row r="1177">
-      <c r="A1177" t="inlineStr">
+    <row r="1176">
+      <c r="A1176" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1177" t="n">
+      <c r="B1176" t="n">
         <v>3478</v>
       </c>
-      <c r="C1177" t="inlineStr">
+      <c r="C1176" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1177" t="inlineStr">
+      <c r="D1176" t="inlineStr">
         <is>
           <t>просп Європейського Союзу (Правди) 58</t>
         </is>
       </c>
-      <c r="E1177" t="inlineStr">
+      <c r="E1176" t="inlineStr">
         <is>
           <t>Київ</t>
         </is>
       </c>
-      <c r="F1177" t="inlineStr">
+      <c r="F1176" t="inlineStr">
         <is>
           <t>Kiev</t>
         </is>
       </c>
-      <c r="G1177" t="n">
+      <c r="G1176" t="n">
         <v>50.5047315</v>
       </c>
-      <c r="H1177" t="n">
+      <c r="H1176" t="n">
         <v>30.4374307</v>
       </c>
-      <c r="I1177" t="inlineStr">
+      <c r="I1176" t="inlineStr">
         <is>
           <t>Пн: 09:00-21:00
 Вт: 09:00-21:00
@@ -54469,48 +54417,48 @@
 Нд: 09:00-21:00</t>
         </is>
       </c>
-      <c r="J1177" t="inlineStr">
+      <c r="J1176" t="inlineStr">
         <is>
           <t>Kiev</t>
         </is>
       </c>
     </row>
-    <row r="1178">
-      <c r="A1178" t="inlineStr">
+    <row r="1177">
+      <c r="A1177" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1178" t="n">
+      <c r="B1177" t="n">
         <v>3479</v>
       </c>
-      <c r="C1178" t="inlineStr">
+      <c r="C1177" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1178" t="inlineStr">
+      <c r="D1177" t="inlineStr">
         <is>
           <t>вул Європейського Союзу (Правди) 47</t>
         </is>
       </c>
-      <c r="E1178" t="inlineStr">
+      <c r="E1177" t="inlineStr">
         <is>
           <t>Київ</t>
         </is>
       </c>
-      <c r="F1178" t="inlineStr">
+      <c r="F1177" t="inlineStr">
         <is>
           <t>м. Київ</t>
         </is>
       </c>
-      <c r="G1178" t="n">
+      <c r="G1177" t="n">
         <v>50.5037667</v>
       </c>
-      <c r="H1178" t="n">
+      <c r="H1177" t="n">
         <v>30.419093</v>
       </c>
-      <c r="I1178" t="inlineStr">
+      <c r="I1177" t="inlineStr">
         <is>
           <t>Пн: 10:00-22:00
 Вт: 10:00-22:00
@@ -54521,48 +54469,48 @@
 Нд: 10:00-22:00</t>
         </is>
       </c>
-      <c r="J1178" t="inlineStr">
+      <c r="J1177" t="inlineStr">
         <is>
           <t>м. Київ</t>
         </is>
       </c>
     </row>
-    <row r="1179">
-      <c r="A1179" t="inlineStr">
+    <row r="1178">
+      <c r="A1178" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1179" t="n">
+      <c r="B1178" t="n">
         <v>3480</v>
       </c>
-      <c r="C1179" t="inlineStr">
+      <c r="C1178" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1179" t="inlineStr">
+      <c r="D1178" t="inlineStr">
         <is>
           <t>вул Центральна 82а</t>
         </is>
       </c>
-      <c r="E1179" t="inlineStr">
+      <c r="E1178" t="inlineStr">
         <is>
           <t>Гайворон</t>
         </is>
       </c>
-      <c r="F1179" t="inlineStr">
+      <c r="F1178" t="inlineStr">
         <is>
           <t>Кіровоградська</t>
         </is>
       </c>
-      <c r="G1179" t="n">
+      <c r="G1178" t="n">
         <v>48.3375082</v>
       </c>
-      <c r="H1179" t="n">
+      <c r="H1178" t="n">
         <v>29.8730446</v>
       </c>
-      <c r="I1179" t="inlineStr">
+      <c r="I1178" t="inlineStr">
         <is>
           <t>Пн: 09:00-18:00
 Вт: 09:00-18:00
@@ -54573,48 +54521,48 @@
 Нд: 09:00-15:00</t>
         </is>
       </c>
-      <c r="J1179" t="inlineStr">
+      <c r="J1178" t="inlineStr">
         <is>
           <t>Кіровоградська</t>
         </is>
       </c>
     </row>
-    <row r="1180">
-      <c r="A1180" t="inlineStr">
+    <row r="1179">
+      <c r="A1179" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1180" t="n">
+      <c r="B1179" t="n">
         <v>3483</v>
       </c>
-      <c r="C1180" t="inlineStr">
+      <c r="C1179" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1180" t="inlineStr">
+      <c r="D1179" t="inlineStr">
         <is>
           <t>просп Коцюбинського 19</t>
         </is>
       </c>
-      <c r="E1180" t="inlineStr">
+      <c r="E1179" t="inlineStr">
         <is>
           <t>Вінниця</t>
         </is>
       </c>
-      <c r="F1180" t="inlineStr">
+      <c r="F1179" t="inlineStr">
         <is>
           <t>Vinnyts'ka</t>
         </is>
       </c>
-      <c r="G1180" t="n">
+      <c r="G1179" t="n">
         <v>49.239071</v>
       </c>
-      <c r="H1180" t="n">
+      <c r="H1179" t="n">
         <v>28.4981039</v>
       </c>
-      <c r="I1180" t="inlineStr">
+      <c r="I1179" t="inlineStr">
         <is>
           <t>Пн: 08:00-18:00
 Вт: 08:00-18:00
@@ -54625,48 +54573,48 @@
 Нд: 09:00-17:00</t>
         </is>
       </c>
-      <c r="J1180" t="inlineStr">
+      <c r="J1179" t="inlineStr">
         <is>
           <t>Vinnyts'ka</t>
         </is>
       </c>
     </row>
-    <row r="1181">
-      <c r="A1181" t="inlineStr">
+    <row r="1180">
+      <c r="A1180" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1181" t="n">
+      <c r="B1180" t="n">
         <v>3485</v>
       </c>
-      <c r="C1181" t="inlineStr">
+      <c r="C1180" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1181" t="inlineStr">
+      <c r="D1180" t="inlineStr">
         <is>
           <t>вул Котляра (був. Червоноармійська) 8/10</t>
         </is>
       </c>
-      <c r="E1181" t="inlineStr">
+      <c r="E1180" t="inlineStr">
         <is>
           <t>Харків</t>
         </is>
       </c>
-      <c r="F1181" t="inlineStr">
+      <c r="F1180" t="inlineStr">
         <is>
           <t>Харківська</t>
         </is>
       </c>
-      <c r="G1181" t="n">
+      <c r="G1180" t="n">
         <v>49.9892648</v>
       </c>
-      <c r="H1181" t="n">
+      <c r="H1180" t="n">
         <v>36.2077698</v>
       </c>
-      <c r="I1181" t="inlineStr">
+      <c r="I1180" t="inlineStr">
         <is>
           <t>Пн: 09:00-18:00
 Вт: 09:00-18:00
@@ -54677,48 +54625,48 @@
 Нд: 09:00-17:00</t>
         </is>
       </c>
-      <c r="J1181" t="inlineStr">
+      <c r="J1180" t="inlineStr">
         <is>
           <t>Харківська</t>
         </is>
       </c>
     </row>
-    <row r="1182">
-      <c r="A1182" t="inlineStr">
+    <row r="1181">
+      <c r="A1181" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1182" t="n">
+      <c r="B1181" t="n">
         <v>3491</v>
       </c>
-      <c r="C1182" t="inlineStr">
+      <c r="C1181" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1182" t="inlineStr">
+      <c r="D1181" t="inlineStr">
         <is>
           <t>вул Інститутська 10</t>
         </is>
       </c>
-      <c r="E1182" t="inlineStr">
+      <c r="E1181" t="inlineStr">
         <is>
           <t>Хмельницький</t>
         </is>
       </c>
-      <c r="F1182" t="inlineStr">
+      <c r="F1181" t="inlineStr">
         <is>
           <t>Хмельницька</t>
         </is>
       </c>
-      <c r="G1182" t="n">
+      <c r="G1181" t="n">
         <v>49.4098499</v>
       </c>
-      <c r="H1182" t="n">
+      <c r="H1181" t="n">
         <v>26.9605436</v>
       </c>
-      <c r="I1182" t="inlineStr">
+      <c r="I1181" t="inlineStr">
         <is>
           <t>Пн: 09:00-19:00
 Вт: 09:00-19:00
@@ -54729,48 +54677,48 @@
 Нд: 10:00-18:00</t>
         </is>
       </c>
-      <c r="J1182" t="inlineStr">
+      <c r="J1181" t="inlineStr">
         <is>
           <t>Хмельницька</t>
         </is>
       </c>
     </row>
-    <row r="1183">
-      <c r="A1183" t="inlineStr">
+    <row r="1182">
+      <c r="A1182" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1183" t="n">
+      <c r="B1182" t="n">
         <v>3494</v>
       </c>
-      <c r="C1183" t="inlineStr">
+      <c r="C1182" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1183" t="inlineStr">
+      <c r="D1182" t="inlineStr">
         <is>
           <t>вул Шевченків Шлях 144-А</t>
         </is>
       </c>
-      <c r="E1183" t="inlineStr">
+      <c r="E1182" t="inlineStr">
         <is>
           <t>Березань</t>
         </is>
       </c>
-      <c r="F1183" t="inlineStr">
+      <c r="F1182" t="inlineStr">
         <is>
           <t>Kiev</t>
         </is>
       </c>
-      <c r="G1183" t="n">
+      <c r="G1182" t="n">
         <v>50.3119113</v>
       </c>
-      <c r="H1183" t="n">
+      <c r="H1182" t="n">
         <v>31.4678577</v>
       </c>
-      <c r="I1183" t="inlineStr">
+      <c r="I1182" t="inlineStr">
         <is>
           <t>Пн: 09:00-17:00
 Вт: 09:00-17:00
@@ -54781,48 +54729,48 @@
 Нд: 10:00-16:00</t>
         </is>
       </c>
-      <c r="J1183" t="inlineStr">
+      <c r="J1182" t="inlineStr">
         <is>
           <t>Kiev</t>
         </is>
       </c>
     </row>
-    <row r="1184">
-      <c r="A1184" t="inlineStr">
+    <row r="1183">
+      <c r="A1183" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1184" t="n">
+      <c r="B1183" t="n">
         <v>3495</v>
       </c>
-      <c r="C1184" t="inlineStr">
+      <c r="C1183" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1184" t="inlineStr">
+      <c r="D1183" t="inlineStr">
         <is>
           <t>вул Міцкевича 1</t>
         </is>
       </c>
-      <c r="E1184" t="inlineStr">
+      <c r="E1183" t="inlineStr">
         <is>
           <t>Борислав</t>
         </is>
       </c>
-      <c r="F1184" t="inlineStr">
+      <c r="F1183" t="inlineStr">
         <is>
           <t>Львівська</t>
         </is>
       </c>
-      <c r="G1184" t="n">
+      <c r="G1183" t="n">
         <v>49.287286</v>
       </c>
-      <c r="H1184" t="n">
+      <c r="H1183" t="n">
         <v>23.4159004</v>
       </c>
-      <c r="I1184" t="inlineStr">
+      <c r="I1183" t="inlineStr">
         <is>
           <t>Пн: 09:00-18:00
 Вт: 09:00-18:00
@@ -54833,48 +54781,48 @@
 Нд: 10:00-17:00</t>
         </is>
       </c>
-      <c r="J1184" t="inlineStr">
+      <c r="J1183" t="inlineStr">
         <is>
           <t>Львівська</t>
         </is>
       </c>
     </row>
-    <row r="1185">
-      <c r="A1185" t="inlineStr">
+    <row r="1184">
+      <c r="A1184" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1185" t="n">
+      <c r="B1184" t="n">
         <v>3496</v>
       </c>
-      <c r="C1185" t="inlineStr">
+      <c r="C1184" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1185" t="inlineStr">
+      <c r="D1184" t="inlineStr">
         <is>
           <t>вул І.Франка 1</t>
         </is>
       </c>
-      <c r="E1185" t="inlineStr">
+      <c r="E1184" t="inlineStr">
         <is>
           <t>Верховина</t>
         </is>
       </c>
-      <c r="F1185" t="inlineStr">
+      <c r="F1184" t="inlineStr">
         <is>
           <t>Івано-Франківська</t>
         </is>
       </c>
-      <c r="G1185" t="n">
+      <c r="G1184" t="n">
         <v>48.1549768</v>
       </c>
-      <c r="H1185" t="n">
+      <c r="H1184" t="n">
         <v>24.8291227</v>
       </c>
-      <c r="I1185" t="inlineStr">
+      <c r="I1184" t="inlineStr">
         <is>
           <t>Пн: 09:00-18:00
 Вт: 09:00-18:00
@@ -54885,48 +54833,48 @@
 Нд: 10:00-16:00</t>
         </is>
       </c>
-      <c r="J1185" t="inlineStr">
+      <c r="J1184" t="inlineStr">
         <is>
           <t>Івано-Франківська</t>
         </is>
       </c>
     </row>
-    <row r="1186">
-      <c r="A1186" t="inlineStr">
+    <row r="1185">
+      <c r="A1185" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1186" t="n">
+      <c r="B1185" t="n">
         <v>3498</v>
       </c>
-      <c r="C1186" t="inlineStr">
+      <c r="C1185" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1186" t="inlineStr">
+      <c r="D1185" t="inlineStr">
         <is>
           <t>просп Олександра Поля 1/9</t>
         </is>
       </c>
-      <c r="E1186" t="inlineStr">
+      <c r="E1185" t="inlineStr">
         <is>
           <t>Дніпро</t>
         </is>
       </c>
-      <c r="F1186" t="inlineStr">
+      <c r="F1185" t="inlineStr">
         <is>
           <t>Дніпропетровська</t>
         </is>
       </c>
-      <c r="G1186" t="n">
+      <c r="G1185" t="n">
         <v>48.4642698</v>
       </c>
-      <c r="H1186" t="n">
+      <c r="H1185" t="n">
         <v>35.0290126</v>
       </c>
-      <c r="I1186" t="inlineStr">
+      <c r="I1185" t="inlineStr">
         <is>
           <t>Пн: 09:00-19:00
 Вт: 09:00-19:00
@@ -54937,48 +54885,48 @@
 Нд: 09:00-18:00</t>
         </is>
       </c>
-      <c r="J1186" t="inlineStr">
+      <c r="J1185" t="inlineStr">
         <is>
           <t>Дніпропетровська</t>
         </is>
       </c>
     </row>
-    <row r="1187">
-      <c r="A1187" t="inlineStr">
+    <row r="1186">
+      <c r="A1186" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1187" t="n">
+      <c r="B1186" t="n">
         <v>3501</v>
       </c>
-      <c r="C1187" t="inlineStr">
+      <c r="C1186" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1187" t="inlineStr">
+      <c r="D1186" t="inlineStr">
         <is>
           <t>просп Дмитра Яворницького (К.Маркса) 65</t>
         </is>
       </c>
-      <c r="E1187" t="inlineStr">
+      <c r="E1186" t="inlineStr">
         <is>
           <t>Дніпро</t>
         </is>
       </c>
-      <c r="F1187" t="inlineStr">
+      <c r="F1186" t="inlineStr">
         <is>
           <t>Дніпропетровська</t>
         </is>
       </c>
-      <c r="G1187" t="n">
+      <c r="G1186" t="n">
         <v>48.4647786</v>
       </c>
-      <c r="H1187" t="n">
+      <c r="H1186" t="n">
         <v>35.0447223</v>
       </c>
-      <c r="I1187" t="inlineStr">
+      <c r="I1186" t="inlineStr">
         <is>
           <t>Пн: 09:00-19:00
 Вт: 09:00-19:00
@@ -54989,48 +54937,48 @@
 Нд: 09:00-18:00</t>
         </is>
       </c>
-      <c r="J1187" t="inlineStr">
+      <c r="J1186" t="inlineStr">
         <is>
           <t>Дніпропетровська</t>
         </is>
       </c>
     </row>
-    <row r="1188">
-      <c r="A1188" t="inlineStr">
+    <row r="1187">
+      <c r="A1187" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1188" t="n">
+      <c r="B1187" t="n">
         <v>3503</v>
       </c>
-      <c r="C1188" t="inlineStr">
+      <c r="C1187" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1188" t="inlineStr">
+      <c r="D1187" t="inlineStr">
         <is>
           <t>вул Привокзальна 3</t>
         </is>
       </c>
-      <c r="E1188" t="inlineStr">
+      <c r="E1187" t="inlineStr">
         <is>
           <t>Київ</t>
         </is>
       </c>
-      <c r="F1188" t="inlineStr">
+      <c r="F1187" t="inlineStr">
         <is>
           <t>Kiev</t>
         </is>
       </c>
-      <c r="G1188" t="n">
+      <c r="G1187" t="n">
         <v>50.4305963</v>
       </c>
-      <c r="H1188" t="n">
+      <c r="H1187" t="n">
         <v>30.6518096</v>
       </c>
-      <c r="I1188" t="inlineStr">
+      <c r="I1187" t="inlineStr">
         <is>
           <t>Пн: 10:00-17:00
 Вт: 10:00-17:00
@@ -55041,48 +54989,48 @@
 Нд: 10:00-17:00</t>
         </is>
       </c>
-      <c r="J1188" t="inlineStr">
+      <c r="J1187" t="inlineStr">
         <is>
           <t>Kiev</t>
         </is>
       </c>
     </row>
-    <row r="1189">
-      <c r="A1189" t="inlineStr">
+    <row r="1188">
+      <c r="A1188" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1189" t="n">
+      <c r="B1188" t="n">
         <v>3505</v>
       </c>
-      <c r="C1189" t="inlineStr">
+      <c r="C1188" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1189" t="inlineStr">
+      <c r="D1188" t="inlineStr">
         <is>
           <t>пл Шевченка 26</t>
         </is>
       </c>
-      <c r="E1189" t="inlineStr">
+      <c r="E1188" t="inlineStr">
         <is>
           <t>Коломия</t>
         </is>
       </c>
-      <c r="F1189" t="inlineStr">
+      <c r="F1188" t="inlineStr">
         <is>
           <t>Івано-Франківська</t>
         </is>
       </c>
-      <c r="G1189" t="n">
+      <c r="G1188" t="n">
         <v>48.5249278</v>
       </c>
-      <c r="H1189" t="n">
+      <c r="H1188" t="n">
         <v>25.0375409</v>
       </c>
-      <c r="I1189" t="inlineStr">
+      <c r="I1188" t="inlineStr">
         <is>
           <t>Пн: 09:00-18:00
 Вт: 09:00-18:00
@@ -55093,48 +55041,48 @@
 Нд: 10:00-17:00</t>
         </is>
       </c>
-      <c r="J1189" t="inlineStr">
+      <c r="J1188" t="inlineStr">
         <is>
           <t>Івано-Франківська</t>
         </is>
       </c>
     </row>
-    <row r="1190">
-      <c r="A1190" t="inlineStr">
+    <row r="1189">
+      <c r="A1189" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1190" t="n">
+      <c r="B1189" t="n">
         <v>3506</v>
       </c>
-      <c r="C1190" t="inlineStr">
+      <c r="C1189" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1190" t="inlineStr">
+      <c r="D1189" t="inlineStr">
         <is>
           <t>вул Медова 5</t>
         </is>
       </c>
-      <c r="E1190" t="inlineStr">
+      <c r="E1189" t="inlineStr">
         <is>
           <t>Кремeнець</t>
         </is>
       </c>
-      <c r="F1190" t="inlineStr">
+      <c r="F1189" t="inlineStr">
         <is>
           <t>Тернопільська</t>
         </is>
       </c>
-      <c r="G1190" t="n">
+      <c r="G1189" t="n">
         <v>50.095605</v>
       </c>
-      <c r="H1190" t="n">
+      <c r="H1189" t="n">
         <v>25.7259463</v>
       </c>
-      <c r="I1190" t="inlineStr">
+      <c r="I1189" t="inlineStr">
         <is>
           <t>Пн: 09:00-19:00
 Вт: 09:00-19:00
@@ -55145,48 +55093,48 @@
 Нд: 10:00-16:00</t>
         </is>
       </c>
-      <c r="J1190" t="inlineStr">
+      <c r="J1189" t="inlineStr">
         <is>
           <t>Тернопільська</t>
         </is>
       </c>
     </row>
-    <row r="1191">
-      <c r="A1191" t="inlineStr">
+    <row r="1190">
+      <c r="A1190" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1191" t="n">
+      <c r="B1190" t="n">
         <v>3508</v>
       </c>
-      <c r="C1191" t="inlineStr">
+      <c r="C1190" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1191" t="inlineStr">
+      <c r="D1190" t="inlineStr">
         <is>
           <t>вул Шевченка 100</t>
         </is>
       </c>
-      <c r="E1191" t="inlineStr">
+      <c r="E1190" t="inlineStr">
         <is>
           <t>Люботин</t>
         </is>
       </c>
-      <c r="F1191" t="inlineStr">
+      <c r="F1190" t="inlineStr">
         <is>
           <t>Харківська</t>
         </is>
       </c>
-      <c r="G1191" t="n">
+      <c r="G1190" t="n">
         <v>49.9407992</v>
       </c>
-      <c r="H1191" t="n">
+      <c r="H1190" t="n">
         <v>35.9262566</v>
       </c>
-      <c r="I1191" t="inlineStr">
+      <c r="I1190" t="inlineStr">
         <is>
           <t>Пн: 08:00-18:00
 Вт: 08:00-18:00
@@ -55197,100 +55145,48 @@
 Нд: 08:00-16:00</t>
         </is>
       </c>
-      <c r="J1191" t="inlineStr">
+      <c r="J1190" t="inlineStr">
         <is>
           <t>Харківська</t>
         </is>
       </c>
     </row>
-    <row r="1192">
-      <c r="A1192" t="inlineStr">
+    <row r="1191">
+      <c r="A1191" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1192" t="n">
-        <v>3509</v>
-      </c>
-      <c r="C1192" t="inlineStr">
+      <c r="B1191" t="n">
+        <v>3510</v>
+      </c>
+      <c r="C1191" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1192" t="inlineStr">
-        <is>
-          <t>вул Шевченка 42</t>
-        </is>
-      </c>
-      <c r="E1192" t="inlineStr">
-        <is>
-          <t>Овруч</t>
-        </is>
-      </c>
-      <c r="F1192" t="inlineStr">
-        <is>
-          <t>Житомирська</t>
-        </is>
-      </c>
-      <c r="G1192" t="n">
-        <v>51.3197441</v>
-      </c>
-      <c r="H1192" t="n">
-        <v>28.8004248</v>
-      </c>
-      <c r="I1192" t="inlineStr">
-        <is>
-          <t>Пн: 09:00-18:00
-Вт: 09:00-18:00
-Ср: 09:00-18:00
-Чт: 09:00-16:00
-Пт: 09:00-18:00
-Сб: 09:00-18:00
-Нд: 09:00-18:00</t>
-        </is>
-      </c>
-      <c r="J1192" t="inlineStr">
-        <is>
-          <t>Житомирська</t>
-        </is>
-      </c>
-    </row>
-    <row r="1193">
-      <c r="A1193" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1193" t="n">
-        <v>3510</v>
-      </c>
-      <c r="C1193" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1193" t="inlineStr">
+      <c r="D1191" t="inlineStr">
         <is>
           <t>вул Петропавлівська 49</t>
         </is>
       </c>
-      <c r="E1193" t="inlineStr">
+      <c r="E1191" t="inlineStr">
         <is>
           <t>Суми</t>
         </is>
       </c>
-      <c r="F1193" t="inlineStr">
+      <c r="F1191" t="inlineStr">
         <is>
           <t>Сумська</t>
         </is>
       </c>
-      <c r="G1193" t="n">
+      <c r="G1191" t="n">
         <v>50.9065729</v>
       </c>
-      <c r="H1193" t="n">
+      <c r="H1191" t="n">
         <v>34.796901</v>
       </c>
-      <c r="I1193" t="inlineStr">
+      <c r="I1191" t="inlineStr">
         <is>
           <t>Пн: 09:00-18:00
 Вт: 09:00-18:00
@@ -55301,48 +55197,48 @@
 Нд: 09:00-18:00</t>
         </is>
       </c>
-      <c r="J1193" t="inlineStr">
+      <c r="J1191" t="inlineStr">
         <is>
           <t>Сумська</t>
         </is>
       </c>
     </row>
-    <row r="1194">
-      <c r="A1194" t="inlineStr">
+    <row r="1192">
+      <c r="A1192" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1194" t="n">
+      <c r="B1192" t="n">
         <v>3512</v>
       </c>
-      <c r="C1194" t="inlineStr">
+      <c r="C1192" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1194" t="inlineStr">
+      <c r="D1192" t="inlineStr">
         <is>
           <t>вул Валентинівська (Блюхера) 37/128</t>
         </is>
       </c>
-      <c r="E1194" t="inlineStr">
+      <c r="E1192" t="inlineStr">
         <is>
           <t>Харків</t>
         </is>
       </c>
-      <c r="F1194" t="inlineStr">
+      <c r="F1192" t="inlineStr">
         <is>
           <t>Харківська</t>
         </is>
       </c>
-      <c r="G1194" t="n">
+      <c r="G1192" t="n">
         <v>50.0098371</v>
       </c>
-      <c r="H1194" t="n">
+      <c r="H1192" t="n">
         <v>36.3503577</v>
       </c>
-      <c r="I1194" t="inlineStr">
+      <c r="I1192" t="inlineStr">
         <is>
           <t>Пн: 09:00-19:00
 Вт: 09:00-19:00
@@ -55353,48 +55249,48 @@
 Нд: 09:00-18:00</t>
         </is>
       </c>
-      <c r="J1194" t="inlineStr">
+      <c r="J1192" t="inlineStr">
         <is>
           <t>Харківська</t>
         </is>
       </c>
     </row>
-    <row r="1195">
-      <c r="A1195" t="inlineStr">
+    <row r="1193">
+      <c r="A1193" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1195" t="n">
+      <c r="B1193" t="n">
         <v>3514</v>
       </c>
-      <c r="C1195" t="inlineStr">
+      <c r="C1193" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1195" t="inlineStr">
+      <c r="D1193" t="inlineStr">
         <is>
           <t>вул Центральна 32а</t>
         </is>
       </c>
-      <c r="E1195" t="inlineStr">
+      <c r="E1193" t="inlineStr">
         <is>
           <t>Чемерівці</t>
         </is>
       </c>
-      <c r="F1195" t="inlineStr">
+      <c r="F1193" t="inlineStr">
         <is>
           <t>Хмельницька</t>
         </is>
       </c>
-      <c r="G1195" t="n">
+      <c r="G1193" t="n">
         <v>49.011295</v>
       </c>
-      <c r="H1195" t="n">
+      <c r="H1193" t="n">
         <v>26.340395</v>
       </c>
-      <c r="I1195" t="inlineStr">
+      <c r="I1193" t="inlineStr">
         <is>
           <t>Пн: 08:00-18:00
 Вт: 08:00-18:00
@@ -55405,48 +55301,48 @@
 Нд: 09:00-15:00</t>
         </is>
       </c>
-      <c r="J1195" t="inlineStr">
+      <c r="J1193" t="inlineStr">
         <is>
           <t>Хмельницька</t>
         </is>
       </c>
     </row>
-    <row r="1196">
-      <c r="A1196" t="inlineStr">
+    <row r="1194">
+      <c r="A1194" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1196" t="n">
+      <c r="B1194" t="n">
         <v>3515</v>
       </c>
-      <c r="C1196" t="inlineStr">
+      <c r="C1194" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1196" t="inlineStr">
+      <c r="D1194" t="inlineStr">
         <is>
           <t>вул Р. Шухевича 1а</t>
         </is>
       </c>
-      <c r="E1196" t="inlineStr">
+      <c r="E1194" t="inlineStr">
         <is>
           <t>Хмельницький</t>
         </is>
       </c>
-      <c r="F1196" t="inlineStr">
+      <c r="F1194" t="inlineStr">
         <is>
           <t>Хмельницька</t>
         </is>
       </c>
-      <c r="G1196" t="n">
+      <c r="G1194" t="n">
         <v>49.4360713</v>
       </c>
-      <c r="H1196" t="n">
+      <c r="H1194" t="n">
         <v>26.9572295</v>
       </c>
-      <c r="I1196" t="inlineStr">
+      <c r="I1194" t="inlineStr">
         <is>
           <t>Пн: 09:00-18:00
 Вт: 09:00-18:00
@@ -55457,48 +55353,48 @@
 Нд: 09:00-18:00</t>
         </is>
       </c>
-      <c r="J1196" t="inlineStr">
+      <c r="J1194" t="inlineStr">
         <is>
           <t>Хмельницька</t>
         </is>
       </c>
     </row>
-    <row r="1197">
-      <c r="A1197" t="inlineStr">
+    <row r="1195">
+      <c r="A1195" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1197" t="n">
+      <c r="B1195" t="n">
         <v>3516</v>
       </c>
-      <c r="C1197" t="inlineStr">
+      <c r="C1195" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1197" t="inlineStr">
+      <c r="D1195" t="inlineStr">
         <is>
           <t>просп Відрадний 69/1</t>
         </is>
       </c>
-      <c r="E1197" t="inlineStr">
+      <c r="E1195" t="inlineStr">
         <is>
           <t>Київ</t>
         </is>
       </c>
-      <c r="F1197" t="inlineStr">
+      <c r="F1195" t="inlineStr">
         <is>
           <t>Kiev</t>
         </is>
       </c>
-      <c r="G1197" t="n">
+      <c r="G1195" t="n">
         <v>50.428885</v>
       </c>
-      <c r="H1197" t="n">
+      <c r="H1195" t="n">
         <v>30.4309396</v>
       </c>
-      <c r="I1197" t="inlineStr">
+      <c r="I1195" t="inlineStr">
         <is>
           <t>Пн: 09:00-18:00
 Вт: 09:00-18:00
@@ -55509,48 +55405,48 @@
 Нд: 10:00-17:00</t>
         </is>
       </c>
-      <c r="J1197" t="inlineStr">
+      <c r="J1195" t="inlineStr">
         <is>
           <t>Kiev</t>
         </is>
       </c>
     </row>
-    <row r="1198">
-      <c r="A1198" t="inlineStr">
+    <row r="1196">
+      <c r="A1196" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1198" t="n">
+      <c r="B1196" t="n">
         <v>3517</v>
       </c>
-      <c r="C1198" t="inlineStr">
+      <c r="C1196" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1198" t="inlineStr">
+      <c r="D1196" t="inlineStr">
         <is>
           <t>просп Свободи (Леніна) 16Д</t>
         </is>
       </c>
-      <c r="E1198" t="inlineStr">
+      <c r="E1196" t="inlineStr">
         <is>
           <t>Хмільник</t>
         </is>
       </c>
-      <c r="F1198" t="inlineStr">
+      <c r="F1196" t="inlineStr">
         <is>
           <t>Vinnyts'ka</t>
         </is>
       </c>
-      <c r="G1198" t="n">
+      <c r="G1196" t="n">
         <v>49.5576747</v>
       </c>
-      <c r="H1198" t="n">
+      <c r="H1196" t="n">
         <v>27.9528561</v>
       </c>
-      <c r="I1198" t="inlineStr">
+      <c r="I1196" t="inlineStr">
         <is>
           <t>Пн: 08:00-17:00
 Вт: 08:00-17:00
@@ -55561,48 +55457,48 @@
 Нд: Вихідний</t>
         </is>
       </c>
-      <c r="J1198" t="inlineStr">
+      <c r="J1196" t="inlineStr">
         <is>
           <t>Vinnyts'ka</t>
         </is>
       </c>
     </row>
-    <row r="1199">
-      <c r="A1199" t="inlineStr">
+    <row r="1197">
+      <c r="A1197" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1199" t="n">
+      <c r="B1197" t="n">
         <v>3520</v>
       </c>
-      <c r="C1199" t="inlineStr">
+      <c r="C1197" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1199" t="inlineStr">
+      <c r="D1197" t="inlineStr">
         <is>
           <t>пл Шевченка 6</t>
         </is>
       </c>
-      <c r="E1199" t="inlineStr">
+      <c r="E1197" t="inlineStr">
         <is>
           <t>Славута</t>
         </is>
       </c>
-      <c r="F1199" t="inlineStr">
+      <c r="F1197" t="inlineStr">
         <is>
           <t>Хмельницька</t>
         </is>
       </c>
-      <c r="G1199" t="n">
+      <c r="G1197" t="n">
         <v>50.2957898</v>
       </c>
-      <c r="H1199" t="n">
+      <c r="H1197" t="n">
         <v>26.8570458</v>
       </c>
-      <c r="I1199" t="inlineStr">
+      <c r="I1197" t="inlineStr">
         <is>
           <t>Пн: 08:00-17:00
 Вт: 08:00-17:00
@@ -55613,48 +55509,48 @@
 Нд: 08:00-17:00</t>
         </is>
       </c>
-      <c r="J1199" t="inlineStr">
+      <c r="J1197" t="inlineStr">
         <is>
           <t>Хмельницька</t>
         </is>
       </c>
     </row>
-    <row r="1200">
-      <c r="A1200" t="inlineStr">
+    <row r="1198">
+      <c r="A1198" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1200" t="n">
+      <c r="B1198" t="n">
         <v>3526</v>
       </c>
-      <c r="C1200" t="inlineStr">
+      <c r="C1198" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1200" t="inlineStr">
+      <c r="D1198" t="inlineStr">
         <is>
           <t>вул Незалежності 65</t>
         </is>
       </c>
-      <c r="E1200" t="inlineStr">
+      <c r="E1198" t="inlineStr">
         <is>
           <t>Камянка-Бузька</t>
         </is>
       </c>
-      <c r="F1200" t="inlineStr">
+      <c r="F1198" t="inlineStr">
         <is>
           <t>Львівська</t>
         </is>
       </c>
-      <c r="G1200" t="n">
+      <c r="G1198" t="n">
         <v>50.107376</v>
       </c>
-      <c r="H1200" t="n">
+      <c r="H1198" t="n">
         <v>24.3436341</v>
       </c>
-      <c r="I1200" t="inlineStr">
+      <c r="I1198" t="inlineStr">
         <is>
           <t>Пн: 09:00-18:00
 Вт: 09:00-18:00
@@ -55665,48 +55561,48 @@
 Нд: 09:00-16:00</t>
         </is>
       </c>
-      <c r="J1200" t="inlineStr">
+      <c r="J1198" t="inlineStr">
         <is>
           <t>Львівська</t>
         </is>
       </c>
     </row>
-    <row r="1201">
-      <c r="A1201" t="inlineStr">
+    <row r="1199">
+      <c r="A1199" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1201" t="n">
+      <c r="B1199" t="n">
         <v>3527</v>
       </c>
-      <c r="C1201" t="inlineStr">
+      <c r="C1199" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1201" t="inlineStr">
+      <c r="D1199" t="inlineStr">
         <is>
           <t>вул Шевченка 116</t>
         </is>
       </c>
-      <c r="E1201" t="inlineStr">
+      <c r="E1199" t="inlineStr">
         <is>
           <t>Дунаївці</t>
         </is>
       </c>
-      <c r="F1201" t="inlineStr">
+      <c r="F1199" t="inlineStr">
         <is>
           <t>Хмельницька</t>
         </is>
       </c>
-      <c r="G1201" t="n">
+      <c r="G1199" t="n">
         <v>48.8922754</v>
       </c>
-      <c r="H1201" t="n">
+      <c r="H1199" t="n">
         <v>26.8568241</v>
       </c>
-      <c r="I1201" t="inlineStr">
+      <c r="I1199" t="inlineStr">
         <is>
           <t>Пн: 09:00-18:00
 Вт: 09:00-18:00
@@ -55717,48 +55613,48 @@
 Нд: 09:00-14:00</t>
         </is>
       </c>
-      <c r="J1201" t="inlineStr">
+      <c r="J1199" t="inlineStr">
         <is>
           <t>Хмельницька</t>
         </is>
       </c>
     </row>
-    <row r="1202">
-      <c r="A1202" t="inlineStr">
+    <row r="1200">
+      <c r="A1200" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1202" t="n">
+      <c r="B1200" t="n">
         <v>3530</v>
       </c>
-      <c r="C1202" t="inlineStr">
+      <c r="C1200" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1202" t="inlineStr">
+      <c r="D1200" t="inlineStr">
         <is>
           <t>вул Савіцького 14</t>
         </is>
       </c>
-      <c r="E1202" t="inlineStr">
+      <c r="E1200" t="inlineStr">
         <is>
           <t>Летичів</t>
         </is>
       </c>
-      <c r="F1202" t="inlineStr">
+      <c r="F1200" t="inlineStr">
         <is>
           <t>Хмельницька</t>
         </is>
       </c>
-      <c r="G1202" t="n">
+      <c r="G1200" t="n">
         <v>49.3813788</v>
       </c>
-      <c r="H1202" t="n">
+      <c r="H1200" t="n">
         <v>27.6197046</v>
       </c>
-      <c r="I1202" t="inlineStr">
+      <c r="I1200" t="inlineStr">
         <is>
           <t>Пн: 09:00-18:00
 Вт: 09:00-18:00
@@ -55769,48 +55665,48 @@
 Нд: 09:00-18:00</t>
         </is>
       </c>
-      <c r="J1202" t="inlineStr">
+      <c r="J1200" t="inlineStr">
         <is>
           <t>Хмельницька</t>
         </is>
       </c>
     </row>
-    <row r="1203">
-      <c r="A1203" t="inlineStr">
+    <row r="1201">
+      <c r="A1201" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1203" t="n">
+      <c r="B1201" t="n">
         <v>3531</v>
       </c>
-      <c r="C1203" t="inlineStr">
+      <c r="C1201" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1203" t="inlineStr">
+      <c r="D1201" t="inlineStr">
         <is>
           <t>вул Берестейський (Перемоги) 26</t>
         </is>
       </c>
-      <c r="E1203" t="inlineStr">
+      <c r="E1201" t="inlineStr">
         <is>
           <t>Київ</t>
         </is>
       </c>
-      <c r="F1203" t="inlineStr">
+      <c r="F1201" t="inlineStr">
         <is>
           <t>м. Київ</t>
         </is>
       </c>
-      <c r="G1203" t="n">
+      <c r="G1201" t="n">
         <v>50.4515345</v>
       </c>
-      <c r="H1203" t="n">
+      <c r="H1201" t="n">
         <v>30.4678476</v>
       </c>
-      <c r="I1203" t="inlineStr">
+      <c r="I1201" t="inlineStr">
         <is>
           <t>Пн: 10:00-21:00
 Вт: 10:00-21:00
@@ -55821,48 +55717,48 @@
 Нд: 10:00-21:00</t>
         </is>
       </c>
-      <c r="J1203" t="inlineStr">
+      <c r="J1201" t="inlineStr">
         <is>
           <t>м. Київ</t>
         </is>
       </c>
     </row>
-    <row r="1204">
-      <c r="A1204" t="inlineStr">
+    <row r="1202">
+      <c r="A1202" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1204" t="n">
+      <c r="B1202" t="n">
         <v>3532</v>
       </c>
-      <c r="C1204" t="inlineStr">
+      <c r="C1202" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1204" t="inlineStr">
+      <c r="D1202" t="inlineStr">
         <is>
           <t>вул Київська 26</t>
         </is>
       </c>
-      <c r="E1204" t="inlineStr">
+      <c r="E1202" t="inlineStr">
         <is>
           <t>Іванків</t>
         </is>
       </c>
-      <c r="F1204" t="inlineStr">
+      <c r="F1202" t="inlineStr">
         <is>
           <t>Kiev</t>
         </is>
       </c>
-      <c r="G1204" t="n">
+      <c r="G1202" t="n">
         <v>50.9338356</v>
       </c>
-      <c r="H1204" t="n">
+      <c r="H1202" t="n">
         <v>29.9031381</v>
       </c>
-      <c r="I1204" t="inlineStr">
+      <c r="I1202" t="inlineStr">
         <is>
           <t>Пн: 08:00-18:00
 Вт: 08:00-18:00
@@ -55873,48 +55769,48 @@
 Нд: 09:00-17:00</t>
         </is>
       </c>
-      <c r="J1204" t="inlineStr">
+      <c r="J1202" t="inlineStr">
         <is>
           <t>Kiev</t>
         </is>
       </c>
     </row>
-    <row r="1205">
-      <c r="A1205" t="inlineStr">
+    <row r="1203">
+      <c r="A1203" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1205" t="n">
+      <c r="B1203" t="n">
         <v>3534</v>
       </c>
-      <c r="C1205" t="inlineStr">
+      <c r="C1203" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1205" t="inlineStr">
+      <c r="D1203" t="inlineStr">
         <is>
           <t>вул Шевченка 74а</t>
         </is>
       </c>
-      <c r="E1205" t="inlineStr">
+      <c r="E1203" t="inlineStr">
         <is>
           <t>Городенка</t>
         </is>
       </c>
-      <c r="F1205" t="inlineStr">
+      <c r="F1203" t="inlineStr">
         <is>
           <t>Івано-Франківська</t>
         </is>
       </c>
-      <c r="G1205" t="n">
+      <c r="G1203" t="n">
         <v>48.66888903427731</v>
       </c>
-      <c r="H1205" t="n">
+      <c r="H1203" t="n">
         <v>25.50435338169336</v>
       </c>
-      <c r="I1205" t="inlineStr">
+      <c r="I1203" t="inlineStr">
         <is>
           <t>Пн: 08:00-18:00
 Вт: 08:00-18:00
@@ -55925,48 +55821,48 @@
 Нд: 10:00-17:00</t>
         </is>
       </c>
-      <c r="J1205" t="inlineStr">
+      <c r="J1203" t="inlineStr">
         <is>
           <t>Івано-Франківська</t>
         </is>
       </c>
     </row>
-    <row r="1206">
-      <c r="A1206" t="inlineStr">
+    <row r="1204">
+      <c r="A1204" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1206" t="n">
+      <c r="B1204" t="n">
         <v>3535</v>
       </c>
-      <c r="C1206" t="inlineStr">
+      <c r="C1204" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1206" t="inlineStr">
+      <c r="D1204" t="inlineStr">
         <is>
           <t>вул Бекетова 21</t>
         </is>
       </c>
-      <c r="E1206" t="inlineStr">
+      <c r="E1204" t="inlineStr">
         <is>
           <t>Харків</t>
         </is>
       </c>
-      <c r="F1206" t="inlineStr">
+      <c r="F1204" t="inlineStr">
         <is>
           <t>Харківська</t>
         </is>
       </c>
-      <c r="G1206" t="n">
+      <c r="G1204" t="n">
         <v>49.9512627</v>
       </c>
-      <c r="H1206" t="n">
+      <c r="H1204" t="n">
         <v>36.371922</v>
       </c>
-      <c r="I1206" t="inlineStr">
+      <c r="I1204" t="inlineStr">
         <is>
           <t>Пн: 09:00-17:00
 Вт: 09:00-17:00
@@ -55977,48 +55873,48 @@
 Нд: 09:00-16:00</t>
         </is>
       </c>
-      <c r="J1206" t="inlineStr">
+      <c r="J1204" t="inlineStr">
         <is>
           <t>Харківська</t>
         </is>
       </c>
     </row>
-    <row r="1207">
-      <c r="A1207" t="inlineStr">
+    <row r="1205">
+      <c r="A1205" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1207" t="n">
+      <c r="B1205" t="n">
         <v>3541</v>
       </c>
-      <c r="C1207" t="inlineStr">
+      <c r="C1205" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1207" t="inlineStr">
+      <c r="D1205" t="inlineStr">
         <is>
           <t>вул Одеська 121, А/1</t>
         </is>
       </c>
-      <c r="E1207" t="inlineStr">
+      <c r="E1205" t="inlineStr">
         <is>
           <t>Первомайськ</t>
         </is>
       </c>
-      <c r="F1207" t="inlineStr">
+      <c r="F1205" t="inlineStr">
         <is>
           <t>Миколаївська</t>
         </is>
       </c>
-      <c r="G1207" t="n">
+      <c r="G1205" t="n">
         <v>48.0228289</v>
       </c>
-      <c r="H1207" t="n">
+      <c r="H1205" t="n">
         <v>30.8511121</v>
       </c>
-      <c r="I1207" t="inlineStr">
+      <c r="I1205" t="inlineStr">
         <is>
           <t>Пн: 09:00-18:00
 Вт: 09:00-18:00
@@ -56029,48 +55925,48 @@
 Нд: 09:00-18:00</t>
         </is>
       </c>
-      <c r="J1207" t="inlineStr">
+      <c r="J1205" t="inlineStr">
         <is>
           <t>Миколаївська</t>
         </is>
       </c>
     </row>
-    <row r="1208">
-      <c r="A1208" t="inlineStr">
+    <row r="1206">
+      <c r="A1206" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1208" t="n">
+      <c r="B1206" t="n">
         <v>3542</v>
       </c>
-      <c r="C1208" t="inlineStr">
+      <c r="C1206" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1208" t="inlineStr">
+      <c r="D1206" t="inlineStr">
         <is>
           <t>просп Героїв Харкова 274</t>
         </is>
       </c>
-      <c r="E1208" t="inlineStr">
+      <c r="E1206" t="inlineStr">
         <is>
           <t>Харків</t>
         </is>
       </c>
-      <c r="F1208" t="inlineStr">
+      <c r="F1206" t="inlineStr">
         <is>
           <t>Харківська</t>
         </is>
       </c>
-      <c r="G1208" t="n">
+      <c r="G1206" t="n">
         <v>49.9432342</v>
       </c>
-      <c r="H1208" t="n">
+      <c r="H1206" t="n">
         <v>36.3984342</v>
       </c>
-      <c r="I1208" t="inlineStr">
+      <c r="I1206" t="inlineStr">
         <is>
           <t>Пн: 09:00-18:00
 Вт: 09:00-18:00
@@ -56081,48 +55977,48 @@
 Нд: 09:00-17:00</t>
         </is>
       </c>
-      <c r="J1208" t="inlineStr">
+      <c r="J1206" t="inlineStr">
         <is>
           <t>Харківська</t>
         </is>
       </c>
     </row>
-    <row r="1209">
-      <c r="A1209" t="inlineStr">
+    <row r="1207">
+      <c r="A1207" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1209" t="n">
+      <c r="B1207" t="n">
         <v>3543</v>
       </c>
-      <c r="C1209" t="inlineStr">
+      <c r="C1207" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1209" t="inlineStr">
+      <c r="D1207" t="inlineStr">
         <is>
           <t>вул Салтівське шосе 147</t>
         </is>
       </c>
-      <c r="E1209" t="inlineStr">
+      <c r="E1207" t="inlineStr">
         <is>
           <t>Харків</t>
         </is>
       </c>
-      <c r="F1209" t="inlineStr">
+      <c r="F1207" t="inlineStr">
         <is>
           <t>Харківська</t>
         </is>
       </c>
-      <c r="G1209" t="n">
+      <c r="G1207" t="n">
         <v>49.9908024</v>
       </c>
-      <c r="H1209" t="n">
+      <c r="H1207" t="n">
         <v>36.3585856</v>
       </c>
-      <c r="I1209" t="inlineStr">
+      <c r="I1207" t="inlineStr">
         <is>
           <t>Пн: 09:00-18:00
 Вт: 09:00-18:00
@@ -56133,48 +56029,48 @@
 Нд: 09:00-17:00</t>
         </is>
       </c>
-      <c r="J1209" t="inlineStr">
+      <c r="J1207" t="inlineStr">
         <is>
           <t>Харківська</t>
         </is>
       </c>
     </row>
-    <row r="1210">
-      <c r="A1210" t="inlineStr">
+    <row r="1208">
+      <c r="A1208" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1210" t="n">
+      <c r="B1208" t="n">
         <v>3544</v>
       </c>
-      <c r="C1210" t="inlineStr">
+      <c r="C1208" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1210" t="inlineStr">
+      <c r="D1208" t="inlineStr">
         <is>
           <t>просп Петра Григоренка 3</t>
         </is>
       </c>
-      <c r="E1210" t="inlineStr">
+      <c r="E1208" t="inlineStr">
         <is>
           <t>Харків</t>
         </is>
       </c>
-      <c r="F1210" t="inlineStr">
+      <c r="F1208" t="inlineStr">
         <is>
           <t>Харківська</t>
         </is>
       </c>
-      <c r="G1210" t="n">
+      <c r="G1208" t="n">
         <v>49.9650438</v>
       </c>
-      <c r="H1210" t="n">
+      <c r="H1208" t="n">
         <v>36.3219614</v>
       </c>
-      <c r="I1210" t="inlineStr">
+      <c r="I1208" t="inlineStr">
         <is>
           <t>Пн: 09:00-18:00
 Вт: 09:00-18:00
@@ -56185,48 +56081,48 @@
 Нд: 09:00-17:00</t>
         </is>
       </c>
-      <c r="J1210" t="inlineStr">
+      <c r="J1208" t="inlineStr">
         <is>
           <t>Харківська</t>
         </is>
       </c>
     </row>
-    <row r="1211">
-      <c r="A1211" t="inlineStr">
+    <row r="1209">
+      <c r="A1209" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1211" t="n">
+      <c r="B1209" t="n">
         <v>3545</v>
       </c>
-      <c r="C1211" t="inlineStr">
+      <c r="C1209" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1211" t="inlineStr">
+      <c r="D1209" t="inlineStr">
         <is>
           <t>просп Аерокосмічний (Гагаріна) 177</t>
         </is>
       </c>
-      <c r="E1211" t="inlineStr">
+      <c r="E1209" t="inlineStr">
         <is>
           <t>Харків</t>
         </is>
       </c>
-      <c r="F1211" t="inlineStr">
+      <c r="F1209" t="inlineStr">
         <is>
           <t>Харківська</t>
         </is>
       </c>
-      <c r="G1211" t="n">
+      <c r="G1209" t="n">
         <v>50.0169162</v>
       </c>
-      <c r="H1211" t="n">
+      <c r="H1209" t="n">
         <v>36.2067146</v>
       </c>
-      <c r="I1211" t="inlineStr">
+      <c r="I1209" t="inlineStr">
         <is>
           <t>Пн: 09:00-18:00
 Вт: 09:00-18:00
@@ -56237,48 +56133,48 @@
 Нд: 09:00-17:00</t>
         </is>
       </c>
-      <c r="J1211" t="inlineStr">
+      <c r="J1209" t="inlineStr">
         <is>
           <t>Харківська</t>
         </is>
       </c>
     </row>
-    <row r="1212">
-      <c r="A1212" t="inlineStr">
+    <row r="1210">
+      <c r="A1210" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1212" t="n">
+      <c r="B1210" t="n">
         <v>3547</v>
       </c>
-      <c r="C1212" t="inlineStr">
+      <c r="C1210" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1212" t="inlineStr">
+      <c r="D1210" t="inlineStr">
         <is>
           <t>вул Олімпійська 75</t>
         </is>
       </c>
-      <c r="E1212" t="inlineStr">
+      <c r="E1210" t="inlineStr">
         <is>
           <t>Хотин</t>
         </is>
       </c>
-      <c r="F1212" t="inlineStr">
+      <c r="F1210" t="inlineStr">
         <is>
           <t>Чернівецька</t>
         </is>
       </c>
-      <c r="G1212" t="n">
+      <c r="G1210" t="n">
         <v>48.5043413</v>
       </c>
-      <c r="H1212" t="n">
+      <c r="H1210" t="n">
         <v>26.490402</v>
       </c>
-      <c r="I1212" t="inlineStr">
+      <c r="I1210" t="inlineStr">
         <is>
           <t>Пн: 09:00-18:00
 Вт: 09:00-18:00
@@ -56289,48 +56185,48 @@
 Нд: 10:00-14:00</t>
         </is>
       </c>
-      <c r="J1212" t="inlineStr">
+      <c r="J1210" t="inlineStr">
         <is>
           <t>Чернівецька</t>
         </is>
       </c>
     </row>
-    <row r="1213">
-      <c r="A1213" t="inlineStr">
+    <row r="1211">
+      <c r="A1211" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1213" t="n">
+      <c r="B1211" t="n">
         <v>3549</v>
       </c>
-      <c r="C1213" t="inlineStr">
+      <c r="C1211" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1213" t="inlineStr">
+      <c r="D1211" t="inlineStr">
         <is>
           <t>вул Жовтнева 4-А</t>
         </is>
       </c>
-      <c r="E1213" t="inlineStr">
+      <c r="E1211" t="inlineStr">
         <is>
           <t>Гребінка</t>
         </is>
       </c>
-      <c r="F1213" t="inlineStr">
+      <c r="F1211" t="inlineStr">
         <is>
           <t>Полтавська</t>
         </is>
       </c>
-      <c r="G1213" t="n">
+      <c r="G1211" t="n">
         <v>50.1185138</v>
       </c>
-      <c r="H1213" t="n">
+      <c r="H1211" t="n">
         <v>32.4391051</v>
       </c>
-      <c r="I1213" t="inlineStr">
+      <c r="I1211" t="inlineStr">
         <is>
           <t>Пн: 09:00-17:00
 Вт: 09:00-17:00
@@ -56341,48 +56237,100 @@
 Нд: 09:00-14:00</t>
         </is>
       </c>
-      <c r="J1213" t="inlineStr">
+      <c r="J1211" t="inlineStr">
         <is>
           <t>Полтавська</t>
         </is>
       </c>
     </row>
-    <row r="1214">
-      <c r="A1214" t="inlineStr">
+    <row r="1212">
+      <c r="A1212" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1214" t="n">
-        <v>3550</v>
-      </c>
-      <c r="C1214" t="inlineStr">
+      <c r="B1212" t="n">
+        <v>3551</v>
+      </c>
+      <c r="C1212" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1214" t="inlineStr">
+      <c r="D1212" t="inlineStr">
+        <is>
+          <t>вул Шевченка 50</t>
+        </is>
+      </c>
+      <c r="E1212" t="inlineStr">
+        <is>
+          <t>Богородчани</t>
+        </is>
+      </c>
+      <c r="F1212" t="inlineStr">
+        <is>
+          <t>Івано-Франківська</t>
+        </is>
+      </c>
+      <c r="G1212" t="n">
+        <v>48.809756</v>
+      </c>
+      <c r="H1212" t="n">
+        <v>24.5400082</v>
+      </c>
+      <c r="I1212" t="inlineStr">
+        <is>
+          <t>Пн: 09:00-18:00
+Вт: 09:00-18:00
+Ср: 09:00-18:00
+Чт: 09:00-18:00
+Пт: 09:00-18:00
+Сб: 09:00-17:00
+Нд: 10:00-16:00</t>
+        </is>
+      </c>
+      <c r="J1212" t="inlineStr">
+        <is>
+          <t>Івано-Франківська</t>
+        </is>
+      </c>
+    </row>
+    <row r="1213">
+      <c r="A1213" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1213" t="n">
+        <v>3552</v>
+      </c>
+      <c r="C1213" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1213" t="inlineStr">
         <is>
           <t>вул Макухи 1</t>
         </is>
       </c>
-      <c r="E1214" t="inlineStr">
+      <c r="E1213" t="inlineStr">
         <is>
           <t>Тлумач</t>
         </is>
       </c>
-      <c r="F1214" t="inlineStr">
+      <c r="F1213" t="inlineStr">
         <is>
           <t>Івано-Франківська</t>
         </is>
       </c>
-      <c r="G1214" t="n">
+      <c r="G1213" t="n">
         <v>48.8652727</v>
       </c>
-      <c r="H1214" t="n">
+      <c r="H1213" t="n">
         <v>25.0043864</v>
       </c>
-      <c r="I1214" t="inlineStr">
+      <c r="I1213" t="inlineStr">
         <is>
           <t>Пн: 09:00-17:00
 Вт: 09:00-17:00
@@ -56393,9 +56341,61 @@
 Нд: Вихідний</t>
         </is>
       </c>
+      <c r="J1213" t="inlineStr">
+        <is>
+          <t>Івано-Франківська</t>
+        </is>
+      </c>
+    </row>
+    <row r="1214">
+      <c r="A1214" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1214" t="n">
+        <v>3554</v>
+      </c>
+      <c r="C1214" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1214" t="inlineStr">
+        <is>
+          <t>вул Городоцька 137</t>
+        </is>
+      </c>
+      <c r="E1214" t="inlineStr">
+        <is>
+          <t>Львів</t>
+        </is>
+      </c>
+      <c r="F1214" t="inlineStr">
+        <is>
+          <t>Львівська</t>
+        </is>
+      </c>
+      <c r="G1214" t="n">
+        <v>49.8367768</v>
+      </c>
+      <c r="H1214" t="n">
+        <v>24.0028087</v>
+      </c>
+      <c r="I1214" t="inlineStr">
+        <is>
+          <t>Пн: 09:00-19:00
+Вт: 09:00-19:00
+Ср: 09:00-19:00
+Чт: 09:00-19:00
+Пт: 09:00-19:00
+Сб: 09:00-18:00
+Нд: 10:00-18:00</t>
+        </is>
+      </c>
       <c r="J1214" t="inlineStr">
         <is>
-          <t>Івано-Франківська</t>
+          <t>Львівська</t>
         </is>
       </c>
     </row>
@@ -56406,7 +56406,7 @@
         </is>
       </c>
       <c r="B1215" t="n">
-        <v>3551</v>
+        <v>3555</v>
       </c>
       <c r="C1215" t="inlineStr">
         <is>
@@ -56415,39 +56415,91 @@
       </c>
       <c r="D1215" t="inlineStr">
         <is>
-          <t>вул Шевченка 50</t>
+          <t>вул Здолбунівська 15</t>
         </is>
       </c>
       <c r="E1215" t="inlineStr">
         <is>
-          <t>Богородчани</t>
+          <t>Київ</t>
         </is>
       </c>
       <c r="F1215" t="inlineStr">
         <is>
-          <t>Івано-Франківська</t>
+          <t>м. Київ</t>
         </is>
       </c>
       <c r="G1215" t="n">
-        <v>48.809756</v>
+        <v>50.4185123</v>
       </c>
       <c r="H1215" t="n">
-        <v>24.5400082</v>
+        <v>30.631541</v>
       </c>
       <c r="I1215" t="inlineStr">
+        <is>
+          <t>Пн: 10:00-20:00
+Вт: 10:00-20:00
+Ср: 10:00-20:00
+Чт: 10:00-20:00
+Пт: 10:00-20:00
+Сб: 10:00-20:00
+Нд: 10:00-20:00</t>
+        </is>
+      </c>
+      <c r="J1215" t="inlineStr">
+        <is>
+          <t>м. Київ</t>
+        </is>
+      </c>
+    </row>
+    <row r="1216">
+      <c r="A1216" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1216" t="n">
+        <v>3556</v>
+      </c>
+      <c r="C1216" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1216" t="inlineStr">
+        <is>
+          <t>вул Шевченка 42</t>
+        </is>
+      </c>
+      <c r="E1216" t="inlineStr">
+        <is>
+          <t>Овруч</t>
+        </is>
+      </c>
+      <c r="F1216" t="inlineStr">
+        <is>
+          <t>Житомирська</t>
+        </is>
+      </c>
+      <c r="G1216" t="n">
+        <v>51.3197441</v>
+      </c>
+      <c r="H1216" t="n">
+        <v>28.8004248</v>
+      </c>
+      <c r="I1216" t="inlineStr">
         <is>
           <t>Пн: 09:00-18:00
 Вт: 09:00-18:00
 Ср: 09:00-18:00
 Чт: 09:00-18:00
 Пт: 09:00-18:00
-Сб: 09:00-17:00
-Нд: 10:00-16:00</t>
-        </is>
-      </c>
-      <c r="J1215" t="inlineStr">
-        <is>
-          <t>Івано-Франківська</t>
+Сб: 09:00-18:00
+Нд: 09:00-18:00</t>
+        </is>
+      </c>
+      <c r="J1216" t="inlineStr">
+        <is>
+          <t>Житомирська</t>
         </is>
       </c>
     </row>

--- a/all_shops.xlsx
+++ b/all_shops.xlsx
@@ -55730,7 +55730,7 @@
         </is>
       </c>
       <c r="B1202" t="n">
-        <v>3532</v>
+        <v>3534</v>
       </c>
       <c r="C1202" t="inlineStr">
         <is>
@@ -55739,26 +55739,754 @@
       </c>
       <c r="D1202" t="inlineStr">
         <is>
+          <t>вул Шевченка 74а</t>
+        </is>
+      </c>
+      <c r="E1202" t="inlineStr">
+        <is>
+          <t>Городенка</t>
+        </is>
+      </c>
+      <c r="F1202" t="inlineStr">
+        <is>
+          <t>Івано-Франківська</t>
+        </is>
+      </c>
+      <c r="G1202" t="n">
+        <v>48.66888903427731</v>
+      </c>
+      <c r="H1202" t="n">
+        <v>25.50435338169336</v>
+      </c>
+      <c r="I1202" t="inlineStr">
+        <is>
+          <t>Пн: 08:00-18:00
+Вт: 08:00-18:00
+Ср: 08:00-18:00
+Чт: 08:00-18:00
+Пт: 08:00-18:00
+Сб: 08:00-18:00
+Нд: 10:00-17:00</t>
+        </is>
+      </c>
+      <c r="J1202" t="inlineStr">
+        <is>
+          <t>Івано-Франківська</t>
+        </is>
+      </c>
+    </row>
+    <row r="1203">
+      <c r="A1203" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1203" t="n">
+        <v>3535</v>
+      </c>
+      <c r="C1203" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1203" t="inlineStr">
+        <is>
+          <t>вул Бекетова 21</t>
+        </is>
+      </c>
+      <c r="E1203" t="inlineStr">
+        <is>
+          <t>Харків</t>
+        </is>
+      </c>
+      <c r="F1203" t="inlineStr">
+        <is>
+          <t>Харківська</t>
+        </is>
+      </c>
+      <c r="G1203" t="n">
+        <v>49.9512627</v>
+      </c>
+      <c r="H1203" t="n">
+        <v>36.371922</v>
+      </c>
+      <c r="I1203" t="inlineStr">
+        <is>
+          <t>Пн: 09:00-17:00
+Вт: 09:00-17:00
+Ср: 09:00-17:00
+Чт: 09:00-17:00
+Пт: 09:00-17:00
+Сб: 09:00-17:00
+Нд: 09:00-16:00</t>
+        </is>
+      </c>
+      <c r="J1203" t="inlineStr">
+        <is>
+          <t>Харківська</t>
+        </is>
+      </c>
+    </row>
+    <row r="1204">
+      <c r="A1204" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1204" t="n">
+        <v>3541</v>
+      </c>
+      <c r="C1204" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1204" t="inlineStr">
+        <is>
+          <t>вул Одеська 121, А/1</t>
+        </is>
+      </c>
+      <c r="E1204" t="inlineStr">
+        <is>
+          <t>Первомайськ</t>
+        </is>
+      </c>
+      <c r="F1204" t="inlineStr">
+        <is>
+          <t>Миколаївська</t>
+        </is>
+      </c>
+      <c r="G1204" t="n">
+        <v>48.0228289</v>
+      </c>
+      <c r="H1204" t="n">
+        <v>30.8511121</v>
+      </c>
+      <c r="I1204" t="inlineStr">
+        <is>
+          <t>Пн: 09:00-18:00
+Вт: 09:00-18:00
+Ср: 09:00-18:00
+Чт: 09:00-18:00
+Пт: 09:00-18:00
+Сб: 09:00-18:00
+Нд: 09:00-18:00</t>
+        </is>
+      </c>
+      <c r="J1204" t="inlineStr">
+        <is>
+          <t>Миколаївська</t>
+        </is>
+      </c>
+    </row>
+    <row r="1205">
+      <c r="A1205" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1205" t="n">
+        <v>3542</v>
+      </c>
+      <c r="C1205" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1205" t="inlineStr">
+        <is>
+          <t>просп Героїв Харкова 274</t>
+        </is>
+      </c>
+      <c r="E1205" t="inlineStr">
+        <is>
+          <t>Харків</t>
+        </is>
+      </c>
+      <c r="F1205" t="inlineStr">
+        <is>
+          <t>Харківська</t>
+        </is>
+      </c>
+      <c r="G1205" t="n">
+        <v>49.9432342</v>
+      </c>
+      <c r="H1205" t="n">
+        <v>36.3984342</v>
+      </c>
+      <c r="I1205" t="inlineStr">
+        <is>
+          <t>Пн: 09:00-18:00
+Вт: 09:00-18:00
+Ср: 09:00-18:00
+Чт: 09:00-18:00
+Пт: 09:00-18:00
+Сб: 09:00-17:00
+Нд: 09:00-17:00</t>
+        </is>
+      </c>
+      <c r="J1205" t="inlineStr">
+        <is>
+          <t>Харківська</t>
+        </is>
+      </c>
+    </row>
+    <row r="1206">
+      <c r="A1206" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1206" t="n">
+        <v>3543</v>
+      </c>
+      <c r="C1206" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1206" t="inlineStr">
+        <is>
+          <t>вул Салтівське шосе 147</t>
+        </is>
+      </c>
+      <c r="E1206" t="inlineStr">
+        <is>
+          <t>Харків</t>
+        </is>
+      </c>
+      <c r="F1206" t="inlineStr">
+        <is>
+          <t>Харківська</t>
+        </is>
+      </c>
+      <c r="G1206" t="n">
+        <v>49.9908024</v>
+      </c>
+      <c r="H1206" t="n">
+        <v>36.3585856</v>
+      </c>
+      <c r="I1206" t="inlineStr">
+        <is>
+          <t>Пн: 09:00-18:00
+Вт: 09:00-18:00
+Ср: 09:00-18:00
+Чт: 09:00-18:00
+Пт: 09:00-18:00
+Сб: 09:00-17:00
+Нд: 09:00-17:00</t>
+        </is>
+      </c>
+      <c r="J1206" t="inlineStr">
+        <is>
+          <t>Харківська</t>
+        </is>
+      </c>
+    </row>
+    <row r="1207">
+      <c r="A1207" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1207" t="n">
+        <v>3544</v>
+      </c>
+      <c r="C1207" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1207" t="inlineStr">
+        <is>
+          <t>просп Петра Григоренка 3</t>
+        </is>
+      </c>
+      <c r="E1207" t="inlineStr">
+        <is>
+          <t>Харків</t>
+        </is>
+      </c>
+      <c r="F1207" t="inlineStr">
+        <is>
+          <t>Харківська</t>
+        </is>
+      </c>
+      <c r="G1207" t="n">
+        <v>49.9650438</v>
+      </c>
+      <c r="H1207" t="n">
+        <v>36.3219614</v>
+      </c>
+      <c r="I1207" t="inlineStr">
+        <is>
+          <t>Пн: 09:00-18:00
+Вт: 09:00-18:00
+Ср: 09:00-18:00
+Чт: 09:00-18:00
+Пт: 09:00-18:00
+Сб: 09:00-17:00
+Нд: 09:00-17:00</t>
+        </is>
+      </c>
+      <c r="J1207" t="inlineStr">
+        <is>
+          <t>Харківська</t>
+        </is>
+      </c>
+    </row>
+    <row r="1208">
+      <c r="A1208" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1208" t="n">
+        <v>3545</v>
+      </c>
+      <c r="C1208" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1208" t="inlineStr">
+        <is>
+          <t>просп Аерокосмічний (Гагаріна) 177</t>
+        </is>
+      </c>
+      <c r="E1208" t="inlineStr">
+        <is>
+          <t>Харків</t>
+        </is>
+      </c>
+      <c r="F1208" t="inlineStr">
+        <is>
+          <t>Харківська</t>
+        </is>
+      </c>
+      <c r="G1208" t="n">
+        <v>50.0169162</v>
+      </c>
+      <c r="H1208" t="n">
+        <v>36.2067146</v>
+      </c>
+      <c r="I1208" t="inlineStr">
+        <is>
+          <t>Пн: 09:00-18:00
+Вт: 09:00-18:00
+Ср: 09:00-18:00
+Чт: 09:00-18:00
+Пт: 09:00-18:00
+Сб: 09:00-17:00
+Нд: 09:00-17:00</t>
+        </is>
+      </c>
+      <c r="J1208" t="inlineStr">
+        <is>
+          <t>Харківська</t>
+        </is>
+      </c>
+    </row>
+    <row r="1209">
+      <c r="A1209" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1209" t="n">
+        <v>3547</v>
+      </c>
+      <c r="C1209" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1209" t="inlineStr">
+        <is>
+          <t>вул Олімпійська 75</t>
+        </is>
+      </c>
+      <c r="E1209" t="inlineStr">
+        <is>
+          <t>Хотин</t>
+        </is>
+      </c>
+      <c r="F1209" t="inlineStr">
+        <is>
+          <t>Чернівецька</t>
+        </is>
+      </c>
+      <c r="G1209" t="n">
+        <v>48.5043413</v>
+      </c>
+      <c r="H1209" t="n">
+        <v>26.490402</v>
+      </c>
+      <c r="I1209" t="inlineStr">
+        <is>
+          <t>Пн: 09:00-18:00
+Вт: 09:00-18:00
+Ср: 09:00-18:00
+Чт: 09:00-18:00
+Пт: 09:00-18:00
+Сб: 09:00-17:00
+Нд: 10:00-14:00</t>
+        </is>
+      </c>
+      <c r="J1209" t="inlineStr">
+        <is>
+          <t>Чернівецька</t>
+        </is>
+      </c>
+    </row>
+    <row r="1210">
+      <c r="A1210" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1210" t="n">
+        <v>3549</v>
+      </c>
+      <c r="C1210" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1210" t="inlineStr">
+        <is>
+          <t>вул Жовтнева 4-А</t>
+        </is>
+      </c>
+      <c r="E1210" t="inlineStr">
+        <is>
+          <t>Гребінка</t>
+        </is>
+      </c>
+      <c r="F1210" t="inlineStr">
+        <is>
+          <t>Полтавська</t>
+        </is>
+      </c>
+      <c r="G1210" t="n">
+        <v>50.1185138</v>
+      </c>
+      <c r="H1210" t="n">
+        <v>32.4391051</v>
+      </c>
+      <c r="I1210" t="inlineStr">
+        <is>
+          <t>Пн: 09:00-17:00
+Вт: 09:00-17:00
+Ср: 09:00-17:00
+Чт: 09:00-17:00
+Пт: 09:00-17:00
+Сб: 09:00-14:00
+Нд: 09:00-14:00</t>
+        </is>
+      </c>
+      <c r="J1210" t="inlineStr">
+        <is>
+          <t>Полтавська</t>
+        </is>
+      </c>
+    </row>
+    <row r="1211">
+      <c r="A1211" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1211" t="n">
+        <v>3551</v>
+      </c>
+      <c r="C1211" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1211" t="inlineStr">
+        <is>
+          <t>вул Шевченка 50</t>
+        </is>
+      </c>
+      <c r="E1211" t="inlineStr">
+        <is>
+          <t>Богородчани</t>
+        </is>
+      </c>
+      <c r="F1211" t="inlineStr">
+        <is>
+          <t>Івано-Франківська</t>
+        </is>
+      </c>
+      <c r="G1211" t="n">
+        <v>48.809756</v>
+      </c>
+      <c r="H1211" t="n">
+        <v>24.5400082</v>
+      </c>
+      <c r="I1211" t="inlineStr">
+        <is>
+          <t>Пн: 09:00-18:00
+Вт: 09:00-18:00
+Ср: 09:00-18:00
+Чт: 09:00-18:00
+Пт: 09:00-18:00
+Сб: 09:00-17:00
+Нд: 10:00-16:00</t>
+        </is>
+      </c>
+      <c r="J1211" t="inlineStr">
+        <is>
+          <t>Івано-Франківська</t>
+        </is>
+      </c>
+    </row>
+    <row r="1212">
+      <c r="A1212" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1212" t="n">
+        <v>3552</v>
+      </c>
+      <c r="C1212" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1212" t="inlineStr">
+        <is>
+          <t>вул Макухи 1</t>
+        </is>
+      </c>
+      <c r="E1212" t="inlineStr">
+        <is>
+          <t>Тлумач</t>
+        </is>
+      </c>
+      <c r="F1212" t="inlineStr">
+        <is>
+          <t>Івано-Франківська</t>
+        </is>
+      </c>
+      <c r="G1212" t="n">
+        <v>48.8652727</v>
+      </c>
+      <c r="H1212" t="n">
+        <v>25.0043864</v>
+      </c>
+      <c r="I1212" t="inlineStr">
+        <is>
+          <t>Пн: 09:00-17:00
+Вт: 09:00-17:00
+Ср: 09:00-17:00
+Чт: 09:00-17:00
+Пт: 09:00-17:00
+Сб: Вихідний
+Нд: Вихідний</t>
+        </is>
+      </c>
+      <c r="J1212" t="inlineStr">
+        <is>
+          <t>Івано-Франківська</t>
+        </is>
+      </c>
+    </row>
+    <row r="1213">
+      <c r="A1213" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1213" t="n">
+        <v>3554</v>
+      </c>
+      <c r="C1213" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1213" t="inlineStr">
+        <is>
+          <t>вул Городоцька 137</t>
+        </is>
+      </c>
+      <c r="E1213" t="inlineStr">
+        <is>
+          <t>Львів</t>
+        </is>
+      </c>
+      <c r="F1213" t="inlineStr">
+        <is>
+          <t>Львівська</t>
+        </is>
+      </c>
+      <c r="G1213" t="n">
+        <v>49.8367768</v>
+      </c>
+      <c r="H1213" t="n">
+        <v>24.0028087</v>
+      </c>
+      <c r="I1213" t="inlineStr">
+        <is>
+          <t>Пн: 09:00-19:00
+Вт: 09:00-19:00
+Ср: 09:00-19:00
+Чт: 09:00-19:00
+Пт: 09:00-19:00
+Сб: 09:00-18:00
+Нд: 10:00-18:00</t>
+        </is>
+      </c>
+      <c r="J1213" t="inlineStr">
+        <is>
+          <t>Львівська</t>
+        </is>
+      </c>
+    </row>
+    <row r="1214">
+      <c r="A1214" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1214" t="n">
+        <v>3555</v>
+      </c>
+      <c r="C1214" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1214" t="inlineStr">
+        <is>
+          <t>вул Здолбунівська 15</t>
+        </is>
+      </c>
+      <c r="E1214" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="F1214" t="inlineStr">
+        <is>
+          <t>м. Київ</t>
+        </is>
+      </c>
+      <c r="G1214" t="n">
+        <v>50.4185123</v>
+      </c>
+      <c r="H1214" t="n">
+        <v>30.631541</v>
+      </c>
+      <c r="I1214" t="inlineStr">
+        <is>
+          <t>Пн: 10:00-20:00
+Вт: 10:00-20:00
+Ср: 10:00-20:00
+Чт: 10:00-20:00
+Пт: 10:00-20:00
+Сб: 10:00-20:00
+Нд: 10:00-20:00</t>
+        </is>
+      </c>
+      <c r="J1214" t="inlineStr">
+        <is>
+          <t>м. Київ</t>
+        </is>
+      </c>
+    </row>
+    <row r="1215">
+      <c r="A1215" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1215" t="n">
+        <v>3556</v>
+      </c>
+      <c r="C1215" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1215" t="inlineStr">
+        <is>
+          <t>вул Шевченка 42</t>
+        </is>
+      </c>
+      <c r="E1215" t="inlineStr">
+        <is>
+          <t>Овруч</t>
+        </is>
+      </c>
+      <c r="F1215" t="inlineStr">
+        <is>
+          <t>Житомирська</t>
+        </is>
+      </c>
+      <c r="G1215" t="n">
+        <v>51.3197441</v>
+      </c>
+      <c r="H1215" t="n">
+        <v>28.8004248</v>
+      </c>
+      <c r="I1215" t="inlineStr">
+        <is>
+          <t>Пн: 09:00-18:00
+Вт: 09:00-18:00
+Ср: 09:00-18:00
+Чт: 09:00-18:00
+Пт: 09:00-18:00
+Сб: 09:00-18:00
+Нд: 09:00-18:00</t>
+        </is>
+      </c>
+      <c r="J1215" t="inlineStr">
+        <is>
+          <t>Житомирська</t>
+        </is>
+      </c>
+    </row>
+    <row r="1216">
+      <c r="A1216" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1216" t="n">
+        <v>3557</v>
+      </c>
+      <c r="C1216" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1216" t="inlineStr">
+        <is>
           <t>вул Київська 26</t>
         </is>
       </c>
-      <c r="E1202" t="inlineStr">
+      <c r="E1216" t="inlineStr">
         <is>
           <t>Іванків</t>
         </is>
       </c>
-      <c r="F1202" t="inlineStr">
+      <c r="F1216" t="inlineStr">
         <is>
           <t>Kiev</t>
         </is>
       </c>
-      <c r="G1202" t="n">
+      <c r="G1216" t="n">
         <v>50.9338356</v>
       </c>
-      <c r="H1202" t="n">
+      <c r="H1216" t="n">
         <v>29.9031381</v>
       </c>
-      <c r="I1202" t="inlineStr">
+      <c r="I1216" t="inlineStr">
         <is>
           <t>Пн: 08:00-18:00
 Вт: 08:00-18:00
@@ -55769,737 +56497,9 @@
 Нд: 09:00-17:00</t>
         </is>
       </c>
-      <c r="J1202" t="inlineStr">
+      <c r="J1216" t="inlineStr">
         <is>
           <t>Kiev</t>
-        </is>
-      </c>
-    </row>
-    <row r="1203">
-      <c r="A1203" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1203" t="n">
-        <v>3534</v>
-      </c>
-      <c r="C1203" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1203" t="inlineStr">
-        <is>
-          <t>вул Шевченка 74а</t>
-        </is>
-      </c>
-      <c r="E1203" t="inlineStr">
-        <is>
-          <t>Городенка</t>
-        </is>
-      </c>
-      <c r="F1203" t="inlineStr">
-        <is>
-          <t>Івано-Франківська</t>
-        </is>
-      </c>
-      <c r="G1203" t="n">
-        <v>48.66888903427731</v>
-      </c>
-      <c r="H1203" t="n">
-        <v>25.50435338169336</v>
-      </c>
-      <c r="I1203" t="inlineStr">
-        <is>
-          <t>Пн: 08:00-18:00
-Вт: 08:00-18:00
-Ср: 08:00-18:00
-Чт: 08:00-18:00
-Пт: 08:00-18:00
-Сб: 08:00-18:00
-Нд: 10:00-17:00</t>
-        </is>
-      </c>
-      <c r="J1203" t="inlineStr">
-        <is>
-          <t>Івано-Франківська</t>
-        </is>
-      </c>
-    </row>
-    <row r="1204">
-      <c r="A1204" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1204" t="n">
-        <v>3535</v>
-      </c>
-      <c r="C1204" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1204" t="inlineStr">
-        <is>
-          <t>вул Бекетова 21</t>
-        </is>
-      </c>
-      <c r="E1204" t="inlineStr">
-        <is>
-          <t>Харків</t>
-        </is>
-      </c>
-      <c r="F1204" t="inlineStr">
-        <is>
-          <t>Харківська</t>
-        </is>
-      </c>
-      <c r="G1204" t="n">
-        <v>49.9512627</v>
-      </c>
-      <c r="H1204" t="n">
-        <v>36.371922</v>
-      </c>
-      <c r="I1204" t="inlineStr">
-        <is>
-          <t>Пн: 09:00-17:00
-Вт: 09:00-17:00
-Ср: 09:00-17:00
-Чт: 09:00-17:00
-Пт: 09:00-17:00
-Сб: 09:00-17:00
-Нд: 09:00-16:00</t>
-        </is>
-      </c>
-      <c r="J1204" t="inlineStr">
-        <is>
-          <t>Харківська</t>
-        </is>
-      </c>
-    </row>
-    <row r="1205">
-      <c r="A1205" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1205" t="n">
-        <v>3541</v>
-      </c>
-      <c r="C1205" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1205" t="inlineStr">
-        <is>
-          <t>вул Одеська 121, А/1</t>
-        </is>
-      </c>
-      <c r="E1205" t="inlineStr">
-        <is>
-          <t>Первомайськ</t>
-        </is>
-      </c>
-      <c r="F1205" t="inlineStr">
-        <is>
-          <t>Миколаївська</t>
-        </is>
-      </c>
-      <c r="G1205" t="n">
-        <v>48.0228289</v>
-      </c>
-      <c r="H1205" t="n">
-        <v>30.8511121</v>
-      </c>
-      <c r="I1205" t="inlineStr">
-        <is>
-          <t>Пн: 09:00-18:00
-Вт: 09:00-18:00
-Ср: 09:00-18:00
-Чт: 09:00-18:00
-Пт: 09:00-18:00
-Сб: 09:00-18:00
-Нд: 09:00-18:00</t>
-        </is>
-      </c>
-      <c r="J1205" t="inlineStr">
-        <is>
-          <t>Миколаївська</t>
-        </is>
-      </c>
-    </row>
-    <row r="1206">
-      <c r="A1206" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1206" t="n">
-        <v>3542</v>
-      </c>
-      <c r="C1206" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1206" t="inlineStr">
-        <is>
-          <t>просп Героїв Харкова 274</t>
-        </is>
-      </c>
-      <c r="E1206" t="inlineStr">
-        <is>
-          <t>Харків</t>
-        </is>
-      </c>
-      <c r="F1206" t="inlineStr">
-        <is>
-          <t>Харківська</t>
-        </is>
-      </c>
-      <c r="G1206" t="n">
-        <v>49.9432342</v>
-      </c>
-      <c r="H1206" t="n">
-        <v>36.3984342</v>
-      </c>
-      <c r="I1206" t="inlineStr">
-        <is>
-          <t>Пн: 09:00-18:00
-Вт: 09:00-18:00
-Ср: 09:00-18:00
-Чт: 09:00-18:00
-Пт: 09:00-18:00
-Сб: 09:00-17:00
-Нд: 09:00-17:00</t>
-        </is>
-      </c>
-      <c r="J1206" t="inlineStr">
-        <is>
-          <t>Харківська</t>
-        </is>
-      </c>
-    </row>
-    <row r="1207">
-      <c r="A1207" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1207" t="n">
-        <v>3543</v>
-      </c>
-      <c r="C1207" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1207" t="inlineStr">
-        <is>
-          <t>вул Салтівське шосе 147</t>
-        </is>
-      </c>
-      <c r="E1207" t="inlineStr">
-        <is>
-          <t>Харків</t>
-        </is>
-      </c>
-      <c r="F1207" t="inlineStr">
-        <is>
-          <t>Харківська</t>
-        </is>
-      </c>
-      <c r="G1207" t="n">
-        <v>49.9908024</v>
-      </c>
-      <c r="H1207" t="n">
-        <v>36.3585856</v>
-      </c>
-      <c r="I1207" t="inlineStr">
-        <is>
-          <t>Пн: 09:00-18:00
-Вт: 09:00-18:00
-Ср: 09:00-18:00
-Чт: 09:00-18:00
-Пт: 09:00-18:00
-Сб: 09:00-17:00
-Нд: 09:00-17:00</t>
-        </is>
-      </c>
-      <c r="J1207" t="inlineStr">
-        <is>
-          <t>Харківська</t>
-        </is>
-      </c>
-    </row>
-    <row r="1208">
-      <c r="A1208" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1208" t="n">
-        <v>3544</v>
-      </c>
-      <c r="C1208" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1208" t="inlineStr">
-        <is>
-          <t>просп Петра Григоренка 3</t>
-        </is>
-      </c>
-      <c r="E1208" t="inlineStr">
-        <is>
-          <t>Харків</t>
-        </is>
-      </c>
-      <c r="F1208" t="inlineStr">
-        <is>
-          <t>Харківська</t>
-        </is>
-      </c>
-      <c r="G1208" t="n">
-        <v>49.9650438</v>
-      </c>
-      <c r="H1208" t="n">
-        <v>36.3219614</v>
-      </c>
-      <c r="I1208" t="inlineStr">
-        <is>
-          <t>Пн: 09:00-18:00
-Вт: 09:00-18:00
-Ср: 09:00-18:00
-Чт: 09:00-18:00
-Пт: 09:00-18:00
-Сб: 09:00-17:00
-Нд: 09:00-17:00</t>
-        </is>
-      </c>
-      <c r="J1208" t="inlineStr">
-        <is>
-          <t>Харківська</t>
-        </is>
-      </c>
-    </row>
-    <row r="1209">
-      <c r="A1209" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1209" t="n">
-        <v>3545</v>
-      </c>
-      <c r="C1209" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1209" t="inlineStr">
-        <is>
-          <t>просп Аерокосмічний (Гагаріна) 177</t>
-        </is>
-      </c>
-      <c r="E1209" t="inlineStr">
-        <is>
-          <t>Харків</t>
-        </is>
-      </c>
-      <c r="F1209" t="inlineStr">
-        <is>
-          <t>Харківська</t>
-        </is>
-      </c>
-      <c r="G1209" t="n">
-        <v>50.0169162</v>
-      </c>
-      <c r="H1209" t="n">
-        <v>36.2067146</v>
-      </c>
-      <c r="I1209" t="inlineStr">
-        <is>
-          <t>Пн: 09:00-18:00
-Вт: 09:00-18:00
-Ср: 09:00-18:00
-Чт: 09:00-18:00
-Пт: 09:00-18:00
-Сб: 09:00-17:00
-Нд: 09:00-17:00</t>
-        </is>
-      </c>
-      <c r="J1209" t="inlineStr">
-        <is>
-          <t>Харківська</t>
-        </is>
-      </c>
-    </row>
-    <row r="1210">
-      <c r="A1210" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1210" t="n">
-        <v>3547</v>
-      </c>
-      <c r="C1210" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1210" t="inlineStr">
-        <is>
-          <t>вул Олімпійська 75</t>
-        </is>
-      </c>
-      <c r="E1210" t="inlineStr">
-        <is>
-          <t>Хотин</t>
-        </is>
-      </c>
-      <c r="F1210" t="inlineStr">
-        <is>
-          <t>Чернівецька</t>
-        </is>
-      </c>
-      <c r="G1210" t="n">
-        <v>48.5043413</v>
-      </c>
-      <c r="H1210" t="n">
-        <v>26.490402</v>
-      </c>
-      <c r="I1210" t="inlineStr">
-        <is>
-          <t>Пн: 09:00-18:00
-Вт: 09:00-18:00
-Ср: 09:00-18:00
-Чт: 09:00-18:00
-Пт: 09:00-18:00
-Сб: 09:00-17:00
-Нд: 10:00-14:00</t>
-        </is>
-      </c>
-      <c r="J1210" t="inlineStr">
-        <is>
-          <t>Чернівецька</t>
-        </is>
-      </c>
-    </row>
-    <row r="1211">
-      <c r="A1211" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1211" t="n">
-        <v>3549</v>
-      </c>
-      <c r="C1211" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1211" t="inlineStr">
-        <is>
-          <t>вул Жовтнева 4-А</t>
-        </is>
-      </c>
-      <c r="E1211" t="inlineStr">
-        <is>
-          <t>Гребінка</t>
-        </is>
-      </c>
-      <c r="F1211" t="inlineStr">
-        <is>
-          <t>Полтавська</t>
-        </is>
-      </c>
-      <c r="G1211" t="n">
-        <v>50.1185138</v>
-      </c>
-      <c r="H1211" t="n">
-        <v>32.4391051</v>
-      </c>
-      <c r="I1211" t="inlineStr">
-        <is>
-          <t>Пн: 09:00-17:00
-Вт: 09:00-17:00
-Ср: 09:00-17:00
-Чт: 09:00-17:00
-Пт: 09:00-17:00
-Сб: 09:00-14:00
-Нд: 09:00-14:00</t>
-        </is>
-      </c>
-      <c r="J1211" t="inlineStr">
-        <is>
-          <t>Полтавська</t>
-        </is>
-      </c>
-    </row>
-    <row r="1212">
-      <c r="A1212" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1212" t="n">
-        <v>3551</v>
-      </c>
-      <c r="C1212" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1212" t="inlineStr">
-        <is>
-          <t>вул Шевченка 50</t>
-        </is>
-      </c>
-      <c r="E1212" t="inlineStr">
-        <is>
-          <t>Богородчани</t>
-        </is>
-      </c>
-      <c r="F1212" t="inlineStr">
-        <is>
-          <t>Івано-Франківська</t>
-        </is>
-      </c>
-      <c r="G1212" t="n">
-        <v>48.809756</v>
-      </c>
-      <c r="H1212" t="n">
-        <v>24.5400082</v>
-      </c>
-      <c r="I1212" t="inlineStr">
-        <is>
-          <t>Пн: 09:00-18:00
-Вт: 09:00-18:00
-Ср: 09:00-18:00
-Чт: 09:00-18:00
-Пт: 09:00-18:00
-Сб: 09:00-17:00
-Нд: 10:00-16:00</t>
-        </is>
-      </c>
-      <c r="J1212" t="inlineStr">
-        <is>
-          <t>Івано-Франківська</t>
-        </is>
-      </c>
-    </row>
-    <row r="1213">
-      <c r="A1213" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1213" t="n">
-        <v>3552</v>
-      </c>
-      <c r="C1213" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1213" t="inlineStr">
-        <is>
-          <t>вул Макухи 1</t>
-        </is>
-      </c>
-      <c r="E1213" t="inlineStr">
-        <is>
-          <t>Тлумач</t>
-        </is>
-      </c>
-      <c r="F1213" t="inlineStr">
-        <is>
-          <t>Івано-Франківська</t>
-        </is>
-      </c>
-      <c r="G1213" t="n">
-        <v>48.8652727</v>
-      </c>
-      <c r="H1213" t="n">
-        <v>25.0043864</v>
-      </c>
-      <c r="I1213" t="inlineStr">
-        <is>
-          <t>Пн: 09:00-17:00
-Вт: 09:00-17:00
-Ср: 09:00-17:00
-Чт: 09:00-17:00
-Пт: 09:00-17:00
-Сб: Вихідний
-Нд: Вихідний</t>
-        </is>
-      </c>
-      <c r="J1213" t="inlineStr">
-        <is>
-          <t>Івано-Франківська</t>
-        </is>
-      </c>
-    </row>
-    <row r="1214">
-      <c r="A1214" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1214" t="n">
-        <v>3554</v>
-      </c>
-      <c r="C1214" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1214" t="inlineStr">
-        <is>
-          <t>вул Городоцька 137</t>
-        </is>
-      </c>
-      <c r="E1214" t="inlineStr">
-        <is>
-          <t>Львів</t>
-        </is>
-      </c>
-      <c r="F1214" t="inlineStr">
-        <is>
-          <t>Львівська</t>
-        </is>
-      </c>
-      <c r="G1214" t="n">
-        <v>49.8367768</v>
-      </c>
-      <c r="H1214" t="n">
-        <v>24.0028087</v>
-      </c>
-      <c r="I1214" t="inlineStr">
-        <is>
-          <t>Пн: 09:00-19:00
-Вт: 09:00-19:00
-Ср: 09:00-19:00
-Чт: 09:00-19:00
-Пт: 09:00-19:00
-Сб: 09:00-18:00
-Нд: 10:00-18:00</t>
-        </is>
-      </c>
-      <c r="J1214" t="inlineStr">
-        <is>
-          <t>Львівська</t>
-        </is>
-      </c>
-    </row>
-    <row r="1215">
-      <c r="A1215" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1215" t="n">
-        <v>3555</v>
-      </c>
-      <c r="C1215" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1215" t="inlineStr">
-        <is>
-          <t>вул Здолбунівська 15</t>
-        </is>
-      </c>
-      <c r="E1215" t="inlineStr">
-        <is>
-          <t>Київ</t>
-        </is>
-      </c>
-      <c r="F1215" t="inlineStr">
-        <is>
-          <t>м. Київ</t>
-        </is>
-      </c>
-      <c r="G1215" t="n">
-        <v>50.4185123</v>
-      </c>
-      <c r="H1215" t="n">
-        <v>30.631541</v>
-      </c>
-      <c r="I1215" t="inlineStr">
-        <is>
-          <t>Пн: 10:00-20:00
-Вт: 10:00-20:00
-Ср: 10:00-20:00
-Чт: 10:00-20:00
-Пт: 10:00-20:00
-Сб: 10:00-20:00
-Нд: 10:00-20:00</t>
-        </is>
-      </c>
-      <c r="J1215" t="inlineStr">
-        <is>
-          <t>м. Київ</t>
-        </is>
-      </c>
-    </row>
-    <row r="1216">
-      <c r="A1216" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1216" t="n">
-        <v>3556</v>
-      </c>
-      <c r="C1216" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1216" t="inlineStr">
-        <is>
-          <t>вул Шевченка 42</t>
-        </is>
-      </c>
-      <c r="E1216" t="inlineStr">
-        <is>
-          <t>Овруч</t>
-        </is>
-      </c>
-      <c r="F1216" t="inlineStr">
-        <is>
-          <t>Житомирська</t>
-        </is>
-      </c>
-      <c r="G1216" t="n">
-        <v>51.3197441</v>
-      </c>
-      <c r="H1216" t="n">
-        <v>28.8004248</v>
-      </c>
-      <c r="I1216" t="inlineStr">
-        <is>
-          <t>Пн: 09:00-18:00
-Вт: 09:00-18:00
-Ср: 09:00-18:00
-Чт: 09:00-18:00
-Пт: 09:00-18:00
-Сб: 09:00-18:00
-Нд: 09:00-18:00</t>
-        </is>
-      </c>
-      <c r="J1216" t="inlineStr">
-        <is>
-          <t>Житомирська</t>
         </is>
       </c>
     </row>

--- a/all_shops.xlsx
+++ b/all_shops.xlsx
@@ -52987,7 +52987,7 @@
         </is>
       </c>
       <c r="B1149" t="n">
-        <v>3413</v>
+        <v>3414</v>
       </c>
       <c r="C1149" t="inlineStr">
         <is>
@@ -52996,78 +52996,26 @@
       </c>
       <c r="D1149" t="inlineStr">
         <is>
-          <t>вул Андріївська 5</t>
+          <t>просп Адмиральський 37</t>
         </is>
       </c>
       <c r="E1149" t="inlineStr">
         <is>
-          <t>Березне</t>
+          <t>Одеса</t>
         </is>
       </c>
       <c r="F1149" t="inlineStr">
         <is>
-          <t>Рівненська</t>
+          <t>Odessa</t>
         </is>
       </c>
       <c r="G1149" t="n">
-        <v>51.0019955</v>
+        <v>46.43745</v>
       </c>
       <c r="H1149" t="n">
-        <v>26.7547284</v>
+        <v>30.72675</v>
       </c>
       <c r="I1149" t="inlineStr">
-        <is>
-          <t>Пн: 09:00-18:00
-Вт: 09:00-18:00
-Ср: 09:00-18:00
-Чт: 09:00-18:00
-Пт: 09:00-18:00
-Сб: 09:00-16:00
-Нд: Вихідний</t>
-        </is>
-      </c>
-      <c r="J1149" t="inlineStr">
-        <is>
-          <t>Рівненська</t>
-        </is>
-      </c>
-    </row>
-    <row r="1150">
-      <c r="A1150" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1150" t="n">
-        <v>3414</v>
-      </c>
-      <c r="C1150" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1150" t="inlineStr">
-        <is>
-          <t>просп Адмиральський 37</t>
-        </is>
-      </c>
-      <c r="E1150" t="inlineStr">
-        <is>
-          <t>Одеса</t>
-        </is>
-      </c>
-      <c r="F1150" t="inlineStr">
-        <is>
-          <t>Odessa</t>
-        </is>
-      </c>
-      <c r="G1150" t="n">
-        <v>46.43745</v>
-      </c>
-      <c r="H1150" t="n">
-        <v>30.72675</v>
-      </c>
-      <c r="I1150" t="inlineStr">
         <is>
           <t>Пн: 09:00-18:00
 Вт: 09:00-18:00
@@ -53078,48 +53026,48 @@
 Нд: 09:00-18:00</t>
         </is>
       </c>
-      <c r="J1150" t="inlineStr">
+      <c r="J1149" t="inlineStr">
         <is>
           <t>Odessa</t>
         </is>
       </c>
     </row>
-    <row r="1151">
-      <c r="A1151" t="inlineStr">
+    <row r="1150">
+      <c r="A1150" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1151" t="n">
+      <c r="B1150" t="n">
         <v>3420</v>
       </c>
-      <c r="C1151" t="inlineStr">
+      <c r="C1150" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1151" t="inlineStr">
+      <c r="D1150" t="inlineStr">
         <is>
           <t>вул Ушинського 10</t>
         </is>
       </c>
-      <c r="E1151" t="inlineStr">
+      <c r="E1150" t="inlineStr">
         <is>
           <t>Одеса</t>
         </is>
       </c>
-      <c r="F1151" t="inlineStr">
+      <c r="F1150" t="inlineStr">
         <is>
           <t>Odessa</t>
         </is>
       </c>
-      <c r="G1151" t="n">
+      <c r="G1150" t="n">
         <v>46.4845584</v>
       </c>
-      <c r="H1151" t="n">
+      <c r="H1150" t="n">
         <v>30.7208259</v>
       </c>
-      <c r="I1151" t="inlineStr">
+      <c r="I1150" t="inlineStr">
         <is>
           <t>Пн: 09:00-18:00
 Вт: 09:00-18:00
@@ -53130,48 +53078,48 @@
 Нд: Вихідний</t>
         </is>
       </c>
-      <c r="J1151" t="inlineStr">
+      <c r="J1150" t="inlineStr">
         <is>
           <t>Odessa</t>
         </is>
       </c>
     </row>
-    <row r="1152">
-      <c r="A1152" t="inlineStr">
+    <row r="1151">
+      <c r="A1151" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1152" t="n">
+      <c r="B1151" t="n">
         <v>3421</v>
       </c>
-      <c r="C1152" t="inlineStr">
+      <c r="C1151" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1152" t="inlineStr">
+      <c r="D1151" t="inlineStr">
         <is>
           <t>вул Святоюріївська 10/2</t>
         </is>
       </c>
-      <c r="E1152" t="inlineStr">
+      <c r="E1151" t="inlineStr">
         <is>
           <t>Вишневе</t>
         </is>
       </c>
-      <c r="F1152" t="inlineStr">
+      <c r="F1151" t="inlineStr">
         <is>
           <t>Kiev</t>
         </is>
       </c>
-      <c r="G1152" t="n">
+      <c r="G1151" t="n">
         <v>50.3833741</v>
       </c>
-      <c r="H1152" t="n">
+      <c r="H1151" t="n">
         <v>30.3731464</v>
       </c>
-      <c r="I1152" t="inlineStr">
+      <c r="I1151" t="inlineStr">
         <is>
           <t>Пн: 09:00-19:00
 Вт: 09:00-19:00
@@ -53182,48 +53130,48 @@
 Нд: 09:00-19:00</t>
         </is>
       </c>
-      <c r="J1152" t="inlineStr">
+      <c r="J1151" t="inlineStr">
         <is>
           <t>Kiev</t>
         </is>
       </c>
     </row>
-    <row r="1153">
-      <c r="A1153" t="inlineStr">
+    <row r="1152">
+      <c r="A1152" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1153" t="n">
+      <c r="B1152" t="n">
         <v>3422</v>
       </c>
-      <c r="C1153" t="inlineStr">
+      <c r="C1152" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1153" t="inlineStr">
+      <c r="D1152" t="inlineStr">
         <is>
           <t>вул Європейська (Жовтнева) 31а</t>
         </is>
       </c>
-      <c r="E1153" t="inlineStr">
+      <c r="E1152" t="inlineStr">
         <is>
           <t>Вишневе</t>
         </is>
       </c>
-      <c r="F1153" t="inlineStr">
+      <c r="F1152" t="inlineStr">
         <is>
           <t>Kiev</t>
         </is>
       </c>
-      <c r="G1153" t="n">
+      <c r="G1152" t="n">
         <v>50.3919298</v>
       </c>
-      <c r="H1153" t="n">
+      <c r="H1152" t="n">
         <v>30.3759122</v>
       </c>
-      <c r="I1153" t="inlineStr">
+      <c r="I1152" t="inlineStr">
         <is>
           <t>Пн: 10:00-19:00
 Вт: 10:00-19:00
@@ -53234,48 +53182,48 @@
 Нд: 10:00-18:00</t>
         </is>
       </c>
-      <c r="J1153" t="inlineStr">
+      <c r="J1152" t="inlineStr">
         <is>
           <t>Kiev</t>
         </is>
       </c>
     </row>
-    <row r="1154">
-      <c r="A1154" t="inlineStr">
+    <row r="1153">
+      <c r="A1153" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1154" t="n">
+      <c r="B1153" t="n">
         <v>3424</v>
       </c>
-      <c r="C1154" t="inlineStr">
+      <c r="C1153" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1154" t="inlineStr">
+      <c r="D1153" t="inlineStr">
         <is>
           <t>просп Свободи 47</t>
         </is>
       </c>
-      <c r="E1154" t="inlineStr">
+      <c r="E1153" t="inlineStr">
         <is>
           <t>Кременчук</t>
         </is>
       </c>
-      <c r="F1154" t="inlineStr">
+      <c r="F1153" t="inlineStr">
         <is>
           <t>Полтавська</t>
         </is>
       </c>
-      <c r="G1154" t="n">
+      <c r="G1153" t="n">
         <v>49.0886626</v>
       </c>
-      <c r="H1154" t="n">
+      <c r="H1153" t="n">
         <v>33.4285175</v>
       </c>
-      <c r="I1154" t="inlineStr">
+      <c r="I1153" t="inlineStr">
         <is>
           <t>Пн: 09:00-19:00
 Вт: 09:00-19:00
@@ -53286,48 +53234,48 @@
 Нд: 09:00-17:00</t>
         </is>
       </c>
-      <c r="J1154" t="inlineStr">
+      <c r="J1153" t="inlineStr">
         <is>
           <t>Полтавська</t>
         </is>
       </c>
     </row>
-    <row r="1155">
-      <c r="A1155" t="inlineStr">
+    <row r="1154">
+      <c r="A1154" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1155" t="n">
+      <c r="B1154" t="n">
         <v>3428</v>
       </c>
-      <c r="C1155" t="inlineStr">
+      <c r="C1154" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1155" t="inlineStr">
+      <c r="D1154" t="inlineStr">
         <is>
           <t>пл Миру 11</t>
         </is>
       </c>
-      <c r="E1155" t="inlineStr">
+      <c r="E1154" t="inlineStr">
         <is>
           <t>Гадяч</t>
         </is>
       </c>
-      <c r="F1155" t="inlineStr">
+      <c r="F1154" t="inlineStr">
         <is>
           <t>Полтавська</t>
         </is>
       </c>
-      <c r="G1155" t="n">
+      <c r="G1154" t="n">
         <v>50.3739846</v>
       </c>
-      <c r="H1155" t="n">
+      <c r="H1154" t="n">
         <v>33.9836438</v>
       </c>
-      <c r="I1155" t="inlineStr">
+      <c r="I1154" t="inlineStr">
         <is>
           <t>Пн: 09:00-17:00
 Вт: 09:00-17:00
@@ -53338,48 +53286,48 @@
 Нд: 09:00-17:00</t>
         </is>
       </c>
-      <c r="J1155" t="inlineStr">
+      <c r="J1154" t="inlineStr">
         <is>
           <t>Полтавська</t>
         </is>
       </c>
     </row>
-    <row r="1156">
-      <c r="A1156" t="inlineStr">
+    <row r="1155">
+      <c r="A1155" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1156" t="n">
+      <c r="B1155" t="n">
         <v>3432</v>
       </c>
-      <c r="C1156" t="inlineStr">
+      <c r="C1155" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1156" t="inlineStr">
+      <c r="D1155" t="inlineStr">
         <is>
           <t>бул Шевченка 385</t>
         </is>
       </c>
-      <c r="E1156" t="inlineStr">
+      <c r="E1155" t="inlineStr">
         <is>
           <t>Черкаси</t>
         </is>
       </c>
-      <c r="F1156" t="inlineStr">
+      <c r="F1155" t="inlineStr">
         <is>
           <t>Черкаська</t>
         </is>
       </c>
-      <c r="G1156" t="n">
+      <c r="G1155" t="n">
         <v>49.424669</v>
       </c>
-      <c r="H1156" t="n">
+      <c r="H1155" t="n">
         <v>32.0953677</v>
       </c>
-      <c r="I1156" t="inlineStr">
+      <c r="I1155" t="inlineStr">
         <is>
           <t>Пн: 10:00-20:00
 Вт: 10:00-20:00
@@ -53390,48 +53338,48 @@
 Нд: 10:00-20:00</t>
         </is>
       </c>
-      <c r="J1156" t="inlineStr">
+      <c r="J1155" t="inlineStr">
         <is>
           <t>Черкаська</t>
         </is>
       </c>
     </row>
-    <row r="1157">
-      <c r="A1157" t="inlineStr">
+    <row r="1156">
+      <c r="A1156" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1157" t="n">
+      <c r="B1156" t="n">
         <v>3435</v>
       </c>
-      <c r="C1157" t="inlineStr">
+      <c r="C1156" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1157" t="inlineStr">
+      <c r="D1156" t="inlineStr">
         <is>
           <t>просп Науки 1/2</t>
         </is>
       </c>
-      <c r="E1157" t="inlineStr">
+      <c r="E1156" t="inlineStr">
         <is>
           <t>Київ</t>
         </is>
       </c>
-      <c r="F1157" t="inlineStr">
+      <c r="F1156" t="inlineStr">
         <is>
           <t>м. Київ</t>
         </is>
       </c>
-      <c r="G1157" t="n">
+      <c r="G1156" t="n">
         <v>50.4064898</v>
       </c>
-      <c r="H1157" t="n">
+      <c r="H1156" t="n">
         <v>30.519621</v>
       </c>
-      <c r="I1157" t="inlineStr">
+      <c r="I1156" t="inlineStr">
         <is>
           <t>Пн: 07:00-22:00
 Вт: 07:00-22:00
@@ -53442,48 +53390,48 @@
 Нд: 07:00-22:00</t>
         </is>
       </c>
-      <c r="J1157" t="inlineStr">
+      <c r="J1156" t="inlineStr">
         <is>
           <t>м. Київ</t>
         </is>
       </c>
     </row>
-    <row r="1158">
-      <c r="A1158" t="inlineStr">
+    <row r="1157">
+      <c r="A1157" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1158" t="n">
+      <c r="B1157" t="n">
         <v>3437</v>
       </c>
-      <c r="C1158" t="inlineStr">
+      <c r="C1157" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1158" t="inlineStr">
+      <c r="D1157" t="inlineStr">
         <is>
           <t>просп Богоявленський 338</t>
         </is>
       </c>
-      <c r="E1158" t="inlineStr">
+      <c r="E1157" t="inlineStr">
         <is>
           <t>Миколаїв (Миколаївська)</t>
         </is>
       </c>
-      <c r="F1158" t="inlineStr">
+      <c r="F1157" t="inlineStr">
         <is>
           <t>Миколаївська</t>
         </is>
       </c>
-      <c r="G1158" t="n">
+      <c r="G1157" t="n">
         <v>46.8557792</v>
       </c>
-      <c r="H1158" t="n">
+      <c r="H1157" t="n">
         <v>32.0141945</v>
       </c>
-      <c r="I1158" t="inlineStr">
+      <c r="I1157" t="inlineStr">
         <is>
           <t>Пн: 09:00-18:00
 Вт: 09:00-18:00
@@ -53494,48 +53442,48 @@
 Нд: 09:00-18:00</t>
         </is>
       </c>
-      <c r="J1158" t="inlineStr">
+      <c r="J1157" t="inlineStr">
         <is>
           <t>Миколаївська</t>
         </is>
       </c>
     </row>
-    <row r="1159">
-      <c r="A1159" t="inlineStr">
+    <row r="1158">
+      <c r="A1158" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1159" t="n">
+      <c r="B1158" t="n">
         <v>3441</v>
       </c>
-      <c r="C1159" t="inlineStr">
+      <c r="C1158" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1159" t="inlineStr">
+      <c r="D1158" t="inlineStr">
         <is>
           <t>вул Українська 71а</t>
         </is>
       </c>
-      <c r="E1159" t="inlineStr">
+      <c r="E1158" t="inlineStr">
         <is>
           <t>Путила</t>
         </is>
       </c>
-      <c r="F1159" t="inlineStr">
+      <c r="F1158" t="inlineStr">
         <is>
           <t>Чернівецька</t>
         </is>
       </c>
-      <c r="G1159" t="n">
+      <c r="G1158" t="n">
         <v>47.998305</v>
       </c>
-      <c r="H1159" t="n">
+      <c r="H1158" t="n">
         <v>25.0850933</v>
       </c>
-      <c r="I1159" t="inlineStr">
+      <c r="I1158" t="inlineStr">
         <is>
           <t>Пн: 09:00-18:00
 Вт: 09:00-18:00
@@ -53546,48 +53494,48 @@
 Нд: 10:00-16:00</t>
         </is>
       </c>
-      <c r="J1159" t="inlineStr">
+      <c r="J1158" t="inlineStr">
         <is>
           <t>Чернівецька</t>
         </is>
       </c>
     </row>
-    <row r="1160">
-      <c r="A1160" t="inlineStr">
+    <row r="1159">
+      <c r="A1159" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1160" t="n">
+      <c r="B1159" t="n">
         <v>3445</v>
       </c>
-      <c r="C1160" t="inlineStr">
+      <c r="C1159" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1160" t="inlineStr">
+      <c r="D1159" t="inlineStr">
         <is>
           <t>вул Шевченка 73</t>
         </is>
       </c>
-      <c r="E1160" t="inlineStr">
+      <c r="E1159" t="inlineStr">
         <is>
           <t>Снятин</t>
         </is>
       </c>
-      <c r="F1160" t="inlineStr">
+      <c r="F1159" t="inlineStr">
         <is>
           <t>Івано-Франківська</t>
         </is>
       </c>
-      <c r="G1160" t="n">
+      <c r="G1159" t="n">
         <v>48.4514483</v>
       </c>
-      <c r="H1160" t="n">
+      <c r="H1159" t="n">
         <v>25.5551122</v>
       </c>
-      <c r="I1160" t="inlineStr">
+      <c r="I1159" t="inlineStr">
         <is>
           <t>Пн: 09:00-18:00
 Вт: 09:00-18:00
@@ -53598,48 +53546,48 @@
 Нд: Вихідний</t>
         </is>
       </c>
-      <c r="J1160" t="inlineStr">
+      <c r="J1159" t="inlineStr">
         <is>
           <t>Івано-Франківська</t>
         </is>
       </c>
     </row>
-    <row r="1161">
-      <c r="A1161" t="inlineStr">
+    <row r="1160">
+      <c r="A1160" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1161" t="n">
+      <c r="B1160" t="n">
         <v>3454</v>
       </c>
-      <c r="C1161" t="inlineStr">
+      <c r="C1160" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1161" t="inlineStr">
+      <c r="D1160" t="inlineStr">
         <is>
           <t>вул Зелена 1а</t>
         </is>
       </c>
-      <c r="E1161" t="inlineStr">
+      <c r="E1160" t="inlineStr">
         <is>
           <t>Мостиська</t>
         </is>
       </c>
-      <c r="F1161" t="inlineStr">
+      <c r="F1160" t="inlineStr">
         <is>
           <t>Львівська</t>
         </is>
       </c>
-      <c r="G1161" t="n">
+      <c r="G1160" t="n">
         <v>49.7913487</v>
       </c>
-      <c r="H1161" t="n">
+      <c r="H1160" t="n">
         <v>23.1536667</v>
       </c>
-      <c r="I1161" t="inlineStr">
+      <c r="I1160" t="inlineStr">
         <is>
           <t>Пн: 09:00-19:00
 Вт: 09:00-19:00
@@ -53650,48 +53598,48 @@
 Нд: 10:00-17:00</t>
         </is>
       </c>
-      <c r="J1161" t="inlineStr">
+      <c r="J1160" t="inlineStr">
         <is>
           <t>Львівська</t>
         </is>
       </c>
     </row>
-    <row r="1162">
-      <c r="A1162" t="inlineStr">
+    <row r="1161">
+      <c r="A1161" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1162" t="n">
+      <c r="B1161" t="n">
         <v>3463</v>
       </c>
-      <c r="C1162" t="inlineStr">
+      <c r="C1161" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1162" t="inlineStr">
+      <c r="D1161" t="inlineStr">
         <is>
           <t>вул Грушевського 41А</t>
         </is>
       </c>
-      <c r="E1162" t="inlineStr">
+      <c r="E1161" t="inlineStr">
         <is>
           <t>Первомайськ</t>
         </is>
       </c>
-      <c r="F1162" t="inlineStr">
+      <c r="F1161" t="inlineStr">
         <is>
           <t>Миколаївська</t>
         </is>
       </c>
-      <c r="G1162" t="n">
+      <c r="G1161" t="n">
         <v>48.0425652</v>
       </c>
-      <c r="H1162" t="n">
+      <c r="H1161" t="n">
         <v>30.8444596</v>
       </c>
-      <c r="I1162" t="inlineStr">
+      <c r="I1161" t="inlineStr">
         <is>
           <t>Пн: 08:00-18:00
 Вт: 08:00-18:00
@@ -53702,48 +53650,48 @@
 Нд: 08:00-18:00</t>
         </is>
       </c>
-      <c r="J1162" t="inlineStr">
+      <c r="J1161" t="inlineStr">
         <is>
           <t>Миколаївська</t>
         </is>
       </c>
     </row>
-    <row r="1163">
-      <c r="A1163" t="inlineStr">
+    <row r="1162">
+      <c r="A1162" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1163" t="n">
+      <c r="B1162" t="n">
         <v>3464</v>
       </c>
-      <c r="C1163" t="inlineStr">
+      <c r="C1162" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1163" t="inlineStr">
+      <c r="D1162" t="inlineStr">
         <is>
           <t>вул Огієнка 41</t>
         </is>
       </c>
-      <c r="E1163" t="inlineStr">
+      <c r="E1162" t="inlineStr">
         <is>
           <t>Камянець-Подільский</t>
         </is>
       </c>
-      <c r="F1163" t="inlineStr">
+      <c r="F1162" t="inlineStr">
         <is>
           <t>Хмельницька</t>
         </is>
       </c>
-      <c r="G1163" t="n">
+      <c r="G1162" t="n">
         <v>48.681053</v>
       </c>
-      <c r="H1163" t="n">
+      <c r="H1162" t="n">
         <v>26.5871481</v>
       </c>
-      <c r="I1163" t="inlineStr">
+      <c r="I1162" t="inlineStr">
         <is>
           <t>Пн: 08:00-18:00
 Вт: 08:00-18:00
@@ -53754,48 +53702,48 @@
 Нд: 10:00-16:00</t>
         </is>
       </c>
-      <c r="J1163" t="inlineStr">
+      <c r="J1162" t="inlineStr">
         <is>
           <t>Хмельницька</t>
         </is>
       </c>
     </row>
-    <row r="1164">
-      <c r="A1164" t="inlineStr">
+    <row r="1163">
+      <c r="A1163" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1164" t="n">
+      <c r="B1163" t="n">
         <v>3465</v>
       </c>
-      <c r="C1164" t="inlineStr">
+      <c r="C1163" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1164" t="inlineStr">
+      <c r="D1163" t="inlineStr">
         <is>
           <t>вул Хмельницька 6</t>
         </is>
       </c>
-      <c r="E1164" t="inlineStr">
+      <c r="E1163" t="inlineStr">
         <is>
           <t>Ярмолинці</t>
         </is>
       </c>
-      <c r="F1164" t="inlineStr">
+      <c r="F1163" t="inlineStr">
         <is>
           <t>Хмельницька</t>
         </is>
       </c>
-      <c r="G1164" t="n">
+      <c r="G1163" t="n">
         <v>49.19112</v>
       </c>
-      <c r="H1164" t="n">
+      <c r="H1163" t="n">
         <v>26.83537</v>
       </c>
-      <c r="I1164" t="inlineStr">
+      <c r="I1163" t="inlineStr">
         <is>
           <t>Пн: 09:00-18:00
 Вт: 09:00-18:00
@@ -53806,48 +53754,48 @@
 Нд: Вихідний</t>
         </is>
       </c>
-      <c r="J1164" t="inlineStr">
+      <c r="J1163" t="inlineStr">
         <is>
           <t>Хмельницька</t>
         </is>
       </c>
     </row>
-    <row r="1165">
-      <c r="A1165" t="inlineStr">
+    <row r="1164">
+      <c r="A1164" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1165" t="n">
+      <c r="B1164" t="n">
         <v>3466</v>
       </c>
-      <c r="C1165" t="inlineStr">
+      <c r="C1164" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1165" t="inlineStr">
+      <c r="D1164" t="inlineStr">
         <is>
           <t>просп Берестейський (Перемоги) 86а</t>
         </is>
       </c>
-      <c r="E1165" t="inlineStr">
+      <c r="E1164" t="inlineStr">
         <is>
           <t>Київ</t>
         </is>
       </c>
-      <c r="F1165" t="inlineStr">
+      <c r="F1164" t="inlineStr">
         <is>
           <t>Kiev</t>
         </is>
       </c>
-      <c r="G1165" t="n">
+      <c r="G1164" t="n">
         <v>50.4588998</v>
       </c>
-      <c r="H1165" t="n">
+      <c r="H1164" t="n">
         <v>30.4041254</v>
       </c>
-      <c r="I1165" t="inlineStr">
+      <c r="I1164" t="inlineStr">
         <is>
           <t>Пн: 10:00-21:00
 Вт: 10:00-21:00
@@ -53858,48 +53806,48 @@
 Нд: 10:00-21:00</t>
         </is>
       </c>
-      <c r="J1165" t="inlineStr">
+      <c r="J1164" t="inlineStr">
         <is>
           <t>Kiev</t>
         </is>
       </c>
     </row>
-    <row r="1166">
-      <c r="A1166" t="inlineStr">
+    <row r="1165">
+      <c r="A1165" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1166" t="n">
+      <c r="B1165" t="n">
         <v>3467</v>
       </c>
-      <c r="C1166" t="inlineStr">
+      <c r="C1165" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1166" t="inlineStr">
+      <c r="D1165" t="inlineStr">
         <is>
           <t>вул Харківська 2/2</t>
         </is>
       </c>
-      <c r="E1166" t="inlineStr">
+      <c r="E1165" t="inlineStr">
         <is>
           <t>Суми</t>
         </is>
       </c>
-      <c r="F1166" t="inlineStr">
+      <c r="F1165" t="inlineStr">
         <is>
           <t>Сумська</t>
         </is>
       </c>
-      <c r="G1166" t="n">
+      <c r="G1165" t="n">
         <v>50.9041752</v>
       </c>
-      <c r="H1166" t="n">
+      <c r="H1165" t="n">
         <v>34.8048057</v>
       </c>
-      <c r="I1166" t="inlineStr">
+      <c r="I1165" t="inlineStr">
         <is>
           <t>Пн: 10:00-19:00
 Вт: 10:00-19:00
@@ -53910,48 +53858,48 @@
 Нд: 10:00-19:00</t>
         </is>
       </c>
-      <c r="J1166" t="inlineStr">
+      <c r="J1165" t="inlineStr">
         <is>
           <t>Сумська</t>
         </is>
       </c>
     </row>
-    <row r="1167">
-      <c r="A1167" t="inlineStr">
+    <row r="1166">
+      <c r="A1166" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1167" t="n">
+      <c r="B1166" t="n">
         <v>3470</v>
       </c>
-      <c r="C1167" t="inlineStr">
+      <c r="C1166" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1167" t="inlineStr">
+      <c r="D1166" t="inlineStr">
         <is>
           <t>вул  Хрещатик 13</t>
         </is>
       </c>
-      <c r="E1167" t="inlineStr">
+      <c r="E1166" t="inlineStr">
         <is>
           <t>Київ</t>
         </is>
       </c>
-      <c r="F1167" t="inlineStr">
+      <c r="F1166" t="inlineStr">
         <is>
           <t>м. Київ</t>
         </is>
       </c>
-      <c r="G1167" t="n">
+      <c r="G1166" t="n">
         <v>50.4487897</v>
       </c>
-      <c r="H1167" t="n">
+      <c r="H1166" t="n">
         <v>30.5233361</v>
       </c>
-      <c r="I1167" t="inlineStr">
+      <c r="I1166" t="inlineStr">
         <is>
           <t>Пн: 10:00-20:00
 Вт: 10:00-20:00
@@ -53962,48 +53910,48 @@
 Нд: 10:00-20:00</t>
         </is>
       </c>
-      <c r="J1167" t="inlineStr">
+      <c r="J1166" t="inlineStr">
         <is>
           <t>м. Київ</t>
         </is>
       </c>
     </row>
-    <row r="1168">
-      <c r="A1168" t="inlineStr">
+    <row r="1167">
+      <c r="A1167" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1168" t="n">
+      <c r="B1167" t="n">
         <v>3471</v>
       </c>
-      <c r="C1168" t="inlineStr">
+      <c r="C1167" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1168" t="inlineStr">
+      <c r="D1167" t="inlineStr">
         <is>
           <t>вул Університетська 45</t>
         </is>
       </c>
-      <c r="E1168" t="inlineStr">
+      <c r="E1167" t="inlineStr">
         <is>
           <t>Словянськ</t>
         </is>
       </c>
-      <c r="F1168" t="inlineStr">
+      <c r="F1167" t="inlineStr">
         <is>
           <t>Дніпропетровська</t>
         </is>
       </c>
-      <c r="G1168" t="n">
+      <c r="G1167" t="n">
         <v>48.0008788</v>
       </c>
-      <c r="H1168" t="n">
+      <c r="H1167" t="n">
         <v>33.4821954</v>
       </c>
-      <c r="I1168" t="inlineStr">
+      <c r="I1167" t="inlineStr">
         <is>
           <t>Пн: 10:00-17:00
 Вт: 10:00-17:00
@@ -54014,48 +53962,48 @@
 Нд: Вихідний</t>
         </is>
       </c>
-      <c r="J1168" t="inlineStr">
+      <c r="J1167" t="inlineStr">
         <is>
           <t>Дніпропетровська</t>
         </is>
       </c>
     </row>
-    <row r="1169">
-      <c r="A1169" t="inlineStr">
+    <row r="1168">
+      <c r="A1168" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1169" t="n">
+      <c r="B1168" t="n">
         <v>3472</v>
       </c>
-      <c r="C1169" t="inlineStr">
+      <c r="C1168" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1169" t="inlineStr">
+      <c r="D1168" t="inlineStr">
         <is>
           <t>вул Чернівецька 2Б</t>
         </is>
       </c>
-      <c r="E1169" t="inlineStr">
+      <c r="E1168" t="inlineStr">
         <is>
           <t>Сторожинець</t>
         </is>
       </c>
-      <c r="F1169" t="inlineStr">
+      <c r="F1168" t="inlineStr">
         <is>
           <t>Чернівецька</t>
         </is>
       </c>
-      <c r="G1169" t="n">
+      <c r="G1168" t="n">
         <v>48.1604917</v>
       </c>
-      <c r="H1169" t="n">
+      <c r="H1168" t="n">
         <v>25.721244</v>
       </c>
-      <c r="I1169" t="inlineStr">
+      <c r="I1168" t="inlineStr">
         <is>
           <t>Пн: 09:00-18:00
 Вт: 09:00-18:00
@@ -54066,48 +54014,48 @@
 Нд: Вихідний</t>
         </is>
       </c>
-      <c r="J1169" t="inlineStr">
+      <c r="J1168" t="inlineStr">
         <is>
           <t>Чернівецька</t>
         </is>
       </c>
     </row>
-    <row r="1170">
-      <c r="A1170" t="inlineStr">
+    <row r="1169">
+      <c r="A1169" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1170" t="n">
+      <c r="B1169" t="n">
         <v>3474</v>
       </c>
-      <c r="C1170" t="inlineStr">
+      <c r="C1169" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1170" t="inlineStr">
+      <c r="D1169" t="inlineStr">
         <is>
           <t>вул Нескорених (Героїв Праці) 13</t>
         </is>
       </c>
-      <c r="E1170" t="inlineStr">
+      <c r="E1169" t="inlineStr">
         <is>
           <t>Харків</t>
         </is>
       </c>
-      <c r="F1170" t="inlineStr">
+      <c r="F1169" t="inlineStr">
         <is>
           <t>Харківська</t>
         </is>
       </c>
-      <c r="G1170" t="n">
+      <c r="G1169" t="n">
         <v>50.0254117</v>
       </c>
-      <c r="H1170" t="n">
+      <c r="H1169" t="n">
         <v>36.3369339</v>
       </c>
-      <c r="I1170" t="inlineStr">
+      <c r="I1169" t="inlineStr">
         <is>
           <t>Пн: 09:00-18:00
 Вт: 09:00-18:00
@@ -54118,48 +54066,48 @@
 Нд: 09:00-17:00</t>
         </is>
       </c>
-      <c r="J1170" t="inlineStr">
+      <c r="J1169" t="inlineStr">
         <is>
           <t>Харківська</t>
         </is>
       </c>
     </row>
-    <row r="1171">
-      <c r="A1171" t="inlineStr">
+    <row r="1170">
+      <c r="A1170" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1171" t="n">
+      <c r="B1170" t="n">
         <v>3478</v>
       </c>
-      <c r="C1171" t="inlineStr">
+      <c r="C1170" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1171" t="inlineStr">
+      <c r="D1170" t="inlineStr">
         <is>
           <t>просп Європейського Союзу (Правди) 58</t>
         </is>
       </c>
-      <c r="E1171" t="inlineStr">
+      <c r="E1170" t="inlineStr">
         <is>
           <t>Київ</t>
         </is>
       </c>
-      <c r="F1171" t="inlineStr">
+      <c r="F1170" t="inlineStr">
         <is>
           <t>Kiev</t>
         </is>
       </c>
-      <c r="G1171" t="n">
+      <c r="G1170" t="n">
         <v>50.5047315</v>
       </c>
-      <c r="H1171" t="n">
+      <c r="H1170" t="n">
         <v>30.4374307</v>
       </c>
-      <c r="I1171" t="inlineStr">
+      <c r="I1170" t="inlineStr">
         <is>
           <t>Пн: 09:00-21:00
 Вт: 09:00-21:00
@@ -54170,48 +54118,48 @@
 Нд: 09:00-21:00</t>
         </is>
       </c>
-      <c r="J1171" t="inlineStr">
+      <c r="J1170" t="inlineStr">
         <is>
           <t>Kiev</t>
         </is>
       </c>
     </row>
-    <row r="1172">
-      <c r="A1172" t="inlineStr">
+    <row r="1171">
+      <c r="A1171" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1172" t="n">
+      <c r="B1171" t="n">
         <v>3479</v>
       </c>
-      <c r="C1172" t="inlineStr">
+      <c r="C1171" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1172" t="inlineStr">
+      <c r="D1171" t="inlineStr">
         <is>
           <t>вул Європейського Союзу (Правди) 47</t>
         </is>
       </c>
-      <c r="E1172" t="inlineStr">
+      <c r="E1171" t="inlineStr">
         <is>
           <t>Київ</t>
         </is>
       </c>
-      <c r="F1172" t="inlineStr">
+      <c r="F1171" t="inlineStr">
         <is>
           <t>м. Київ</t>
         </is>
       </c>
-      <c r="G1172" t="n">
+      <c r="G1171" t="n">
         <v>50.5037667</v>
       </c>
-      <c r="H1172" t="n">
+      <c r="H1171" t="n">
         <v>30.419093</v>
       </c>
-      <c r="I1172" t="inlineStr">
+      <c r="I1171" t="inlineStr">
         <is>
           <t>Пн: 10:00-22:00
 Вт: 10:00-22:00
@@ -54222,48 +54170,48 @@
 Нд: 10:00-22:00</t>
         </is>
       </c>
-      <c r="J1172" t="inlineStr">
+      <c r="J1171" t="inlineStr">
         <is>
           <t>м. Київ</t>
         </is>
       </c>
     </row>
-    <row r="1173">
-      <c r="A1173" t="inlineStr">
+    <row r="1172">
+      <c r="A1172" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1173" t="n">
+      <c r="B1172" t="n">
         <v>3483</v>
       </c>
-      <c r="C1173" t="inlineStr">
+      <c r="C1172" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1173" t="inlineStr">
+      <c r="D1172" t="inlineStr">
         <is>
           <t>просп Коцюбинського 19</t>
         </is>
       </c>
-      <c r="E1173" t="inlineStr">
+      <c r="E1172" t="inlineStr">
         <is>
           <t>Вінниця</t>
         </is>
       </c>
-      <c r="F1173" t="inlineStr">
+      <c r="F1172" t="inlineStr">
         <is>
           <t>Vinnyts'ka</t>
         </is>
       </c>
-      <c r="G1173" t="n">
+      <c r="G1172" t="n">
         <v>49.239071</v>
       </c>
-      <c r="H1173" t="n">
+      <c r="H1172" t="n">
         <v>28.4981039</v>
       </c>
-      <c r="I1173" t="inlineStr">
+      <c r="I1172" t="inlineStr">
         <is>
           <t>Пн: 08:00-18:00
 Вт: 08:00-18:00
@@ -54274,48 +54222,48 @@
 Нд: 09:00-17:00</t>
         </is>
       </c>
-      <c r="J1173" t="inlineStr">
+      <c r="J1172" t="inlineStr">
         <is>
           <t>Vinnyts'ka</t>
         </is>
       </c>
     </row>
-    <row r="1174">
-      <c r="A1174" t="inlineStr">
+    <row r="1173">
+      <c r="A1173" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1174" t="n">
+      <c r="B1173" t="n">
         <v>3485</v>
       </c>
-      <c r="C1174" t="inlineStr">
+      <c r="C1173" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1174" t="inlineStr">
+      <c r="D1173" t="inlineStr">
         <is>
           <t>вул Котляра (був. Червоноармійська) 8/10</t>
         </is>
       </c>
-      <c r="E1174" t="inlineStr">
+      <c r="E1173" t="inlineStr">
         <is>
           <t>Харків</t>
         </is>
       </c>
-      <c r="F1174" t="inlineStr">
+      <c r="F1173" t="inlineStr">
         <is>
           <t>Харківська</t>
         </is>
       </c>
-      <c r="G1174" t="n">
+      <c r="G1173" t="n">
         <v>49.9892648</v>
       </c>
-      <c r="H1174" t="n">
+      <c r="H1173" t="n">
         <v>36.2077698</v>
       </c>
-      <c r="I1174" t="inlineStr">
+      <c r="I1173" t="inlineStr">
         <is>
           <t>Пн: 09:00-18:00
 Вт: 09:00-18:00
@@ -54326,48 +54274,48 @@
 Нд: 09:00-17:00</t>
         </is>
       </c>
-      <c r="J1174" t="inlineStr">
+      <c r="J1173" t="inlineStr">
         <is>
           <t>Харківська</t>
         </is>
       </c>
     </row>
-    <row r="1175">
-      <c r="A1175" t="inlineStr">
+    <row r="1174">
+      <c r="A1174" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1175" t="n">
+      <c r="B1174" t="n">
         <v>3491</v>
       </c>
-      <c r="C1175" t="inlineStr">
+      <c r="C1174" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1175" t="inlineStr">
+      <c r="D1174" t="inlineStr">
         <is>
           <t>вул Інститутська 10</t>
         </is>
       </c>
-      <c r="E1175" t="inlineStr">
+      <c r="E1174" t="inlineStr">
         <is>
           <t>Хмельницький</t>
         </is>
       </c>
-      <c r="F1175" t="inlineStr">
+      <c r="F1174" t="inlineStr">
         <is>
           <t>Хмельницька</t>
         </is>
       </c>
-      <c r="G1175" t="n">
+      <c r="G1174" t="n">
         <v>49.4098499</v>
       </c>
-      <c r="H1175" t="n">
+      <c r="H1174" t="n">
         <v>26.9605436</v>
       </c>
-      <c r="I1175" t="inlineStr">
+      <c r="I1174" t="inlineStr">
         <is>
           <t>Пн: 09:00-19:00
 Вт: 09:00-19:00
@@ -54378,48 +54326,48 @@
 Нд: 10:00-18:00</t>
         </is>
       </c>
-      <c r="J1175" t="inlineStr">
+      <c r="J1174" t="inlineStr">
         <is>
           <t>Хмельницька</t>
         </is>
       </c>
     </row>
-    <row r="1176">
-      <c r="A1176" t="inlineStr">
+    <row r="1175">
+      <c r="A1175" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1176" t="n">
+      <c r="B1175" t="n">
         <v>3494</v>
       </c>
-      <c r="C1176" t="inlineStr">
+      <c r="C1175" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1176" t="inlineStr">
+      <c r="D1175" t="inlineStr">
         <is>
           <t>вул Шевченків Шлях 144-А</t>
         </is>
       </c>
-      <c r="E1176" t="inlineStr">
+      <c r="E1175" t="inlineStr">
         <is>
           <t>Березань</t>
         </is>
       </c>
-      <c r="F1176" t="inlineStr">
+      <c r="F1175" t="inlineStr">
         <is>
           <t>Kiev</t>
         </is>
       </c>
-      <c r="G1176" t="n">
+      <c r="G1175" t="n">
         <v>50.3119113</v>
       </c>
-      <c r="H1176" t="n">
+      <c r="H1175" t="n">
         <v>31.4678577</v>
       </c>
-      <c r="I1176" t="inlineStr">
+      <c r="I1175" t="inlineStr">
         <is>
           <t>Пн: 09:00-17:00
 Вт: 09:00-17:00
@@ -54430,48 +54378,48 @@
 Нд: 10:00-16:00</t>
         </is>
       </c>
-      <c r="J1176" t="inlineStr">
+      <c r="J1175" t="inlineStr">
         <is>
           <t>Kiev</t>
         </is>
       </c>
     </row>
-    <row r="1177">
-      <c r="A1177" t="inlineStr">
+    <row r="1176">
+      <c r="A1176" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1177" t="n">
+      <c r="B1176" t="n">
         <v>3495</v>
       </c>
-      <c r="C1177" t="inlineStr">
+      <c r="C1176" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1177" t="inlineStr">
+      <c r="D1176" t="inlineStr">
         <is>
           <t>вул Міцкевича 1</t>
         </is>
       </c>
-      <c r="E1177" t="inlineStr">
+      <c r="E1176" t="inlineStr">
         <is>
           <t>Борислав</t>
         </is>
       </c>
-      <c r="F1177" t="inlineStr">
+      <c r="F1176" t="inlineStr">
         <is>
           <t>Львівська</t>
         </is>
       </c>
-      <c r="G1177" t="n">
+      <c r="G1176" t="n">
         <v>49.287286</v>
       </c>
-      <c r="H1177" t="n">
+      <c r="H1176" t="n">
         <v>23.4159004</v>
       </c>
-      <c r="I1177" t="inlineStr">
+      <c r="I1176" t="inlineStr">
         <is>
           <t>Пн: 09:00-18:00
 Вт: 09:00-18:00
@@ -54482,48 +54430,48 @@
 Нд: 10:00-17:00</t>
         </is>
       </c>
-      <c r="J1177" t="inlineStr">
+      <c r="J1176" t="inlineStr">
         <is>
           <t>Львівська</t>
         </is>
       </c>
     </row>
-    <row r="1178">
-      <c r="A1178" t="inlineStr">
+    <row r="1177">
+      <c r="A1177" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1178" t="n">
+      <c r="B1177" t="n">
         <v>3496</v>
       </c>
-      <c r="C1178" t="inlineStr">
+      <c r="C1177" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1178" t="inlineStr">
+      <c r="D1177" t="inlineStr">
         <is>
           <t>вул І.Франка 1</t>
         </is>
       </c>
-      <c r="E1178" t="inlineStr">
+      <c r="E1177" t="inlineStr">
         <is>
           <t>Верховина</t>
         </is>
       </c>
-      <c r="F1178" t="inlineStr">
+      <c r="F1177" t="inlineStr">
         <is>
           <t>Івано-Франківська</t>
         </is>
       </c>
-      <c r="G1178" t="n">
+      <c r="G1177" t="n">
         <v>48.1549768</v>
       </c>
-      <c r="H1178" t="n">
+      <c r="H1177" t="n">
         <v>24.8291227</v>
       </c>
-      <c r="I1178" t="inlineStr">
+      <c r="I1177" t="inlineStr">
         <is>
           <t>Пн: 09:00-18:00
 Вт: 09:00-18:00
@@ -54534,48 +54482,48 @@
 Нд: 10:00-16:00</t>
         </is>
       </c>
-      <c r="J1178" t="inlineStr">
+      <c r="J1177" t="inlineStr">
         <is>
           <t>Івано-Франківська</t>
         </is>
       </c>
     </row>
-    <row r="1179">
-      <c r="A1179" t="inlineStr">
+    <row r="1178">
+      <c r="A1178" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1179" t="n">
+      <c r="B1178" t="n">
         <v>3498</v>
       </c>
-      <c r="C1179" t="inlineStr">
+      <c r="C1178" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1179" t="inlineStr">
+      <c r="D1178" t="inlineStr">
         <is>
           <t>просп Олександра Поля 1/9</t>
         </is>
       </c>
-      <c r="E1179" t="inlineStr">
+      <c r="E1178" t="inlineStr">
         <is>
           <t>Дніпро</t>
         </is>
       </c>
-      <c r="F1179" t="inlineStr">
+      <c r="F1178" t="inlineStr">
         <is>
           <t>Дніпропетровська</t>
         </is>
       </c>
-      <c r="G1179" t="n">
+      <c r="G1178" t="n">
         <v>48.4642698</v>
       </c>
-      <c r="H1179" t="n">
+      <c r="H1178" t="n">
         <v>35.0290126</v>
       </c>
-      <c r="I1179" t="inlineStr">
+      <c r="I1178" t="inlineStr">
         <is>
           <t>Пн: 09:00-19:00
 Вт: 09:00-19:00
@@ -54586,48 +54534,48 @@
 Нд: 09:00-18:00</t>
         </is>
       </c>
-      <c r="J1179" t="inlineStr">
+      <c r="J1178" t="inlineStr">
         <is>
           <t>Дніпропетровська</t>
         </is>
       </c>
     </row>
-    <row r="1180">
-      <c r="A1180" t="inlineStr">
+    <row r="1179">
+      <c r="A1179" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1180" t="n">
+      <c r="B1179" t="n">
         <v>3501</v>
       </c>
-      <c r="C1180" t="inlineStr">
+      <c r="C1179" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1180" t="inlineStr">
+      <c r="D1179" t="inlineStr">
         <is>
           <t>просп Дмитра Яворницького (К.Маркса) 65</t>
         </is>
       </c>
-      <c r="E1180" t="inlineStr">
+      <c r="E1179" t="inlineStr">
         <is>
           <t>Дніпро</t>
         </is>
       </c>
-      <c r="F1180" t="inlineStr">
+      <c r="F1179" t="inlineStr">
         <is>
           <t>Дніпропетровська</t>
         </is>
       </c>
-      <c r="G1180" t="n">
+      <c r="G1179" t="n">
         <v>48.4647786</v>
       </c>
-      <c r="H1180" t="n">
+      <c r="H1179" t="n">
         <v>35.0447223</v>
       </c>
-      <c r="I1180" t="inlineStr">
+      <c r="I1179" t="inlineStr">
         <is>
           <t>Пн: 09:00-19:00
 Вт: 09:00-19:00
@@ -54638,48 +54586,48 @@
 Нд: 09:00-18:00</t>
         </is>
       </c>
-      <c r="J1180" t="inlineStr">
+      <c r="J1179" t="inlineStr">
         <is>
           <t>Дніпропетровська</t>
         </is>
       </c>
     </row>
-    <row r="1181">
-      <c r="A1181" t="inlineStr">
+    <row r="1180">
+      <c r="A1180" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1181" t="n">
+      <c r="B1180" t="n">
         <v>3503</v>
       </c>
-      <c r="C1181" t="inlineStr">
+      <c r="C1180" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1181" t="inlineStr">
+      <c r="D1180" t="inlineStr">
         <is>
           <t>вул Привокзальна 3</t>
         </is>
       </c>
-      <c r="E1181" t="inlineStr">
+      <c r="E1180" t="inlineStr">
         <is>
           <t>Київ</t>
         </is>
       </c>
-      <c r="F1181" t="inlineStr">
+      <c r="F1180" t="inlineStr">
         <is>
           <t>Kiev</t>
         </is>
       </c>
-      <c r="G1181" t="n">
+      <c r="G1180" t="n">
         <v>50.4305963</v>
       </c>
-      <c r="H1181" t="n">
+      <c r="H1180" t="n">
         <v>30.6518096</v>
       </c>
-      <c r="I1181" t="inlineStr">
+      <c r="I1180" t="inlineStr">
         <is>
           <t>Пн: 10:00-17:00
 Вт: 10:00-17:00
@@ -54690,48 +54638,48 @@
 Нд: 10:00-17:00</t>
         </is>
       </c>
-      <c r="J1181" t="inlineStr">
+      <c r="J1180" t="inlineStr">
         <is>
           <t>Kiev</t>
         </is>
       </c>
     </row>
-    <row r="1182">
-      <c r="A1182" t="inlineStr">
+    <row r="1181">
+      <c r="A1181" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1182" t="n">
+      <c r="B1181" t="n">
         <v>3505</v>
       </c>
-      <c r="C1182" t="inlineStr">
+      <c r="C1181" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1182" t="inlineStr">
+      <c r="D1181" t="inlineStr">
         <is>
           <t>пл Шевченка 26</t>
         </is>
       </c>
-      <c r="E1182" t="inlineStr">
+      <c r="E1181" t="inlineStr">
         <is>
           <t>Коломия</t>
         </is>
       </c>
-      <c r="F1182" t="inlineStr">
+      <c r="F1181" t="inlineStr">
         <is>
           <t>Івано-Франківська</t>
         </is>
       </c>
-      <c r="G1182" t="n">
+      <c r="G1181" t="n">
         <v>48.5249278</v>
       </c>
-      <c r="H1182" t="n">
+      <c r="H1181" t="n">
         <v>25.0375409</v>
       </c>
-      <c r="I1182" t="inlineStr">
+      <c r="I1181" t="inlineStr">
         <is>
           <t>Пн: 09:00-18:00
 Вт: 09:00-18:00
@@ -54742,48 +54690,48 @@
 Нд: 10:00-17:00</t>
         </is>
       </c>
-      <c r="J1182" t="inlineStr">
+      <c r="J1181" t="inlineStr">
         <is>
           <t>Івано-Франківська</t>
         </is>
       </c>
     </row>
-    <row r="1183">
-      <c r="A1183" t="inlineStr">
+    <row r="1182">
+      <c r="A1182" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1183" t="n">
+      <c r="B1182" t="n">
         <v>3506</v>
       </c>
-      <c r="C1183" t="inlineStr">
+      <c r="C1182" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1183" t="inlineStr">
+      <c r="D1182" t="inlineStr">
         <is>
           <t>вул Медова 5</t>
         </is>
       </c>
-      <c r="E1183" t="inlineStr">
+      <c r="E1182" t="inlineStr">
         <is>
           <t>Кремeнець</t>
         </is>
       </c>
-      <c r="F1183" t="inlineStr">
+      <c r="F1182" t="inlineStr">
         <is>
           <t>Тернопільська</t>
         </is>
       </c>
-      <c r="G1183" t="n">
+      <c r="G1182" t="n">
         <v>50.095605</v>
       </c>
-      <c r="H1183" t="n">
+      <c r="H1182" t="n">
         <v>25.7259463</v>
       </c>
-      <c r="I1183" t="inlineStr">
+      <c r="I1182" t="inlineStr">
         <is>
           <t>Пн: 09:00-19:00
 Вт: 09:00-19:00
@@ -54794,48 +54742,48 @@
 Нд: 10:00-16:00</t>
         </is>
       </c>
-      <c r="J1183" t="inlineStr">
+      <c r="J1182" t="inlineStr">
         <is>
           <t>Тернопільська</t>
         </is>
       </c>
     </row>
-    <row r="1184">
-      <c r="A1184" t="inlineStr">
+    <row r="1183">
+      <c r="A1183" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1184" t="n">
+      <c r="B1183" t="n">
         <v>3508</v>
       </c>
-      <c r="C1184" t="inlineStr">
+      <c r="C1183" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1184" t="inlineStr">
+      <c r="D1183" t="inlineStr">
         <is>
           <t>вул Шевченка 100</t>
         </is>
       </c>
-      <c r="E1184" t="inlineStr">
+      <c r="E1183" t="inlineStr">
         <is>
           <t>Люботин</t>
         </is>
       </c>
-      <c r="F1184" t="inlineStr">
+      <c r="F1183" t="inlineStr">
         <is>
           <t>Харківська</t>
         </is>
       </c>
-      <c r="G1184" t="n">
+      <c r="G1183" t="n">
         <v>49.9407992</v>
       </c>
-      <c r="H1184" t="n">
+      <c r="H1183" t="n">
         <v>35.9262566</v>
       </c>
-      <c r="I1184" t="inlineStr">
+      <c r="I1183" t="inlineStr">
         <is>
           <t>Пн: 08:00-18:00
 Вт: 08:00-18:00
@@ -54846,48 +54794,48 @@
 Нд: 08:00-16:00</t>
         </is>
       </c>
-      <c r="J1184" t="inlineStr">
+      <c r="J1183" t="inlineStr">
         <is>
           <t>Харківська</t>
         </is>
       </c>
     </row>
-    <row r="1185">
-      <c r="A1185" t="inlineStr">
+    <row r="1184">
+      <c r="A1184" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1185" t="n">
+      <c r="B1184" t="n">
         <v>3510</v>
       </c>
-      <c r="C1185" t="inlineStr">
+      <c r="C1184" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1185" t="inlineStr">
+      <c r="D1184" t="inlineStr">
         <is>
           <t>вул Петропавлівська 49</t>
         </is>
       </c>
-      <c r="E1185" t="inlineStr">
+      <c r="E1184" t="inlineStr">
         <is>
           <t>Суми</t>
         </is>
       </c>
-      <c r="F1185" t="inlineStr">
+      <c r="F1184" t="inlineStr">
         <is>
           <t>Сумська</t>
         </is>
       </c>
-      <c r="G1185" t="n">
+      <c r="G1184" t="n">
         <v>50.9065729</v>
       </c>
-      <c r="H1185" t="n">
+      <c r="H1184" t="n">
         <v>34.796901</v>
       </c>
-      <c r="I1185" t="inlineStr">
+      <c r="I1184" t="inlineStr">
         <is>
           <t>Пн: 09:00-18:00
 Вт: 09:00-18:00
@@ -54898,48 +54846,48 @@
 Нд: 09:00-18:00</t>
         </is>
       </c>
-      <c r="J1185" t="inlineStr">
+      <c r="J1184" t="inlineStr">
         <is>
           <t>Сумська</t>
         </is>
       </c>
     </row>
-    <row r="1186">
-      <c r="A1186" t="inlineStr">
+    <row r="1185">
+      <c r="A1185" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1186" t="n">
+      <c r="B1185" t="n">
         <v>3512</v>
       </c>
-      <c r="C1186" t="inlineStr">
+      <c r="C1185" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1186" t="inlineStr">
+      <c r="D1185" t="inlineStr">
         <is>
           <t>вул Валентинівська (Блюхера) 37/128</t>
         </is>
       </c>
-      <c r="E1186" t="inlineStr">
+      <c r="E1185" t="inlineStr">
         <is>
           <t>Харків</t>
         </is>
       </c>
-      <c r="F1186" t="inlineStr">
+      <c r="F1185" t="inlineStr">
         <is>
           <t>Харківська</t>
         </is>
       </c>
-      <c r="G1186" t="n">
+      <c r="G1185" t="n">
         <v>50.0098371</v>
       </c>
-      <c r="H1186" t="n">
+      <c r="H1185" t="n">
         <v>36.3503577</v>
       </c>
-      <c r="I1186" t="inlineStr">
+      <c r="I1185" t="inlineStr">
         <is>
           <t>Пн: 09:00-19:00
 Вт: 09:00-19:00
@@ -54950,48 +54898,48 @@
 Нд: 09:00-18:00</t>
         </is>
       </c>
-      <c r="J1186" t="inlineStr">
+      <c r="J1185" t="inlineStr">
         <is>
           <t>Харківська</t>
         </is>
       </c>
     </row>
-    <row r="1187">
-      <c r="A1187" t="inlineStr">
+    <row r="1186">
+      <c r="A1186" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1187" t="n">
+      <c r="B1186" t="n">
         <v>3514</v>
       </c>
-      <c r="C1187" t="inlineStr">
+      <c r="C1186" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1187" t="inlineStr">
+      <c r="D1186" t="inlineStr">
         <is>
           <t>вул Центральна 32а</t>
         </is>
       </c>
-      <c r="E1187" t="inlineStr">
+      <c r="E1186" t="inlineStr">
         <is>
           <t>Чемерівці</t>
         </is>
       </c>
-      <c r="F1187" t="inlineStr">
+      <c r="F1186" t="inlineStr">
         <is>
           <t>Хмельницька</t>
         </is>
       </c>
-      <c r="G1187" t="n">
+      <c r="G1186" t="n">
         <v>49.011295</v>
       </c>
-      <c r="H1187" t="n">
+      <c r="H1186" t="n">
         <v>26.340395</v>
       </c>
-      <c r="I1187" t="inlineStr">
+      <c r="I1186" t="inlineStr">
         <is>
           <t>Пн: 08:00-18:00
 Вт: 08:00-18:00
@@ -55002,48 +54950,48 @@
 Нд: 09:00-15:00</t>
         </is>
       </c>
-      <c r="J1187" t="inlineStr">
+      <c r="J1186" t="inlineStr">
         <is>
           <t>Хмельницька</t>
         </is>
       </c>
     </row>
-    <row r="1188">
-      <c r="A1188" t="inlineStr">
+    <row r="1187">
+      <c r="A1187" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1188" t="n">
+      <c r="B1187" t="n">
         <v>3516</v>
       </c>
-      <c r="C1188" t="inlineStr">
+      <c r="C1187" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1188" t="inlineStr">
+      <c r="D1187" t="inlineStr">
         <is>
           <t>просп Відрадний 69/1</t>
         </is>
       </c>
-      <c r="E1188" t="inlineStr">
+      <c r="E1187" t="inlineStr">
         <is>
           <t>Київ</t>
         </is>
       </c>
-      <c r="F1188" t="inlineStr">
+      <c r="F1187" t="inlineStr">
         <is>
           <t>Kiev</t>
         </is>
       </c>
-      <c r="G1188" t="n">
+      <c r="G1187" t="n">
         <v>50.428885</v>
       </c>
-      <c r="H1188" t="n">
+      <c r="H1187" t="n">
         <v>30.4309396</v>
       </c>
-      <c r="I1188" t="inlineStr">
+      <c r="I1187" t="inlineStr">
         <is>
           <t>Пн: 09:00-18:00
 Вт: 09:00-18:00
@@ -55054,48 +55002,48 @@
 Нд: 10:00-17:00</t>
         </is>
       </c>
-      <c r="J1188" t="inlineStr">
+      <c r="J1187" t="inlineStr">
         <is>
           <t>Kiev</t>
         </is>
       </c>
     </row>
-    <row r="1189">
-      <c r="A1189" t="inlineStr">
+    <row r="1188">
+      <c r="A1188" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1189" t="n">
+      <c r="B1188" t="n">
         <v>3517</v>
       </c>
-      <c r="C1189" t="inlineStr">
+      <c r="C1188" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1189" t="inlineStr">
+      <c r="D1188" t="inlineStr">
         <is>
           <t>просп Свободи (Леніна) 16Д</t>
         </is>
       </c>
-      <c r="E1189" t="inlineStr">
+      <c r="E1188" t="inlineStr">
         <is>
           <t>Хмільник</t>
         </is>
       </c>
-      <c r="F1189" t="inlineStr">
+      <c r="F1188" t="inlineStr">
         <is>
           <t>Vinnyts'ka</t>
         </is>
       </c>
-      <c r="G1189" t="n">
+      <c r="G1188" t="n">
         <v>49.5576747</v>
       </c>
-      <c r="H1189" t="n">
+      <c r="H1188" t="n">
         <v>27.9528561</v>
       </c>
-      <c r="I1189" t="inlineStr">
+      <c r="I1188" t="inlineStr">
         <is>
           <t>Пн: 08:00-17:00
 Вт: 08:00-17:00
@@ -55106,48 +55054,48 @@
 Нд: Вихідний</t>
         </is>
       </c>
-      <c r="J1189" t="inlineStr">
+      <c r="J1188" t="inlineStr">
         <is>
           <t>Vinnyts'ka</t>
         </is>
       </c>
     </row>
-    <row r="1190">
-      <c r="A1190" t="inlineStr">
+    <row r="1189">
+      <c r="A1189" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1190" t="n">
+      <c r="B1189" t="n">
         <v>3520</v>
       </c>
-      <c r="C1190" t="inlineStr">
+      <c r="C1189" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1190" t="inlineStr">
+      <c r="D1189" t="inlineStr">
         <is>
           <t>пл Шевченка 6</t>
         </is>
       </c>
-      <c r="E1190" t="inlineStr">
+      <c r="E1189" t="inlineStr">
         <is>
           <t>Славута</t>
         </is>
       </c>
-      <c r="F1190" t="inlineStr">
+      <c r="F1189" t="inlineStr">
         <is>
           <t>Хмельницька</t>
         </is>
       </c>
-      <c r="G1190" t="n">
+      <c r="G1189" t="n">
         <v>50.2957898</v>
       </c>
-      <c r="H1190" t="n">
+      <c r="H1189" t="n">
         <v>26.8570458</v>
       </c>
-      <c r="I1190" t="inlineStr">
+      <c r="I1189" t="inlineStr">
         <is>
           <t>Пн: 08:00-17:00
 Вт: 08:00-17:00
@@ -55158,48 +55106,48 @@
 Нд: 08:00-17:00</t>
         </is>
       </c>
-      <c r="J1190" t="inlineStr">
+      <c r="J1189" t="inlineStr">
         <is>
           <t>Хмельницька</t>
         </is>
       </c>
     </row>
-    <row r="1191">
-      <c r="A1191" t="inlineStr">
+    <row r="1190">
+      <c r="A1190" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1191" t="n">
+      <c r="B1190" t="n">
         <v>3526</v>
       </c>
-      <c r="C1191" t="inlineStr">
+      <c r="C1190" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1191" t="inlineStr">
+      <c r="D1190" t="inlineStr">
         <is>
           <t>вул Незалежності 65</t>
         </is>
       </c>
-      <c r="E1191" t="inlineStr">
+      <c r="E1190" t="inlineStr">
         <is>
           <t>Камянка-Бузька</t>
         </is>
       </c>
-      <c r="F1191" t="inlineStr">
+      <c r="F1190" t="inlineStr">
         <is>
           <t>Львівська</t>
         </is>
       </c>
-      <c r="G1191" t="n">
+      <c r="G1190" t="n">
         <v>50.107376</v>
       </c>
-      <c r="H1191" t="n">
+      <c r="H1190" t="n">
         <v>24.3436341</v>
       </c>
-      <c r="I1191" t="inlineStr">
+      <c r="I1190" t="inlineStr">
         <is>
           <t>Пн: 09:00-18:00
 Вт: 09:00-18:00
@@ -55210,48 +55158,48 @@
 Нд: 09:00-16:00</t>
         </is>
       </c>
-      <c r="J1191" t="inlineStr">
+      <c r="J1190" t="inlineStr">
         <is>
           <t>Львівська</t>
         </is>
       </c>
     </row>
-    <row r="1192">
-      <c r="A1192" t="inlineStr">
+    <row r="1191">
+      <c r="A1191" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1192" t="n">
+      <c r="B1191" t="n">
         <v>3530</v>
       </c>
-      <c r="C1192" t="inlineStr">
+      <c r="C1191" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1192" t="inlineStr">
+      <c r="D1191" t="inlineStr">
         <is>
           <t>вул Савіцького 14</t>
         </is>
       </c>
-      <c r="E1192" t="inlineStr">
+      <c r="E1191" t="inlineStr">
         <is>
           <t>Летичів</t>
         </is>
       </c>
-      <c r="F1192" t="inlineStr">
+      <c r="F1191" t="inlineStr">
         <is>
           <t>Хмельницька</t>
         </is>
       </c>
-      <c r="G1192" t="n">
+      <c r="G1191" t="n">
         <v>49.3813788</v>
       </c>
-      <c r="H1192" t="n">
+      <c r="H1191" t="n">
         <v>27.6197046</v>
       </c>
-      <c r="I1192" t="inlineStr">
+      <c r="I1191" t="inlineStr">
         <is>
           <t>Пн: 09:00-18:00
 Вт: 09:00-18:00
@@ -55262,48 +55210,48 @@
 Нд: 09:00-18:00</t>
         </is>
       </c>
-      <c r="J1192" t="inlineStr">
+      <c r="J1191" t="inlineStr">
         <is>
           <t>Хмельницька</t>
         </is>
       </c>
     </row>
-    <row r="1193">
-      <c r="A1193" t="inlineStr">
+    <row r="1192">
+      <c r="A1192" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1193" t="n">
+      <c r="B1192" t="n">
         <v>3531</v>
       </c>
-      <c r="C1193" t="inlineStr">
+      <c r="C1192" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1193" t="inlineStr">
+      <c r="D1192" t="inlineStr">
         <is>
           <t>вул Берестейський (Перемоги) 26</t>
         </is>
       </c>
-      <c r="E1193" t="inlineStr">
+      <c r="E1192" t="inlineStr">
         <is>
           <t>Київ</t>
         </is>
       </c>
-      <c r="F1193" t="inlineStr">
+      <c r="F1192" t="inlineStr">
         <is>
           <t>м. Київ</t>
         </is>
       </c>
-      <c r="G1193" t="n">
+      <c r="G1192" t="n">
         <v>50.4515345</v>
       </c>
-      <c r="H1193" t="n">
+      <c r="H1192" t="n">
         <v>30.4678476</v>
       </c>
-      <c r="I1193" t="inlineStr">
+      <c r="I1192" t="inlineStr">
         <is>
           <t>Пн: 10:00-21:00
 Вт: 10:00-21:00
@@ -55314,48 +55262,48 @@
 Нд: 10:00-21:00</t>
         </is>
       </c>
-      <c r="J1193" t="inlineStr">
+      <c r="J1192" t="inlineStr">
         <is>
           <t>м. Київ</t>
         </is>
       </c>
     </row>
-    <row r="1194">
-      <c r="A1194" t="inlineStr">
+    <row r="1193">
+      <c r="A1193" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1194" t="n">
+      <c r="B1193" t="n">
         <v>3534</v>
       </c>
-      <c r="C1194" t="inlineStr">
+      <c r="C1193" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1194" t="inlineStr">
+      <c r="D1193" t="inlineStr">
         <is>
           <t>вул Шевченка 74а</t>
         </is>
       </c>
-      <c r="E1194" t="inlineStr">
+      <c r="E1193" t="inlineStr">
         <is>
           <t>Городенка</t>
         </is>
       </c>
-      <c r="F1194" t="inlineStr">
+      <c r="F1193" t="inlineStr">
         <is>
           <t>Івано-Франківська</t>
         </is>
       </c>
-      <c r="G1194" t="n">
+      <c r="G1193" t="n">
         <v>48.66888903427731</v>
       </c>
-      <c r="H1194" t="n">
+      <c r="H1193" t="n">
         <v>25.50435338169336</v>
       </c>
-      <c r="I1194" t="inlineStr">
+      <c r="I1193" t="inlineStr">
         <is>
           <t>Пн: 08:00-18:00
 Вт: 08:00-18:00
@@ -55366,48 +55314,48 @@
 Нд: 10:00-17:00</t>
         </is>
       </c>
-      <c r="J1194" t="inlineStr">
+      <c r="J1193" t="inlineStr">
         <is>
           <t>Івано-Франківська</t>
         </is>
       </c>
     </row>
-    <row r="1195">
-      <c r="A1195" t="inlineStr">
+    <row r="1194">
+      <c r="A1194" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1195" t="n">
+      <c r="B1194" t="n">
         <v>3535</v>
       </c>
-      <c r="C1195" t="inlineStr">
+      <c r="C1194" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1195" t="inlineStr">
+      <c r="D1194" t="inlineStr">
         <is>
           <t>вул Бекетова 21</t>
         </is>
       </c>
-      <c r="E1195" t="inlineStr">
+      <c r="E1194" t="inlineStr">
         <is>
           <t>Харків</t>
         </is>
       </c>
-      <c r="F1195" t="inlineStr">
+      <c r="F1194" t="inlineStr">
         <is>
           <t>Харківська</t>
         </is>
       </c>
-      <c r="G1195" t="n">
+      <c r="G1194" t="n">
         <v>49.9512627</v>
       </c>
-      <c r="H1195" t="n">
+      <c r="H1194" t="n">
         <v>36.371922</v>
       </c>
-      <c r="I1195" t="inlineStr">
+      <c r="I1194" t="inlineStr">
         <is>
           <t>Пн: 09:00-17:00
 Вт: 09:00-17:00
@@ -55418,48 +55366,48 @@
 Нд: 09:00-16:00</t>
         </is>
       </c>
-      <c r="J1195" t="inlineStr">
+      <c r="J1194" t="inlineStr">
         <is>
           <t>Харківська</t>
         </is>
       </c>
     </row>
-    <row r="1196">
-      <c r="A1196" t="inlineStr">
+    <row r="1195">
+      <c r="A1195" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1196" t="n">
+      <c r="B1195" t="n">
         <v>3541</v>
       </c>
-      <c r="C1196" t="inlineStr">
+      <c r="C1195" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1196" t="inlineStr">
+      <c r="D1195" t="inlineStr">
         <is>
           <t>вул Одеська 121, А/1</t>
         </is>
       </c>
-      <c r="E1196" t="inlineStr">
+      <c r="E1195" t="inlineStr">
         <is>
           <t>Первомайськ</t>
         </is>
       </c>
-      <c r="F1196" t="inlineStr">
+      <c r="F1195" t="inlineStr">
         <is>
           <t>Миколаївська</t>
         </is>
       </c>
-      <c r="G1196" t="n">
+      <c r="G1195" t="n">
         <v>48.0228289</v>
       </c>
-      <c r="H1196" t="n">
+      <c r="H1195" t="n">
         <v>30.8511121</v>
       </c>
-      <c r="I1196" t="inlineStr">
+      <c r="I1195" t="inlineStr">
         <is>
           <t>Пн: 09:00-18:00
 Вт: 09:00-18:00
@@ -55470,48 +55418,48 @@
 Нд: 09:00-18:00</t>
         </is>
       </c>
-      <c r="J1196" t="inlineStr">
+      <c r="J1195" t="inlineStr">
         <is>
           <t>Миколаївська</t>
         </is>
       </c>
     </row>
-    <row r="1197">
-      <c r="A1197" t="inlineStr">
+    <row r="1196">
+      <c r="A1196" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1197" t="n">
+      <c r="B1196" t="n">
         <v>3542</v>
       </c>
-      <c r="C1197" t="inlineStr">
+      <c r="C1196" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1197" t="inlineStr">
+      <c r="D1196" t="inlineStr">
         <is>
           <t>просп Героїв Харкова 274</t>
         </is>
       </c>
-      <c r="E1197" t="inlineStr">
+      <c r="E1196" t="inlineStr">
         <is>
           <t>Харків</t>
         </is>
       </c>
-      <c r="F1197" t="inlineStr">
+      <c r="F1196" t="inlineStr">
         <is>
           <t>Харківська</t>
         </is>
       </c>
-      <c r="G1197" t="n">
+      <c r="G1196" t="n">
         <v>49.9432342</v>
       </c>
-      <c r="H1197" t="n">
+      <c r="H1196" t="n">
         <v>36.3984342</v>
       </c>
-      <c r="I1197" t="inlineStr">
+      <c r="I1196" t="inlineStr">
         <is>
           <t>Пн: 09:00-18:00
 Вт: 09:00-18:00
@@ -55522,48 +55470,48 @@
 Нд: 09:00-17:00</t>
         </is>
       </c>
-      <c r="J1197" t="inlineStr">
+      <c r="J1196" t="inlineStr">
         <is>
           <t>Харківська</t>
         </is>
       </c>
     </row>
-    <row r="1198">
-      <c r="A1198" t="inlineStr">
+    <row r="1197">
+      <c r="A1197" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1198" t="n">
+      <c r="B1197" t="n">
         <v>3543</v>
       </c>
-      <c r="C1198" t="inlineStr">
+      <c r="C1197" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1198" t="inlineStr">
+      <c r="D1197" t="inlineStr">
         <is>
           <t>вул Салтівське шосе 147</t>
         </is>
       </c>
-      <c r="E1198" t="inlineStr">
+      <c r="E1197" t="inlineStr">
         <is>
           <t>Харків</t>
         </is>
       </c>
-      <c r="F1198" t="inlineStr">
+      <c r="F1197" t="inlineStr">
         <is>
           <t>Харківська</t>
         </is>
       </c>
-      <c r="G1198" t="n">
+      <c r="G1197" t="n">
         <v>49.9908024</v>
       </c>
-      <c r="H1198" t="n">
+      <c r="H1197" t="n">
         <v>36.3585856</v>
       </c>
-      <c r="I1198" t="inlineStr">
+      <c r="I1197" t="inlineStr">
         <is>
           <t>Пн: 09:00-18:00
 Вт: 09:00-18:00
@@ -55574,48 +55522,48 @@
 Нд: 09:00-17:00</t>
         </is>
       </c>
-      <c r="J1198" t="inlineStr">
+      <c r="J1197" t="inlineStr">
         <is>
           <t>Харківська</t>
         </is>
       </c>
     </row>
-    <row r="1199">
-      <c r="A1199" t="inlineStr">
+    <row r="1198">
+      <c r="A1198" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1199" t="n">
+      <c r="B1198" t="n">
         <v>3544</v>
       </c>
-      <c r="C1199" t="inlineStr">
+      <c r="C1198" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1199" t="inlineStr">
+      <c r="D1198" t="inlineStr">
         <is>
           <t>просп Петра Григоренка 3</t>
         </is>
       </c>
-      <c r="E1199" t="inlineStr">
+      <c r="E1198" t="inlineStr">
         <is>
           <t>Харків</t>
         </is>
       </c>
-      <c r="F1199" t="inlineStr">
+      <c r="F1198" t="inlineStr">
         <is>
           <t>Харківська</t>
         </is>
       </c>
-      <c r="G1199" t="n">
+      <c r="G1198" t="n">
         <v>49.9650438</v>
       </c>
-      <c r="H1199" t="n">
+      <c r="H1198" t="n">
         <v>36.3219614</v>
       </c>
-      <c r="I1199" t="inlineStr">
+      <c r="I1198" t="inlineStr">
         <is>
           <t>Пн: 09:00-18:00
 Вт: 09:00-18:00
@@ -55626,48 +55574,48 @@
 Нд: 09:00-17:00</t>
         </is>
       </c>
-      <c r="J1199" t="inlineStr">
+      <c r="J1198" t="inlineStr">
         <is>
           <t>Харківська</t>
         </is>
       </c>
     </row>
-    <row r="1200">
-      <c r="A1200" t="inlineStr">
+    <row r="1199">
+      <c r="A1199" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1200" t="n">
+      <c r="B1199" t="n">
         <v>3545</v>
       </c>
-      <c r="C1200" t="inlineStr">
+      <c r="C1199" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1200" t="inlineStr">
+      <c r="D1199" t="inlineStr">
         <is>
           <t>просп Аерокосмічний (Гагаріна) 177</t>
         </is>
       </c>
-      <c r="E1200" t="inlineStr">
+      <c r="E1199" t="inlineStr">
         <is>
           <t>Харків</t>
         </is>
       </c>
-      <c r="F1200" t="inlineStr">
+      <c r="F1199" t="inlineStr">
         <is>
           <t>Харківська</t>
         </is>
       </c>
-      <c r="G1200" t="n">
+      <c r="G1199" t="n">
         <v>50.0169162</v>
       </c>
-      <c r="H1200" t="n">
+      <c r="H1199" t="n">
         <v>36.2067146</v>
       </c>
-      <c r="I1200" t="inlineStr">
+      <c r="I1199" t="inlineStr">
         <is>
           <t>Пн: 09:00-18:00
 Вт: 09:00-18:00
@@ -55678,48 +55626,48 @@
 Нд: 09:00-17:00</t>
         </is>
       </c>
-      <c r="J1200" t="inlineStr">
+      <c r="J1199" t="inlineStr">
         <is>
           <t>Харківська</t>
         </is>
       </c>
     </row>
-    <row r="1201">
-      <c r="A1201" t="inlineStr">
+    <row r="1200">
+      <c r="A1200" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1201" t="n">
+      <c r="B1200" t="n">
         <v>3547</v>
       </c>
-      <c r="C1201" t="inlineStr">
+      <c r="C1200" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1201" t="inlineStr">
+      <c r="D1200" t="inlineStr">
         <is>
           <t>вул Олімпійська 75</t>
         </is>
       </c>
-      <c r="E1201" t="inlineStr">
+      <c r="E1200" t="inlineStr">
         <is>
           <t>Хотин</t>
         </is>
       </c>
-      <c r="F1201" t="inlineStr">
+      <c r="F1200" t="inlineStr">
         <is>
           <t>Чернівецька</t>
         </is>
       </c>
-      <c r="G1201" t="n">
+      <c r="G1200" t="n">
         <v>48.5043413</v>
       </c>
-      <c r="H1201" t="n">
+      <c r="H1200" t="n">
         <v>26.490402</v>
       </c>
-      <c r="I1201" t="inlineStr">
+      <c r="I1200" t="inlineStr">
         <is>
           <t>Пн: 09:00-18:00
 Вт: 09:00-18:00
@@ -55730,48 +55678,48 @@
 Нд: 10:00-14:00</t>
         </is>
       </c>
-      <c r="J1201" t="inlineStr">
+      <c r="J1200" t="inlineStr">
         <is>
           <t>Чернівецька</t>
         </is>
       </c>
     </row>
-    <row r="1202">
-      <c r="A1202" t="inlineStr">
+    <row r="1201">
+      <c r="A1201" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1202" t="n">
+      <c r="B1201" t="n">
         <v>3549</v>
       </c>
-      <c r="C1202" t="inlineStr">
+      <c r="C1201" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1202" t="inlineStr">
+      <c r="D1201" t="inlineStr">
         <is>
           <t>вул Жовтнева 4-А</t>
         </is>
       </c>
-      <c r="E1202" t="inlineStr">
+      <c r="E1201" t="inlineStr">
         <is>
           <t>Гребінка</t>
         </is>
       </c>
-      <c r="F1202" t="inlineStr">
+      <c r="F1201" t="inlineStr">
         <is>
           <t>Полтавська</t>
         </is>
       </c>
-      <c r="G1202" t="n">
+      <c r="G1201" t="n">
         <v>50.1185138</v>
       </c>
-      <c r="H1202" t="n">
+      <c r="H1201" t="n">
         <v>32.4391051</v>
       </c>
-      <c r="I1202" t="inlineStr">
+      <c r="I1201" t="inlineStr">
         <is>
           <t>Пн: 09:00-17:00
 Вт: 09:00-17:00
@@ -55782,48 +55730,48 @@
 Нд: 09:00-14:00</t>
         </is>
       </c>
-      <c r="J1202" t="inlineStr">
+      <c r="J1201" t="inlineStr">
         <is>
           <t>Полтавська</t>
         </is>
       </c>
     </row>
-    <row r="1203">
-      <c r="A1203" t="inlineStr">
+    <row r="1202">
+      <c r="A1202" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1203" t="n">
+      <c r="B1202" t="n">
         <v>3551</v>
       </c>
-      <c r="C1203" t="inlineStr">
+      <c r="C1202" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1203" t="inlineStr">
+      <c r="D1202" t="inlineStr">
         <is>
           <t>вул Шевченка 50</t>
         </is>
       </c>
-      <c r="E1203" t="inlineStr">
+      <c r="E1202" t="inlineStr">
         <is>
           <t>Богородчани</t>
         </is>
       </c>
-      <c r="F1203" t="inlineStr">
+      <c r="F1202" t="inlineStr">
         <is>
           <t>Івано-Франківська</t>
         </is>
       </c>
-      <c r="G1203" t="n">
+      <c r="G1202" t="n">
         <v>48.809756</v>
       </c>
-      <c r="H1203" t="n">
+      <c r="H1202" t="n">
         <v>24.5400082</v>
       </c>
-      <c r="I1203" t="inlineStr">
+      <c r="I1202" t="inlineStr">
         <is>
           <t>Пн: 09:00-18:00
 Вт: 09:00-18:00
@@ -55834,48 +55782,48 @@
 Нд: 10:00-16:00</t>
         </is>
       </c>
-      <c r="J1203" t="inlineStr">
+      <c r="J1202" t="inlineStr">
         <is>
           <t>Івано-Франківська</t>
         </is>
       </c>
     </row>
-    <row r="1204">
-      <c r="A1204" t="inlineStr">
+    <row r="1203">
+      <c r="A1203" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1204" t="n">
+      <c r="B1203" t="n">
         <v>3554</v>
       </c>
-      <c r="C1204" t="inlineStr">
+      <c r="C1203" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1204" t="inlineStr">
+      <c r="D1203" t="inlineStr">
         <is>
           <t>вул Городоцька 137</t>
         </is>
       </c>
-      <c r="E1204" t="inlineStr">
+      <c r="E1203" t="inlineStr">
         <is>
           <t>Львів</t>
         </is>
       </c>
-      <c r="F1204" t="inlineStr">
+      <c r="F1203" t="inlineStr">
         <is>
           <t>Львівська</t>
         </is>
       </c>
-      <c r="G1204" t="n">
+      <c r="G1203" t="n">
         <v>49.8367768</v>
       </c>
-      <c r="H1204" t="n">
+      <c r="H1203" t="n">
         <v>24.0028087</v>
       </c>
-      <c r="I1204" t="inlineStr">
+      <c r="I1203" t="inlineStr">
         <is>
           <t>Пн: 09:00-19:00
 Вт: 09:00-19:00
@@ -55886,48 +55834,48 @@
 Нд: 10:00-18:00</t>
         </is>
       </c>
-      <c r="J1204" t="inlineStr">
+      <c r="J1203" t="inlineStr">
         <is>
           <t>Львівська</t>
         </is>
       </c>
     </row>
-    <row r="1205">
-      <c r="A1205" t="inlineStr">
+    <row r="1204">
+      <c r="A1204" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1205" t="n">
+      <c r="B1204" t="n">
         <v>3555</v>
       </c>
-      <c r="C1205" t="inlineStr">
+      <c r="C1204" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1205" t="inlineStr">
+      <c r="D1204" t="inlineStr">
         <is>
           <t>вул Здолбунівська 15</t>
         </is>
       </c>
-      <c r="E1205" t="inlineStr">
+      <c r="E1204" t="inlineStr">
         <is>
           <t>Київ</t>
         </is>
       </c>
-      <c r="F1205" t="inlineStr">
+      <c r="F1204" t="inlineStr">
         <is>
           <t>м. Київ</t>
         </is>
       </c>
-      <c r="G1205" t="n">
+      <c r="G1204" t="n">
         <v>50.4185123</v>
       </c>
-      <c r="H1205" t="n">
+      <c r="H1204" t="n">
         <v>30.631541</v>
       </c>
-      <c r="I1205" t="inlineStr">
+      <c r="I1204" t="inlineStr">
         <is>
           <t>Пн: 10:00-20:00
 Вт: 10:00-20:00
@@ -55938,48 +55886,48 @@
 Нд: 10:00-20:00</t>
         </is>
       </c>
-      <c r="J1205" t="inlineStr">
+      <c r="J1204" t="inlineStr">
         <is>
           <t>м. Київ</t>
         </is>
       </c>
     </row>
-    <row r="1206">
-      <c r="A1206" t="inlineStr">
+    <row r="1205">
+      <c r="A1205" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1206" t="n">
+      <c r="B1205" t="n">
         <v>3556</v>
       </c>
-      <c r="C1206" t="inlineStr">
+      <c r="C1205" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1206" t="inlineStr">
+      <c r="D1205" t="inlineStr">
         <is>
           <t>вул Шевченка 42</t>
         </is>
       </c>
-      <c r="E1206" t="inlineStr">
+      <c r="E1205" t="inlineStr">
         <is>
           <t>Овруч</t>
         </is>
       </c>
-      <c r="F1206" t="inlineStr">
+      <c r="F1205" t="inlineStr">
         <is>
           <t>Житомирська</t>
         </is>
       </c>
-      <c r="G1206" t="n">
+      <c r="G1205" t="n">
         <v>51.3197441</v>
       </c>
-      <c r="H1206" t="n">
+      <c r="H1205" t="n">
         <v>28.8004248</v>
       </c>
-      <c r="I1206" t="inlineStr">
+      <c r="I1205" t="inlineStr">
         <is>
           <t>Пн: 09:00-18:00
 Вт: 09:00-18:00
@@ -55990,48 +55938,48 @@
 Нд: 09:00-18:00</t>
         </is>
       </c>
-      <c r="J1206" t="inlineStr">
+      <c r="J1205" t="inlineStr">
         <is>
           <t>Житомирська</t>
         </is>
       </c>
     </row>
-    <row r="1207">
-      <c r="A1207" t="inlineStr">
+    <row r="1206">
+      <c r="A1206" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1207" t="n">
+      <c r="B1206" t="n">
         <v>3558</v>
       </c>
-      <c r="C1207" t="inlineStr">
+      <c r="C1206" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1207" t="inlineStr">
+      <c r="D1206" t="inlineStr">
         <is>
           <t>вул Київська 26</t>
         </is>
       </c>
-      <c r="E1207" t="inlineStr">
+      <c r="E1206" t="inlineStr">
         <is>
           <t>Іванків</t>
         </is>
       </c>
-      <c r="F1207" t="inlineStr">
+      <c r="F1206" t="inlineStr">
         <is>
           <t>Kiev</t>
         </is>
       </c>
-      <c r="G1207" t="n">
+      <c r="G1206" t="n">
         <v>50.9338356</v>
       </c>
-      <c r="H1207" t="n">
+      <c r="H1206" t="n">
         <v>29.9031381</v>
       </c>
-      <c r="I1207" t="inlineStr">
+      <c r="I1206" t="inlineStr">
         <is>
           <t>Пн: 08:00-18:00
 Вт: 08:00-18:00
@@ -56042,48 +55990,48 @@
 Нд: 09:00-17:00</t>
         </is>
       </c>
-      <c r="J1207" t="inlineStr">
+      <c r="J1206" t="inlineStr">
         <is>
           <t>Kiev</t>
         </is>
       </c>
     </row>
-    <row r="1208">
-      <c r="A1208" t="inlineStr">
+    <row r="1207">
+      <c r="A1207" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1208" t="n">
+      <c r="B1207" t="n">
         <v>3559</v>
       </c>
-      <c r="C1208" t="inlineStr">
+      <c r="C1207" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1208" t="inlineStr">
+      <c r="D1207" t="inlineStr">
         <is>
           <t>просп Соборний 51</t>
         </is>
       </c>
-      <c r="E1208" t="inlineStr">
+      <c r="E1207" t="inlineStr">
         <is>
           <t>Запоріжжя</t>
         </is>
       </c>
-      <c r="F1208" t="inlineStr">
+      <c r="F1207" t="inlineStr">
         <is>
           <t>Zaporizhia</t>
         </is>
       </c>
-      <c r="G1208" t="n">
+      <c r="G1207" t="n">
         <v>47.8176164</v>
       </c>
-      <c r="H1208" t="n">
+      <c r="H1207" t="n">
         <v>35.1753352</v>
       </c>
-      <c r="I1208" t="inlineStr">
+      <c r="I1207" t="inlineStr">
         <is>
           <t>Пн: 09:00-19:00
 Вт: 09:00-19:00
@@ -56094,48 +56042,48 @@
 Нд: 10:00-18:00</t>
         </is>
       </c>
-      <c r="J1208" t="inlineStr">
+      <c r="J1207" t="inlineStr">
         <is>
           <t>Zaporizhia</t>
         </is>
       </c>
     </row>
-    <row r="1209">
-      <c r="A1209" t="inlineStr">
+    <row r="1208">
+      <c r="A1208" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1209" t="n">
+      <c r="B1208" t="n">
         <v>3560</v>
       </c>
-      <c r="C1209" t="inlineStr">
+      <c r="C1208" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1209" t="inlineStr">
+      <c r="D1208" t="inlineStr">
         <is>
           <t>вул Палацова 9</t>
         </is>
       </c>
-      <c r="E1209" t="inlineStr">
+      <c r="E1208" t="inlineStr">
         <is>
           <t>Краматорськ</t>
         </is>
       </c>
-      <c r="F1209" t="inlineStr">
+      <c r="F1208" t="inlineStr">
         <is>
           <t>Донецька</t>
         </is>
       </c>
-      <c r="G1209" t="n">
+      <c r="G1208" t="n">
         <v>48.7366237</v>
       </c>
-      <c r="H1209" t="n">
+      <c r="H1208" t="n">
         <v>37.5916381</v>
       </c>
-      <c r="I1209" t="inlineStr">
+      <c r="I1208" t="inlineStr">
         <is>
           <t>Пн: 09:00-17:00
 Вт: 09:00-17:00
@@ -56146,48 +56094,48 @@
 Нд: 09:00-17:00</t>
         </is>
       </c>
-      <c r="J1209" t="inlineStr">
+      <c r="J1208" t="inlineStr">
         <is>
           <t>Донецька</t>
         </is>
       </c>
     </row>
-    <row r="1210">
-      <c r="A1210" t="inlineStr">
+    <row r="1209">
+      <c r="A1209" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1210" t="n">
+      <c r="B1209" t="n">
         <v>3561</v>
       </c>
-      <c r="C1210" t="inlineStr">
+      <c r="C1209" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1210" t="inlineStr">
+      <c r="D1209" t="inlineStr">
         <is>
           <t>вул Ф. Караманець (Ватутіна) 29</t>
         </is>
       </c>
-      <c r="E1210" t="inlineStr">
+      <c r="E1209" t="inlineStr">
         <is>
           <t>Кривий Ріг</t>
         </is>
       </c>
-      <c r="F1210" t="inlineStr">
+      <c r="F1209" t="inlineStr">
         <is>
           <t>Дніпропетровська</t>
         </is>
       </c>
-      <c r="G1210" t="n">
+      <c r="G1209" t="n">
         <v>48.024687</v>
       </c>
-      <c r="H1210" t="n">
+      <c r="H1209" t="n">
         <v>33.4709468</v>
       </c>
-      <c r="I1210" t="inlineStr">
+      <c r="I1209" t="inlineStr">
         <is>
           <t>Пн: 09:00-18:00
 Вт: 09:00-18:00
@@ -56198,9 +56146,61 @@
 Нд: Вихідний</t>
         </is>
       </c>
+      <c r="J1209" t="inlineStr">
+        <is>
+          <t>Дніпропетровська</t>
+        </is>
+      </c>
+    </row>
+    <row r="1210">
+      <c r="A1210" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1210" t="n">
+        <v>3563</v>
+      </c>
+      <c r="C1210" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1210" t="inlineStr">
+        <is>
+          <t>вул Шевченка 116</t>
+        </is>
+      </c>
+      <c r="E1210" t="inlineStr">
+        <is>
+          <t>Дунаївці</t>
+        </is>
+      </c>
+      <c r="F1210" t="inlineStr">
+        <is>
+          <t>Хмельницька</t>
+        </is>
+      </c>
+      <c r="G1210" t="n">
+        <v>48.8922754</v>
+      </c>
+      <c r="H1210" t="n">
+        <v>26.8568241</v>
+      </c>
+      <c r="I1210" t="inlineStr">
+        <is>
+          <t>Пн: 09:00-18:00
+Вт: 09:00-18:00
+Ср: 09:00-18:00
+Чт: 09:00-18:00
+Пт: 09:00-18:00
+Сб: 09:00-14:00
+Нд: Вихідний</t>
+        </is>
+      </c>
       <c r="J1210" t="inlineStr">
         <is>
-          <t>Дніпропетровська</t>
+          <t>Хмельницька</t>
         </is>
       </c>
     </row>
@@ -56211,7 +56211,7 @@
         </is>
       </c>
       <c r="B1211" t="n">
-        <v>3562</v>
+        <v>3565</v>
       </c>
       <c r="C1211" t="inlineStr">
         <is>
@@ -56220,26 +56220,130 @@
       </c>
       <c r="D1211" t="inlineStr">
         <is>
+          <t>вул Небесної Сотні 85</t>
+        </is>
+      </c>
+      <c r="E1211" t="inlineStr">
+        <is>
+          <t>Романів</t>
+        </is>
+      </c>
+      <c r="F1211" t="inlineStr">
+        <is>
+          <t>Житомирська</t>
+        </is>
+      </c>
+      <c r="G1211" t="n">
+        <v>50.1401752</v>
+      </c>
+      <c r="H1211" t="n">
+        <v>27.9354775</v>
+      </c>
+      <c r="I1211" t="inlineStr">
+        <is>
+          <t>Пн: 08:00-18:00
+Вт: 08:00-18:00
+Ср: 08:00-18:00
+Чт: 08:00-18:00
+Пт: 08:00-18:00
+Сб: 08:00-17:00
+Нд: 09:00-17:00</t>
+        </is>
+      </c>
+      <c r="J1211" t="inlineStr">
+        <is>
+          <t>Житомирська</t>
+        </is>
+      </c>
+    </row>
+    <row r="1212">
+      <c r="A1212" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1212" t="n">
+        <v>3566</v>
+      </c>
+      <c r="C1212" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1212" t="inlineStr">
+        <is>
+          <t>вул Р. Шухевича 1а</t>
+        </is>
+      </c>
+      <c r="E1212" t="inlineStr">
+        <is>
+          <t>Хмельницький</t>
+        </is>
+      </c>
+      <c r="F1212" t="inlineStr">
+        <is>
+          <t>Хмельницька</t>
+        </is>
+      </c>
+      <c r="G1212" t="n">
+        <v>49.4360713</v>
+      </c>
+      <c r="H1212" t="n">
+        <v>26.9572295</v>
+      </c>
+      <c r="I1212" t="inlineStr">
+        <is>
+          <t>Пн: 09:00-19:00
+Вт: 09:00-19:00
+Ср: 09:00-19:00
+Чт: 09:00-19:00
+Пт: 09:00-19:00
+Сб: 10:00-18:00
+Нд: 10:00-18:00</t>
+        </is>
+      </c>
+      <c r="J1212" t="inlineStr">
+        <is>
+          <t>Хмельницька</t>
+        </is>
+      </c>
+    </row>
+    <row r="1213">
+      <c r="A1213" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1213" t="n">
+        <v>3567</v>
+      </c>
+      <c r="C1213" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1213" t="inlineStr">
+        <is>
           <t>вул Макухи 1</t>
         </is>
       </c>
-      <c r="E1211" t="inlineStr">
+      <c r="E1213" t="inlineStr">
         <is>
           <t>Тлумач</t>
         </is>
       </c>
-      <c r="F1211" t="inlineStr">
+      <c r="F1213" t="inlineStr">
         <is>
           <t>Івано-Франківська</t>
         </is>
       </c>
-      <c r="G1211" t="n">
+      <c r="G1213" t="n">
         <v>48.8652727</v>
       </c>
-      <c r="H1211" t="n">
+      <c r="H1213" t="n">
         <v>25.0043864</v>
       </c>
-      <c r="I1211" t="inlineStr">
+      <c r="I1213" t="inlineStr">
         <is>
           <t>Пн: 09:00-17:00
 Вт: 09:00-17:00
@@ -56250,165 +56354,61 @@
 Нд: Вихідний</t>
         </is>
       </c>
-      <c r="J1211" t="inlineStr">
+      <c r="J1213" t="inlineStr">
         <is>
           <t>Івано-Франківська</t>
         </is>
       </c>
     </row>
-    <row r="1212">
-      <c r="A1212" t="inlineStr">
+    <row r="1214">
+      <c r="A1214" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1212" t="n">
-        <v>3563</v>
-      </c>
-      <c r="C1212" t="inlineStr">
+      <c r="B1214" t="n">
+        <v>3568</v>
+      </c>
+      <c r="C1214" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1212" t="inlineStr">
-        <is>
-          <t>вул Шевченка 116</t>
-        </is>
-      </c>
-      <c r="E1212" t="inlineStr">
-        <is>
-          <t>Дунаївці</t>
-        </is>
-      </c>
-      <c r="F1212" t="inlineStr">
-        <is>
-          <t>Хмельницька</t>
-        </is>
-      </c>
-      <c r="G1212" t="n">
-        <v>48.8922754</v>
-      </c>
-      <c r="H1212" t="n">
-        <v>26.8568241</v>
-      </c>
-      <c r="I1212" t="inlineStr">
+      <c r="D1214" t="inlineStr">
+        <is>
+          <t>вул Андріївська 5</t>
+        </is>
+      </c>
+      <c r="E1214" t="inlineStr">
+        <is>
+          <t>Березне</t>
+        </is>
+      </c>
+      <c r="F1214" t="inlineStr">
+        <is>
+          <t>Рівненська</t>
+        </is>
+      </c>
+      <c r="G1214" t="n">
+        <v>51.0019955</v>
+      </c>
+      <c r="H1214" t="n">
+        <v>26.7547284</v>
+      </c>
+      <c r="I1214" t="inlineStr">
         <is>
           <t>Пн: 09:00-18:00
 Вт: 09:00-18:00
 Ср: 09:00-18:00
 Чт: 09:00-18:00
 Пт: 09:00-18:00
-Сб: 09:00-14:00
-Нд: Вихідний</t>
-        </is>
-      </c>
-      <c r="J1212" t="inlineStr">
-        <is>
-          <t>Хмельницька</t>
-        </is>
-      </c>
-    </row>
-    <row r="1213">
-      <c r="A1213" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1213" t="n">
-        <v>3565</v>
-      </c>
-      <c r="C1213" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1213" t="inlineStr">
-        <is>
-          <t>вул Небесної Сотні 85</t>
-        </is>
-      </c>
-      <c r="E1213" t="inlineStr">
-        <is>
-          <t>Романів</t>
-        </is>
-      </c>
-      <c r="F1213" t="inlineStr">
-        <is>
-          <t>Житомирська</t>
-        </is>
-      </c>
-      <c r="G1213" t="n">
-        <v>50.1401752</v>
-      </c>
-      <c r="H1213" t="n">
-        <v>27.9354775</v>
-      </c>
-      <c r="I1213" t="inlineStr">
-        <is>
-          <t>Пн: 08:00-18:00
-Вт: 08:00-18:00
-Ср: 08:00-18:00
-Чт: 08:00-18:00
-Пт: 08:00-18:00
-Сб: 08:00-17:00
-Нд: 09:00-17:00</t>
-        </is>
-      </c>
-      <c r="J1213" t="inlineStr">
-        <is>
-          <t>Житомирська</t>
-        </is>
-      </c>
-    </row>
-    <row r="1214">
-      <c r="A1214" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1214" t="n">
-        <v>3566</v>
-      </c>
-      <c r="C1214" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1214" t="inlineStr">
-        <is>
-          <t>вул Р. Шухевича 1а</t>
-        </is>
-      </c>
-      <c r="E1214" t="inlineStr">
-        <is>
-          <t>Хмельницький</t>
-        </is>
-      </c>
-      <c r="F1214" t="inlineStr">
-        <is>
-          <t>Хмельницька</t>
-        </is>
-      </c>
-      <c r="G1214" t="n">
-        <v>49.4360713</v>
-      </c>
-      <c r="H1214" t="n">
-        <v>26.9572295</v>
-      </c>
-      <c r="I1214" t="inlineStr">
-        <is>
-          <t>Пн: 09:00-19:00
-Вт: 09:00-19:00
-Ср: 09:00-19:00
-Чт: 09:00-19:00
-Пт: 09:00-19:00
-Сб: 10:00-18:00
-Нд: 10:00-18:00</t>
+Сб: 09:00-16:00
+Нд: 09:00-16:00</t>
         </is>
       </c>
       <c r="J1214" t="inlineStr">
         <is>
-          <t>Хмельницька</t>
+          <t>Рівненська</t>
         </is>
       </c>
     </row>

--- a/all_shops.xlsx
+++ b/all_shops.xlsx
@@ -55639,7 +55639,7 @@
         </is>
       </c>
       <c r="B1200" t="n">
-        <v>3551</v>
+        <v>3554</v>
       </c>
       <c r="C1200" t="inlineStr">
         <is>
@@ -55648,78 +55648,26 @@
       </c>
       <c r="D1200" t="inlineStr">
         <is>
-          <t>вул Шевченка 50</t>
+          <t>вул Городоцька 137</t>
         </is>
       </c>
       <c r="E1200" t="inlineStr">
         <is>
-          <t>Богородчани</t>
+          <t>Львів</t>
         </is>
       </c>
       <c r="F1200" t="inlineStr">
         <is>
-          <t>Івано-Франківська</t>
+          <t>Львівська</t>
         </is>
       </c>
       <c r="G1200" t="n">
-        <v>48.809756</v>
+        <v>49.8367768</v>
       </c>
       <c r="H1200" t="n">
-        <v>24.5400082</v>
+        <v>24.0028087</v>
       </c>
       <c r="I1200" t="inlineStr">
-        <is>
-          <t>Пн: 09:00-18:00
-Вт: 09:00-18:00
-Ср: 09:00-18:00
-Чт: 09:00-18:00
-Пт: 09:00-18:00
-Сб: 09:00-17:00
-Нд: 10:00-16:00</t>
-        </is>
-      </c>
-      <c r="J1200" t="inlineStr">
-        <is>
-          <t>Івано-Франківська</t>
-        </is>
-      </c>
-    </row>
-    <row r="1201">
-      <c r="A1201" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1201" t="n">
-        <v>3554</v>
-      </c>
-      <c r="C1201" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1201" t="inlineStr">
-        <is>
-          <t>вул Городоцька 137</t>
-        </is>
-      </c>
-      <c r="E1201" t="inlineStr">
-        <is>
-          <t>Львів</t>
-        </is>
-      </c>
-      <c r="F1201" t="inlineStr">
-        <is>
-          <t>Львівська</t>
-        </is>
-      </c>
-      <c r="G1201" t="n">
-        <v>49.8367768</v>
-      </c>
-      <c r="H1201" t="n">
-        <v>24.0028087</v>
-      </c>
-      <c r="I1201" t="inlineStr">
         <is>
           <t>Пн: 09:00-19:00
 Вт: 09:00-19:00
@@ -55730,48 +55678,48 @@
 Нд: 10:00-18:00</t>
         </is>
       </c>
-      <c r="J1201" t="inlineStr">
+      <c r="J1200" t="inlineStr">
         <is>
           <t>Львівська</t>
         </is>
       </c>
     </row>
-    <row r="1202">
-      <c r="A1202" t="inlineStr">
+    <row r="1201">
+      <c r="A1201" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1202" t="n">
+      <c r="B1201" t="n">
         <v>3555</v>
       </c>
-      <c r="C1202" t="inlineStr">
+      <c r="C1201" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1202" t="inlineStr">
+      <c r="D1201" t="inlineStr">
         <is>
           <t>вул Здолбунівська 15</t>
         </is>
       </c>
-      <c r="E1202" t="inlineStr">
+      <c r="E1201" t="inlineStr">
         <is>
           <t>Київ</t>
         </is>
       </c>
-      <c r="F1202" t="inlineStr">
+      <c r="F1201" t="inlineStr">
         <is>
           <t>м. Київ</t>
         </is>
       </c>
-      <c r="G1202" t="n">
+      <c r="G1201" t="n">
         <v>50.4185123</v>
       </c>
-      <c r="H1202" t="n">
+      <c r="H1201" t="n">
         <v>30.631541</v>
       </c>
-      <c r="I1202" t="inlineStr">
+      <c r="I1201" t="inlineStr">
         <is>
           <t>Пн: 10:00-20:00
 Вт: 10:00-20:00
@@ -55782,48 +55730,48 @@
 Нд: 10:00-20:00</t>
         </is>
       </c>
-      <c r="J1202" t="inlineStr">
+      <c r="J1201" t="inlineStr">
         <is>
           <t>м. Київ</t>
         </is>
       </c>
     </row>
-    <row r="1203">
-      <c r="A1203" t="inlineStr">
+    <row r="1202">
+      <c r="A1202" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1203" t="n">
+      <c r="B1202" t="n">
         <v>3556</v>
       </c>
-      <c r="C1203" t="inlineStr">
+      <c r="C1202" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1203" t="inlineStr">
+      <c r="D1202" t="inlineStr">
         <is>
           <t>вул Шевченка 42</t>
         </is>
       </c>
-      <c r="E1203" t="inlineStr">
+      <c r="E1202" t="inlineStr">
         <is>
           <t>Овруч</t>
         </is>
       </c>
-      <c r="F1203" t="inlineStr">
+      <c r="F1202" t="inlineStr">
         <is>
           <t>Житомирська</t>
         </is>
       </c>
-      <c r="G1203" t="n">
+      <c r="G1202" t="n">
         <v>51.3197441</v>
       </c>
-      <c r="H1203" t="n">
+      <c r="H1202" t="n">
         <v>28.8004248</v>
       </c>
-      <c r="I1203" t="inlineStr">
+      <c r="I1202" t="inlineStr">
         <is>
           <t>Пн: 09:00-18:00
 Вт: 09:00-18:00
@@ -55834,48 +55782,48 @@
 Нд: 09:00-18:00</t>
         </is>
       </c>
-      <c r="J1203" t="inlineStr">
+      <c r="J1202" t="inlineStr">
         <is>
           <t>Житомирська</t>
         </is>
       </c>
     </row>
-    <row r="1204">
-      <c r="A1204" t="inlineStr">
+    <row r="1203">
+      <c r="A1203" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1204" t="n">
+      <c r="B1203" t="n">
         <v>3558</v>
       </c>
-      <c r="C1204" t="inlineStr">
+      <c r="C1203" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1204" t="inlineStr">
+      <c r="D1203" t="inlineStr">
         <is>
           <t>вул Київська 26</t>
         </is>
       </c>
-      <c r="E1204" t="inlineStr">
+      <c r="E1203" t="inlineStr">
         <is>
           <t>Іванків</t>
         </is>
       </c>
-      <c r="F1204" t="inlineStr">
+      <c r="F1203" t="inlineStr">
         <is>
           <t>Kiev</t>
         </is>
       </c>
-      <c r="G1204" t="n">
+      <c r="G1203" t="n">
         <v>50.9338356</v>
       </c>
-      <c r="H1204" t="n">
+      <c r="H1203" t="n">
         <v>29.9031381</v>
       </c>
-      <c r="I1204" t="inlineStr">
+      <c r="I1203" t="inlineStr">
         <is>
           <t>Пн: 08:00-18:00
 Вт: 08:00-18:00
@@ -55886,48 +55834,48 @@
 Нд: 09:00-17:00</t>
         </is>
       </c>
-      <c r="J1204" t="inlineStr">
+      <c r="J1203" t="inlineStr">
         <is>
           <t>Kiev</t>
         </is>
       </c>
     </row>
-    <row r="1205">
-      <c r="A1205" t="inlineStr">
+    <row r="1204">
+      <c r="A1204" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1205" t="n">
+      <c r="B1204" t="n">
         <v>3559</v>
       </c>
-      <c r="C1205" t="inlineStr">
+      <c r="C1204" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1205" t="inlineStr">
+      <c r="D1204" t="inlineStr">
         <is>
           <t>просп Соборний 51</t>
         </is>
       </c>
-      <c r="E1205" t="inlineStr">
+      <c r="E1204" t="inlineStr">
         <is>
           <t>Запоріжжя</t>
         </is>
       </c>
-      <c r="F1205" t="inlineStr">
+      <c r="F1204" t="inlineStr">
         <is>
           <t>Zaporizhia</t>
         </is>
       </c>
-      <c r="G1205" t="n">
+      <c r="G1204" t="n">
         <v>47.8176164</v>
       </c>
-      <c r="H1205" t="n">
+      <c r="H1204" t="n">
         <v>35.1753352</v>
       </c>
-      <c r="I1205" t="inlineStr">
+      <c r="I1204" t="inlineStr">
         <is>
           <t>Пн: 09:00-19:00
 Вт: 09:00-19:00
@@ -55938,48 +55886,48 @@
 Нд: 10:00-18:00</t>
         </is>
       </c>
-      <c r="J1205" t="inlineStr">
+      <c r="J1204" t="inlineStr">
         <is>
           <t>Zaporizhia</t>
         </is>
       </c>
     </row>
-    <row r="1206">
-      <c r="A1206" t="inlineStr">
+    <row r="1205">
+      <c r="A1205" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1206" t="n">
+      <c r="B1205" t="n">
         <v>3560</v>
       </c>
-      <c r="C1206" t="inlineStr">
+      <c r="C1205" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1206" t="inlineStr">
+      <c r="D1205" t="inlineStr">
         <is>
           <t>вул Палацова 9</t>
         </is>
       </c>
-      <c r="E1206" t="inlineStr">
+      <c r="E1205" t="inlineStr">
         <is>
           <t>Краматорськ</t>
         </is>
       </c>
-      <c r="F1206" t="inlineStr">
+      <c r="F1205" t="inlineStr">
         <is>
           <t>Донецька</t>
         </is>
       </c>
-      <c r="G1206" t="n">
+      <c r="G1205" t="n">
         <v>48.7366237</v>
       </c>
-      <c r="H1206" t="n">
+      <c r="H1205" t="n">
         <v>37.5916381</v>
       </c>
-      <c r="I1206" t="inlineStr">
+      <c r="I1205" t="inlineStr">
         <is>
           <t>Пн: 09:00-17:00
 Вт: 09:00-17:00
@@ -55990,48 +55938,48 @@
 Нд: 09:00-17:00</t>
         </is>
       </c>
-      <c r="J1206" t="inlineStr">
+      <c r="J1205" t="inlineStr">
         <is>
           <t>Донецька</t>
         </is>
       </c>
     </row>
-    <row r="1207">
-      <c r="A1207" t="inlineStr">
+    <row r="1206">
+      <c r="A1206" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1207" t="n">
+      <c r="B1206" t="n">
         <v>3561</v>
       </c>
-      <c r="C1207" t="inlineStr">
+      <c r="C1206" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1207" t="inlineStr">
+      <c r="D1206" t="inlineStr">
         <is>
           <t>вул Ф. Караманець (Ватутіна) 29</t>
         </is>
       </c>
-      <c r="E1207" t="inlineStr">
+      <c r="E1206" t="inlineStr">
         <is>
           <t>Кривий Ріг</t>
         </is>
       </c>
-      <c r="F1207" t="inlineStr">
+      <c r="F1206" t="inlineStr">
         <is>
           <t>Дніпропетровська</t>
         </is>
       </c>
-      <c r="G1207" t="n">
+      <c r="G1206" t="n">
         <v>48.024687</v>
       </c>
-      <c r="H1207" t="n">
+      <c r="H1206" t="n">
         <v>33.4709468</v>
       </c>
-      <c r="I1207" t="inlineStr">
+      <c r="I1206" t="inlineStr">
         <is>
           <t>Пн: 09:00-18:00
 Вт: 09:00-18:00
@@ -56042,48 +55990,48 @@
 Нд: Вихідний</t>
         </is>
       </c>
-      <c r="J1207" t="inlineStr">
+      <c r="J1206" t="inlineStr">
         <is>
           <t>Дніпропетровська</t>
         </is>
       </c>
     </row>
-    <row r="1208">
-      <c r="A1208" t="inlineStr">
+    <row r="1207">
+      <c r="A1207" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1208" t="n">
+      <c r="B1207" t="n">
         <v>3563</v>
       </c>
-      <c r="C1208" t="inlineStr">
+      <c r="C1207" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1208" t="inlineStr">
+      <c r="D1207" t="inlineStr">
         <is>
           <t>вул Шевченка 116</t>
         </is>
       </c>
-      <c r="E1208" t="inlineStr">
+      <c r="E1207" t="inlineStr">
         <is>
           <t>Дунаївці</t>
         </is>
       </c>
-      <c r="F1208" t="inlineStr">
+      <c r="F1207" t="inlineStr">
         <is>
           <t>Хмельницька</t>
         </is>
       </c>
-      <c r="G1208" t="n">
+      <c r="G1207" t="n">
         <v>48.8922754</v>
       </c>
-      <c r="H1208" t="n">
+      <c r="H1207" t="n">
         <v>26.8568241</v>
       </c>
-      <c r="I1208" t="inlineStr">
+      <c r="I1207" t="inlineStr">
         <is>
           <t>Пн: 09:00-18:00
 Вт: 09:00-18:00
@@ -56094,48 +56042,48 @@
 Нд: Вихідний</t>
         </is>
       </c>
-      <c r="J1208" t="inlineStr">
+      <c r="J1207" t="inlineStr">
         <is>
           <t>Хмельницька</t>
         </is>
       </c>
     </row>
-    <row r="1209">
-      <c r="A1209" t="inlineStr">
+    <row r="1208">
+      <c r="A1208" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1209" t="n">
+      <c r="B1208" t="n">
         <v>3566</v>
       </c>
-      <c r="C1209" t="inlineStr">
+      <c r="C1208" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1209" t="inlineStr">
+      <c r="D1208" t="inlineStr">
         <is>
           <t>вул Р. Шухевича 1а</t>
         </is>
       </c>
-      <c r="E1209" t="inlineStr">
+      <c r="E1208" t="inlineStr">
         <is>
           <t>Хмельницький</t>
         </is>
       </c>
-      <c r="F1209" t="inlineStr">
+      <c r="F1208" t="inlineStr">
         <is>
           <t>Хмельницька</t>
         </is>
       </c>
-      <c r="G1209" t="n">
+      <c r="G1208" t="n">
         <v>49.4360713</v>
       </c>
-      <c r="H1209" t="n">
+      <c r="H1208" t="n">
         <v>26.9572295</v>
       </c>
-      <c r="I1209" t="inlineStr">
+      <c r="I1208" t="inlineStr">
         <is>
           <t>Пн: 09:00-19:00
 Вт: 09:00-19:00
@@ -56146,48 +56094,48 @@
 Нд: 10:00-18:00</t>
         </is>
       </c>
-      <c r="J1209" t="inlineStr">
+      <c r="J1208" t="inlineStr">
         <is>
           <t>Хмельницька</t>
         </is>
       </c>
     </row>
-    <row r="1210">
-      <c r="A1210" t="inlineStr">
+    <row r="1209">
+      <c r="A1209" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1210" t="n">
+      <c r="B1209" t="n">
         <v>3567</v>
       </c>
-      <c r="C1210" t="inlineStr">
+      <c r="C1209" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1210" t="inlineStr">
+      <c r="D1209" t="inlineStr">
         <is>
           <t>вул Макухи 1</t>
         </is>
       </c>
-      <c r="E1210" t="inlineStr">
+      <c r="E1209" t="inlineStr">
         <is>
           <t>Тлумач</t>
         </is>
       </c>
-      <c r="F1210" t="inlineStr">
+      <c r="F1209" t="inlineStr">
         <is>
           <t>Івано-Франківська</t>
         </is>
       </c>
-      <c r="G1210" t="n">
+      <c r="G1209" t="n">
         <v>48.8652727</v>
       </c>
-      <c r="H1210" t="n">
+      <c r="H1209" t="n">
         <v>25.0043864</v>
       </c>
-      <c r="I1210" t="inlineStr">
+      <c r="I1209" t="inlineStr">
         <is>
           <t>Пн: 09:00-17:00
 Вт: 09:00-17:00
@@ -56198,48 +56146,48 @@
 Нд: Вихідний</t>
         </is>
       </c>
-      <c r="J1210" t="inlineStr">
+      <c r="J1209" t="inlineStr">
         <is>
           <t>Івано-Франківська</t>
         </is>
       </c>
     </row>
-    <row r="1211">
-      <c r="A1211" t="inlineStr">
+    <row r="1210">
+      <c r="A1210" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1211" t="n">
+      <c r="B1210" t="n">
         <v>3568</v>
       </c>
-      <c r="C1211" t="inlineStr">
+      <c r="C1210" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1211" t="inlineStr">
+      <c r="D1210" t="inlineStr">
         <is>
           <t>вул Андріївська 5</t>
         </is>
       </c>
-      <c r="E1211" t="inlineStr">
+      <c r="E1210" t="inlineStr">
         <is>
           <t>Березне</t>
         </is>
       </c>
-      <c r="F1211" t="inlineStr">
+      <c r="F1210" t="inlineStr">
         <is>
           <t>Рівненська</t>
         </is>
       </c>
-      <c r="G1211" t="n">
+      <c r="G1210" t="n">
         <v>51.0019955</v>
       </c>
-      <c r="H1211" t="n">
+      <c r="H1210" t="n">
         <v>26.7547284</v>
       </c>
-      <c r="I1211" t="inlineStr">
+      <c r="I1210" t="inlineStr">
         <is>
           <t>Пн: 09:00-18:00
 Вт: 09:00-18:00
@@ -56250,48 +56198,48 @@
 Нд: 09:00-16:00</t>
         </is>
       </c>
-      <c r="J1211" t="inlineStr">
+      <c r="J1210" t="inlineStr">
         <is>
           <t>Рівненська</t>
         </is>
       </c>
     </row>
-    <row r="1212">
-      <c r="A1212" t="inlineStr">
+    <row r="1211">
+      <c r="A1211" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1212" t="n">
+      <c r="B1211" t="n">
         <v>3569</v>
       </c>
-      <c r="C1212" t="inlineStr">
+      <c r="C1211" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1212" t="inlineStr">
+      <c r="D1211" t="inlineStr">
         <is>
           <t>вул Широка 37</t>
         </is>
       </c>
-      <c r="E1212" t="inlineStr">
+      <c r="E1211" t="inlineStr">
         <is>
           <t>Сарни</t>
         </is>
       </c>
-      <c r="F1212" t="inlineStr">
+      <c r="F1211" t="inlineStr">
         <is>
           <t>Рівненська</t>
         </is>
       </c>
-      <c r="G1212" t="n">
+      <c r="G1211" t="n">
         <v>51.3355537</v>
       </c>
-      <c r="H1212" t="n">
+      <c r="H1211" t="n">
         <v>26.6158412</v>
       </c>
-      <c r="I1212" t="inlineStr">
+      <c r="I1211" t="inlineStr">
         <is>
           <t>Пн: 09:00-18:00
 Вт: 09:00-18:00
@@ -56302,48 +56250,48 @@
 Нд: 09:00-17:00</t>
         </is>
       </c>
-      <c r="J1212" t="inlineStr">
+      <c r="J1211" t="inlineStr">
         <is>
           <t>Рівненська</t>
         </is>
       </c>
     </row>
-    <row r="1213">
-      <c r="A1213" t="inlineStr">
+    <row r="1212">
+      <c r="A1212" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1213" t="n">
+      <c r="B1212" t="n">
         <v>3570</v>
       </c>
-      <c r="C1213" t="inlineStr">
+      <c r="C1212" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1213" t="inlineStr">
+      <c r="D1212" t="inlineStr">
         <is>
           <t>вул Січових Стрільців 33А</t>
         </is>
       </c>
-      <c r="E1213" t="inlineStr">
+      <c r="E1212" t="inlineStr">
         <is>
           <t>Бурштин</t>
         </is>
       </c>
-      <c r="F1213" t="inlineStr">
+      <c r="F1212" t="inlineStr">
         <is>
           <t>Івано-Франківська</t>
         </is>
       </c>
-      <c r="G1213" t="n">
+      <c r="G1212" t="n">
         <v>49.2511835</v>
       </c>
-      <c r="H1213" t="n">
+      <c r="H1212" t="n">
         <v>24.6288295</v>
       </c>
-      <c r="I1213" t="inlineStr">
+      <c r="I1212" t="inlineStr">
         <is>
           <t>Пн: 09:00-18:00
 Вт: 09:00-18:00
@@ -56354,48 +56302,48 @@
 Нд: Вихідний</t>
         </is>
       </c>
-      <c r="J1213" t="inlineStr">
+      <c r="J1212" t="inlineStr">
         <is>
           <t>Івано-Франківська</t>
         </is>
       </c>
     </row>
-    <row r="1214">
-      <c r="A1214" t="inlineStr">
+    <row r="1213">
+      <c r="A1213" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1214" t="n">
+      <c r="B1213" t="n">
         <v>3571</v>
       </c>
-      <c r="C1214" t="inlineStr">
+      <c r="C1213" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1214" t="inlineStr">
+      <c r="D1213" t="inlineStr">
         <is>
           <t>вул Небесної Сотні 85</t>
         </is>
       </c>
-      <c r="E1214" t="inlineStr">
+      <c r="E1213" t="inlineStr">
         <is>
           <t>Романів</t>
         </is>
       </c>
-      <c r="F1214" t="inlineStr">
+      <c r="F1213" t="inlineStr">
         <is>
           <t>Житомирська</t>
         </is>
       </c>
-      <c r="G1214" t="n">
+      <c r="G1213" t="n">
         <v>50.141605</v>
       </c>
-      <c r="H1214" t="n">
+      <c r="H1213" t="n">
         <v>27.934655</v>
       </c>
-      <c r="I1214" t="inlineStr">
+      <c r="I1213" t="inlineStr">
         <is>
           <t>Пн: 08:00-18:00
 Вт: 08:00-18:00
@@ -56406,9 +56354,61 @@
 Нд: 09:00-17:00</t>
         </is>
       </c>
+      <c r="J1213" t="inlineStr">
+        <is>
+          <t>Житомирська</t>
+        </is>
+      </c>
+    </row>
+    <row r="1214">
+      <c r="A1214" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1214" t="n">
+        <v>3572</v>
+      </c>
+      <c r="C1214" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1214" t="inlineStr">
+        <is>
+          <t>вул Шевченка 50</t>
+        </is>
+      </c>
+      <c r="E1214" t="inlineStr">
+        <is>
+          <t>Богородчани</t>
+        </is>
+      </c>
+      <c r="F1214" t="inlineStr">
+        <is>
+          <t>Івано-Франківська</t>
+        </is>
+      </c>
+      <c r="G1214" t="n">
+        <v>48.809756</v>
+      </c>
+      <c r="H1214" t="n">
+        <v>24.5400082</v>
+      </c>
+      <c r="I1214" t="inlineStr">
+        <is>
+          <t>Пн: 09:00-18:00
+Вт: 09:00-18:00
+Ср: 09:00-18:00
+Чт: 09:00-18:00
+Пт: 09:00-18:00
+Сб: 09:00-17:00
+Нд: Вихідний</t>
+        </is>
+      </c>
       <c r="J1214" t="inlineStr">
         <is>
-          <t>Житомирська</t>
+          <t>Івано-Франківська</t>
         </is>
       </c>
     </row>

--- a/all_shops.xlsx
+++ b/all_shops.xlsx
@@ -53165,7 +53165,7 @@
         </is>
       </c>
       <c r="B1152" t="n">
-        <v>3463</v>
+        <v>3464</v>
       </c>
       <c r="C1152" t="inlineStr">
         <is>
@@ -53174,78 +53174,26 @@
       </c>
       <c r="D1152" t="inlineStr">
         <is>
-          <t>вул Грушевського 41А</t>
+          <t>вул Огієнка 41</t>
         </is>
       </c>
       <c r="E1152" t="inlineStr">
         <is>
-          <t>Первомайськ</t>
+          <t>Камянець-Подільский</t>
         </is>
       </c>
       <c r="F1152" t="inlineStr">
         <is>
-          <t>Миколаївська</t>
+          <t>Хмельницька</t>
         </is>
       </c>
       <c r="G1152" t="n">
-        <v>48.0425652</v>
+        <v>48.681053</v>
       </c>
       <c r="H1152" t="n">
-        <v>30.8444596</v>
+        <v>26.5871481</v>
       </c>
       <c r="I1152" t="inlineStr">
-        <is>
-          <t>Пн: 08:00-18:00
-Вт: 08:00-18:00
-Ср: Вихідний
-Чт: 08:00-18:00
-Пт: 08:00-18:00
-Сб: Вихідний
-Нд: 08:00-18:00</t>
-        </is>
-      </c>
-      <c r="J1152" t="inlineStr">
-        <is>
-          <t>Миколаївська</t>
-        </is>
-      </c>
-    </row>
-    <row r="1153">
-      <c r="A1153" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1153" t="n">
-        <v>3464</v>
-      </c>
-      <c r="C1153" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1153" t="inlineStr">
-        <is>
-          <t>вул Огієнка 41</t>
-        </is>
-      </c>
-      <c r="E1153" t="inlineStr">
-        <is>
-          <t>Камянець-Подільский</t>
-        </is>
-      </c>
-      <c r="F1153" t="inlineStr">
-        <is>
-          <t>Хмельницька</t>
-        </is>
-      </c>
-      <c r="G1153" t="n">
-        <v>48.681053</v>
-      </c>
-      <c r="H1153" t="n">
-        <v>26.5871481</v>
-      </c>
-      <c r="I1153" t="inlineStr">
         <is>
           <t>Пн: 08:00-18:00
 Вт: 08:00-18:00
@@ -53256,48 +53204,48 @@
 Нд: 10:00-16:00</t>
         </is>
       </c>
-      <c r="J1153" t="inlineStr">
+      <c r="J1152" t="inlineStr">
         <is>
           <t>Хмельницька</t>
         </is>
       </c>
     </row>
-    <row r="1154">
-      <c r="A1154" t="inlineStr">
+    <row r="1153">
+      <c r="A1153" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1154" t="n">
+      <c r="B1153" t="n">
         <v>3465</v>
       </c>
-      <c r="C1154" t="inlineStr">
+      <c r="C1153" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1154" t="inlineStr">
+      <c r="D1153" t="inlineStr">
         <is>
           <t>вул Хмельницька 6</t>
         </is>
       </c>
-      <c r="E1154" t="inlineStr">
+      <c r="E1153" t="inlineStr">
         <is>
           <t>Ярмолинці</t>
         </is>
       </c>
-      <c r="F1154" t="inlineStr">
+      <c r="F1153" t="inlineStr">
         <is>
           <t>Хмельницька</t>
         </is>
       </c>
-      <c r="G1154" t="n">
+      <c r="G1153" t="n">
         <v>49.19112</v>
       </c>
-      <c r="H1154" t="n">
+      <c r="H1153" t="n">
         <v>26.83537</v>
       </c>
-      <c r="I1154" t="inlineStr">
+      <c r="I1153" t="inlineStr">
         <is>
           <t>Пн: 09:00-18:00
 Вт: 09:00-18:00
@@ -53308,48 +53256,48 @@
 Нд: Вихідний</t>
         </is>
       </c>
-      <c r="J1154" t="inlineStr">
+      <c r="J1153" t="inlineStr">
         <is>
           <t>Хмельницька</t>
         </is>
       </c>
     </row>
-    <row r="1155">
-      <c r="A1155" t="inlineStr">
+    <row r="1154">
+      <c r="A1154" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1155" t="n">
+      <c r="B1154" t="n">
         <v>3466</v>
       </c>
-      <c r="C1155" t="inlineStr">
+      <c r="C1154" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1155" t="inlineStr">
+      <c r="D1154" t="inlineStr">
         <is>
           <t>просп Берестейський (Перемоги) 86а</t>
         </is>
       </c>
-      <c r="E1155" t="inlineStr">
+      <c r="E1154" t="inlineStr">
         <is>
           <t>Київ</t>
         </is>
       </c>
-      <c r="F1155" t="inlineStr">
+      <c r="F1154" t="inlineStr">
         <is>
           <t>Kiev</t>
         </is>
       </c>
-      <c r="G1155" t="n">
+      <c r="G1154" t="n">
         <v>50.4588998</v>
       </c>
-      <c r="H1155" t="n">
+      <c r="H1154" t="n">
         <v>30.4041254</v>
       </c>
-      <c r="I1155" t="inlineStr">
+      <c r="I1154" t="inlineStr">
         <is>
           <t>Пн: 10:00-21:00
 Вт: 10:00-21:00
@@ -53360,48 +53308,48 @@
 Нд: 10:00-21:00</t>
         </is>
       </c>
-      <c r="J1155" t="inlineStr">
+      <c r="J1154" t="inlineStr">
         <is>
           <t>Kiev</t>
         </is>
       </c>
     </row>
-    <row r="1156">
-      <c r="A1156" t="inlineStr">
+    <row r="1155">
+      <c r="A1155" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1156" t="n">
+      <c r="B1155" t="n">
         <v>3467</v>
       </c>
-      <c r="C1156" t="inlineStr">
+      <c r="C1155" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1156" t="inlineStr">
+      <c r="D1155" t="inlineStr">
         <is>
           <t>вул Харківська 2/2</t>
         </is>
       </c>
-      <c r="E1156" t="inlineStr">
+      <c r="E1155" t="inlineStr">
         <is>
           <t>Суми</t>
         </is>
       </c>
-      <c r="F1156" t="inlineStr">
+      <c r="F1155" t="inlineStr">
         <is>
           <t>Сумська</t>
         </is>
       </c>
-      <c r="G1156" t="n">
+      <c r="G1155" t="n">
         <v>50.9041752</v>
       </c>
-      <c r="H1156" t="n">
+      <c r="H1155" t="n">
         <v>34.8048057</v>
       </c>
-      <c r="I1156" t="inlineStr">
+      <c r="I1155" t="inlineStr">
         <is>
           <t>Пн: 10:00-19:00
 Вт: 10:00-19:00
@@ -53412,48 +53360,48 @@
 Нд: 10:00-19:00</t>
         </is>
       </c>
-      <c r="J1156" t="inlineStr">
+      <c r="J1155" t="inlineStr">
         <is>
           <t>Сумська</t>
         </is>
       </c>
     </row>
-    <row r="1157">
-      <c r="A1157" t="inlineStr">
+    <row r="1156">
+      <c r="A1156" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1157" t="n">
+      <c r="B1156" t="n">
         <v>3470</v>
       </c>
-      <c r="C1157" t="inlineStr">
+      <c r="C1156" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1157" t="inlineStr">
+      <c r="D1156" t="inlineStr">
         <is>
           <t>вул  Хрещатик 13</t>
         </is>
       </c>
-      <c r="E1157" t="inlineStr">
+      <c r="E1156" t="inlineStr">
         <is>
           <t>Київ</t>
         </is>
       </c>
-      <c r="F1157" t="inlineStr">
+      <c r="F1156" t="inlineStr">
         <is>
           <t>м. Київ</t>
         </is>
       </c>
-      <c r="G1157" t="n">
+      <c r="G1156" t="n">
         <v>50.4487897</v>
       </c>
-      <c r="H1157" t="n">
+      <c r="H1156" t="n">
         <v>30.5233361</v>
       </c>
-      <c r="I1157" t="inlineStr">
+      <c r="I1156" t="inlineStr">
         <is>
           <t>Пн: 10:00-20:00
 Вт: 10:00-20:00
@@ -53464,48 +53412,48 @@
 Нд: 10:00-20:00</t>
         </is>
       </c>
-      <c r="J1157" t="inlineStr">
+      <c r="J1156" t="inlineStr">
         <is>
           <t>м. Київ</t>
         </is>
       </c>
     </row>
-    <row r="1158">
-      <c r="A1158" t="inlineStr">
+    <row r="1157">
+      <c r="A1157" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1158" t="n">
+      <c r="B1157" t="n">
         <v>3471</v>
       </c>
-      <c r="C1158" t="inlineStr">
+      <c r="C1157" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1158" t="inlineStr">
+      <c r="D1157" t="inlineStr">
         <is>
           <t>вул Університетська 45</t>
         </is>
       </c>
-      <c r="E1158" t="inlineStr">
+      <c r="E1157" t="inlineStr">
         <is>
           <t>Словянськ</t>
         </is>
       </c>
-      <c r="F1158" t="inlineStr">
+      <c r="F1157" t="inlineStr">
         <is>
           <t>Дніпропетровська</t>
         </is>
       </c>
-      <c r="G1158" t="n">
+      <c r="G1157" t="n">
         <v>48.0008788</v>
       </c>
-      <c r="H1158" t="n">
+      <c r="H1157" t="n">
         <v>33.4821954</v>
       </c>
-      <c r="I1158" t="inlineStr">
+      <c r="I1157" t="inlineStr">
         <is>
           <t>Пн: 10:00-17:00
 Вт: 10:00-17:00
@@ -53516,48 +53464,48 @@
 Нд: Вихідний</t>
         </is>
       </c>
-      <c r="J1158" t="inlineStr">
+      <c r="J1157" t="inlineStr">
         <is>
           <t>Дніпропетровська</t>
         </is>
       </c>
     </row>
-    <row r="1159">
-      <c r="A1159" t="inlineStr">
+    <row r="1158">
+      <c r="A1158" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1159" t="n">
+      <c r="B1158" t="n">
         <v>3472</v>
       </c>
-      <c r="C1159" t="inlineStr">
+      <c r="C1158" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1159" t="inlineStr">
+      <c r="D1158" t="inlineStr">
         <is>
           <t>вул Чернівецька 2Б</t>
         </is>
       </c>
-      <c r="E1159" t="inlineStr">
+      <c r="E1158" t="inlineStr">
         <is>
           <t>Сторожинець</t>
         </is>
       </c>
-      <c r="F1159" t="inlineStr">
+      <c r="F1158" t="inlineStr">
         <is>
           <t>Чернівецька</t>
         </is>
       </c>
-      <c r="G1159" t="n">
+      <c r="G1158" t="n">
         <v>48.1604917</v>
       </c>
-      <c r="H1159" t="n">
+      <c r="H1158" t="n">
         <v>25.721244</v>
       </c>
-      <c r="I1159" t="inlineStr">
+      <c r="I1158" t="inlineStr">
         <is>
           <t>Пн: 09:00-18:00
 Вт: 09:00-18:00
@@ -53568,48 +53516,48 @@
 Нд: Вихідний</t>
         </is>
       </c>
-      <c r="J1159" t="inlineStr">
+      <c r="J1158" t="inlineStr">
         <is>
           <t>Чернівецька</t>
         </is>
       </c>
     </row>
-    <row r="1160">
-      <c r="A1160" t="inlineStr">
+    <row r="1159">
+      <c r="A1159" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1160" t="n">
+      <c r="B1159" t="n">
         <v>3474</v>
       </c>
-      <c r="C1160" t="inlineStr">
+      <c r="C1159" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1160" t="inlineStr">
+      <c r="D1159" t="inlineStr">
         <is>
           <t>вул Нескорених (Героїв Праці) 13</t>
         </is>
       </c>
-      <c r="E1160" t="inlineStr">
+      <c r="E1159" t="inlineStr">
         <is>
           <t>Харків</t>
         </is>
       </c>
-      <c r="F1160" t="inlineStr">
+      <c r="F1159" t="inlineStr">
         <is>
           <t>Харківська</t>
         </is>
       </c>
-      <c r="G1160" t="n">
+      <c r="G1159" t="n">
         <v>50.0254117</v>
       </c>
-      <c r="H1160" t="n">
+      <c r="H1159" t="n">
         <v>36.3369339</v>
       </c>
-      <c r="I1160" t="inlineStr">
+      <c r="I1159" t="inlineStr">
         <is>
           <t>Пн: 09:00-18:00
 Вт: 09:00-18:00
@@ -53620,48 +53568,48 @@
 Нд: 09:00-17:00</t>
         </is>
       </c>
-      <c r="J1160" t="inlineStr">
+      <c r="J1159" t="inlineStr">
         <is>
           <t>Харківська</t>
         </is>
       </c>
     </row>
-    <row r="1161">
-      <c r="A1161" t="inlineStr">
+    <row r="1160">
+      <c r="A1160" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1161" t="n">
+      <c r="B1160" t="n">
         <v>3478</v>
       </c>
-      <c r="C1161" t="inlineStr">
+      <c r="C1160" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1161" t="inlineStr">
+      <c r="D1160" t="inlineStr">
         <is>
           <t>просп Європейського Союзу (Правди) 58</t>
         </is>
       </c>
-      <c r="E1161" t="inlineStr">
+      <c r="E1160" t="inlineStr">
         <is>
           <t>Київ</t>
         </is>
       </c>
-      <c r="F1161" t="inlineStr">
+      <c r="F1160" t="inlineStr">
         <is>
           <t>Kiev</t>
         </is>
       </c>
-      <c r="G1161" t="n">
+      <c r="G1160" t="n">
         <v>50.5047315</v>
       </c>
-      <c r="H1161" t="n">
+      <c r="H1160" t="n">
         <v>30.4374307</v>
       </c>
-      <c r="I1161" t="inlineStr">
+      <c r="I1160" t="inlineStr">
         <is>
           <t>Пн: 09:00-21:00
 Вт: 09:00-21:00
@@ -53672,48 +53620,48 @@
 Нд: 09:00-21:00</t>
         </is>
       </c>
-      <c r="J1161" t="inlineStr">
+      <c r="J1160" t="inlineStr">
         <is>
           <t>Kiev</t>
         </is>
       </c>
     </row>
-    <row r="1162">
-      <c r="A1162" t="inlineStr">
+    <row r="1161">
+      <c r="A1161" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1162" t="n">
+      <c r="B1161" t="n">
         <v>3479</v>
       </c>
-      <c r="C1162" t="inlineStr">
+      <c r="C1161" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1162" t="inlineStr">
+      <c r="D1161" t="inlineStr">
         <is>
           <t>вул Європейського Союзу (Правди) 47</t>
         </is>
       </c>
-      <c r="E1162" t="inlineStr">
+      <c r="E1161" t="inlineStr">
         <is>
           <t>Київ</t>
         </is>
       </c>
-      <c r="F1162" t="inlineStr">
+      <c r="F1161" t="inlineStr">
         <is>
           <t>м. Київ</t>
         </is>
       </c>
-      <c r="G1162" t="n">
+      <c r="G1161" t="n">
         <v>50.5037667</v>
       </c>
-      <c r="H1162" t="n">
+      <c r="H1161" t="n">
         <v>30.419093</v>
       </c>
-      <c r="I1162" t="inlineStr">
+      <c r="I1161" t="inlineStr">
         <is>
           <t>Пн: 10:00-22:00
 Вт: 10:00-22:00
@@ -53724,48 +53672,48 @@
 Нд: 10:00-22:00</t>
         </is>
       </c>
-      <c r="J1162" t="inlineStr">
+      <c r="J1161" t="inlineStr">
         <is>
           <t>м. Київ</t>
         </is>
       </c>
     </row>
-    <row r="1163">
-      <c r="A1163" t="inlineStr">
+    <row r="1162">
+      <c r="A1162" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1163" t="n">
+      <c r="B1162" t="n">
         <v>3483</v>
       </c>
-      <c r="C1163" t="inlineStr">
+      <c r="C1162" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1163" t="inlineStr">
+      <c r="D1162" t="inlineStr">
         <is>
           <t>просп Коцюбинського 19</t>
         </is>
       </c>
-      <c r="E1163" t="inlineStr">
+      <c r="E1162" t="inlineStr">
         <is>
           <t>Вінниця</t>
         </is>
       </c>
-      <c r="F1163" t="inlineStr">
+      <c r="F1162" t="inlineStr">
         <is>
           <t>Vinnyts'ka</t>
         </is>
       </c>
-      <c r="G1163" t="n">
+      <c r="G1162" t="n">
         <v>49.239071</v>
       </c>
-      <c r="H1163" t="n">
+      <c r="H1162" t="n">
         <v>28.4981039</v>
       </c>
-      <c r="I1163" t="inlineStr">
+      <c r="I1162" t="inlineStr">
         <is>
           <t>Пн: 08:00-18:00
 Вт: 08:00-18:00
@@ -53776,48 +53724,48 @@
 Нд: 09:00-17:00</t>
         </is>
       </c>
-      <c r="J1163" t="inlineStr">
+      <c r="J1162" t="inlineStr">
         <is>
           <t>Vinnyts'ka</t>
         </is>
       </c>
     </row>
-    <row r="1164">
-      <c r="A1164" t="inlineStr">
+    <row r="1163">
+      <c r="A1163" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1164" t="n">
+      <c r="B1163" t="n">
         <v>3485</v>
       </c>
-      <c r="C1164" t="inlineStr">
+      <c r="C1163" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1164" t="inlineStr">
+      <c r="D1163" t="inlineStr">
         <is>
           <t>вул Котляра (був. Червоноармійська) 8/10</t>
         </is>
       </c>
-      <c r="E1164" t="inlineStr">
+      <c r="E1163" t="inlineStr">
         <is>
           <t>Харків</t>
         </is>
       </c>
-      <c r="F1164" t="inlineStr">
+      <c r="F1163" t="inlineStr">
         <is>
           <t>Харківська</t>
         </is>
       </c>
-      <c r="G1164" t="n">
+      <c r="G1163" t="n">
         <v>49.9892648</v>
       </c>
-      <c r="H1164" t="n">
+      <c r="H1163" t="n">
         <v>36.2077698</v>
       </c>
-      <c r="I1164" t="inlineStr">
+      <c r="I1163" t="inlineStr">
         <is>
           <t>Пн: 09:00-18:00
 Вт: 09:00-18:00
@@ -53828,48 +53776,48 @@
 Нд: 09:00-17:00</t>
         </is>
       </c>
-      <c r="J1164" t="inlineStr">
+      <c r="J1163" t="inlineStr">
         <is>
           <t>Харківська</t>
         </is>
       </c>
     </row>
-    <row r="1165">
-      <c r="A1165" t="inlineStr">
+    <row r="1164">
+      <c r="A1164" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1165" t="n">
+      <c r="B1164" t="n">
         <v>3491</v>
       </c>
-      <c r="C1165" t="inlineStr">
+      <c r="C1164" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1165" t="inlineStr">
+      <c r="D1164" t="inlineStr">
         <is>
           <t>вул Інститутська 10</t>
         </is>
       </c>
-      <c r="E1165" t="inlineStr">
+      <c r="E1164" t="inlineStr">
         <is>
           <t>Хмельницький</t>
         </is>
       </c>
-      <c r="F1165" t="inlineStr">
+      <c r="F1164" t="inlineStr">
         <is>
           <t>Хмельницька</t>
         </is>
       </c>
-      <c r="G1165" t="n">
+      <c r="G1164" t="n">
         <v>49.4098499</v>
       </c>
-      <c r="H1165" t="n">
+      <c r="H1164" t="n">
         <v>26.9605436</v>
       </c>
-      <c r="I1165" t="inlineStr">
+      <c r="I1164" t="inlineStr">
         <is>
           <t>Пн: 09:00-19:00
 Вт: 09:00-19:00
@@ -53880,48 +53828,48 @@
 Нд: 10:00-18:00</t>
         </is>
       </c>
-      <c r="J1165" t="inlineStr">
+      <c r="J1164" t="inlineStr">
         <is>
           <t>Хмельницька</t>
         </is>
       </c>
     </row>
-    <row r="1166">
-      <c r="A1166" t="inlineStr">
+    <row r="1165">
+      <c r="A1165" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1166" t="n">
+      <c r="B1165" t="n">
         <v>3494</v>
       </c>
-      <c r="C1166" t="inlineStr">
+      <c r="C1165" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1166" t="inlineStr">
+      <c r="D1165" t="inlineStr">
         <is>
           <t>вул Шевченків Шлях 144-А</t>
         </is>
       </c>
-      <c r="E1166" t="inlineStr">
+      <c r="E1165" t="inlineStr">
         <is>
           <t>Березань</t>
         </is>
       </c>
-      <c r="F1166" t="inlineStr">
+      <c r="F1165" t="inlineStr">
         <is>
           <t>Kiev</t>
         </is>
       </c>
-      <c r="G1166" t="n">
+      <c r="G1165" t="n">
         <v>50.3119113</v>
       </c>
-      <c r="H1166" t="n">
+      <c r="H1165" t="n">
         <v>31.4678577</v>
       </c>
-      <c r="I1166" t="inlineStr">
+      <c r="I1165" t="inlineStr">
         <is>
           <t>Пн: 09:00-17:00
 Вт: 09:00-17:00
@@ -53932,48 +53880,48 @@
 Нд: 10:00-16:00</t>
         </is>
       </c>
-      <c r="J1166" t="inlineStr">
+      <c r="J1165" t="inlineStr">
         <is>
           <t>Kiev</t>
         </is>
       </c>
     </row>
-    <row r="1167">
-      <c r="A1167" t="inlineStr">
+    <row r="1166">
+      <c r="A1166" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1167" t="n">
+      <c r="B1166" t="n">
         <v>3495</v>
       </c>
-      <c r="C1167" t="inlineStr">
+      <c r="C1166" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1167" t="inlineStr">
+      <c r="D1166" t="inlineStr">
         <is>
           <t>вул Міцкевича 1</t>
         </is>
       </c>
-      <c r="E1167" t="inlineStr">
+      <c r="E1166" t="inlineStr">
         <is>
           <t>Борислав</t>
         </is>
       </c>
-      <c r="F1167" t="inlineStr">
+      <c r="F1166" t="inlineStr">
         <is>
           <t>Львівська</t>
         </is>
       </c>
-      <c r="G1167" t="n">
+      <c r="G1166" t="n">
         <v>49.287286</v>
       </c>
-      <c r="H1167" t="n">
+      <c r="H1166" t="n">
         <v>23.4159004</v>
       </c>
-      <c r="I1167" t="inlineStr">
+      <c r="I1166" t="inlineStr">
         <is>
           <t>Пн: 09:00-18:00
 Вт: 09:00-18:00
@@ -53984,48 +53932,48 @@
 Нд: 10:00-17:00</t>
         </is>
       </c>
-      <c r="J1167" t="inlineStr">
+      <c r="J1166" t="inlineStr">
         <is>
           <t>Львівська</t>
         </is>
       </c>
     </row>
-    <row r="1168">
-      <c r="A1168" t="inlineStr">
+    <row r="1167">
+      <c r="A1167" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1168" t="n">
+      <c r="B1167" t="n">
         <v>3496</v>
       </c>
-      <c r="C1168" t="inlineStr">
+      <c r="C1167" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1168" t="inlineStr">
+      <c r="D1167" t="inlineStr">
         <is>
           <t>вул І.Франка 1</t>
         </is>
       </c>
-      <c r="E1168" t="inlineStr">
+      <c r="E1167" t="inlineStr">
         <is>
           <t>Верховина</t>
         </is>
       </c>
-      <c r="F1168" t="inlineStr">
+      <c r="F1167" t="inlineStr">
         <is>
           <t>Івано-Франківська</t>
         </is>
       </c>
-      <c r="G1168" t="n">
+      <c r="G1167" t="n">
         <v>48.1549768</v>
       </c>
-      <c r="H1168" t="n">
+      <c r="H1167" t="n">
         <v>24.8291227</v>
       </c>
-      <c r="I1168" t="inlineStr">
+      <c r="I1167" t="inlineStr">
         <is>
           <t>Пн: 09:00-18:00
 Вт: 09:00-18:00
@@ -54036,48 +53984,48 @@
 Нд: 10:00-16:00</t>
         </is>
       </c>
-      <c r="J1168" t="inlineStr">
+      <c r="J1167" t="inlineStr">
         <is>
           <t>Івано-Франківська</t>
         </is>
       </c>
     </row>
-    <row r="1169">
-      <c r="A1169" t="inlineStr">
+    <row r="1168">
+      <c r="A1168" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1169" t="n">
+      <c r="B1168" t="n">
         <v>3498</v>
       </c>
-      <c r="C1169" t="inlineStr">
+      <c r="C1168" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1169" t="inlineStr">
+      <c r="D1168" t="inlineStr">
         <is>
           <t>просп Олександра Поля 1/9</t>
         </is>
       </c>
-      <c r="E1169" t="inlineStr">
+      <c r="E1168" t="inlineStr">
         <is>
           <t>Дніпро</t>
         </is>
       </c>
-      <c r="F1169" t="inlineStr">
+      <c r="F1168" t="inlineStr">
         <is>
           <t>Дніпропетровська</t>
         </is>
       </c>
-      <c r="G1169" t="n">
+      <c r="G1168" t="n">
         <v>48.4642698</v>
       </c>
-      <c r="H1169" t="n">
+      <c r="H1168" t="n">
         <v>35.0290126</v>
       </c>
-      <c r="I1169" t="inlineStr">
+      <c r="I1168" t="inlineStr">
         <is>
           <t>Пн: 09:00-19:00
 Вт: 09:00-19:00
@@ -54088,48 +54036,48 @@
 Нд: 09:00-18:00</t>
         </is>
       </c>
-      <c r="J1169" t="inlineStr">
+      <c r="J1168" t="inlineStr">
         <is>
           <t>Дніпропетровська</t>
         </is>
       </c>
     </row>
-    <row r="1170">
-      <c r="A1170" t="inlineStr">
+    <row r="1169">
+      <c r="A1169" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1170" t="n">
+      <c r="B1169" t="n">
         <v>3501</v>
       </c>
-      <c r="C1170" t="inlineStr">
+      <c r="C1169" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1170" t="inlineStr">
+      <c r="D1169" t="inlineStr">
         <is>
           <t>просп Дмитра Яворницького (К.Маркса) 65</t>
         </is>
       </c>
-      <c r="E1170" t="inlineStr">
+      <c r="E1169" t="inlineStr">
         <is>
           <t>Дніпро</t>
         </is>
       </c>
-      <c r="F1170" t="inlineStr">
+      <c r="F1169" t="inlineStr">
         <is>
           <t>Дніпропетровська</t>
         </is>
       </c>
-      <c r="G1170" t="n">
+      <c r="G1169" t="n">
         <v>48.4647786</v>
       </c>
-      <c r="H1170" t="n">
+      <c r="H1169" t="n">
         <v>35.0447223</v>
       </c>
-      <c r="I1170" t="inlineStr">
+      <c r="I1169" t="inlineStr">
         <is>
           <t>Пн: 09:00-19:00
 Вт: 09:00-19:00
@@ -54140,48 +54088,48 @@
 Нд: 09:00-18:00</t>
         </is>
       </c>
-      <c r="J1170" t="inlineStr">
+      <c r="J1169" t="inlineStr">
         <is>
           <t>Дніпропетровська</t>
         </is>
       </c>
     </row>
-    <row r="1171">
-      <c r="A1171" t="inlineStr">
+    <row r="1170">
+      <c r="A1170" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1171" t="n">
+      <c r="B1170" t="n">
         <v>3503</v>
       </c>
-      <c r="C1171" t="inlineStr">
+      <c r="C1170" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1171" t="inlineStr">
+      <c r="D1170" t="inlineStr">
         <is>
           <t>вул Привокзальна 3</t>
         </is>
       </c>
-      <c r="E1171" t="inlineStr">
+      <c r="E1170" t="inlineStr">
         <is>
           <t>Київ</t>
         </is>
       </c>
-      <c r="F1171" t="inlineStr">
+      <c r="F1170" t="inlineStr">
         <is>
           <t>Kiev</t>
         </is>
       </c>
-      <c r="G1171" t="n">
+      <c r="G1170" t="n">
         <v>50.4305963</v>
       </c>
-      <c r="H1171" t="n">
+      <c r="H1170" t="n">
         <v>30.6518096</v>
       </c>
-      <c r="I1171" t="inlineStr">
+      <c r="I1170" t="inlineStr">
         <is>
           <t>Пн: 10:00-17:00
 Вт: 10:00-17:00
@@ -54192,48 +54140,48 @@
 Нд: 10:00-17:00</t>
         </is>
       </c>
-      <c r="J1171" t="inlineStr">
+      <c r="J1170" t="inlineStr">
         <is>
           <t>Kiev</t>
         </is>
       </c>
     </row>
-    <row r="1172">
-      <c r="A1172" t="inlineStr">
+    <row r="1171">
+      <c r="A1171" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1172" t="n">
+      <c r="B1171" t="n">
         <v>3505</v>
       </c>
-      <c r="C1172" t="inlineStr">
+      <c r="C1171" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1172" t="inlineStr">
+      <c r="D1171" t="inlineStr">
         <is>
           <t>пл Шевченка 26</t>
         </is>
       </c>
-      <c r="E1172" t="inlineStr">
+      <c r="E1171" t="inlineStr">
         <is>
           <t>Коломия</t>
         </is>
       </c>
-      <c r="F1172" t="inlineStr">
+      <c r="F1171" t="inlineStr">
         <is>
           <t>Івано-Франківська</t>
         </is>
       </c>
-      <c r="G1172" t="n">
+      <c r="G1171" t="n">
         <v>48.5249278</v>
       </c>
-      <c r="H1172" t="n">
+      <c r="H1171" t="n">
         <v>25.0375409</v>
       </c>
-      <c r="I1172" t="inlineStr">
+      <c r="I1171" t="inlineStr">
         <is>
           <t>Пн: 09:00-18:00
 Вт: 09:00-18:00
@@ -54244,48 +54192,48 @@
 Нд: 10:00-17:00</t>
         </is>
       </c>
-      <c r="J1172" t="inlineStr">
+      <c r="J1171" t="inlineStr">
         <is>
           <t>Івано-Франківська</t>
         </is>
       </c>
     </row>
-    <row r="1173">
-      <c r="A1173" t="inlineStr">
+    <row r="1172">
+      <c r="A1172" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1173" t="n">
+      <c r="B1172" t="n">
         <v>3506</v>
       </c>
-      <c r="C1173" t="inlineStr">
+      <c r="C1172" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1173" t="inlineStr">
+      <c r="D1172" t="inlineStr">
         <is>
           <t>вул Медова 5</t>
         </is>
       </c>
-      <c r="E1173" t="inlineStr">
+      <c r="E1172" t="inlineStr">
         <is>
           <t>Кремeнець</t>
         </is>
       </c>
-      <c r="F1173" t="inlineStr">
+      <c r="F1172" t="inlineStr">
         <is>
           <t>Тернопільська</t>
         </is>
       </c>
-      <c r="G1173" t="n">
+      <c r="G1172" t="n">
         <v>50.095605</v>
       </c>
-      <c r="H1173" t="n">
+      <c r="H1172" t="n">
         <v>25.7259463</v>
       </c>
-      <c r="I1173" t="inlineStr">
+      <c r="I1172" t="inlineStr">
         <is>
           <t>Пн: 09:00-19:00
 Вт: 09:00-19:00
@@ -54296,48 +54244,48 @@
 Нд: 10:00-16:00</t>
         </is>
       </c>
-      <c r="J1173" t="inlineStr">
+      <c r="J1172" t="inlineStr">
         <is>
           <t>Тернопільська</t>
         </is>
       </c>
     </row>
-    <row r="1174">
-      <c r="A1174" t="inlineStr">
+    <row r="1173">
+      <c r="A1173" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1174" t="n">
+      <c r="B1173" t="n">
         <v>3508</v>
       </c>
-      <c r="C1174" t="inlineStr">
+      <c r="C1173" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1174" t="inlineStr">
+      <c r="D1173" t="inlineStr">
         <is>
           <t>вул Шевченка 100</t>
         </is>
       </c>
-      <c r="E1174" t="inlineStr">
+      <c r="E1173" t="inlineStr">
         <is>
           <t>Люботин</t>
         </is>
       </c>
-      <c r="F1174" t="inlineStr">
+      <c r="F1173" t="inlineStr">
         <is>
           <t>Харківська</t>
         </is>
       </c>
-      <c r="G1174" t="n">
+      <c r="G1173" t="n">
         <v>49.9407992</v>
       </c>
-      <c r="H1174" t="n">
+      <c r="H1173" t="n">
         <v>35.9262566</v>
       </c>
-      <c r="I1174" t="inlineStr">
+      <c r="I1173" t="inlineStr">
         <is>
           <t>Пн: 08:00-18:00
 Вт: 08:00-18:00
@@ -54348,48 +54296,48 @@
 Нд: 08:00-16:00</t>
         </is>
       </c>
-      <c r="J1174" t="inlineStr">
+      <c r="J1173" t="inlineStr">
         <is>
           <t>Харківська</t>
         </is>
       </c>
     </row>
-    <row r="1175">
-      <c r="A1175" t="inlineStr">
+    <row r="1174">
+      <c r="A1174" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1175" t="n">
+      <c r="B1174" t="n">
         <v>3510</v>
       </c>
-      <c r="C1175" t="inlineStr">
+      <c r="C1174" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1175" t="inlineStr">
+      <c r="D1174" t="inlineStr">
         <is>
           <t>вул Петропавлівська 49</t>
         </is>
       </c>
-      <c r="E1175" t="inlineStr">
+      <c r="E1174" t="inlineStr">
         <is>
           <t>Суми</t>
         </is>
       </c>
-      <c r="F1175" t="inlineStr">
+      <c r="F1174" t="inlineStr">
         <is>
           <t>Сумська</t>
         </is>
       </c>
-      <c r="G1175" t="n">
+      <c r="G1174" t="n">
         <v>50.9065729</v>
       </c>
-      <c r="H1175" t="n">
+      <c r="H1174" t="n">
         <v>34.796901</v>
       </c>
-      <c r="I1175" t="inlineStr">
+      <c r="I1174" t="inlineStr">
         <is>
           <t>Пн: 09:00-18:00
 Вт: 09:00-18:00
@@ -54400,48 +54348,48 @@
 Нд: 09:00-18:00</t>
         </is>
       </c>
-      <c r="J1175" t="inlineStr">
+      <c r="J1174" t="inlineStr">
         <is>
           <t>Сумська</t>
         </is>
       </c>
     </row>
-    <row r="1176">
-      <c r="A1176" t="inlineStr">
+    <row r="1175">
+      <c r="A1175" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1176" t="n">
+      <c r="B1175" t="n">
         <v>3512</v>
       </c>
-      <c r="C1176" t="inlineStr">
+      <c r="C1175" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1176" t="inlineStr">
+      <c r="D1175" t="inlineStr">
         <is>
           <t>вул Валентинівська (Блюхера) 37/128</t>
         </is>
       </c>
-      <c r="E1176" t="inlineStr">
+      <c r="E1175" t="inlineStr">
         <is>
           <t>Харків</t>
         </is>
       </c>
-      <c r="F1176" t="inlineStr">
+      <c r="F1175" t="inlineStr">
         <is>
           <t>Харківська</t>
         </is>
       </c>
-      <c r="G1176" t="n">
+      <c r="G1175" t="n">
         <v>50.0098371</v>
       </c>
-      <c r="H1176" t="n">
+      <c r="H1175" t="n">
         <v>36.3503577</v>
       </c>
-      <c r="I1176" t="inlineStr">
+      <c r="I1175" t="inlineStr">
         <is>
           <t>Пн: 09:00-19:00
 Вт: 09:00-19:00
@@ -54452,48 +54400,48 @@
 Нд: 09:00-18:00</t>
         </is>
       </c>
-      <c r="J1176" t="inlineStr">
+      <c r="J1175" t="inlineStr">
         <is>
           <t>Харківська</t>
         </is>
       </c>
     </row>
-    <row r="1177">
-      <c r="A1177" t="inlineStr">
+    <row r="1176">
+      <c r="A1176" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1177" t="n">
+      <c r="B1176" t="n">
         <v>3514</v>
       </c>
-      <c r="C1177" t="inlineStr">
+      <c r="C1176" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1177" t="inlineStr">
+      <c r="D1176" t="inlineStr">
         <is>
           <t>вул Центральна 32а</t>
         </is>
       </c>
-      <c r="E1177" t="inlineStr">
+      <c r="E1176" t="inlineStr">
         <is>
           <t>Чемерівці</t>
         </is>
       </c>
-      <c r="F1177" t="inlineStr">
+      <c r="F1176" t="inlineStr">
         <is>
           <t>Хмельницька</t>
         </is>
       </c>
-      <c r="G1177" t="n">
+      <c r="G1176" t="n">
         <v>49.011295</v>
       </c>
-      <c r="H1177" t="n">
+      <c r="H1176" t="n">
         <v>26.340395</v>
       </c>
-      <c r="I1177" t="inlineStr">
+      <c r="I1176" t="inlineStr">
         <is>
           <t>Пн: 08:00-18:00
 Вт: 08:00-18:00
@@ -54504,48 +54452,48 @@
 Нд: 09:00-15:00</t>
         </is>
       </c>
-      <c r="J1177" t="inlineStr">
+      <c r="J1176" t="inlineStr">
         <is>
           <t>Хмельницька</t>
         </is>
       </c>
     </row>
-    <row r="1178">
-      <c r="A1178" t="inlineStr">
+    <row r="1177">
+      <c r="A1177" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1178" t="n">
+      <c r="B1177" t="n">
         <v>3516</v>
       </c>
-      <c r="C1178" t="inlineStr">
+      <c r="C1177" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1178" t="inlineStr">
+      <c r="D1177" t="inlineStr">
         <is>
           <t>просп Відрадний 69/1</t>
         </is>
       </c>
-      <c r="E1178" t="inlineStr">
+      <c r="E1177" t="inlineStr">
         <is>
           <t>Київ</t>
         </is>
       </c>
-      <c r="F1178" t="inlineStr">
+      <c r="F1177" t="inlineStr">
         <is>
           <t>Kiev</t>
         </is>
       </c>
-      <c r="G1178" t="n">
+      <c r="G1177" t="n">
         <v>50.428885</v>
       </c>
-      <c r="H1178" t="n">
+      <c r="H1177" t="n">
         <v>30.4309396</v>
       </c>
-      <c r="I1178" t="inlineStr">
+      <c r="I1177" t="inlineStr">
         <is>
           <t>Пн: 09:00-18:00
 Вт: 09:00-18:00
@@ -54556,48 +54504,48 @@
 Нд: 10:00-17:00</t>
         </is>
       </c>
-      <c r="J1178" t="inlineStr">
+      <c r="J1177" t="inlineStr">
         <is>
           <t>Kiev</t>
         </is>
       </c>
     </row>
-    <row r="1179">
-      <c r="A1179" t="inlineStr">
+    <row r="1178">
+      <c r="A1178" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1179" t="n">
+      <c r="B1178" t="n">
         <v>3517</v>
       </c>
-      <c r="C1179" t="inlineStr">
+      <c r="C1178" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1179" t="inlineStr">
+      <c r="D1178" t="inlineStr">
         <is>
           <t>просп Свободи (Леніна) 16Д</t>
         </is>
       </c>
-      <c r="E1179" t="inlineStr">
+      <c r="E1178" t="inlineStr">
         <is>
           <t>Хмільник</t>
         </is>
       </c>
-      <c r="F1179" t="inlineStr">
+      <c r="F1178" t="inlineStr">
         <is>
           <t>Vinnyts'ka</t>
         </is>
       </c>
-      <c r="G1179" t="n">
+      <c r="G1178" t="n">
         <v>49.5576747</v>
       </c>
-      <c r="H1179" t="n">
+      <c r="H1178" t="n">
         <v>27.9528561</v>
       </c>
-      <c r="I1179" t="inlineStr">
+      <c r="I1178" t="inlineStr">
         <is>
           <t>Пн: 08:00-17:00
 Вт: 08:00-17:00
@@ -54608,48 +54556,48 @@
 Нд: Вихідний</t>
         </is>
       </c>
-      <c r="J1179" t="inlineStr">
+      <c r="J1178" t="inlineStr">
         <is>
           <t>Vinnyts'ka</t>
         </is>
       </c>
     </row>
-    <row r="1180">
-      <c r="A1180" t="inlineStr">
+    <row r="1179">
+      <c r="A1179" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1180" t="n">
+      <c r="B1179" t="n">
         <v>3520</v>
       </c>
-      <c r="C1180" t="inlineStr">
+      <c r="C1179" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1180" t="inlineStr">
+      <c r="D1179" t="inlineStr">
         <is>
           <t>пл Шевченка 6</t>
         </is>
       </c>
-      <c r="E1180" t="inlineStr">
+      <c r="E1179" t="inlineStr">
         <is>
           <t>Славута</t>
         </is>
       </c>
-      <c r="F1180" t="inlineStr">
+      <c r="F1179" t="inlineStr">
         <is>
           <t>Хмельницька</t>
         </is>
       </c>
-      <c r="G1180" t="n">
+      <c r="G1179" t="n">
         <v>50.2957898</v>
       </c>
-      <c r="H1180" t="n">
+      <c r="H1179" t="n">
         <v>26.8570458</v>
       </c>
-      <c r="I1180" t="inlineStr">
+      <c r="I1179" t="inlineStr">
         <is>
           <t>Пн: 08:00-17:00
 Вт: 08:00-17:00
@@ -54660,48 +54608,48 @@
 Нд: 08:00-17:00</t>
         </is>
       </c>
-      <c r="J1180" t="inlineStr">
+      <c r="J1179" t="inlineStr">
         <is>
           <t>Хмельницька</t>
         </is>
       </c>
     </row>
-    <row r="1181">
-      <c r="A1181" t="inlineStr">
+    <row r="1180">
+      <c r="A1180" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1181" t="n">
+      <c r="B1180" t="n">
         <v>3526</v>
       </c>
-      <c r="C1181" t="inlineStr">
+      <c r="C1180" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1181" t="inlineStr">
+      <c r="D1180" t="inlineStr">
         <is>
           <t>вул Незалежності 65</t>
         </is>
       </c>
-      <c r="E1181" t="inlineStr">
+      <c r="E1180" t="inlineStr">
         <is>
           <t>Камянка-Бузька</t>
         </is>
       </c>
-      <c r="F1181" t="inlineStr">
+      <c r="F1180" t="inlineStr">
         <is>
           <t>Львівська</t>
         </is>
       </c>
-      <c r="G1181" t="n">
+      <c r="G1180" t="n">
         <v>50.107376</v>
       </c>
-      <c r="H1181" t="n">
+      <c r="H1180" t="n">
         <v>24.3436341</v>
       </c>
-      <c r="I1181" t="inlineStr">
+      <c r="I1180" t="inlineStr">
         <is>
           <t>Пн: 09:00-18:00
 Вт: 09:00-18:00
@@ -54712,48 +54660,48 @@
 Нд: 09:00-16:00</t>
         </is>
       </c>
-      <c r="J1181" t="inlineStr">
+      <c r="J1180" t="inlineStr">
         <is>
           <t>Львівська</t>
         </is>
       </c>
     </row>
-    <row r="1182">
-      <c r="A1182" t="inlineStr">
+    <row r="1181">
+      <c r="A1181" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1182" t="n">
+      <c r="B1181" t="n">
         <v>3530</v>
       </c>
-      <c r="C1182" t="inlineStr">
+      <c r="C1181" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1182" t="inlineStr">
+      <c r="D1181" t="inlineStr">
         <is>
           <t>вул Савіцького 14</t>
         </is>
       </c>
-      <c r="E1182" t="inlineStr">
+      <c r="E1181" t="inlineStr">
         <is>
           <t>Летичів</t>
         </is>
       </c>
-      <c r="F1182" t="inlineStr">
+      <c r="F1181" t="inlineStr">
         <is>
           <t>Хмельницька</t>
         </is>
       </c>
-      <c r="G1182" t="n">
+      <c r="G1181" t="n">
         <v>49.3813788</v>
       </c>
-      <c r="H1182" t="n">
+      <c r="H1181" t="n">
         <v>27.6197046</v>
       </c>
-      <c r="I1182" t="inlineStr">
+      <c r="I1181" t="inlineStr">
         <is>
           <t>Пн: 09:00-18:00
 Вт: 09:00-18:00
@@ -54764,48 +54712,48 @@
 Нд: 09:00-18:00</t>
         </is>
       </c>
-      <c r="J1182" t="inlineStr">
+      <c r="J1181" t="inlineStr">
         <is>
           <t>Хмельницька</t>
         </is>
       </c>
     </row>
-    <row r="1183">
-      <c r="A1183" t="inlineStr">
+    <row r="1182">
+      <c r="A1182" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1183" t="n">
+      <c r="B1182" t="n">
         <v>3531</v>
       </c>
-      <c r="C1183" t="inlineStr">
+      <c r="C1182" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1183" t="inlineStr">
+      <c r="D1182" t="inlineStr">
         <is>
           <t>вул Берестейський (Перемоги) 26</t>
         </is>
       </c>
-      <c r="E1183" t="inlineStr">
+      <c r="E1182" t="inlineStr">
         <is>
           <t>Київ</t>
         </is>
       </c>
-      <c r="F1183" t="inlineStr">
+      <c r="F1182" t="inlineStr">
         <is>
           <t>м. Київ</t>
         </is>
       </c>
-      <c r="G1183" t="n">
+      <c r="G1182" t="n">
         <v>50.4515345</v>
       </c>
-      <c r="H1183" t="n">
+      <c r="H1182" t="n">
         <v>30.4678476</v>
       </c>
-      <c r="I1183" t="inlineStr">
+      <c r="I1182" t="inlineStr">
         <is>
           <t>Пн: 10:00-21:00
 Вт: 10:00-21:00
@@ -54816,48 +54764,48 @@
 Нд: 10:00-21:00</t>
         </is>
       </c>
-      <c r="J1183" t="inlineStr">
+      <c r="J1182" t="inlineStr">
         <is>
           <t>м. Київ</t>
         </is>
       </c>
     </row>
-    <row r="1184">
-      <c r="A1184" t="inlineStr">
+    <row r="1183">
+      <c r="A1183" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1184" t="n">
+      <c r="B1183" t="n">
         <v>3534</v>
       </c>
-      <c r="C1184" t="inlineStr">
+      <c r="C1183" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1184" t="inlineStr">
+      <c r="D1183" t="inlineStr">
         <is>
           <t>вул Шевченка 74а</t>
         </is>
       </c>
-      <c r="E1184" t="inlineStr">
+      <c r="E1183" t="inlineStr">
         <is>
           <t>Городенка</t>
         </is>
       </c>
-      <c r="F1184" t="inlineStr">
+      <c r="F1183" t="inlineStr">
         <is>
           <t>Івано-Франківська</t>
         </is>
       </c>
-      <c r="G1184" t="n">
+      <c r="G1183" t="n">
         <v>48.66888903427731</v>
       </c>
-      <c r="H1184" t="n">
+      <c r="H1183" t="n">
         <v>25.50435338169336</v>
       </c>
-      <c r="I1184" t="inlineStr">
+      <c r="I1183" t="inlineStr">
         <is>
           <t>Пн: 08:00-18:00
 Вт: 08:00-18:00
@@ -54868,48 +54816,48 @@
 Нд: 10:00-17:00</t>
         </is>
       </c>
-      <c r="J1184" t="inlineStr">
+      <c r="J1183" t="inlineStr">
         <is>
           <t>Івано-Франківська</t>
         </is>
       </c>
     </row>
-    <row r="1185">
-      <c r="A1185" t="inlineStr">
+    <row r="1184">
+      <c r="A1184" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1185" t="n">
+      <c r="B1184" t="n">
         <v>3535</v>
       </c>
-      <c r="C1185" t="inlineStr">
+      <c r="C1184" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1185" t="inlineStr">
+      <c r="D1184" t="inlineStr">
         <is>
           <t>вул Бекетова 21</t>
         </is>
       </c>
-      <c r="E1185" t="inlineStr">
+      <c r="E1184" t="inlineStr">
         <is>
           <t>Харків</t>
         </is>
       </c>
-      <c r="F1185" t="inlineStr">
+      <c r="F1184" t="inlineStr">
         <is>
           <t>Харківська</t>
         </is>
       </c>
-      <c r="G1185" t="n">
+      <c r="G1184" t="n">
         <v>49.9512627</v>
       </c>
-      <c r="H1185" t="n">
+      <c r="H1184" t="n">
         <v>36.371922</v>
       </c>
-      <c r="I1185" t="inlineStr">
+      <c r="I1184" t="inlineStr">
         <is>
           <t>Пн: 09:00-17:00
 Вт: 09:00-17:00
@@ -54920,48 +54868,48 @@
 Нд: 09:00-16:00</t>
         </is>
       </c>
-      <c r="J1185" t="inlineStr">
+      <c r="J1184" t="inlineStr">
         <is>
           <t>Харківська</t>
         </is>
       </c>
     </row>
-    <row r="1186">
-      <c r="A1186" t="inlineStr">
+    <row r="1185">
+      <c r="A1185" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1186" t="n">
+      <c r="B1185" t="n">
         <v>3541</v>
       </c>
-      <c r="C1186" t="inlineStr">
+      <c r="C1185" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1186" t="inlineStr">
+      <c r="D1185" t="inlineStr">
         <is>
           <t>вул Одеська 121, А/1</t>
         </is>
       </c>
-      <c r="E1186" t="inlineStr">
+      <c r="E1185" t="inlineStr">
         <is>
           <t>Первомайськ</t>
         </is>
       </c>
-      <c r="F1186" t="inlineStr">
+      <c r="F1185" t="inlineStr">
         <is>
           <t>Миколаївська</t>
         </is>
       </c>
-      <c r="G1186" t="n">
+      <c r="G1185" t="n">
         <v>48.0228289</v>
       </c>
-      <c r="H1186" t="n">
+      <c r="H1185" t="n">
         <v>30.8511121</v>
       </c>
-      <c r="I1186" t="inlineStr">
+      <c r="I1185" t="inlineStr">
         <is>
           <t>Пн: 09:00-18:00
 Вт: 09:00-18:00
@@ -54972,48 +54920,48 @@
 Нд: 09:00-18:00</t>
         </is>
       </c>
-      <c r="J1186" t="inlineStr">
+      <c r="J1185" t="inlineStr">
         <is>
           <t>Миколаївська</t>
         </is>
       </c>
     </row>
-    <row r="1187">
-      <c r="A1187" t="inlineStr">
+    <row r="1186">
+      <c r="A1186" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1187" t="n">
+      <c r="B1186" t="n">
         <v>3542</v>
       </c>
-      <c r="C1187" t="inlineStr">
+      <c r="C1186" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1187" t="inlineStr">
+      <c r="D1186" t="inlineStr">
         <is>
           <t>просп Героїв Харкова 274</t>
         </is>
       </c>
-      <c r="E1187" t="inlineStr">
+      <c r="E1186" t="inlineStr">
         <is>
           <t>Харків</t>
         </is>
       </c>
-      <c r="F1187" t="inlineStr">
+      <c r="F1186" t="inlineStr">
         <is>
           <t>Харківська</t>
         </is>
       </c>
-      <c r="G1187" t="n">
+      <c r="G1186" t="n">
         <v>49.9432342</v>
       </c>
-      <c r="H1187" t="n">
+      <c r="H1186" t="n">
         <v>36.3984342</v>
       </c>
-      <c r="I1187" t="inlineStr">
+      <c r="I1186" t="inlineStr">
         <is>
           <t>Пн: 09:00-18:00
 Вт: 09:00-18:00
@@ -55024,48 +54972,48 @@
 Нд: 09:00-17:00</t>
         </is>
       </c>
-      <c r="J1187" t="inlineStr">
+      <c r="J1186" t="inlineStr">
         <is>
           <t>Харківська</t>
         </is>
       </c>
     </row>
-    <row r="1188">
-      <c r="A1188" t="inlineStr">
+    <row r="1187">
+      <c r="A1187" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1188" t="n">
+      <c r="B1187" t="n">
         <v>3543</v>
       </c>
-      <c r="C1188" t="inlineStr">
+      <c r="C1187" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1188" t="inlineStr">
+      <c r="D1187" t="inlineStr">
         <is>
           <t>вул Салтівське шосе 147</t>
         </is>
       </c>
-      <c r="E1188" t="inlineStr">
+      <c r="E1187" t="inlineStr">
         <is>
           <t>Харків</t>
         </is>
       </c>
-      <c r="F1188" t="inlineStr">
+      <c r="F1187" t="inlineStr">
         <is>
           <t>Харківська</t>
         </is>
       </c>
-      <c r="G1188" t="n">
+      <c r="G1187" t="n">
         <v>49.9908024</v>
       </c>
-      <c r="H1188" t="n">
+      <c r="H1187" t="n">
         <v>36.3585856</v>
       </c>
-      <c r="I1188" t="inlineStr">
+      <c r="I1187" t="inlineStr">
         <is>
           <t>Пн: 09:00-18:00
 Вт: 09:00-18:00
@@ -55076,48 +55024,48 @@
 Нд: 09:00-17:00</t>
         </is>
       </c>
-      <c r="J1188" t="inlineStr">
+      <c r="J1187" t="inlineStr">
         <is>
           <t>Харківська</t>
         </is>
       </c>
     </row>
-    <row r="1189">
-      <c r="A1189" t="inlineStr">
+    <row r="1188">
+      <c r="A1188" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1189" t="n">
+      <c r="B1188" t="n">
         <v>3544</v>
       </c>
-      <c r="C1189" t="inlineStr">
+      <c r="C1188" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1189" t="inlineStr">
+      <c r="D1188" t="inlineStr">
         <is>
           <t>просп Петра Григоренка 3</t>
         </is>
       </c>
-      <c r="E1189" t="inlineStr">
+      <c r="E1188" t="inlineStr">
         <is>
           <t>Харків</t>
         </is>
       </c>
-      <c r="F1189" t="inlineStr">
+      <c r="F1188" t="inlineStr">
         <is>
           <t>Харківська</t>
         </is>
       </c>
-      <c r="G1189" t="n">
+      <c r="G1188" t="n">
         <v>49.9650438</v>
       </c>
-      <c r="H1189" t="n">
+      <c r="H1188" t="n">
         <v>36.3219614</v>
       </c>
-      <c r="I1189" t="inlineStr">
+      <c r="I1188" t="inlineStr">
         <is>
           <t>Пн: 09:00-18:00
 Вт: 09:00-18:00
@@ -55128,48 +55076,48 @@
 Нд: 09:00-17:00</t>
         </is>
       </c>
-      <c r="J1189" t="inlineStr">
+      <c r="J1188" t="inlineStr">
         <is>
           <t>Харківська</t>
         </is>
       </c>
     </row>
-    <row r="1190">
-      <c r="A1190" t="inlineStr">
+    <row r="1189">
+      <c r="A1189" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1190" t="n">
+      <c r="B1189" t="n">
         <v>3545</v>
       </c>
-      <c r="C1190" t="inlineStr">
+      <c r="C1189" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1190" t="inlineStr">
+      <c r="D1189" t="inlineStr">
         <is>
           <t>просп Аерокосмічний (Гагаріна) 177</t>
         </is>
       </c>
-      <c r="E1190" t="inlineStr">
+      <c r="E1189" t="inlineStr">
         <is>
           <t>Харків</t>
         </is>
       </c>
-      <c r="F1190" t="inlineStr">
+      <c r="F1189" t="inlineStr">
         <is>
           <t>Харківська</t>
         </is>
       </c>
-      <c r="G1190" t="n">
+      <c r="G1189" t="n">
         <v>50.0169162</v>
       </c>
-      <c r="H1190" t="n">
+      <c r="H1189" t="n">
         <v>36.2067146</v>
       </c>
-      <c r="I1190" t="inlineStr">
+      <c r="I1189" t="inlineStr">
         <is>
           <t>Пн: 09:00-18:00
 Вт: 09:00-18:00
@@ -55180,48 +55128,48 @@
 Нд: 09:00-17:00</t>
         </is>
       </c>
-      <c r="J1190" t="inlineStr">
+      <c r="J1189" t="inlineStr">
         <is>
           <t>Харківська</t>
         </is>
       </c>
     </row>
-    <row r="1191">
-      <c r="A1191" t="inlineStr">
+    <row r="1190">
+      <c r="A1190" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1191" t="n">
+      <c r="B1190" t="n">
         <v>3547</v>
       </c>
-      <c r="C1191" t="inlineStr">
+      <c r="C1190" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1191" t="inlineStr">
+      <c r="D1190" t="inlineStr">
         <is>
           <t>вул Олімпійська 75</t>
         </is>
       </c>
-      <c r="E1191" t="inlineStr">
+      <c r="E1190" t="inlineStr">
         <is>
           <t>Хотин</t>
         </is>
       </c>
-      <c r="F1191" t="inlineStr">
+      <c r="F1190" t="inlineStr">
         <is>
           <t>Чернівецька</t>
         </is>
       </c>
-      <c r="G1191" t="n">
+      <c r="G1190" t="n">
         <v>48.5043413</v>
       </c>
-      <c r="H1191" t="n">
+      <c r="H1190" t="n">
         <v>26.490402</v>
       </c>
-      <c r="I1191" t="inlineStr">
+      <c r="I1190" t="inlineStr">
         <is>
           <t>Пн: 09:00-18:00
 Вт: 09:00-18:00
@@ -55232,48 +55180,48 @@
 Нд: 10:00-14:00</t>
         </is>
       </c>
-      <c r="J1191" t="inlineStr">
+      <c r="J1190" t="inlineStr">
         <is>
           <t>Чернівецька</t>
         </is>
       </c>
     </row>
-    <row r="1192">
-      <c r="A1192" t="inlineStr">
+    <row r="1191">
+      <c r="A1191" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1192" t="n">
+      <c r="B1191" t="n">
         <v>3549</v>
       </c>
-      <c r="C1192" t="inlineStr">
+      <c r="C1191" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1192" t="inlineStr">
+      <c r="D1191" t="inlineStr">
         <is>
           <t>вул Жовтнева 4-А</t>
         </is>
       </c>
-      <c r="E1192" t="inlineStr">
+      <c r="E1191" t="inlineStr">
         <is>
           <t>Гребінка</t>
         </is>
       </c>
-      <c r="F1192" t="inlineStr">
+      <c r="F1191" t="inlineStr">
         <is>
           <t>Полтавська</t>
         </is>
       </c>
-      <c r="G1192" t="n">
+      <c r="G1191" t="n">
         <v>50.1185138</v>
       </c>
-      <c r="H1192" t="n">
+      <c r="H1191" t="n">
         <v>32.4391051</v>
       </c>
-      <c r="I1192" t="inlineStr">
+      <c r="I1191" t="inlineStr">
         <is>
           <t>Пн: 09:00-17:00
 Вт: 09:00-17:00
@@ -55284,48 +55232,48 @@
 Нд: 09:00-14:00</t>
         </is>
       </c>
-      <c r="J1192" t="inlineStr">
+      <c r="J1191" t="inlineStr">
         <is>
           <t>Полтавська</t>
         </is>
       </c>
     </row>
-    <row r="1193">
-      <c r="A1193" t="inlineStr">
+    <row r="1192">
+      <c r="A1192" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1193" t="n">
+      <c r="B1192" t="n">
         <v>3554</v>
       </c>
-      <c r="C1193" t="inlineStr">
+      <c r="C1192" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1193" t="inlineStr">
+      <c r="D1192" t="inlineStr">
         <is>
           <t>вул Городоцька 137</t>
         </is>
       </c>
-      <c r="E1193" t="inlineStr">
+      <c r="E1192" t="inlineStr">
         <is>
           <t>Львів</t>
         </is>
       </c>
-      <c r="F1193" t="inlineStr">
+      <c r="F1192" t="inlineStr">
         <is>
           <t>Львівська</t>
         </is>
       </c>
-      <c r="G1193" t="n">
+      <c r="G1192" t="n">
         <v>49.8367768</v>
       </c>
-      <c r="H1193" t="n">
+      <c r="H1192" t="n">
         <v>24.0028087</v>
       </c>
-      <c r="I1193" t="inlineStr">
+      <c r="I1192" t="inlineStr">
         <is>
           <t>Пн: 09:00-19:00
 Вт: 09:00-19:00
@@ -55336,48 +55284,48 @@
 Нд: 10:00-18:00</t>
         </is>
       </c>
-      <c r="J1193" t="inlineStr">
+      <c r="J1192" t="inlineStr">
         <is>
           <t>Львівська</t>
         </is>
       </c>
     </row>
-    <row r="1194">
-      <c r="A1194" t="inlineStr">
+    <row r="1193">
+      <c r="A1193" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1194" t="n">
+      <c r="B1193" t="n">
         <v>3555</v>
       </c>
-      <c r="C1194" t="inlineStr">
+      <c r="C1193" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1194" t="inlineStr">
+      <c r="D1193" t="inlineStr">
         <is>
           <t>вул Здолбунівська 15</t>
         </is>
       </c>
-      <c r="E1194" t="inlineStr">
+      <c r="E1193" t="inlineStr">
         <is>
           <t>Київ</t>
         </is>
       </c>
-      <c r="F1194" t="inlineStr">
+      <c r="F1193" t="inlineStr">
         <is>
           <t>м. Київ</t>
         </is>
       </c>
-      <c r="G1194" t="n">
+      <c r="G1193" t="n">
         <v>50.4185123</v>
       </c>
-      <c r="H1194" t="n">
+      <c r="H1193" t="n">
         <v>30.631541</v>
       </c>
-      <c r="I1194" t="inlineStr">
+      <c r="I1193" t="inlineStr">
         <is>
           <t>Пн: 10:00-20:00
 Вт: 10:00-20:00
@@ -55388,48 +55336,48 @@
 Нд: 10:00-20:00</t>
         </is>
       </c>
-      <c r="J1194" t="inlineStr">
+      <c r="J1193" t="inlineStr">
         <is>
           <t>м. Київ</t>
         </is>
       </c>
     </row>
-    <row r="1195">
-      <c r="A1195" t="inlineStr">
+    <row r="1194">
+      <c r="A1194" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1195" t="n">
+      <c r="B1194" t="n">
         <v>3556</v>
       </c>
-      <c r="C1195" t="inlineStr">
+      <c r="C1194" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1195" t="inlineStr">
+      <c r="D1194" t="inlineStr">
         <is>
           <t>вул Шевченка 42</t>
         </is>
       </c>
-      <c r="E1195" t="inlineStr">
+      <c r="E1194" t="inlineStr">
         <is>
           <t>Овруч</t>
         </is>
       </c>
-      <c r="F1195" t="inlineStr">
+      <c r="F1194" t="inlineStr">
         <is>
           <t>Житомирська</t>
         </is>
       </c>
-      <c r="G1195" t="n">
+      <c r="G1194" t="n">
         <v>51.3197441</v>
       </c>
-      <c r="H1195" t="n">
+      <c r="H1194" t="n">
         <v>28.8004248</v>
       </c>
-      <c r="I1195" t="inlineStr">
+      <c r="I1194" t="inlineStr">
         <is>
           <t>Пн: 09:00-18:00
 Вт: 09:00-18:00
@@ -55440,48 +55388,48 @@
 Нд: 09:00-18:00</t>
         </is>
       </c>
-      <c r="J1195" t="inlineStr">
+      <c r="J1194" t="inlineStr">
         <is>
           <t>Житомирська</t>
         </is>
       </c>
     </row>
-    <row r="1196">
-      <c r="A1196" t="inlineStr">
+    <row r="1195">
+      <c r="A1195" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1196" t="n">
+      <c r="B1195" t="n">
         <v>3558</v>
       </c>
-      <c r="C1196" t="inlineStr">
+      <c r="C1195" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1196" t="inlineStr">
+      <c r="D1195" t="inlineStr">
         <is>
           <t>вул Київська 26</t>
         </is>
       </c>
-      <c r="E1196" t="inlineStr">
+      <c r="E1195" t="inlineStr">
         <is>
           <t>Іванків</t>
         </is>
       </c>
-      <c r="F1196" t="inlineStr">
+      <c r="F1195" t="inlineStr">
         <is>
           <t>Kiev</t>
         </is>
       </c>
-      <c r="G1196" t="n">
+      <c r="G1195" t="n">
         <v>50.9338356</v>
       </c>
-      <c r="H1196" t="n">
+      <c r="H1195" t="n">
         <v>29.9031381</v>
       </c>
-      <c r="I1196" t="inlineStr">
+      <c r="I1195" t="inlineStr">
         <is>
           <t>Пн: 08:00-18:00
 Вт: 08:00-18:00
@@ -55492,48 +55440,48 @@
 Нд: 09:00-17:00</t>
         </is>
       </c>
-      <c r="J1196" t="inlineStr">
+      <c r="J1195" t="inlineStr">
         <is>
           <t>Kiev</t>
         </is>
       </c>
     </row>
-    <row r="1197">
-      <c r="A1197" t="inlineStr">
+    <row r="1196">
+      <c r="A1196" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1197" t="n">
+      <c r="B1196" t="n">
         <v>3559</v>
       </c>
-      <c r="C1197" t="inlineStr">
+      <c r="C1196" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1197" t="inlineStr">
+      <c r="D1196" t="inlineStr">
         <is>
           <t>просп Соборний 51</t>
         </is>
       </c>
-      <c r="E1197" t="inlineStr">
+      <c r="E1196" t="inlineStr">
         <is>
           <t>Запоріжжя</t>
         </is>
       </c>
-      <c r="F1197" t="inlineStr">
+      <c r="F1196" t="inlineStr">
         <is>
           <t>Zaporizhia</t>
         </is>
       </c>
-      <c r="G1197" t="n">
+      <c r="G1196" t="n">
         <v>47.8176164</v>
       </c>
-      <c r="H1197" t="n">
+      <c r="H1196" t="n">
         <v>35.1753352</v>
       </c>
-      <c r="I1197" t="inlineStr">
+      <c r="I1196" t="inlineStr">
         <is>
           <t>Пн: 09:00-19:00
 Вт: 09:00-19:00
@@ -55544,48 +55492,48 @@
 Нд: 10:00-18:00</t>
         </is>
       </c>
-      <c r="J1197" t="inlineStr">
+      <c r="J1196" t="inlineStr">
         <is>
           <t>Zaporizhia</t>
         </is>
       </c>
     </row>
-    <row r="1198">
-      <c r="A1198" t="inlineStr">
+    <row r="1197">
+      <c r="A1197" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1198" t="n">
+      <c r="B1197" t="n">
         <v>3560</v>
       </c>
-      <c r="C1198" t="inlineStr">
+      <c r="C1197" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1198" t="inlineStr">
+      <c r="D1197" t="inlineStr">
         <is>
           <t>вул Палацова 9</t>
         </is>
       </c>
-      <c r="E1198" t="inlineStr">
+      <c r="E1197" t="inlineStr">
         <is>
           <t>Краматорськ</t>
         </is>
       </c>
-      <c r="F1198" t="inlineStr">
+      <c r="F1197" t="inlineStr">
         <is>
           <t>Донецька</t>
         </is>
       </c>
-      <c r="G1198" t="n">
+      <c r="G1197" t="n">
         <v>48.7366237</v>
       </c>
-      <c r="H1198" t="n">
+      <c r="H1197" t="n">
         <v>37.5916381</v>
       </c>
-      <c r="I1198" t="inlineStr">
+      <c r="I1197" t="inlineStr">
         <is>
           <t>Пн: 09:00-17:00
 Вт: 09:00-17:00
@@ -55596,48 +55544,48 @@
 Нд: 09:00-17:00</t>
         </is>
       </c>
-      <c r="J1198" t="inlineStr">
+      <c r="J1197" t="inlineStr">
         <is>
           <t>Донецька</t>
         </is>
       </c>
     </row>
-    <row r="1199">
-      <c r="A1199" t="inlineStr">
+    <row r="1198">
+      <c r="A1198" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1199" t="n">
+      <c r="B1198" t="n">
         <v>3561</v>
       </c>
-      <c r="C1199" t="inlineStr">
+      <c r="C1198" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1199" t="inlineStr">
+      <c r="D1198" t="inlineStr">
         <is>
           <t>вул Ф. Караманець (Ватутіна) 29</t>
         </is>
       </c>
-      <c r="E1199" t="inlineStr">
+      <c r="E1198" t="inlineStr">
         <is>
           <t>Кривий Ріг</t>
         </is>
       </c>
-      <c r="F1199" t="inlineStr">
+      <c r="F1198" t="inlineStr">
         <is>
           <t>Дніпропетровська</t>
         </is>
       </c>
-      <c r="G1199" t="n">
+      <c r="G1198" t="n">
         <v>48.024687</v>
       </c>
-      <c r="H1199" t="n">
+      <c r="H1198" t="n">
         <v>33.4709468</v>
       </c>
-      <c r="I1199" t="inlineStr">
+      <c r="I1198" t="inlineStr">
         <is>
           <t>Пн: 09:00-18:00
 Вт: 09:00-18:00
@@ -55648,48 +55596,48 @@
 Нд: Вихідний</t>
         </is>
       </c>
-      <c r="J1199" t="inlineStr">
+      <c r="J1198" t="inlineStr">
         <is>
           <t>Дніпропетровська</t>
         </is>
       </c>
     </row>
-    <row r="1200">
-      <c r="A1200" t="inlineStr">
+    <row r="1199">
+      <c r="A1199" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1200" t="n">
+      <c r="B1199" t="n">
         <v>3563</v>
       </c>
-      <c r="C1200" t="inlineStr">
+      <c r="C1199" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1200" t="inlineStr">
+      <c r="D1199" t="inlineStr">
         <is>
           <t>вул Шевченка 116</t>
         </is>
       </c>
-      <c r="E1200" t="inlineStr">
+      <c r="E1199" t="inlineStr">
         <is>
           <t>Дунаївці</t>
         </is>
       </c>
-      <c r="F1200" t="inlineStr">
+      <c r="F1199" t="inlineStr">
         <is>
           <t>Хмельницька</t>
         </is>
       </c>
-      <c r="G1200" t="n">
+      <c r="G1199" t="n">
         <v>48.8922754</v>
       </c>
-      <c r="H1200" t="n">
+      <c r="H1199" t="n">
         <v>26.8568241</v>
       </c>
-      <c r="I1200" t="inlineStr">
+      <c r="I1199" t="inlineStr">
         <is>
           <t>Пн: 09:00-18:00
 Вт: 09:00-18:00
@@ -55700,48 +55648,48 @@
 Нд: Вихідний</t>
         </is>
       </c>
-      <c r="J1200" t="inlineStr">
+      <c r="J1199" t="inlineStr">
         <is>
           <t>Хмельницька</t>
         </is>
       </c>
     </row>
-    <row r="1201">
-      <c r="A1201" t="inlineStr">
+    <row r="1200">
+      <c r="A1200" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1201" t="n">
+      <c r="B1200" t="n">
         <v>3566</v>
       </c>
-      <c r="C1201" t="inlineStr">
+      <c r="C1200" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1201" t="inlineStr">
+      <c r="D1200" t="inlineStr">
         <is>
           <t>вул Р. Шухевича 1а</t>
         </is>
       </c>
-      <c r="E1201" t="inlineStr">
+      <c r="E1200" t="inlineStr">
         <is>
           <t>Хмельницький</t>
         </is>
       </c>
-      <c r="F1201" t="inlineStr">
+      <c r="F1200" t="inlineStr">
         <is>
           <t>Хмельницька</t>
         </is>
       </c>
-      <c r="G1201" t="n">
+      <c r="G1200" t="n">
         <v>49.4360713</v>
       </c>
-      <c r="H1201" t="n">
+      <c r="H1200" t="n">
         <v>26.9572295</v>
       </c>
-      <c r="I1201" t="inlineStr">
+      <c r="I1200" t="inlineStr">
         <is>
           <t>Пн: 09:00-19:00
 Вт: 09:00-19:00
@@ -55752,48 +55700,48 @@
 Нд: 10:00-18:00</t>
         </is>
       </c>
-      <c r="J1201" t="inlineStr">
+      <c r="J1200" t="inlineStr">
         <is>
           <t>Хмельницька</t>
         </is>
       </c>
     </row>
-    <row r="1202">
-      <c r="A1202" t="inlineStr">
+    <row r="1201">
+      <c r="A1201" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1202" t="n">
+      <c r="B1201" t="n">
         <v>3567</v>
       </c>
-      <c r="C1202" t="inlineStr">
+      <c r="C1201" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1202" t="inlineStr">
+      <c r="D1201" t="inlineStr">
         <is>
           <t>вул Макухи 1</t>
         </is>
       </c>
-      <c r="E1202" t="inlineStr">
+      <c r="E1201" t="inlineStr">
         <is>
           <t>Тлумач</t>
         </is>
       </c>
-      <c r="F1202" t="inlineStr">
+      <c r="F1201" t="inlineStr">
         <is>
           <t>Івано-Франківська</t>
         </is>
       </c>
-      <c r="G1202" t="n">
+      <c r="G1201" t="n">
         <v>48.8652727</v>
       </c>
-      <c r="H1202" t="n">
+      <c r="H1201" t="n">
         <v>25.0043864</v>
       </c>
-      <c r="I1202" t="inlineStr">
+      <c r="I1201" t="inlineStr">
         <is>
           <t>Пн: 09:00-17:00
 Вт: 09:00-17:00
@@ -55804,48 +55752,48 @@
 Нд: Вихідний</t>
         </is>
       </c>
-      <c r="J1202" t="inlineStr">
+      <c r="J1201" t="inlineStr">
         <is>
           <t>Івано-Франківська</t>
         </is>
       </c>
     </row>
-    <row r="1203">
-      <c r="A1203" t="inlineStr">
+    <row r="1202">
+      <c r="A1202" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1203" t="n">
+      <c r="B1202" t="n">
         <v>3568</v>
       </c>
-      <c r="C1203" t="inlineStr">
+      <c r="C1202" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1203" t="inlineStr">
+      <c r="D1202" t="inlineStr">
         <is>
           <t>вул Андріївська 5</t>
         </is>
       </c>
-      <c r="E1203" t="inlineStr">
+      <c r="E1202" t="inlineStr">
         <is>
           <t>Березне</t>
         </is>
       </c>
-      <c r="F1203" t="inlineStr">
+      <c r="F1202" t="inlineStr">
         <is>
           <t>Рівненська</t>
         </is>
       </c>
-      <c r="G1203" t="n">
+      <c r="G1202" t="n">
         <v>51.0019955</v>
       </c>
-      <c r="H1203" t="n">
+      <c r="H1202" t="n">
         <v>26.7547284</v>
       </c>
-      <c r="I1203" t="inlineStr">
+      <c r="I1202" t="inlineStr">
         <is>
           <t>Пн: 09:00-18:00
 Вт: 09:00-18:00
@@ -55856,48 +55804,48 @@
 Нд: 09:00-16:00</t>
         </is>
       </c>
-      <c r="J1203" t="inlineStr">
+      <c r="J1202" t="inlineStr">
         <is>
           <t>Рівненська</t>
         </is>
       </c>
     </row>
-    <row r="1204">
-      <c r="A1204" t="inlineStr">
+    <row r="1203">
+      <c r="A1203" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1204" t="n">
+      <c r="B1203" t="n">
         <v>3569</v>
       </c>
-      <c r="C1204" t="inlineStr">
+      <c r="C1203" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1204" t="inlineStr">
+      <c r="D1203" t="inlineStr">
         <is>
           <t>вул Широка 37</t>
         </is>
       </c>
-      <c r="E1204" t="inlineStr">
+      <c r="E1203" t="inlineStr">
         <is>
           <t>Сарни</t>
         </is>
       </c>
-      <c r="F1204" t="inlineStr">
+      <c r="F1203" t="inlineStr">
         <is>
           <t>Рівненська</t>
         </is>
       </c>
-      <c r="G1204" t="n">
+      <c r="G1203" t="n">
         <v>51.3355537</v>
       </c>
-      <c r="H1204" t="n">
+      <c r="H1203" t="n">
         <v>26.6158412</v>
       </c>
-      <c r="I1204" t="inlineStr">
+      <c r="I1203" t="inlineStr">
         <is>
           <t>Пн: 09:00-18:00
 Вт: 09:00-18:00
@@ -55908,48 +55856,48 @@
 Нд: 09:00-17:00</t>
         </is>
       </c>
-      <c r="J1204" t="inlineStr">
+      <c r="J1203" t="inlineStr">
         <is>
           <t>Рівненська</t>
         </is>
       </c>
     </row>
-    <row r="1205">
-      <c r="A1205" t="inlineStr">
+    <row r="1204">
+      <c r="A1204" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1205" t="n">
+      <c r="B1204" t="n">
         <v>3570</v>
       </c>
-      <c r="C1205" t="inlineStr">
+      <c r="C1204" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1205" t="inlineStr">
+      <c r="D1204" t="inlineStr">
         <is>
           <t>вул Січових Стрільців 33А</t>
         </is>
       </c>
-      <c r="E1205" t="inlineStr">
+      <c r="E1204" t="inlineStr">
         <is>
           <t>Бурштин</t>
         </is>
       </c>
-      <c r="F1205" t="inlineStr">
+      <c r="F1204" t="inlineStr">
         <is>
           <t>Івано-Франківська</t>
         </is>
       </c>
-      <c r="G1205" t="n">
+      <c r="G1204" t="n">
         <v>49.2511835</v>
       </c>
-      <c r="H1205" t="n">
+      <c r="H1204" t="n">
         <v>24.6288295</v>
       </c>
-      <c r="I1205" t="inlineStr">
+      <c r="I1204" t="inlineStr">
         <is>
           <t>Пн: 09:00-18:00
 Вт: 09:00-18:00
@@ -55960,48 +55908,48 @@
 Нд: Вихідний</t>
         </is>
       </c>
-      <c r="J1205" t="inlineStr">
+      <c r="J1204" t="inlineStr">
         <is>
           <t>Івано-Франківська</t>
         </is>
       </c>
     </row>
-    <row r="1206">
-      <c r="A1206" t="inlineStr">
+    <row r="1205">
+      <c r="A1205" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1206" t="n">
+      <c r="B1205" t="n">
         <v>3571</v>
       </c>
-      <c r="C1206" t="inlineStr">
+      <c r="C1205" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1206" t="inlineStr">
+      <c r="D1205" t="inlineStr">
         <is>
           <t>вул Небесної Сотні 85</t>
         </is>
       </c>
-      <c r="E1206" t="inlineStr">
+      <c r="E1205" t="inlineStr">
         <is>
           <t>Романів</t>
         </is>
       </c>
-      <c r="F1206" t="inlineStr">
+      <c r="F1205" t="inlineStr">
         <is>
           <t>Житомирська</t>
         </is>
       </c>
-      <c r="G1206" t="n">
+      <c r="G1205" t="n">
         <v>50.141605</v>
       </c>
-      <c r="H1206" t="n">
+      <c r="H1205" t="n">
         <v>27.934655</v>
       </c>
-      <c r="I1206" t="inlineStr">
+      <c r="I1205" t="inlineStr">
         <is>
           <t>Пн: 08:00-18:00
 Вт: 08:00-18:00
@@ -56012,48 +55960,48 @@
 Нд: 09:00-17:00</t>
         </is>
       </c>
-      <c r="J1206" t="inlineStr">
+      <c r="J1205" t="inlineStr">
         <is>
           <t>Житомирська</t>
         </is>
       </c>
     </row>
-    <row r="1207">
-      <c r="A1207" t="inlineStr">
+    <row r="1206">
+      <c r="A1206" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1207" t="n">
+      <c r="B1206" t="n">
         <v>3573</v>
       </c>
-      <c r="C1207" t="inlineStr">
+      <c r="C1206" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1207" t="inlineStr">
+      <c r="D1206" t="inlineStr">
         <is>
           <t>вул Велика Окружна 4</t>
         </is>
       </c>
-      <c r="E1207" t="inlineStr">
+      <c r="E1206" t="inlineStr">
         <is>
           <t>Київ</t>
         </is>
       </c>
-      <c r="F1207" t="inlineStr">
+      <c r="F1206" t="inlineStr">
         <is>
           <t>Kiev</t>
         </is>
       </c>
-      <c r="G1207" t="n">
+      <c r="G1206" t="n">
         <v>50.4295904</v>
       </c>
-      <c r="H1207" t="n">
+      <c r="H1206" t="n">
         <v>30.3567847</v>
       </c>
-      <c r="I1207" t="inlineStr">
+      <c r="I1206" t="inlineStr">
         <is>
           <t>Пн: 10:00-21:00
 Вт: 10:00-21:00
@@ -56064,48 +56012,48 @@
 Нд: 10:00-21:00</t>
         </is>
       </c>
-      <c r="J1207" t="inlineStr">
+      <c r="J1206" t="inlineStr">
         <is>
           <t>Kiev</t>
         </is>
       </c>
     </row>
-    <row r="1208">
-      <c r="A1208" t="inlineStr">
+    <row r="1207">
+      <c r="A1207" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1208" t="n">
+      <c r="B1207" t="n">
         <v>3574</v>
       </c>
-      <c r="C1208" t="inlineStr">
+      <c r="C1207" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1208" t="inlineStr">
+      <c r="D1207" t="inlineStr">
         <is>
           <t>вул Шевченка 50</t>
         </is>
       </c>
-      <c r="E1208" t="inlineStr">
+      <c r="E1207" t="inlineStr">
         <is>
           <t>Богородчани</t>
         </is>
       </c>
-      <c r="F1208" t="inlineStr">
+      <c r="F1207" t="inlineStr">
         <is>
           <t>Івано-Франківська</t>
         </is>
       </c>
-      <c r="G1208" t="n">
+      <c r="G1207" t="n">
         <v>48.809756</v>
       </c>
-      <c r="H1208" t="n">
+      <c r="H1207" t="n">
         <v>24.5400082</v>
       </c>
-      <c r="I1208" t="inlineStr">
+      <c r="I1207" t="inlineStr">
         <is>
           <t>Пн: 09:00-18:00
 Вт: 09:00-18:00
@@ -56116,48 +56064,48 @@
 Нд: 10:00-16:00</t>
         </is>
       </c>
-      <c r="J1208" t="inlineStr">
+      <c r="J1207" t="inlineStr">
         <is>
           <t>Івано-Франківська</t>
         </is>
       </c>
     </row>
-    <row r="1209">
-      <c r="A1209" t="inlineStr">
+    <row r="1208">
+      <c r="A1208" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1209" t="n">
+      <c r="B1208" t="n">
         <v>3575</v>
       </c>
-      <c r="C1209" t="inlineStr">
+      <c r="C1208" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1209" t="inlineStr">
+      <c r="D1208" t="inlineStr">
         <is>
           <t>просп Богдана Хмельницкого (Героїв Сталінграда) 118Д</t>
         </is>
       </c>
-      <c r="E1209" t="inlineStr">
+      <c r="E1208" t="inlineStr">
         <is>
           <t>Дніпро</t>
         </is>
       </c>
-      <c r="F1209" t="inlineStr">
+      <c r="F1208" t="inlineStr">
         <is>
           <t>Дніпропетровська</t>
         </is>
       </c>
-      <c r="G1209" t="n">
+      <c r="G1208" t="n">
         <v>48.4076054</v>
       </c>
-      <c r="H1209" t="n">
+      <c r="H1208" t="n">
         <v>35.0004028</v>
       </c>
-      <c r="I1209" t="inlineStr">
+      <c r="I1208" t="inlineStr">
         <is>
           <t>Пн: 09:00-19:00
 Вт: 09:00-19:00
@@ -56168,9 +56116,61 @@
 Нд: 09:00-19:00</t>
         </is>
       </c>
+      <c r="J1208" t="inlineStr">
+        <is>
+          <t>Дніпропетровська</t>
+        </is>
+      </c>
+    </row>
+    <row r="1209">
+      <c r="A1209" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1209" t="n">
+        <v>3576</v>
+      </c>
+      <c r="C1209" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1209" t="inlineStr">
+        <is>
+          <t>вул Грушевського 41А</t>
+        </is>
+      </c>
+      <c r="E1209" t="inlineStr">
+        <is>
+          <t>Первомайськ</t>
+        </is>
+      </c>
+      <c r="F1209" t="inlineStr">
+        <is>
+          <t>Миколаївська</t>
+        </is>
+      </c>
+      <c r="G1209" t="n">
+        <v>48.0425652</v>
+      </c>
+      <c r="H1209" t="n">
+        <v>30.8444596</v>
+      </c>
+      <c r="I1209" t="inlineStr">
+        <is>
+          <t>Пн: 08:00-18:00
+Вт: 08:00-18:00
+Ср: Вихідний
+Чт: Вихідний
+Пт: 08:00-18:00
+Сб: 08:00-18:00
+Нд: 08:00-16:00</t>
+        </is>
+      </c>
       <c r="J1209" t="inlineStr">
         <is>
-          <t>Дніпропетровська</t>
+          <t>Миколаївська</t>
         </is>
       </c>
     </row>

--- a/all_shops.xlsx
+++ b/all_shops.xlsx
@@ -53321,7 +53321,7 @@
         </is>
       </c>
       <c r="B1155" t="n">
-        <v>3467</v>
+        <v>3470</v>
       </c>
       <c r="C1155" t="inlineStr">
         <is>
@@ -53330,26 +53330,2834 @@
       </c>
       <c r="D1155" t="inlineStr">
         <is>
+          <t>вул  Хрещатик 13</t>
+        </is>
+      </c>
+      <c r="E1155" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="F1155" t="inlineStr">
+        <is>
+          <t>м. Київ</t>
+        </is>
+      </c>
+      <c r="G1155" t="n">
+        <v>50.4487897</v>
+      </c>
+      <c r="H1155" t="n">
+        <v>30.5233361</v>
+      </c>
+      <c r="I1155" t="inlineStr">
+        <is>
+          <t>Пн: 10:00-20:00
+Вт: 10:00-20:00
+Ср: 10:00-20:00
+Чт: 10:00-20:00
+Пт: 10:00-20:00
+Сб: 10:00-20:00
+Нд: 10:00-20:00</t>
+        </is>
+      </c>
+      <c r="J1155" t="inlineStr">
+        <is>
+          <t>м. Київ</t>
+        </is>
+      </c>
+    </row>
+    <row r="1156">
+      <c r="A1156" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1156" t="n">
+        <v>3471</v>
+      </c>
+      <c r="C1156" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1156" t="inlineStr">
+        <is>
+          <t>вул Університетська 45</t>
+        </is>
+      </c>
+      <c r="E1156" t="inlineStr">
+        <is>
+          <t>Словянськ</t>
+        </is>
+      </c>
+      <c r="F1156" t="inlineStr">
+        <is>
+          <t>Дніпропетровська</t>
+        </is>
+      </c>
+      <c r="G1156" t="n">
+        <v>48.0008788</v>
+      </c>
+      <c r="H1156" t="n">
+        <v>33.4821954</v>
+      </c>
+      <c r="I1156" t="inlineStr">
+        <is>
+          <t>Пн: 10:00-17:00
+Вт: 10:00-17:00
+Ср: 10:00-17:00
+Чт: 10:00-17:00
+Пт: 10:00-17:00
+Сб: 10:00-16:00
+Нд: Вихідний</t>
+        </is>
+      </c>
+      <c r="J1156" t="inlineStr">
+        <is>
+          <t>Дніпропетровська</t>
+        </is>
+      </c>
+    </row>
+    <row r="1157">
+      <c r="A1157" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1157" t="n">
+        <v>3472</v>
+      </c>
+      <c r="C1157" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1157" t="inlineStr">
+        <is>
+          <t>вул Чернівецька 2Б</t>
+        </is>
+      </c>
+      <c r="E1157" t="inlineStr">
+        <is>
+          <t>Сторожинець</t>
+        </is>
+      </c>
+      <c r="F1157" t="inlineStr">
+        <is>
+          <t>Чернівецька</t>
+        </is>
+      </c>
+      <c r="G1157" t="n">
+        <v>48.1604917</v>
+      </c>
+      <c r="H1157" t="n">
+        <v>25.721244</v>
+      </c>
+      <c r="I1157" t="inlineStr">
+        <is>
+          <t>Пн: 09:00-18:00
+Вт: 09:00-18:00
+Ср: 09:00-18:00
+Чт: 09:00-18:00
+Пт: 09:00-18:00
+Сб: 09:00-15:00
+Нд: Вихідний</t>
+        </is>
+      </c>
+      <c r="J1157" t="inlineStr">
+        <is>
+          <t>Чернівецька</t>
+        </is>
+      </c>
+    </row>
+    <row r="1158">
+      <c r="A1158" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1158" t="n">
+        <v>3474</v>
+      </c>
+      <c r="C1158" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1158" t="inlineStr">
+        <is>
+          <t>вул Нескорених (Героїв Праці) 13</t>
+        </is>
+      </c>
+      <c r="E1158" t="inlineStr">
+        <is>
+          <t>Харків</t>
+        </is>
+      </c>
+      <c r="F1158" t="inlineStr">
+        <is>
+          <t>Харківська</t>
+        </is>
+      </c>
+      <c r="G1158" t="n">
+        <v>50.0254117</v>
+      </c>
+      <c r="H1158" t="n">
+        <v>36.3369339</v>
+      </c>
+      <c r="I1158" t="inlineStr">
+        <is>
+          <t>Пн: 09:00-18:00
+Вт: 09:00-18:00
+Ср: 09:00-18:00
+Чт: 09:00-18:00
+Пт: 09:00-18:00
+Сб: 09:00-17:00
+Нд: 09:00-17:00</t>
+        </is>
+      </c>
+      <c r="J1158" t="inlineStr">
+        <is>
+          <t>Харківська</t>
+        </is>
+      </c>
+    </row>
+    <row r="1159">
+      <c r="A1159" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1159" t="n">
+        <v>3478</v>
+      </c>
+      <c r="C1159" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1159" t="inlineStr">
+        <is>
+          <t>просп Європейського Союзу (Правди) 58</t>
+        </is>
+      </c>
+      <c r="E1159" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="F1159" t="inlineStr">
+        <is>
+          <t>Kiev</t>
+        </is>
+      </c>
+      <c r="G1159" t="n">
+        <v>50.5047315</v>
+      </c>
+      <c r="H1159" t="n">
+        <v>30.4374307</v>
+      </c>
+      <c r="I1159" t="inlineStr">
+        <is>
+          <t>Пн: 09:00-21:00
+Вт: 09:00-21:00
+Ср: 09:00-21:00
+Чт: 09:00-21:00
+Пт: 09:00-21:00
+Сб: 09:00-21:00
+Нд: 09:00-21:00</t>
+        </is>
+      </c>
+      <c r="J1159" t="inlineStr">
+        <is>
+          <t>Kiev</t>
+        </is>
+      </c>
+    </row>
+    <row r="1160">
+      <c r="A1160" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1160" t="n">
+        <v>3479</v>
+      </c>
+      <c r="C1160" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1160" t="inlineStr">
+        <is>
+          <t>вул Європейського Союзу (Правди) 47</t>
+        </is>
+      </c>
+      <c r="E1160" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="F1160" t="inlineStr">
+        <is>
+          <t>м. Київ</t>
+        </is>
+      </c>
+      <c r="G1160" t="n">
+        <v>50.5037667</v>
+      </c>
+      <c r="H1160" t="n">
+        <v>30.419093</v>
+      </c>
+      <c r="I1160" t="inlineStr">
+        <is>
+          <t>Пн: 10:00-22:00
+Вт: 10:00-22:00
+Ср: 10:00-22:00
+Чт: 10:00-22:00
+Пт: 10:00-22:00
+Сб: 10:00-22:00
+Нд: 10:00-22:00</t>
+        </is>
+      </c>
+      <c r="J1160" t="inlineStr">
+        <is>
+          <t>м. Київ</t>
+        </is>
+      </c>
+    </row>
+    <row r="1161">
+      <c r="A1161" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1161" t="n">
+        <v>3483</v>
+      </c>
+      <c r="C1161" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1161" t="inlineStr">
+        <is>
+          <t>просп Коцюбинського 19</t>
+        </is>
+      </c>
+      <c r="E1161" t="inlineStr">
+        <is>
+          <t>Вінниця</t>
+        </is>
+      </c>
+      <c r="F1161" t="inlineStr">
+        <is>
+          <t>Vinnyts'ka</t>
+        </is>
+      </c>
+      <c r="G1161" t="n">
+        <v>49.239071</v>
+      </c>
+      <c r="H1161" t="n">
+        <v>28.4981039</v>
+      </c>
+      <c r="I1161" t="inlineStr">
+        <is>
+          <t>Пн: 08:00-18:00
+Вт: 08:00-18:00
+Ср: 08:00-18:00
+Чт: 08:00-18:00
+Пт: 08:00-18:00
+Сб: 09:00-17:00
+Нд: 09:00-17:00</t>
+        </is>
+      </c>
+      <c r="J1161" t="inlineStr">
+        <is>
+          <t>Vinnyts'ka</t>
+        </is>
+      </c>
+    </row>
+    <row r="1162">
+      <c r="A1162" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1162" t="n">
+        <v>3485</v>
+      </c>
+      <c r="C1162" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1162" t="inlineStr">
+        <is>
+          <t>вул Котляра (був. Червоноармійська) 8/10</t>
+        </is>
+      </c>
+      <c r="E1162" t="inlineStr">
+        <is>
+          <t>Харків</t>
+        </is>
+      </c>
+      <c r="F1162" t="inlineStr">
+        <is>
+          <t>Харківська</t>
+        </is>
+      </c>
+      <c r="G1162" t="n">
+        <v>49.9892648</v>
+      </c>
+      <c r="H1162" t="n">
+        <v>36.2077698</v>
+      </c>
+      <c r="I1162" t="inlineStr">
+        <is>
+          <t>Пн: 09:00-18:00
+Вт: 09:00-18:00
+Ср: 09:00-18:00
+Чт: 09:00-18:00
+Пт: 09:00-18:00
+Сб: 09:00-18:00
+Нд: 09:00-17:00</t>
+        </is>
+      </c>
+      <c r="J1162" t="inlineStr">
+        <is>
+          <t>Харківська</t>
+        </is>
+      </c>
+    </row>
+    <row r="1163">
+      <c r="A1163" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1163" t="n">
+        <v>3491</v>
+      </c>
+      <c r="C1163" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1163" t="inlineStr">
+        <is>
+          <t>вул Інститутська 10</t>
+        </is>
+      </c>
+      <c r="E1163" t="inlineStr">
+        <is>
+          <t>Хмельницький</t>
+        </is>
+      </c>
+      <c r="F1163" t="inlineStr">
+        <is>
+          <t>Хмельницька</t>
+        </is>
+      </c>
+      <c r="G1163" t="n">
+        <v>49.4098499</v>
+      </c>
+      <c r="H1163" t="n">
+        <v>26.9605436</v>
+      </c>
+      <c r="I1163" t="inlineStr">
+        <is>
+          <t>Пн: 09:00-19:00
+Вт: 09:00-19:00
+Ср: 09:00-19:00
+Чт: 09:00-19:00
+Пт: 09:00-19:00
+Сб: 10:00-18:00
+Нд: 10:00-18:00</t>
+        </is>
+      </c>
+      <c r="J1163" t="inlineStr">
+        <is>
+          <t>Хмельницька</t>
+        </is>
+      </c>
+    </row>
+    <row r="1164">
+      <c r="A1164" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1164" t="n">
+        <v>3494</v>
+      </c>
+      <c r="C1164" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1164" t="inlineStr">
+        <is>
+          <t>вул Шевченків Шлях 144-А</t>
+        </is>
+      </c>
+      <c r="E1164" t="inlineStr">
+        <is>
+          <t>Березань</t>
+        </is>
+      </c>
+      <c r="F1164" t="inlineStr">
+        <is>
+          <t>Kiev</t>
+        </is>
+      </c>
+      <c r="G1164" t="n">
+        <v>50.3119113</v>
+      </c>
+      <c r="H1164" t="n">
+        <v>31.4678577</v>
+      </c>
+      <c r="I1164" t="inlineStr">
+        <is>
+          <t>Пн: 09:00-17:00
+Вт: 09:00-17:00
+Ср: 09:00-17:00
+Чт: 09:00-17:00
+Пт: 09:00-17:00
+Сб: 10:00-16:00
+Нд: 10:00-16:00</t>
+        </is>
+      </c>
+      <c r="J1164" t="inlineStr">
+        <is>
+          <t>Kiev</t>
+        </is>
+      </c>
+    </row>
+    <row r="1165">
+      <c r="A1165" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1165" t="n">
+        <v>3495</v>
+      </c>
+      <c r="C1165" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1165" t="inlineStr">
+        <is>
+          <t>вул Міцкевича 1</t>
+        </is>
+      </c>
+      <c r="E1165" t="inlineStr">
+        <is>
+          <t>Борислав</t>
+        </is>
+      </c>
+      <c r="F1165" t="inlineStr">
+        <is>
+          <t>Львівська</t>
+        </is>
+      </c>
+      <c r="G1165" t="n">
+        <v>49.287286</v>
+      </c>
+      <c r="H1165" t="n">
+        <v>23.4159004</v>
+      </c>
+      <c r="I1165" t="inlineStr">
+        <is>
+          <t>Пн: 09:00-18:00
+Вт: 09:00-18:00
+Ср: 09:00-18:00
+Чт: 09:00-18:00
+Пт: 09:00-18:00
+Сб: 09:00-17:00
+Нд: 10:00-17:00</t>
+        </is>
+      </c>
+      <c r="J1165" t="inlineStr">
+        <is>
+          <t>Львівська</t>
+        </is>
+      </c>
+    </row>
+    <row r="1166">
+      <c r="A1166" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1166" t="n">
+        <v>3496</v>
+      </c>
+      <c r="C1166" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1166" t="inlineStr">
+        <is>
+          <t>вул І.Франка 1</t>
+        </is>
+      </c>
+      <c r="E1166" t="inlineStr">
+        <is>
+          <t>Верховина</t>
+        </is>
+      </c>
+      <c r="F1166" t="inlineStr">
+        <is>
+          <t>Івано-Франківська</t>
+        </is>
+      </c>
+      <c r="G1166" t="n">
+        <v>48.1549768</v>
+      </c>
+      <c r="H1166" t="n">
+        <v>24.8291227</v>
+      </c>
+      <c r="I1166" t="inlineStr">
+        <is>
+          <t>Пн: 09:00-18:00
+Вт: 09:00-18:00
+Ср: 09:00-18:00
+Чт: 09:00-18:00
+Пт: 09:00-18:00
+Сб: 09:00-17:00
+Нд: 10:00-16:00</t>
+        </is>
+      </c>
+      <c r="J1166" t="inlineStr">
+        <is>
+          <t>Івано-Франківська</t>
+        </is>
+      </c>
+    </row>
+    <row r="1167">
+      <c r="A1167" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1167" t="n">
+        <v>3498</v>
+      </c>
+      <c r="C1167" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1167" t="inlineStr">
+        <is>
+          <t>просп Олександра Поля 1/9</t>
+        </is>
+      </c>
+      <c r="E1167" t="inlineStr">
+        <is>
+          <t>Дніпро</t>
+        </is>
+      </c>
+      <c r="F1167" t="inlineStr">
+        <is>
+          <t>Дніпропетровська</t>
+        </is>
+      </c>
+      <c r="G1167" t="n">
+        <v>48.4642698</v>
+      </c>
+      <c r="H1167" t="n">
+        <v>35.0290126</v>
+      </c>
+      <c r="I1167" t="inlineStr">
+        <is>
+          <t>Пн: 09:00-19:00
+Вт: 09:00-19:00
+Ср: 09:00-19:00
+Чт: 09:00-19:00
+Пт: 09:00-19:00
+Сб: 09:00-19:00
+Нд: 09:00-18:00</t>
+        </is>
+      </c>
+      <c r="J1167" t="inlineStr">
+        <is>
+          <t>Дніпропетровська</t>
+        </is>
+      </c>
+    </row>
+    <row r="1168">
+      <c r="A1168" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1168" t="n">
+        <v>3501</v>
+      </c>
+      <c r="C1168" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1168" t="inlineStr">
+        <is>
+          <t>просп Дмитра Яворницького (К.Маркса) 65</t>
+        </is>
+      </c>
+      <c r="E1168" t="inlineStr">
+        <is>
+          <t>Дніпро</t>
+        </is>
+      </c>
+      <c r="F1168" t="inlineStr">
+        <is>
+          <t>Дніпропетровська</t>
+        </is>
+      </c>
+      <c r="G1168" t="n">
+        <v>48.4647786</v>
+      </c>
+      <c r="H1168" t="n">
+        <v>35.0447223</v>
+      </c>
+      <c r="I1168" t="inlineStr">
+        <is>
+          <t>Пн: 09:00-19:00
+Вт: 09:00-19:00
+Ср: 09:00-19:00
+Чт: 09:00-19:00
+Пт: 09:00-19:00
+Сб: 09:00-18:00
+Нд: 09:00-18:00</t>
+        </is>
+      </c>
+      <c r="J1168" t="inlineStr">
+        <is>
+          <t>Дніпропетровська</t>
+        </is>
+      </c>
+    </row>
+    <row r="1169">
+      <c r="A1169" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1169" t="n">
+        <v>3503</v>
+      </c>
+      <c r="C1169" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1169" t="inlineStr">
+        <is>
+          <t>вул Привокзальна 3</t>
+        </is>
+      </c>
+      <c r="E1169" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="F1169" t="inlineStr">
+        <is>
+          <t>Kiev</t>
+        </is>
+      </c>
+      <c r="G1169" t="n">
+        <v>50.4305963</v>
+      </c>
+      <c r="H1169" t="n">
+        <v>30.6518096</v>
+      </c>
+      <c r="I1169" t="inlineStr">
+        <is>
+          <t>Пн: 10:00-17:00
+Вт: 10:00-17:00
+Ср: 10:00-17:00
+Чт: 10:00-17:00
+Пт: 10:00-17:00
+Сб: 10:00-17:00
+Нд: 10:00-17:00</t>
+        </is>
+      </c>
+      <c r="J1169" t="inlineStr">
+        <is>
+          <t>Kiev</t>
+        </is>
+      </c>
+    </row>
+    <row r="1170">
+      <c r="A1170" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1170" t="n">
+        <v>3505</v>
+      </c>
+      <c r="C1170" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1170" t="inlineStr">
+        <is>
+          <t>пл Шевченка 26</t>
+        </is>
+      </c>
+      <c r="E1170" t="inlineStr">
+        <is>
+          <t>Коломия</t>
+        </is>
+      </c>
+      <c r="F1170" t="inlineStr">
+        <is>
+          <t>Івано-Франківська</t>
+        </is>
+      </c>
+      <c r="G1170" t="n">
+        <v>48.5249278</v>
+      </c>
+      <c r="H1170" t="n">
+        <v>25.0375409</v>
+      </c>
+      <c r="I1170" t="inlineStr">
+        <is>
+          <t>Пн: 09:00-18:00
+Вт: 09:00-18:00
+Ср: 09:00-18:00
+Чт: 09:00-18:00
+Пт: 09:00-18:00
+Сб: 09:00-18:00
+Нд: 10:00-17:00</t>
+        </is>
+      </c>
+      <c r="J1170" t="inlineStr">
+        <is>
+          <t>Івано-Франківська</t>
+        </is>
+      </c>
+    </row>
+    <row r="1171">
+      <c r="A1171" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1171" t="n">
+        <v>3506</v>
+      </c>
+      <c r="C1171" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1171" t="inlineStr">
+        <is>
+          <t>вул Медова 5</t>
+        </is>
+      </c>
+      <c r="E1171" t="inlineStr">
+        <is>
+          <t>Кремeнець</t>
+        </is>
+      </c>
+      <c r="F1171" t="inlineStr">
+        <is>
+          <t>Тернопільська</t>
+        </is>
+      </c>
+      <c r="G1171" t="n">
+        <v>50.095605</v>
+      </c>
+      <c r="H1171" t="n">
+        <v>25.7259463</v>
+      </c>
+      <c r="I1171" t="inlineStr">
+        <is>
+          <t>Пн: 09:00-19:00
+Вт: 09:00-19:00
+Ср: 09:00-19:00
+Чт: 09:00-19:00
+Пт: 09:00-19:00
+Сб: 10:00-16:00
+Нд: 10:00-16:00</t>
+        </is>
+      </c>
+      <c r="J1171" t="inlineStr">
+        <is>
+          <t>Тернопільська</t>
+        </is>
+      </c>
+    </row>
+    <row r="1172">
+      <c r="A1172" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1172" t="n">
+        <v>3508</v>
+      </c>
+      <c r="C1172" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1172" t="inlineStr">
+        <is>
+          <t>вул Шевченка 100</t>
+        </is>
+      </c>
+      <c r="E1172" t="inlineStr">
+        <is>
+          <t>Люботин</t>
+        </is>
+      </c>
+      <c r="F1172" t="inlineStr">
+        <is>
+          <t>Харківська</t>
+        </is>
+      </c>
+      <c r="G1172" t="n">
+        <v>49.9407992</v>
+      </c>
+      <c r="H1172" t="n">
+        <v>35.9262566</v>
+      </c>
+      <c r="I1172" t="inlineStr">
+        <is>
+          <t>Пн: 08:00-18:00
+Вт: 08:00-18:00
+Ср: 08:00-18:00
+Чт: 08:00-18:00
+Пт: 08:00-18:00
+Сб: 08:00-18:00
+Нд: 08:00-16:00</t>
+        </is>
+      </c>
+      <c r="J1172" t="inlineStr">
+        <is>
+          <t>Харківська</t>
+        </is>
+      </c>
+    </row>
+    <row r="1173">
+      <c r="A1173" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1173" t="n">
+        <v>3510</v>
+      </c>
+      <c r="C1173" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1173" t="inlineStr">
+        <is>
+          <t>вул Петропавлівська 49</t>
+        </is>
+      </c>
+      <c r="E1173" t="inlineStr">
+        <is>
+          <t>Суми</t>
+        </is>
+      </c>
+      <c r="F1173" t="inlineStr">
+        <is>
+          <t>Сумська</t>
+        </is>
+      </c>
+      <c r="G1173" t="n">
+        <v>50.9065729</v>
+      </c>
+      <c r="H1173" t="n">
+        <v>34.796901</v>
+      </c>
+      <c r="I1173" t="inlineStr">
+        <is>
+          <t>Пн: 09:00-18:00
+Вт: 09:00-18:00
+Ср: 09:00-18:00
+Чт: 09:00-18:00
+Пт: 09:00-18:00
+Сб: 09:00-18:00
+Нд: 09:00-18:00</t>
+        </is>
+      </c>
+      <c r="J1173" t="inlineStr">
+        <is>
+          <t>Сумська</t>
+        </is>
+      </c>
+    </row>
+    <row r="1174">
+      <c r="A1174" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1174" t="n">
+        <v>3512</v>
+      </c>
+      <c r="C1174" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1174" t="inlineStr">
+        <is>
+          <t>вул Валентинівська (Блюхера) 37/128</t>
+        </is>
+      </c>
+      <c r="E1174" t="inlineStr">
+        <is>
+          <t>Харків</t>
+        </is>
+      </c>
+      <c r="F1174" t="inlineStr">
+        <is>
+          <t>Харківська</t>
+        </is>
+      </c>
+      <c r="G1174" t="n">
+        <v>50.0098371</v>
+      </c>
+      <c r="H1174" t="n">
+        <v>36.3503577</v>
+      </c>
+      <c r="I1174" t="inlineStr">
+        <is>
+          <t>Пн: 09:00-19:00
+Вт: 09:00-19:00
+Ср: 09:00-19:00
+Чт: 09:00-19:00
+Пт: 09:00-19:00
+Сб: 09:00-18:00
+Нд: 09:00-18:00</t>
+        </is>
+      </c>
+      <c r="J1174" t="inlineStr">
+        <is>
+          <t>Харківська</t>
+        </is>
+      </c>
+    </row>
+    <row r="1175">
+      <c r="A1175" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1175" t="n">
+        <v>3514</v>
+      </c>
+      <c r="C1175" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1175" t="inlineStr">
+        <is>
+          <t>вул Центральна 32а</t>
+        </is>
+      </c>
+      <c r="E1175" t="inlineStr">
+        <is>
+          <t>Чемерівці</t>
+        </is>
+      </c>
+      <c r="F1175" t="inlineStr">
+        <is>
+          <t>Хмельницька</t>
+        </is>
+      </c>
+      <c r="G1175" t="n">
+        <v>49.011295</v>
+      </c>
+      <c r="H1175" t="n">
+        <v>26.340395</v>
+      </c>
+      <c r="I1175" t="inlineStr">
+        <is>
+          <t>Пн: 08:00-18:00
+Вт: 08:00-18:00
+Ср: 08:00-18:00
+Чт: 08:00-18:00
+Пт: 08:00-18:00
+Сб: 09:00-16:00
+Нд: 09:00-15:00</t>
+        </is>
+      </c>
+      <c r="J1175" t="inlineStr">
+        <is>
+          <t>Хмельницька</t>
+        </is>
+      </c>
+    </row>
+    <row r="1176">
+      <c r="A1176" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1176" t="n">
+        <v>3516</v>
+      </c>
+      <c r="C1176" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1176" t="inlineStr">
+        <is>
+          <t>просп Відрадний 69/1</t>
+        </is>
+      </c>
+      <c r="E1176" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="F1176" t="inlineStr">
+        <is>
+          <t>Kiev</t>
+        </is>
+      </c>
+      <c r="G1176" t="n">
+        <v>50.428885</v>
+      </c>
+      <c r="H1176" t="n">
+        <v>30.4309396</v>
+      </c>
+      <c r="I1176" t="inlineStr">
+        <is>
+          <t>Пн: 09:00-18:00
+Вт: 09:00-18:00
+Ср: 09:00-18:00
+Чт: 09:00-18:00
+Пт: 09:00-18:00
+Сб: 10:00-17:00
+Нд: 10:00-17:00</t>
+        </is>
+      </c>
+      <c r="J1176" t="inlineStr">
+        <is>
+          <t>Kiev</t>
+        </is>
+      </c>
+    </row>
+    <row r="1177">
+      <c r="A1177" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1177" t="n">
+        <v>3517</v>
+      </c>
+      <c r="C1177" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1177" t="inlineStr">
+        <is>
+          <t>просп Свободи (Леніна) 16Д</t>
+        </is>
+      </c>
+      <c r="E1177" t="inlineStr">
+        <is>
+          <t>Хмільник</t>
+        </is>
+      </c>
+      <c r="F1177" t="inlineStr">
+        <is>
+          <t>Vinnyts'ka</t>
+        </is>
+      </c>
+      <c r="G1177" t="n">
+        <v>49.5576747</v>
+      </c>
+      <c r="H1177" t="n">
+        <v>27.9528561</v>
+      </c>
+      <c r="I1177" t="inlineStr">
+        <is>
+          <t>Пн: 08:00-17:00
+Вт: 08:00-17:00
+Ср: 08:00-17:00
+Чт: 08:00-17:00
+Пт: 08:00-17:00
+Сб: 08:00-17:00
+Нд: Вихідний</t>
+        </is>
+      </c>
+      <c r="J1177" t="inlineStr">
+        <is>
+          <t>Vinnyts'ka</t>
+        </is>
+      </c>
+    </row>
+    <row r="1178">
+      <c r="A1178" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1178" t="n">
+        <v>3520</v>
+      </c>
+      <c r="C1178" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1178" t="inlineStr">
+        <is>
+          <t>пл Шевченка 6</t>
+        </is>
+      </c>
+      <c r="E1178" t="inlineStr">
+        <is>
+          <t>Славута</t>
+        </is>
+      </c>
+      <c r="F1178" t="inlineStr">
+        <is>
+          <t>Хмельницька</t>
+        </is>
+      </c>
+      <c r="G1178" t="n">
+        <v>50.2957898</v>
+      </c>
+      <c r="H1178" t="n">
+        <v>26.8570458</v>
+      </c>
+      <c r="I1178" t="inlineStr">
+        <is>
+          <t>Пн: 08:00-17:00
+Вт: 08:00-17:00
+Ср: 08:00-17:00
+Чт: 08:00-17:00
+Пт: 08:00-17:00
+Сб: 08:00-17:00
+Нд: 08:00-17:00</t>
+        </is>
+      </c>
+      <c r="J1178" t="inlineStr">
+        <is>
+          <t>Хмельницька</t>
+        </is>
+      </c>
+    </row>
+    <row r="1179">
+      <c r="A1179" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1179" t="n">
+        <v>3526</v>
+      </c>
+      <c r="C1179" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1179" t="inlineStr">
+        <is>
+          <t>вул Незалежності 65</t>
+        </is>
+      </c>
+      <c r="E1179" t="inlineStr">
+        <is>
+          <t>Камянка-Бузька</t>
+        </is>
+      </c>
+      <c r="F1179" t="inlineStr">
+        <is>
+          <t>Львівська</t>
+        </is>
+      </c>
+      <c r="G1179" t="n">
+        <v>50.107376</v>
+      </c>
+      <c r="H1179" t="n">
+        <v>24.3436341</v>
+      </c>
+      <c r="I1179" t="inlineStr">
+        <is>
+          <t>Пн: 09:00-18:00
+Вт: 09:00-18:00
+Ср: 09:00-18:00
+Чт: 09:00-18:00
+Пт: 09:00-18:00
+Сб: 09:00-16:00
+Нд: 09:00-16:00</t>
+        </is>
+      </c>
+      <c r="J1179" t="inlineStr">
+        <is>
+          <t>Львівська</t>
+        </is>
+      </c>
+    </row>
+    <row r="1180">
+      <c r="A1180" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1180" t="n">
+        <v>3530</v>
+      </c>
+      <c r="C1180" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1180" t="inlineStr">
+        <is>
+          <t>вул Савіцького 14</t>
+        </is>
+      </c>
+      <c r="E1180" t="inlineStr">
+        <is>
+          <t>Летичів</t>
+        </is>
+      </c>
+      <c r="F1180" t="inlineStr">
+        <is>
+          <t>Хмельницька</t>
+        </is>
+      </c>
+      <c r="G1180" t="n">
+        <v>49.3813788</v>
+      </c>
+      <c r="H1180" t="n">
+        <v>27.6197046</v>
+      </c>
+      <c r="I1180" t="inlineStr">
+        <is>
+          <t>Пн: 09:00-18:00
+Вт: 09:00-18:00
+Ср: 09:00-18:00
+Чт: 09:00-18:00
+Пт: 09:00-18:00
+Сб: 09:00-18:00
+Нд: 09:00-18:00</t>
+        </is>
+      </c>
+      <c r="J1180" t="inlineStr">
+        <is>
+          <t>Хмельницька</t>
+        </is>
+      </c>
+    </row>
+    <row r="1181">
+      <c r="A1181" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1181" t="n">
+        <v>3531</v>
+      </c>
+      <c r="C1181" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1181" t="inlineStr">
+        <is>
+          <t>вул Берестейський (Перемоги) 26</t>
+        </is>
+      </c>
+      <c r="E1181" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="F1181" t="inlineStr">
+        <is>
+          <t>м. Київ</t>
+        </is>
+      </c>
+      <c r="G1181" t="n">
+        <v>50.4515345</v>
+      </c>
+      <c r="H1181" t="n">
+        <v>30.4678476</v>
+      </c>
+      <c r="I1181" t="inlineStr">
+        <is>
+          <t>Пн: 10:00-21:00
+Вт: 10:00-21:00
+Ср: 10:00-21:00
+Чт: 10:00-21:00
+Пт: 10:00-21:00
+Сб: 10:00-21:00
+Нд: 10:00-21:00</t>
+        </is>
+      </c>
+      <c r="J1181" t="inlineStr">
+        <is>
+          <t>м. Київ</t>
+        </is>
+      </c>
+    </row>
+    <row r="1182">
+      <c r="A1182" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1182" t="n">
+        <v>3534</v>
+      </c>
+      <c r="C1182" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1182" t="inlineStr">
+        <is>
+          <t>вул Шевченка 74а</t>
+        </is>
+      </c>
+      <c r="E1182" t="inlineStr">
+        <is>
+          <t>Городенка</t>
+        </is>
+      </c>
+      <c r="F1182" t="inlineStr">
+        <is>
+          <t>Івано-Франківська</t>
+        </is>
+      </c>
+      <c r="G1182" t="n">
+        <v>48.66888903427731</v>
+      </c>
+      <c r="H1182" t="n">
+        <v>25.50435338169336</v>
+      </c>
+      <c r="I1182" t="inlineStr">
+        <is>
+          <t>Пн: 08:00-18:00
+Вт: 08:00-18:00
+Ср: 08:00-18:00
+Чт: 08:00-18:00
+Пт: 08:00-18:00
+Сб: 08:00-18:00
+Нд: 10:00-17:00</t>
+        </is>
+      </c>
+      <c r="J1182" t="inlineStr">
+        <is>
+          <t>Івано-Франківська</t>
+        </is>
+      </c>
+    </row>
+    <row r="1183">
+      <c r="A1183" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1183" t="n">
+        <v>3535</v>
+      </c>
+      <c r="C1183" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1183" t="inlineStr">
+        <is>
+          <t>вул Бекетова 21</t>
+        </is>
+      </c>
+      <c r="E1183" t="inlineStr">
+        <is>
+          <t>Харків</t>
+        </is>
+      </c>
+      <c r="F1183" t="inlineStr">
+        <is>
+          <t>Харківська</t>
+        </is>
+      </c>
+      <c r="G1183" t="n">
+        <v>49.9512627</v>
+      </c>
+      <c r="H1183" t="n">
+        <v>36.371922</v>
+      </c>
+      <c r="I1183" t="inlineStr">
+        <is>
+          <t>Пн: 09:00-17:00
+Вт: 09:00-17:00
+Ср: 09:00-17:00
+Чт: 09:00-17:00
+Пт: 09:00-17:00
+Сб: 09:00-17:00
+Нд: 09:00-16:00</t>
+        </is>
+      </c>
+      <c r="J1183" t="inlineStr">
+        <is>
+          <t>Харківська</t>
+        </is>
+      </c>
+    </row>
+    <row r="1184">
+      <c r="A1184" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1184" t="n">
+        <v>3541</v>
+      </c>
+      <c r="C1184" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1184" t="inlineStr">
+        <is>
+          <t>вул Одеська 121, А/1</t>
+        </is>
+      </c>
+      <c r="E1184" t="inlineStr">
+        <is>
+          <t>Первомайськ</t>
+        </is>
+      </c>
+      <c r="F1184" t="inlineStr">
+        <is>
+          <t>Миколаївська</t>
+        </is>
+      </c>
+      <c r="G1184" t="n">
+        <v>48.0228289</v>
+      </c>
+      <c r="H1184" t="n">
+        <v>30.8511121</v>
+      </c>
+      <c r="I1184" t="inlineStr">
+        <is>
+          <t>Пн: 09:00-18:00
+Вт: 09:00-18:00
+Ср: 09:00-18:00
+Чт: 09:00-18:00
+Пт: 09:00-18:00
+Сб: 09:00-18:00
+Нд: 09:00-18:00</t>
+        </is>
+      </c>
+      <c r="J1184" t="inlineStr">
+        <is>
+          <t>Миколаївська</t>
+        </is>
+      </c>
+    </row>
+    <row r="1185">
+      <c r="A1185" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1185" t="n">
+        <v>3542</v>
+      </c>
+      <c r="C1185" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1185" t="inlineStr">
+        <is>
+          <t>просп Героїв Харкова 274</t>
+        </is>
+      </c>
+      <c r="E1185" t="inlineStr">
+        <is>
+          <t>Харків</t>
+        </is>
+      </c>
+      <c r="F1185" t="inlineStr">
+        <is>
+          <t>Харківська</t>
+        </is>
+      </c>
+      <c r="G1185" t="n">
+        <v>49.9432342</v>
+      </c>
+      <c r="H1185" t="n">
+        <v>36.3984342</v>
+      </c>
+      <c r="I1185" t="inlineStr">
+        <is>
+          <t>Пн: 09:00-18:00
+Вт: 09:00-18:00
+Ср: 09:00-18:00
+Чт: 09:00-18:00
+Пт: 09:00-18:00
+Сб: 09:00-17:00
+Нд: 09:00-17:00</t>
+        </is>
+      </c>
+      <c r="J1185" t="inlineStr">
+        <is>
+          <t>Харківська</t>
+        </is>
+      </c>
+    </row>
+    <row r="1186">
+      <c r="A1186" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1186" t="n">
+        <v>3543</v>
+      </c>
+      <c r="C1186" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1186" t="inlineStr">
+        <is>
+          <t>вул Салтівське шосе 147</t>
+        </is>
+      </c>
+      <c r="E1186" t="inlineStr">
+        <is>
+          <t>Харків</t>
+        </is>
+      </c>
+      <c r="F1186" t="inlineStr">
+        <is>
+          <t>Харківська</t>
+        </is>
+      </c>
+      <c r="G1186" t="n">
+        <v>49.9908024</v>
+      </c>
+      <c r="H1186" t="n">
+        <v>36.3585856</v>
+      </c>
+      <c r="I1186" t="inlineStr">
+        <is>
+          <t>Пн: 09:00-18:00
+Вт: 09:00-18:00
+Ср: 09:00-18:00
+Чт: 09:00-18:00
+Пт: 09:00-18:00
+Сб: 09:00-17:00
+Нд: 09:00-17:00</t>
+        </is>
+      </c>
+      <c r="J1186" t="inlineStr">
+        <is>
+          <t>Харківська</t>
+        </is>
+      </c>
+    </row>
+    <row r="1187">
+      <c r="A1187" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1187" t="n">
+        <v>3544</v>
+      </c>
+      <c r="C1187" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1187" t="inlineStr">
+        <is>
+          <t>просп Петра Григоренка 3</t>
+        </is>
+      </c>
+      <c r="E1187" t="inlineStr">
+        <is>
+          <t>Харків</t>
+        </is>
+      </c>
+      <c r="F1187" t="inlineStr">
+        <is>
+          <t>Харківська</t>
+        </is>
+      </c>
+      <c r="G1187" t="n">
+        <v>49.9650438</v>
+      </c>
+      <c r="H1187" t="n">
+        <v>36.3219614</v>
+      </c>
+      <c r="I1187" t="inlineStr">
+        <is>
+          <t>Пн: 09:00-18:00
+Вт: 09:00-18:00
+Ср: 09:00-18:00
+Чт: 09:00-18:00
+Пт: 09:00-18:00
+Сб: 09:00-17:00
+Нд: 09:00-17:00</t>
+        </is>
+      </c>
+      <c r="J1187" t="inlineStr">
+        <is>
+          <t>Харківська</t>
+        </is>
+      </c>
+    </row>
+    <row r="1188">
+      <c r="A1188" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1188" t="n">
+        <v>3545</v>
+      </c>
+      <c r="C1188" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1188" t="inlineStr">
+        <is>
+          <t>просп Аерокосмічний (Гагаріна) 177</t>
+        </is>
+      </c>
+      <c r="E1188" t="inlineStr">
+        <is>
+          <t>Харків</t>
+        </is>
+      </c>
+      <c r="F1188" t="inlineStr">
+        <is>
+          <t>Харківська</t>
+        </is>
+      </c>
+      <c r="G1188" t="n">
+        <v>50.0169162</v>
+      </c>
+      <c r="H1188" t="n">
+        <v>36.2067146</v>
+      </c>
+      <c r="I1188" t="inlineStr">
+        <is>
+          <t>Пн: 09:00-18:00
+Вт: 09:00-18:00
+Ср: 09:00-18:00
+Чт: 09:00-18:00
+Пт: 09:00-18:00
+Сб: 09:00-17:00
+Нд: 09:00-17:00</t>
+        </is>
+      </c>
+      <c r="J1188" t="inlineStr">
+        <is>
+          <t>Харківська</t>
+        </is>
+      </c>
+    </row>
+    <row r="1189">
+      <c r="A1189" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1189" t="n">
+        <v>3547</v>
+      </c>
+      <c r="C1189" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1189" t="inlineStr">
+        <is>
+          <t>вул Олімпійська 75</t>
+        </is>
+      </c>
+      <c r="E1189" t="inlineStr">
+        <is>
+          <t>Хотин</t>
+        </is>
+      </c>
+      <c r="F1189" t="inlineStr">
+        <is>
+          <t>Чернівецька</t>
+        </is>
+      </c>
+      <c r="G1189" t="n">
+        <v>48.5043413</v>
+      </c>
+      <c r="H1189" t="n">
+        <v>26.490402</v>
+      </c>
+      <c r="I1189" t="inlineStr">
+        <is>
+          <t>Пн: 09:00-18:00
+Вт: 09:00-18:00
+Ср: 09:00-18:00
+Чт: 09:00-18:00
+Пт: 09:00-18:00
+Сб: 09:00-17:00
+Нд: 10:00-14:00</t>
+        </is>
+      </c>
+      <c r="J1189" t="inlineStr">
+        <is>
+          <t>Чернівецька</t>
+        </is>
+      </c>
+    </row>
+    <row r="1190">
+      <c r="A1190" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1190" t="n">
+        <v>3549</v>
+      </c>
+      <c r="C1190" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1190" t="inlineStr">
+        <is>
+          <t>вул Жовтнева 4-А</t>
+        </is>
+      </c>
+      <c r="E1190" t="inlineStr">
+        <is>
+          <t>Гребінка</t>
+        </is>
+      </c>
+      <c r="F1190" t="inlineStr">
+        <is>
+          <t>Полтавська</t>
+        </is>
+      </c>
+      <c r="G1190" t="n">
+        <v>50.1185138</v>
+      </c>
+      <c r="H1190" t="n">
+        <v>32.4391051</v>
+      </c>
+      <c r="I1190" t="inlineStr">
+        <is>
+          <t>Пн: 09:00-17:00
+Вт: 09:00-17:00
+Ср: 09:00-17:00
+Чт: 09:00-17:00
+Пт: 09:00-17:00
+Сб: 09:00-14:00
+Нд: 09:00-14:00</t>
+        </is>
+      </c>
+      <c r="J1190" t="inlineStr">
+        <is>
+          <t>Полтавська</t>
+        </is>
+      </c>
+    </row>
+    <row r="1191">
+      <c r="A1191" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1191" t="n">
+        <v>3554</v>
+      </c>
+      <c r="C1191" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1191" t="inlineStr">
+        <is>
+          <t>вул Городоцька 137</t>
+        </is>
+      </c>
+      <c r="E1191" t="inlineStr">
+        <is>
+          <t>Львів</t>
+        </is>
+      </c>
+      <c r="F1191" t="inlineStr">
+        <is>
+          <t>Львівська</t>
+        </is>
+      </c>
+      <c r="G1191" t="n">
+        <v>49.8367768</v>
+      </c>
+      <c r="H1191" t="n">
+        <v>24.0028087</v>
+      </c>
+      <c r="I1191" t="inlineStr">
+        <is>
+          <t>Пн: 09:00-19:00
+Вт: 09:00-19:00
+Ср: 09:00-19:00
+Чт: 09:00-19:00
+Пт: 09:00-19:00
+Сб: 09:00-18:00
+Нд: 10:00-18:00</t>
+        </is>
+      </c>
+      <c r="J1191" t="inlineStr">
+        <is>
+          <t>Львівська</t>
+        </is>
+      </c>
+    </row>
+    <row r="1192">
+      <c r="A1192" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1192" t="n">
+        <v>3555</v>
+      </c>
+      <c r="C1192" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1192" t="inlineStr">
+        <is>
+          <t>вул Здолбунівська 15</t>
+        </is>
+      </c>
+      <c r="E1192" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="F1192" t="inlineStr">
+        <is>
+          <t>м. Київ</t>
+        </is>
+      </c>
+      <c r="G1192" t="n">
+        <v>50.4185123</v>
+      </c>
+      <c r="H1192" t="n">
+        <v>30.631541</v>
+      </c>
+      <c r="I1192" t="inlineStr">
+        <is>
+          <t>Пн: 10:00-20:00
+Вт: 10:00-20:00
+Ср: 10:00-20:00
+Чт: 10:00-20:00
+Пт: 10:00-20:00
+Сб: 10:00-20:00
+Нд: 10:00-20:00</t>
+        </is>
+      </c>
+      <c r="J1192" t="inlineStr">
+        <is>
+          <t>м. Київ</t>
+        </is>
+      </c>
+    </row>
+    <row r="1193">
+      <c r="A1193" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1193" t="n">
+        <v>3556</v>
+      </c>
+      <c r="C1193" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1193" t="inlineStr">
+        <is>
+          <t>вул Шевченка 42</t>
+        </is>
+      </c>
+      <c r="E1193" t="inlineStr">
+        <is>
+          <t>Овруч</t>
+        </is>
+      </c>
+      <c r="F1193" t="inlineStr">
+        <is>
+          <t>Житомирська</t>
+        </is>
+      </c>
+      <c r="G1193" t="n">
+        <v>51.3197441</v>
+      </c>
+      <c r="H1193" t="n">
+        <v>28.8004248</v>
+      </c>
+      <c r="I1193" t="inlineStr">
+        <is>
+          <t>Пн: 09:00-18:00
+Вт: 09:00-18:00
+Ср: 09:00-18:00
+Чт: 09:00-18:00
+Пт: 09:00-18:00
+Сб: 09:00-18:00
+Нд: 09:00-18:00</t>
+        </is>
+      </c>
+      <c r="J1193" t="inlineStr">
+        <is>
+          <t>Житомирська</t>
+        </is>
+      </c>
+    </row>
+    <row r="1194">
+      <c r="A1194" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1194" t="n">
+        <v>3558</v>
+      </c>
+      <c r="C1194" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1194" t="inlineStr">
+        <is>
+          <t>вул Київська 26</t>
+        </is>
+      </c>
+      <c r="E1194" t="inlineStr">
+        <is>
+          <t>Іванків</t>
+        </is>
+      </c>
+      <c r="F1194" t="inlineStr">
+        <is>
+          <t>Kiev</t>
+        </is>
+      </c>
+      <c r="G1194" t="n">
+        <v>50.9338356</v>
+      </c>
+      <c r="H1194" t="n">
+        <v>29.9031381</v>
+      </c>
+      <c r="I1194" t="inlineStr">
+        <is>
+          <t>Пн: 08:00-18:00
+Вт: 08:00-18:00
+Ср: 08:00-18:00
+Чт: 08:00-18:00
+Пт: 08:00-18:00
+Сб: 08:00-18:00
+Нд: 09:00-17:00</t>
+        </is>
+      </c>
+      <c r="J1194" t="inlineStr">
+        <is>
+          <t>Kiev</t>
+        </is>
+      </c>
+    </row>
+    <row r="1195">
+      <c r="A1195" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1195" t="n">
+        <v>3559</v>
+      </c>
+      <c r="C1195" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1195" t="inlineStr">
+        <is>
+          <t>просп Соборний 51</t>
+        </is>
+      </c>
+      <c r="E1195" t="inlineStr">
+        <is>
+          <t>Запоріжжя</t>
+        </is>
+      </c>
+      <c r="F1195" t="inlineStr">
+        <is>
+          <t>Zaporizhia</t>
+        </is>
+      </c>
+      <c r="G1195" t="n">
+        <v>47.8176164</v>
+      </c>
+      <c r="H1195" t="n">
+        <v>35.1753352</v>
+      </c>
+      <c r="I1195" t="inlineStr">
+        <is>
+          <t>Пн: 09:00-19:00
+Вт: 09:00-19:00
+Ср: 09:00-19:00
+Чт: 09:00-19:00
+Пт: 09:00-19:00
+Сб: 09:00-19:00
+Нд: 10:00-18:00</t>
+        </is>
+      </c>
+      <c r="J1195" t="inlineStr">
+        <is>
+          <t>Zaporizhia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1196">
+      <c r="A1196" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1196" t="n">
+        <v>3560</v>
+      </c>
+      <c r="C1196" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1196" t="inlineStr">
+        <is>
+          <t>вул Палацова 9</t>
+        </is>
+      </c>
+      <c r="E1196" t="inlineStr">
+        <is>
+          <t>Краматорськ</t>
+        </is>
+      </c>
+      <c r="F1196" t="inlineStr">
+        <is>
+          <t>Донецька</t>
+        </is>
+      </c>
+      <c r="G1196" t="n">
+        <v>48.7366237</v>
+      </c>
+      <c r="H1196" t="n">
+        <v>37.5916381</v>
+      </c>
+      <c r="I1196" t="inlineStr">
+        <is>
+          <t>Пн: 09:00-17:00
+Вт: 09:00-17:00
+Ср: 09:00-17:00
+Чт: 09:00-17:00
+Пт: 09:00-17:00
+Сб: 09:00-17:00
+Нд: 09:00-17:00</t>
+        </is>
+      </c>
+      <c r="J1196" t="inlineStr">
+        <is>
+          <t>Донецька</t>
+        </is>
+      </c>
+    </row>
+    <row r="1197">
+      <c r="A1197" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1197" t="n">
+        <v>3561</v>
+      </c>
+      <c r="C1197" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1197" t="inlineStr">
+        <is>
+          <t>вул Ф. Караманець (Ватутіна) 29</t>
+        </is>
+      </c>
+      <c r="E1197" t="inlineStr">
+        <is>
+          <t>Кривий Ріг</t>
+        </is>
+      </c>
+      <c r="F1197" t="inlineStr">
+        <is>
+          <t>Дніпропетровська</t>
+        </is>
+      </c>
+      <c r="G1197" t="n">
+        <v>48.024687</v>
+      </c>
+      <c r="H1197" t="n">
+        <v>33.4709468</v>
+      </c>
+      <c r="I1197" t="inlineStr">
+        <is>
+          <t>Пн: 09:00-18:00
+Вт: 09:00-18:00
+Ср: 09:00-18:00
+Чт: 09:00-18:00
+Пт: 09:00-18:00
+Сб: Вихідний
+Нд: Вихідний</t>
+        </is>
+      </c>
+      <c r="J1197" t="inlineStr">
+        <is>
+          <t>Дніпропетровська</t>
+        </is>
+      </c>
+    </row>
+    <row r="1198">
+      <c r="A1198" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1198" t="n">
+        <v>3563</v>
+      </c>
+      <c r="C1198" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1198" t="inlineStr">
+        <is>
+          <t>вул Шевченка 116</t>
+        </is>
+      </c>
+      <c r="E1198" t="inlineStr">
+        <is>
+          <t>Дунаївці</t>
+        </is>
+      </c>
+      <c r="F1198" t="inlineStr">
+        <is>
+          <t>Хмельницька</t>
+        </is>
+      </c>
+      <c r="G1198" t="n">
+        <v>48.8922754</v>
+      </c>
+      <c r="H1198" t="n">
+        <v>26.8568241</v>
+      </c>
+      <c r="I1198" t="inlineStr">
+        <is>
+          <t>Пн: 09:00-18:00
+Вт: 09:00-18:00
+Ср: 09:00-18:00
+Чт: 09:00-18:00
+Пт: 09:00-18:00
+Сб: 09:00-14:00
+Нд: Вихідний</t>
+        </is>
+      </c>
+      <c r="J1198" t="inlineStr">
+        <is>
+          <t>Хмельницька</t>
+        </is>
+      </c>
+    </row>
+    <row r="1199">
+      <c r="A1199" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1199" t="n">
+        <v>3566</v>
+      </c>
+      <c r="C1199" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1199" t="inlineStr">
+        <is>
+          <t>вул Р. Шухевича 1а</t>
+        </is>
+      </c>
+      <c r="E1199" t="inlineStr">
+        <is>
+          <t>Хмельницький</t>
+        </is>
+      </c>
+      <c r="F1199" t="inlineStr">
+        <is>
+          <t>Хмельницька</t>
+        </is>
+      </c>
+      <c r="G1199" t="n">
+        <v>49.4360713</v>
+      </c>
+      <c r="H1199" t="n">
+        <v>26.9572295</v>
+      </c>
+      <c r="I1199" t="inlineStr">
+        <is>
+          <t>Пн: 09:00-19:00
+Вт: 09:00-19:00
+Ср: 09:00-19:00
+Чт: 09:00-19:00
+Пт: 09:00-19:00
+Сб: 10:00-18:00
+Нд: 10:00-18:00</t>
+        </is>
+      </c>
+      <c r="J1199" t="inlineStr">
+        <is>
+          <t>Хмельницька</t>
+        </is>
+      </c>
+    </row>
+    <row r="1200">
+      <c r="A1200" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1200" t="n">
+        <v>3567</v>
+      </c>
+      <c r="C1200" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1200" t="inlineStr">
+        <is>
+          <t>вул Макухи 1</t>
+        </is>
+      </c>
+      <c r="E1200" t="inlineStr">
+        <is>
+          <t>Тлумач</t>
+        </is>
+      </c>
+      <c r="F1200" t="inlineStr">
+        <is>
+          <t>Івано-Франківська</t>
+        </is>
+      </c>
+      <c r="G1200" t="n">
+        <v>48.8652727</v>
+      </c>
+      <c r="H1200" t="n">
+        <v>25.0043864</v>
+      </c>
+      <c r="I1200" t="inlineStr">
+        <is>
+          <t>Пн: 09:00-17:00
+Вт: 09:00-17:00
+Ср: 09:00-17:00
+Чт: 09:00-17:00
+Пт: 09:00-17:00
+Сб: Вихідний
+Нд: Вихідний</t>
+        </is>
+      </c>
+      <c r="J1200" t="inlineStr">
+        <is>
+          <t>Івано-Франківська</t>
+        </is>
+      </c>
+    </row>
+    <row r="1201">
+      <c r="A1201" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1201" t="n">
+        <v>3568</v>
+      </c>
+      <c r="C1201" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1201" t="inlineStr">
+        <is>
+          <t>вул Андріївська 5</t>
+        </is>
+      </c>
+      <c r="E1201" t="inlineStr">
+        <is>
+          <t>Березне</t>
+        </is>
+      </c>
+      <c r="F1201" t="inlineStr">
+        <is>
+          <t>Рівненська</t>
+        </is>
+      </c>
+      <c r="G1201" t="n">
+        <v>51.0019955</v>
+      </c>
+      <c r="H1201" t="n">
+        <v>26.7547284</v>
+      </c>
+      <c r="I1201" t="inlineStr">
+        <is>
+          <t>Пн: 09:00-18:00
+Вт: 09:00-18:00
+Ср: 09:00-18:00
+Чт: 09:00-18:00
+Пт: 09:00-18:00
+Сб: 09:00-16:00
+Нд: 09:00-16:00</t>
+        </is>
+      </c>
+      <c r="J1201" t="inlineStr">
+        <is>
+          <t>Рівненська</t>
+        </is>
+      </c>
+    </row>
+    <row r="1202">
+      <c r="A1202" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1202" t="n">
+        <v>3569</v>
+      </c>
+      <c r="C1202" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1202" t="inlineStr">
+        <is>
+          <t>вул Широка 37</t>
+        </is>
+      </c>
+      <c r="E1202" t="inlineStr">
+        <is>
+          <t>Сарни</t>
+        </is>
+      </c>
+      <c r="F1202" t="inlineStr">
+        <is>
+          <t>Рівненська</t>
+        </is>
+      </c>
+      <c r="G1202" t="n">
+        <v>51.3355537</v>
+      </c>
+      <c r="H1202" t="n">
+        <v>26.6158412</v>
+      </c>
+      <c r="I1202" t="inlineStr">
+        <is>
+          <t>Пн: 09:00-18:00
+Вт: 09:00-18:00
+Ср: 09:00-18:00
+Чт: 09:00-18:00
+Пт: 09:00-18:00
+Сб: 09:00-18:00
+Нд: 09:00-17:00</t>
+        </is>
+      </c>
+      <c r="J1202" t="inlineStr">
+        <is>
+          <t>Рівненська</t>
+        </is>
+      </c>
+    </row>
+    <row r="1203">
+      <c r="A1203" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1203" t="n">
+        <v>3570</v>
+      </c>
+      <c r="C1203" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1203" t="inlineStr">
+        <is>
+          <t>вул Січових Стрільців 33А</t>
+        </is>
+      </c>
+      <c r="E1203" t="inlineStr">
+        <is>
+          <t>Бурштин</t>
+        </is>
+      </c>
+      <c r="F1203" t="inlineStr">
+        <is>
+          <t>Івано-Франківська</t>
+        </is>
+      </c>
+      <c r="G1203" t="n">
+        <v>49.2511835</v>
+      </c>
+      <c r="H1203" t="n">
+        <v>24.6288295</v>
+      </c>
+      <c r="I1203" t="inlineStr">
+        <is>
+          <t>Пн: 09:00-18:00
+Вт: 09:00-18:00
+Ср: 09:00-18:00
+Чт: 09:00-18:00
+Пт: 09:00-18:00
+Сб: 09:00-17:00
+Нд: Вихідний</t>
+        </is>
+      </c>
+      <c r="J1203" t="inlineStr">
+        <is>
+          <t>Івано-Франківська</t>
+        </is>
+      </c>
+    </row>
+    <row r="1204">
+      <c r="A1204" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1204" t="n">
+        <v>3571</v>
+      </c>
+      <c r="C1204" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1204" t="inlineStr">
+        <is>
+          <t>вул Небесної Сотні 85</t>
+        </is>
+      </c>
+      <c r="E1204" t="inlineStr">
+        <is>
+          <t>Романів</t>
+        </is>
+      </c>
+      <c r="F1204" t="inlineStr">
+        <is>
+          <t>Житомирська</t>
+        </is>
+      </c>
+      <c r="G1204" t="n">
+        <v>50.141605</v>
+      </c>
+      <c r="H1204" t="n">
+        <v>27.934655</v>
+      </c>
+      <c r="I1204" t="inlineStr">
+        <is>
+          <t>Пн: 08:00-18:00
+Вт: 08:00-18:00
+Ср: 08:00-18:00
+Чт: 08:00-18:00
+Пт: 08:00-18:00
+Сб: 08:00-17:00
+Нд: 09:00-17:00</t>
+        </is>
+      </c>
+      <c r="J1204" t="inlineStr">
+        <is>
+          <t>Житомирська</t>
+        </is>
+      </c>
+    </row>
+    <row r="1205">
+      <c r="A1205" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1205" t="n">
+        <v>3573</v>
+      </c>
+      <c r="C1205" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1205" t="inlineStr">
+        <is>
+          <t>вул Велика Окружна 4</t>
+        </is>
+      </c>
+      <c r="E1205" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="F1205" t="inlineStr">
+        <is>
+          <t>Kiev</t>
+        </is>
+      </c>
+      <c r="G1205" t="n">
+        <v>50.4295904</v>
+      </c>
+      <c r="H1205" t="n">
+        <v>30.3567847</v>
+      </c>
+      <c r="I1205" t="inlineStr">
+        <is>
+          <t>Пн: 10:00-21:00
+Вт: 10:00-21:00
+Ср: 10:00-21:00
+Чт: 10:00-21:00
+Пт: 10:00-21:00
+Сб: 10:00-21:00
+Нд: 10:00-21:00</t>
+        </is>
+      </c>
+      <c r="J1205" t="inlineStr">
+        <is>
+          <t>Kiev</t>
+        </is>
+      </c>
+    </row>
+    <row r="1206">
+      <c r="A1206" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1206" t="n">
+        <v>3574</v>
+      </c>
+      <c r="C1206" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1206" t="inlineStr">
+        <is>
+          <t>вул Шевченка 50</t>
+        </is>
+      </c>
+      <c r="E1206" t="inlineStr">
+        <is>
+          <t>Богородчани</t>
+        </is>
+      </c>
+      <c r="F1206" t="inlineStr">
+        <is>
+          <t>Івано-Франківська</t>
+        </is>
+      </c>
+      <c r="G1206" t="n">
+        <v>48.809756</v>
+      </c>
+      <c r="H1206" t="n">
+        <v>24.5400082</v>
+      </c>
+      <c r="I1206" t="inlineStr">
+        <is>
+          <t>Пн: 09:00-18:00
+Вт: 09:00-18:00
+Ср: 09:00-18:00
+Чт: 09:00-18:00
+Пт: 09:00-18:00
+Сб: 09:00-17:00
+Нд: 10:00-16:00</t>
+        </is>
+      </c>
+      <c r="J1206" t="inlineStr">
+        <is>
+          <t>Івано-Франківська</t>
+        </is>
+      </c>
+    </row>
+    <row r="1207">
+      <c r="A1207" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1207" t="n">
+        <v>3575</v>
+      </c>
+      <c r="C1207" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1207" t="inlineStr">
+        <is>
+          <t>просп Богдана Хмельницкого (Героїв Сталінграда) 118Д</t>
+        </is>
+      </c>
+      <c r="E1207" t="inlineStr">
+        <is>
+          <t>Дніпро</t>
+        </is>
+      </c>
+      <c r="F1207" t="inlineStr">
+        <is>
+          <t>Дніпропетровська</t>
+        </is>
+      </c>
+      <c r="G1207" t="n">
+        <v>48.4076054</v>
+      </c>
+      <c r="H1207" t="n">
+        <v>35.0004028</v>
+      </c>
+      <c r="I1207" t="inlineStr">
+        <is>
+          <t>Пн: 09:00-19:00
+Вт: 09:00-19:00
+Ср: 09:00-19:00
+Чт: 09:00-19:00
+Пт: 09:00-19:00
+Сб: 09:00-19:00
+Нд: 09:00-19:00</t>
+        </is>
+      </c>
+      <c r="J1207" t="inlineStr">
+        <is>
+          <t>Дніпропетровська</t>
+        </is>
+      </c>
+    </row>
+    <row r="1208">
+      <c r="A1208" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1208" t="n">
+        <v>3576</v>
+      </c>
+      <c r="C1208" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1208" t="inlineStr">
+        <is>
+          <t>вул Грушевського 41А</t>
+        </is>
+      </c>
+      <c r="E1208" t="inlineStr">
+        <is>
+          <t>Первомайськ</t>
+        </is>
+      </c>
+      <c r="F1208" t="inlineStr">
+        <is>
+          <t>Миколаївська</t>
+        </is>
+      </c>
+      <c r="G1208" t="n">
+        <v>48.0425652</v>
+      </c>
+      <c r="H1208" t="n">
+        <v>30.8444596</v>
+      </c>
+      <c r="I1208" t="inlineStr">
+        <is>
+          <t>Пн: 08:00-18:00
+Вт: 08:00-18:00
+Ср: Вихідний
+Чт: Вихідний
+Пт: 08:00-18:00
+Сб: 08:00-18:00
+Нд: 08:00-16:00</t>
+        </is>
+      </c>
+      <c r="J1208" t="inlineStr">
+        <is>
+          <t>Миколаївська</t>
+        </is>
+      </c>
+    </row>
+    <row r="1209">
+      <c r="A1209" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1209" t="n">
+        <v>3577</v>
+      </c>
+      <c r="C1209" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1209" t="inlineStr">
+        <is>
           <t>вул Харківська 2/2</t>
         </is>
       </c>
-      <c r="E1155" t="inlineStr">
+      <c r="E1209" t="inlineStr">
         <is>
           <t>Суми</t>
         </is>
       </c>
-      <c r="F1155" t="inlineStr">
+      <c r="F1209" t="inlineStr">
         <is>
           <t>Сумська</t>
         </is>
       </c>
-      <c r="G1155" t="n">
+      <c r="G1209" t="n">
         <v>50.9041752</v>
       </c>
-      <c r="H1155" t="n">
+      <c r="H1209" t="n">
         <v>34.8048057</v>
       </c>
-      <c r="I1155" t="inlineStr">
+      <c r="I1209" t="inlineStr">
         <is>
           <t>Пн: 10:00-19:00
 Вт: 10:00-19:00
@@ -53360,2817 +56168,9 @@
 Нд: 10:00-19:00</t>
         </is>
       </c>
-      <c r="J1155" t="inlineStr">
+      <c r="J1209" t="inlineStr">
         <is>
           <t>Сумська</t>
-        </is>
-      </c>
-    </row>
-    <row r="1156">
-      <c r="A1156" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1156" t="n">
-        <v>3470</v>
-      </c>
-      <c r="C1156" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1156" t="inlineStr">
-        <is>
-          <t>вул  Хрещатик 13</t>
-        </is>
-      </c>
-      <c r="E1156" t="inlineStr">
-        <is>
-          <t>Київ</t>
-        </is>
-      </c>
-      <c r="F1156" t="inlineStr">
-        <is>
-          <t>м. Київ</t>
-        </is>
-      </c>
-      <c r="G1156" t="n">
-        <v>50.4487897</v>
-      </c>
-      <c r="H1156" t="n">
-        <v>30.5233361</v>
-      </c>
-      <c r="I1156" t="inlineStr">
-        <is>
-          <t>Пн: 10:00-20:00
-Вт: 10:00-20:00
-Ср: 10:00-20:00
-Чт: 10:00-20:00
-Пт: 10:00-20:00
-Сб: 10:00-20:00
-Нд: 10:00-20:00</t>
-        </is>
-      </c>
-      <c r="J1156" t="inlineStr">
-        <is>
-          <t>м. Київ</t>
-        </is>
-      </c>
-    </row>
-    <row r="1157">
-      <c r="A1157" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1157" t="n">
-        <v>3471</v>
-      </c>
-      <c r="C1157" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1157" t="inlineStr">
-        <is>
-          <t>вул Університетська 45</t>
-        </is>
-      </c>
-      <c r="E1157" t="inlineStr">
-        <is>
-          <t>Словянськ</t>
-        </is>
-      </c>
-      <c r="F1157" t="inlineStr">
-        <is>
-          <t>Дніпропетровська</t>
-        </is>
-      </c>
-      <c r="G1157" t="n">
-        <v>48.0008788</v>
-      </c>
-      <c r="H1157" t="n">
-        <v>33.4821954</v>
-      </c>
-      <c r="I1157" t="inlineStr">
-        <is>
-          <t>Пн: 10:00-17:00
-Вт: 10:00-17:00
-Ср: 10:00-17:00
-Чт: 10:00-17:00
-Пт: 10:00-17:00
-Сб: 10:00-16:00
-Нд: Вихідний</t>
-        </is>
-      </c>
-      <c r="J1157" t="inlineStr">
-        <is>
-          <t>Дніпропетровська</t>
-        </is>
-      </c>
-    </row>
-    <row r="1158">
-      <c r="A1158" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1158" t="n">
-        <v>3472</v>
-      </c>
-      <c r="C1158" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1158" t="inlineStr">
-        <is>
-          <t>вул Чернівецька 2Б</t>
-        </is>
-      </c>
-      <c r="E1158" t="inlineStr">
-        <is>
-          <t>Сторожинець</t>
-        </is>
-      </c>
-      <c r="F1158" t="inlineStr">
-        <is>
-          <t>Чернівецька</t>
-        </is>
-      </c>
-      <c r="G1158" t="n">
-        <v>48.1604917</v>
-      </c>
-      <c r="H1158" t="n">
-        <v>25.721244</v>
-      </c>
-      <c r="I1158" t="inlineStr">
-        <is>
-          <t>Пн: 09:00-18:00
-Вт: 09:00-18:00
-Ср: 09:00-18:00
-Чт: 09:00-18:00
-Пт: 09:00-18:00
-Сб: 09:00-15:00
-Нд: Вихідний</t>
-        </is>
-      </c>
-      <c r="J1158" t="inlineStr">
-        <is>
-          <t>Чернівецька</t>
-        </is>
-      </c>
-    </row>
-    <row r="1159">
-      <c r="A1159" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1159" t="n">
-        <v>3474</v>
-      </c>
-      <c r="C1159" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1159" t="inlineStr">
-        <is>
-          <t>вул Нескорених (Героїв Праці) 13</t>
-        </is>
-      </c>
-      <c r="E1159" t="inlineStr">
-        <is>
-          <t>Харків</t>
-        </is>
-      </c>
-      <c r="F1159" t="inlineStr">
-        <is>
-          <t>Харківська</t>
-        </is>
-      </c>
-      <c r="G1159" t="n">
-        <v>50.0254117</v>
-      </c>
-      <c r="H1159" t="n">
-        <v>36.3369339</v>
-      </c>
-      <c r="I1159" t="inlineStr">
-        <is>
-          <t>Пн: 09:00-18:00
-Вт: 09:00-18:00
-Ср: 09:00-18:00
-Чт: 09:00-18:00
-Пт: 09:00-18:00
-Сб: 09:00-17:00
-Нд: 09:00-17:00</t>
-        </is>
-      </c>
-      <c r="J1159" t="inlineStr">
-        <is>
-          <t>Харківська</t>
-        </is>
-      </c>
-    </row>
-    <row r="1160">
-      <c r="A1160" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1160" t="n">
-        <v>3478</v>
-      </c>
-      <c r="C1160" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1160" t="inlineStr">
-        <is>
-          <t>просп Європейського Союзу (Правди) 58</t>
-        </is>
-      </c>
-      <c r="E1160" t="inlineStr">
-        <is>
-          <t>Київ</t>
-        </is>
-      </c>
-      <c r="F1160" t="inlineStr">
-        <is>
-          <t>Kiev</t>
-        </is>
-      </c>
-      <c r="G1160" t="n">
-        <v>50.5047315</v>
-      </c>
-      <c r="H1160" t="n">
-        <v>30.4374307</v>
-      </c>
-      <c r="I1160" t="inlineStr">
-        <is>
-          <t>Пн: 09:00-21:00
-Вт: 09:00-21:00
-Ср: 09:00-21:00
-Чт: 09:00-21:00
-Пт: 09:00-21:00
-Сб: 09:00-21:00
-Нд: 09:00-21:00</t>
-        </is>
-      </c>
-      <c r="J1160" t="inlineStr">
-        <is>
-          <t>Kiev</t>
-        </is>
-      </c>
-    </row>
-    <row r="1161">
-      <c r="A1161" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1161" t="n">
-        <v>3479</v>
-      </c>
-      <c r="C1161" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1161" t="inlineStr">
-        <is>
-          <t>вул Європейського Союзу (Правди) 47</t>
-        </is>
-      </c>
-      <c r="E1161" t="inlineStr">
-        <is>
-          <t>Київ</t>
-        </is>
-      </c>
-      <c r="F1161" t="inlineStr">
-        <is>
-          <t>м. Київ</t>
-        </is>
-      </c>
-      <c r="G1161" t="n">
-        <v>50.5037667</v>
-      </c>
-      <c r="H1161" t="n">
-        <v>30.419093</v>
-      </c>
-      <c r="I1161" t="inlineStr">
-        <is>
-          <t>Пн: 10:00-22:00
-Вт: 10:00-22:00
-Ср: 10:00-22:00
-Чт: 10:00-22:00
-Пт: 10:00-22:00
-Сб: 10:00-22:00
-Нд: 10:00-22:00</t>
-        </is>
-      </c>
-      <c r="J1161" t="inlineStr">
-        <is>
-          <t>м. Київ</t>
-        </is>
-      </c>
-    </row>
-    <row r="1162">
-      <c r="A1162" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1162" t="n">
-        <v>3483</v>
-      </c>
-      <c r="C1162" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1162" t="inlineStr">
-        <is>
-          <t>просп Коцюбинського 19</t>
-        </is>
-      </c>
-      <c r="E1162" t="inlineStr">
-        <is>
-          <t>Вінниця</t>
-        </is>
-      </c>
-      <c r="F1162" t="inlineStr">
-        <is>
-          <t>Vinnyts'ka</t>
-        </is>
-      </c>
-      <c r="G1162" t="n">
-        <v>49.239071</v>
-      </c>
-      <c r="H1162" t="n">
-        <v>28.4981039</v>
-      </c>
-      <c r="I1162" t="inlineStr">
-        <is>
-          <t>Пн: 08:00-18:00
-Вт: 08:00-18:00
-Ср: 08:00-18:00
-Чт: 08:00-18:00
-Пт: 08:00-18:00
-Сб: 09:00-17:00
-Нд: 09:00-17:00</t>
-        </is>
-      </c>
-      <c r="J1162" t="inlineStr">
-        <is>
-          <t>Vinnyts'ka</t>
-        </is>
-      </c>
-    </row>
-    <row r="1163">
-      <c r="A1163" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1163" t="n">
-        <v>3485</v>
-      </c>
-      <c r="C1163" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1163" t="inlineStr">
-        <is>
-          <t>вул Котляра (був. Червоноармійська) 8/10</t>
-        </is>
-      </c>
-      <c r="E1163" t="inlineStr">
-        <is>
-          <t>Харків</t>
-        </is>
-      </c>
-      <c r="F1163" t="inlineStr">
-        <is>
-          <t>Харківська</t>
-        </is>
-      </c>
-      <c r="G1163" t="n">
-        <v>49.9892648</v>
-      </c>
-      <c r="H1163" t="n">
-        <v>36.2077698</v>
-      </c>
-      <c r="I1163" t="inlineStr">
-        <is>
-          <t>Пн: 09:00-18:00
-Вт: 09:00-18:00
-Ср: 09:00-18:00
-Чт: 09:00-18:00
-Пт: 09:00-18:00
-Сб: 09:00-18:00
-Нд: 09:00-17:00</t>
-        </is>
-      </c>
-      <c r="J1163" t="inlineStr">
-        <is>
-          <t>Харківська</t>
-        </is>
-      </c>
-    </row>
-    <row r="1164">
-      <c r="A1164" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1164" t="n">
-        <v>3491</v>
-      </c>
-      <c r="C1164" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1164" t="inlineStr">
-        <is>
-          <t>вул Інститутська 10</t>
-        </is>
-      </c>
-      <c r="E1164" t="inlineStr">
-        <is>
-          <t>Хмельницький</t>
-        </is>
-      </c>
-      <c r="F1164" t="inlineStr">
-        <is>
-          <t>Хмельницька</t>
-        </is>
-      </c>
-      <c r="G1164" t="n">
-        <v>49.4098499</v>
-      </c>
-      <c r="H1164" t="n">
-        <v>26.9605436</v>
-      </c>
-      <c r="I1164" t="inlineStr">
-        <is>
-          <t>Пн: 09:00-19:00
-Вт: 09:00-19:00
-Ср: 09:00-19:00
-Чт: 09:00-19:00
-Пт: 09:00-19:00
-Сб: 10:00-18:00
-Нд: 10:00-18:00</t>
-        </is>
-      </c>
-      <c r="J1164" t="inlineStr">
-        <is>
-          <t>Хмельницька</t>
-        </is>
-      </c>
-    </row>
-    <row r="1165">
-      <c r="A1165" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1165" t="n">
-        <v>3494</v>
-      </c>
-      <c r="C1165" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1165" t="inlineStr">
-        <is>
-          <t>вул Шевченків Шлях 144-А</t>
-        </is>
-      </c>
-      <c r="E1165" t="inlineStr">
-        <is>
-          <t>Березань</t>
-        </is>
-      </c>
-      <c r="F1165" t="inlineStr">
-        <is>
-          <t>Kiev</t>
-        </is>
-      </c>
-      <c r="G1165" t="n">
-        <v>50.3119113</v>
-      </c>
-      <c r="H1165" t="n">
-        <v>31.4678577</v>
-      </c>
-      <c r="I1165" t="inlineStr">
-        <is>
-          <t>Пн: 09:00-17:00
-Вт: 09:00-17:00
-Ср: 09:00-17:00
-Чт: 09:00-17:00
-Пт: 09:00-17:00
-Сб: 10:00-16:00
-Нд: 10:00-16:00</t>
-        </is>
-      </c>
-      <c r="J1165" t="inlineStr">
-        <is>
-          <t>Kiev</t>
-        </is>
-      </c>
-    </row>
-    <row r="1166">
-      <c r="A1166" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1166" t="n">
-        <v>3495</v>
-      </c>
-      <c r="C1166" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1166" t="inlineStr">
-        <is>
-          <t>вул Міцкевича 1</t>
-        </is>
-      </c>
-      <c r="E1166" t="inlineStr">
-        <is>
-          <t>Борислав</t>
-        </is>
-      </c>
-      <c r="F1166" t="inlineStr">
-        <is>
-          <t>Львівська</t>
-        </is>
-      </c>
-      <c r="G1166" t="n">
-        <v>49.287286</v>
-      </c>
-      <c r="H1166" t="n">
-        <v>23.4159004</v>
-      </c>
-      <c r="I1166" t="inlineStr">
-        <is>
-          <t>Пн: 09:00-18:00
-Вт: 09:00-18:00
-Ср: 09:00-18:00
-Чт: 09:00-18:00
-Пт: 09:00-18:00
-Сб: 09:00-17:00
-Нд: 10:00-17:00</t>
-        </is>
-      </c>
-      <c r="J1166" t="inlineStr">
-        <is>
-          <t>Львівська</t>
-        </is>
-      </c>
-    </row>
-    <row r="1167">
-      <c r="A1167" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1167" t="n">
-        <v>3496</v>
-      </c>
-      <c r="C1167" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1167" t="inlineStr">
-        <is>
-          <t>вул І.Франка 1</t>
-        </is>
-      </c>
-      <c r="E1167" t="inlineStr">
-        <is>
-          <t>Верховина</t>
-        </is>
-      </c>
-      <c r="F1167" t="inlineStr">
-        <is>
-          <t>Івано-Франківська</t>
-        </is>
-      </c>
-      <c r="G1167" t="n">
-        <v>48.1549768</v>
-      </c>
-      <c r="H1167" t="n">
-        <v>24.8291227</v>
-      </c>
-      <c r="I1167" t="inlineStr">
-        <is>
-          <t>Пн: 09:00-18:00
-Вт: 09:00-18:00
-Ср: 09:00-18:00
-Чт: 09:00-18:00
-Пт: 09:00-18:00
-Сб: 09:00-17:00
-Нд: 10:00-16:00</t>
-        </is>
-      </c>
-      <c r="J1167" t="inlineStr">
-        <is>
-          <t>Івано-Франківська</t>
-        </is>
-      </c>
-    </row>
-    <row r="1168">
-      <c r="A1168" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1168" t="n">
-        <v>3498</v>
-      </c>
-      <c r="C1168" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1168" t="inlineStr">
-        <is>
-          <t>просп Олександра Поля 1/9</t>
-        </is>
-      </c>
-      <c r="E1168" t="inlineStr">
-        <is>
-          <t>Дніпро</t>
-        </is>
-      </c>
-      <c r="F1168" t="inlineStr">
-        <is>
-          <t>Дніпропетровська</t>
-        </is>
-      </c>
-      <c r="G1168" t="n">
-        <v>48.4642698</v>
-      </c>
-      <c r="H1168" t="n">
-        <v>35.0290126</v>
-      </c>
-      <c r="I1168" t="inlineStr">
-        <is>
-          <t>Пн: 09:00-19:00
-Вт: 09:00-19:00
-Ср: 09:00-19:00
-Чт: 09:00-19:00
-Пт: 09:00-19:00
-Сб: 09:00-19:00
-Нд: 09:00-18:00</t>
-        </is>
-      </c>
-      <c r="J1168" t="inlineStr">
-        <is>
-          <t>Дніпропетровська</t>
-        </is>
-      </c>
-    </row>
-    <row r="1169">
-      <c r="A1169" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1169" t="n">
-        <v>3501</v>
-      </c>
-      <c r="C1169" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1169" t="inlineStr">
-        <is>
-          <t>просп Дмитра Яворницького (К.Маркса) 65</t>
-        </is>
-      </c>
-      <c r="E1169" t="inlineStr">
-        <is>
-          <t>Дніпро</t>
-        </is>
-      </c>
-      <c r="F1169" t="inlineStr">
-        <is>
-          <t>Дніпропетровська</t>
-        </is>
-      </c>
-      <c r="G1169" t="n">
-        <v>48.4647786</v>
-      </c>
-      <c r="H1169" t="n">
-        <v>35.0447223</v>
-      </c>
-      <c r="I1169" t="inlineStr">
-        <is>
-          <t>Пн: 09:00-19:00
-Вт: 09:00-19:00
-Ср: 09:00-19:00
-Чт: 09:00-19:00
-Пт: 09:00-19:00
-Сб: 09:00-18:00
-Нд: 09:00-18:00</t>
-        </is>
-      </c>
-      <c r="J1169" t="inlineStr">
-        <is>
-          <t>Дніпропетровська</t>
-        </is>
-      </c>
-    </row>
-    <row r="1170">
-      <c r="A1170" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1170" t="n">
-        <v>3503</v>
-      </c>
-      <c r="C1170" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1170" t="inlineStr">
-        <is>
-          <t>вул Привокзальна 3</t>
-        </is>
-      </c>
-      <c r="E1170" t="inlineStr">
-        <is>
-          <t>Київ</t>
-        </is>
-      </c>
-      <c r="F1170" t="inlineStr">
-        <is>
-          <t>Kiev</t>
-        </is>
-      </c>
-      <c r="G1170" t="n">
-        <v>50.4305963</v>
-      </c>
-      <c r="H1170" t="n">
-        <v>30.6518096</v>
-      </c>
-      <c r="I1170" t="inlineStr">
-        <is>
-          <t>Пн: 10:00-17:00
-Вт: 10:00-17:00
-Ср: 10:00-17:00
-Чт: 10:00-17:00
-Пт: 10:00-17:00
-Сб: 10:00-17:00
-Нд: 10:00-17:00</t>
-        </is>
-      </c>
-      <c r="J1170" t="inlineStr">
-        <is>
-          <t>Kiev</t>
-        </is>
-      </c>
-    </row>
-    <row r="1171">
-      <c r="A1171" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1171" t="n">
-        <v>3505</v>
-      </c>
-      <c r="C1171" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1171" t="inlineStr">
-        <is>
-          <t>пл Шевченка 26</t>
-        </is>
-      </c>
-      <c r="E1171" t="inlineStr">
-        <is>
-          <t>Коломия</t>
-        </is>
-      </c>
-      <c r="F1171" t="inlineStr">
-        <is>
-          <t>Івано-Франківська</t>
-        </is>
-      </c>
-      <c r="G1171" t="n">
-        <v>48.5249278</v>
-      </c>
-      <c r="H1171" t="n">
-        <v>25.0375409</v>
-      </c>
-      <c r="I1171" t="inlineStr">
-        <is>
-          <t>Пн: 09:00-18:00
-Вт: 09:00-18:00
-Ср: 09:00-18:00
-Чт: 09:00-18:00
-Пт: 09:00-18:00
-Сб: 09:00-18:00
-Нд: 10:00-17:00</t>
-        </is>
-      </c>
-      <c r="J1171" t="inlineStr">
-        <is>
-          <t>Івано-Франківська</t>
-        </is>
-      </c>
-    </row>
-    <row r="1172">
-      <c r="A1172" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1172" t="n">
-        <v>3506</v>
-      </c>
-      <c r="C1172" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1172" t="inlineStr">
-        <is>
-          <t>вул Медова 5</t>
-        </is>
-      </c>
-      <c r="E1172" t="inlineStr">
-        <is>
-          <t>Кремeнець</t>
-        </is>
-      </c>
-      <c r="F1172" t="inlineStr">
-        <is>
-          <t>Тернопільська</t>
-        </is>
-      </c>
-      <c r="G1172" t="n">
-        <v>50.095605</v>
-      </c>
-      <c r="H1172" t="n">
-        <v>25.7259463</v>
-      </c>
-      <c r="I1172" t="inlineStr">
-        <is>
-          <t>Пн: 09:00-19:00
-Вт: 09:00-19:00
-Ср: 09:00-19:00
-Чт: 09:00-19:00
-Пт: 09:00-19:00
-Сб: 10:00-16:00
-Нд: 10:00-16:00</t>
-        </is>
-      </c>
-      <c r="J1172" t="inlineStr">
-        <is>
-          <t>Тернопільська</t>
-        </is>
-      </c>
-    </row>
-    <row r="1173">
-      <c r="A1173" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1173" t="n">
-        <v>3508</v>
-      </c>
-      <c r="C1173" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1173" t="inlineStr">
-        <is>
-          <t>вул Шевченка 100</t>
-        </is>
-      </c>
-      <c r="E1173" t="inlineStr">
-        <is>
-          <t>Люботин</t>
-        </is>
-      </c>
-      <c r="F1173" t="inlineStr">
-        <is>
-          <t>Харківська</t>
-        </is>
-      </c>
-      <c r="G1173" t="n">
-        <v>49.9407992</v>
-      </c>
-      <c r="H1173" t="n">
-        <v>35.9262566</v>
-      </c>
-      <c r="I1173" t="inlineStr">
-        <is>
-          <t>Пн: 08:00-18:00
-Вт: 08:00-18:00
-Ср: 08:00-18:00
-Чт: 08:00-18:00
-Пт: 08:00-18:00
-Сб: 08:00-18:00
-Нд: 08:00-16:00</t>
-        </is>
-      </c>
-      <c r="J1173" t="inlineStr">
-        <is>
-          <t>Харківська</t>
-        </is>
-      </c>
-    </row>
-    <row r="1174">
-      <c r="A1174" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1174" t="n">
-        <v>3510</v>
-      </c>
-      <c r="C1174" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1174" t="inlineStr">
-        <is>
-          <t>вул Петропавлівська 49</t>
-        </is>
-      </c>
-      <c r="E1174" t="inlineStr">
-        <is>
-          <t>Суми</t>
-        </is>
-      </c>
-      <c r="F1174" t="inlineStr">
-        <is>
-          <t>Сумська</t>
-        </is>
-      </c>
-      <c r="G1174" t="n">
-        <v>50.9065729</v>
-      </c>
-      <c r="H1174" t="n">
-        <v>34.796901</v>
-      </c>
-      <c r="I1174" t="inlineStr">
-        <is>
-          <t>Пн: 09:00-18:00
-Вт: 09:00-18:00
-Ср: 09:00-18:00
-Чт: 09:00-18:00
-Пт: 09:00-18:00
-Сб: 09:00-18:00
-Нд: 09:00-18:00</t>
-        </is>
-      </c>
-      <c r="J1174" t="inlineStr">
-        <is>
-          <t>Сумська</t>
-        </is>
-      </c>
-    </row>
-    <row r="1175">
-      <c r="A1175" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1175" t="n">
-        <v>3512</v>
-      </c>
-      <c r="C1175" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1175" t="inlineStr">
-        <is>
-          <t>вул Валентинівська (Блюхера) 37/128</t>
-        </is>
-      </c>
-      <c r="E1175" t="inlineStr">
-        <is>
-          <t>Харків</t>
-        </is>
-      </c>
-      <c r="F1175" t="inlineStr">
-        <is>
-          <t>Харківська</t>
-        </is>
-      </c>
-      <c r="G1175" t="n">
-        <v>50.0098371</v>
-      </c>
-      <c r="H1175" t="n">
-        <v>36.3503577</v>
-      </c>
-      <c r="I1175" t="inlineStr">
-        <is>
-          <t>Пн: 09:00-19:00
-Вт: 09:00-19:00
-Ср: 09:00-19:00
-Чт: 09:00-19:00
-Пт: 09:00-19:00
-Сб: 09:00-18:00
-Нд: 09:00-18:00</t>
-        </is>
-      </c>
-      <c r="J1175" t="inlineStr">
-        <is>
-          <t>Харківська</t>
-        </is>
-      </c>
-    </row>
-    <row r="1176">
-      <c r="A1176" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1176" t="n">
-        <v>3514</v>
-      </c>
-      <c r="C1176" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1176" t="inlineStr">
-        <is>
-          <t>вул Центральна 32а</t>
-        </is>
-      </c>
-      <c r="E1176" t="inlineStr">
-        <is>
-          <t>Чемерівці</t>
-        </is>
-      </c>
-      <c r="F1176" t="inlineStr">
-        <is>
-          <t>Хмельницька</t>
-        </is>
-      </c>
-      <c r="G1176" t="n">
-        <v>49.011295</v>
-      </c>
-      <c r="H1176" t="n">
-        <v>26.340395</v>
-      </c>
-      <c r="I1176" t="inlineStr">
-        <is>
-          <t>Пн: 08:00-18:00
-Вт: 08:00-18:00
-Ср: 08:00-18:00
-Чт: 08:00-18:00
-Пт: 08:00-18:00
-Сб: 09:00-16:00
-Нд: 09:00-15:00</t>
-        </is>
-      </c>
-      <c r="J1176" t="inlineStr">
-        <is>
-          <t>Хмельницька</t>
-        </is>
-      </c>
-    </row>
-    <row r="1177">
-      <c r="A1177" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1177" t="n">
-        <v>3516</v>
-      </c>
-      <c r="C1177" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1177" t="inlineStr">
-        <is>
-          <t>просп Відрадний 69/1</t>
-        </is>
-      </c>
-      <c r="E1177" t="inlineStr">
-        <is>
-          <t>Київ</t>
-        </is>
-      </c>
-      <c r="F1177" t="inlineStr">
-        <is>
-          <t>Kiev</t>
-        </is>
-      </c>
-      <c r="G1177" t="n">
-        <v>50.428885</v>
-      </c>
-      <c r="H1177" t="n">
-        <v>30.4309396</v>
-      </c>
-      <c r="I1177" t="inlineStr">
-        <is>
-          <t>Пн: 09:00-18:00
-Вт: 09:00-18:00
-Ср: 09:00-18:00
-Чт: 09:00-18:00
-Пт: 09:00-18:00
-Сб: 10:00-17:00
-Нд: 10:00-17:00</t>
-        </is>
-      </c>
-      <c r="J1177" t="inlineStr">
-        <is>
-          <t>Kiev</t>
-        </is>
-      </c>
-    </row>
-    <row r="1178">
-      <c r="A1178" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1178" t="n">
-        <v>3517</v>
-      </c>
-      <c r="C1178" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1178" t="inlineStr">
-        <is>
-          <t>просп Свободи (Леніна) 16Д</t>
-        </is>
-      </c>
-      <c r="E1178" t="inlineStr">
-        <is>
-          <t>Хмільник</t>
-        </is>
-      </c>
-      <c r="F1178" t="inlineStr">
-        <is>
-          <t>Vinnyts'ka</t>
-        </is>
-      </c>
-      <c r="G1178" t="n">
-        <v>49.5576747</v>
-      </c>
-      <c r="H1178" t="n">
-        <v>27.9528561</v>
-      </c>
-      <c r="I1178" t="inlineStr">
-        <is>
-          <t>Пн: 08:00-17:00
-Вт: 08:00-17:00
-Ср: 08:00-17:00
-Чт: 08:00-17:00
-Пт: 08:00-17:00
-Сб: 08:00-17:00
-Нд: Вихідний</t>
-        </is>
-      </c>
-      <c r="J1178" t="inlineStr">
-        <is>
-          <t>Vinnyts'ka</t>
-        </is>
-      </c>
-    </row>
-    <row r="1179">
-      <c r="A1179" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1179" t="n">
-        <v>3520</v>
-      </c>
-      <c r="C1179" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1179" t="inlineStr">
-        <is>
-          <t>пл Шевченка 6</t>
-        </is>
-      </c>
-      <c r="E1179" t="inlineStr">
-        <is>
-          <t>Славута</t>
-        </is>
-      </c>
-      <c r="F1179" t="inlineStr">
-        <is>
-          <t>Хмельницька</t>
-        </is>
-      </c>
-      <c r="G1179" t="n">
-        <v>50.2957898</v>
-      </c>
-      <c r="H1179" t="n">
-        <v>26.8570458</v>
-      </c>
-      <c r="I1179" t="inlineStr">
-        <is>
-          <t>Пн: 08:00-17:00
-Вт: 08:00-17:00
-Ср: 08:00-17:00
-Чт: 08:00-17:00
-Пт: 08:00-17:00
-Сб: 08:00-17:00
-Нд: 08:00-17:00</t>
-        </is>
-      </c>
-      <c r="J1179" t="inlineStr">
-        <is>
-          <t>Хмельницька</t>
-        </is>
-      </c>
-    </row>
-    <row r="1180">
-      <c r="A1180" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1180" t="n">
-        <v>3526</v>
-      </c>
-      <c r="C1180" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1180" t="inlineStr">
-        <is>
-          <t>вул Незалежності 65</t>
-        </is>
-      </c>
-      <c r="E1180" t="inlineStr">
-        <is>
-          <t>Камянка-Бузька</t>
-        </is>
-      </c>
-      <c r="F1180" t="inlineStr">
-        <is>
-          <t>Львівська</t>
-        </is>
-      </c>
-      <c r="G1180" t="n">
-        <v>50.107376</v>
-      </c>
-      <c r="H1180" t="n">
-        <v>24.3436341</v>
-      </c>
-      <c r="I1180" t="inlineStr">
-        <is>
-          <t>Пн: 09:00-18:00
-Вт: 09:00-18:00
-Ср: 09:00-18:00
-Чт: 09:00-18:00
-Пт: 09:00-18:00
-Сб: 09:00-16:00
-Нд: 09:00-16:00</t>
-        </is>
-      </c>
-      <c r="J1180" t="inlineStr">
-        <is>
-          <t>Львівська</t>
-        </is>
-      </c>
-    </row>
-    <row r="1181">
-      <c r="A1181" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1181" t="n">
-        <v>3530</v>
-      </c>
-      <c r="C1181" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1181" t="inlineStr">
-        <is>
-          <t>вул Савіцького 14</t>
-        </is>
-      </c>
-      <c r="E1181" t="inlineStr">
-        <is>
-          <t>Летичів</t>
-        </is>
-      </c>
-      <c r="F1181" t="inlineStr">
-        <is>
-          <t>Хмельницька</t>
-        </is>
-      </c>
-      <c r="G1181" t="n">
-        <v>49.3813788</v>
-      </c>
-      <c r="H1181" t="n">
-        <v>27.6197046</v>
-      </c>
-      <c r="I1181" t="inlineStr">
-        <is>
-          <t>Пн: 09:00-18:00
-Вт: 09:00-18:00
-Ср: 09:00-18:00
-Чт: 09:00-18:00
-Пт: 09:00-18:00
-Сб: 09:00-18:00
-Нд: 09:00-18:00</t>
-        </is>
-      </c>
-      <c r="J1181" t="inlineStr">
-        <is>
-          <t>Хмельницька</t>
-        </is>
-      </c>
-    </row>
-    <row r="1182">
-      <c r="A1182" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1182" t="n">
-        <v>3531</v>
-      </c>
-      <c r="C1182" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1182" t="inlineStr">
-        <is>
-          <t>вул Берестейський (Перемоги) 26</t>
-        </is>
-      </c>
-      <c r="E1182" t="inlineStr">
-        <is>
-          <t>Київ</t>
-        </is>
-      </c>
-      <c r="F1182" t="inlineStr">
-        <is>
-          <t>м. Київ</t>
-        </is>
-      </c>
-      <c r="G1182" t="n">
-        <v>50.4515345</v>
-      </c>
-      <c r="H1182" t="n">
-        <v>30.4678476</v>
-      </c>
-      <c r="I1182" t="inlineStr">
-        <is>
-          <t>Пн: 10:00-21:00
-Вт: 10:00-21:00
-Ср: 10:00-21:00
-Чт: 10:00-21:00
-Пт: 10:00-21:00
-Сб: 10:00-21:00
-Нд: 10:00-21:00</t>
-        </is>
-      </c>
-      <c r="J1182" t="inlineStr">
-        <is>
-          <t>м. Київ</t>
-        </is>
-      </c>
-    </row>
-    <row r="1183">
-      <c r="A1183" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1183" t="n">
-        <v>3534</v>
-      </c>
-      <c r="C1183" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1183" t="inlineStr">
-        <is>
-          <t>вул Шевченка 74а</t>
-        </is>
-      </c>
-      <c r="E1183" t="inlineStr">
-        <is>
-          <t>Городенка</t>
-        </is>
-      </c>
-      <c r="F1183" t="inlineStr">
-        <is>
-          <t>Івано-Франківська</t>
-        </is>
-      </c>
-      <c r="G1183" t="n">
-        <v>48.66888903427731</v>
-      </c>
-      <c r="H1183" t="n">
-        <v>25.50435338169336</v>
-      </c>
-      <c r="I1183" t="inlineStr">
-        <is>
-          <t>Пн: 08:00-18:00
-Вт: 08:00-18:00
-Ср: 08:00-18:00
-Чт: 08:00-18:00
-Пт: 08:00-18:00
-Сб: 08:00-18:00
-Нд: 10:00-17:00</t>
-        </is>
-      </c>
-      <c r="J1183" t="inlineStr">
-        <is>
-          <t>Івано-Франківська</t>
-        </is>
-      </c>
-    </row>
-    <row r="1184">
-      <c r="A1184" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1184" t="n">
-        <v>3535</v>
-      </c>
-      <c r="C1184" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1184" t="inlineStr">
-        <is>
-          <t>вул Бекетова 21</t>
-        </is>
-      </c>
-      <c r="E1184" t="inlineStr">
-        <is>
-          <t>Харків</t>
-        </is>
-      </c>
-      <c r="F1184" t="inlineStr">
-        <is>
-          <t>Харківська</t>
-        </is>
-      </c>
-      <c r="G1184" t="n">
-        <v>49.9512627</v>
-      </c>
-      <c r="H1184" t="n">
-        <v>36.371922</v>
-      </c>
-      <c r="I1184" t="inlineStr">
-        <is>
-          <t>Пн: 09:00-17:00
-Вт: 09:00-17:00
-Ср: 09:00-17:00
-Чт: 09:00-17:00
-Пт: 09:00-17:00
-Сб: 09:00-17:00
-Нд: 09:00-16:00</t>
-        </is>
-      </c>
-      <c r="J1184" t="inlineStr">
-        <is>
-          <t>Харківська</t>
-        </is>
-      </c>
-    </row>
-    <row r="1185">
-      <c r="A1185" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1185" t="n">
-        <v>3541</v>
-      </c>
-      <c r="C1185" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1185" t="inlineStr">
-        <is>
-          <t>вул Одеська 121, А/1</t>
-        </is>
-      </c>
-      <c r="E1185" t="inlineStr">
-        <is>
-          <t>Первомайськ</t>
-        </is>
-      </c>
-      <c r="F1185" t="inlineStr">
-        <is>
-          <t>Миколаївська</t>
-        </is>
-      </c>
-      <c r="G1185" t="n">
-        <v>48.0228289</v>
-      </c>
-      <c r="H1185" t="n">
-        <v>30.8511121</v>
-      </c>
-      <c r="I1185" t="inlineStr">
-        <is>
-          <t>Пн: 09:00-18:00
-Вт: 09:00-18:00
-Ср: 09:00-18:00
-Чт: 09:00-18:00
-Пт: 09:00-18:00
-Сб: 09:00-18:00
-Нд: 09:00-18:00</t>
-        </is>
-      </c>
-      <c r="J1185" t="inlineStr">
-        <is>
-          <t>Миколаївська</t>
-        </is>
-      </c>
-    </row>
-    <row r="1186">
-      <c r="A1186" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1186" t="n">
-        <v>3542</v>
-      </c>
-      <c r="C1186" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1186" t="inlineStr">
-        <is>
-          <t>просп Героїв Харкова 274</t>
-        </is>
-      </c>
-      <c r="E1186" t="inlineStr">
-        <is>
-          <t>Харків</t>
-        </is>
-      </c>
-      <c r="F1186" t="inlineStr">
-        <is>
-          <t>Харківська</t>
-        </is>
-      </c>
-      <c r="G1186" t="n">
-        <v>49.9432342</v>
-      </c>
-      <c r="H1186" t="n">
-        <v>36.3984342</v>
-      </c>
-      <c r="I1186" t="inlineStr">
-        <is>
-          <t>Пн: 09:00-18:00
-Вт: 09:00-18:00
-Ср: 09:00-18:00
-Чт: 09:00-18:00
-Пт: 09:00-18:00
-Сб: 09:00-17:00
-Нд: 09:00-17:00</t>
-        </is>
-      </c>
-      <c r="J1186" t="inlineStr">
-        <is>
-          <t>Харківська</t>
-        </is>
-      </c>
-    </row>
-    <row r="1187">
-      <c r="A1187" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1187" t="n">
-        <v>3543</v>
-      </c>
-      <c r="C1187" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1187" t="inlineStr">
-        <is>
-          <t>вул Салтівське шосе 147</t>
-        </is>
-      </c>
-      <c r="E1187" t="inlineStr">
-        <is>
-          <t>Харків</t>
-        </is>
-      </c>
-      <c r="F1187" t="inlineStr">
-        <is>
-          <t>Харківська</t>
-        </is>
-      </c>
-      <c r="G1187" t="n">
-        <v>49.9908024</v>
-      </c>
-      <c r="H1187" t="n">
-        <v>36.3585856</v>
-      </c>
-      <c r="I1187" t="inlineStr">
-        <is>
-          <t>Пн: 09:00-18:00
-Вт: 09:00-18:00
-Ср: 09:00-18:00
-Чт: 09:00-18:00
-Пт: 09:00-18:00
-Сб: 09:00-17:00
-Нд: 09:00-17:00</t>
-        </is>
-      </c>
-      <c r="J1187" t="inlineStr">
-        <is>
-          <t>Харківська</t>
-        </is>
-      </c>
-    </row>
-    <row r="1188">
-      <c r="A1188" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1188" t="n">
-        <v>3544</v>
-      </c>
-      <c r="C1188" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1188" t="inlineStr">
-        <is>
-          <t>просп Петра Григоренка 3</t>
-        </is>
-      </c>
-      <c r="E1188" t="inlineStr">
-        <is>
-          <t>Харків</t>
-        </is>
-      </c>
-      <c r="F1188" t="inlineStr">
-        <is>
-          <t>Харківська</t>
-        </is>
-      </c>
-      <c r="G1188" t="n">
-        <v>49.9650438</v>
-      </c>
-      <c r="H1188" t="n">
-        <v>36.3219614</v>
-      </c>
-      <c r="I1188" t="inlineStr">
-        <is>
-          <t>Пн: 09:00-18:00
-Вт: 09:00-18:00
-Ср: 09:00-18:00
-Чт: 09:00-18:00
-Пт: 09:00-18:00
-Сб: 09:00-17:00
-Нд: 09:00-17:00</t>
-        </is>
-      </c>
-      <c r="J1188" t="inlineStr">
-        <is>
-          <t>Харківська</t>
-        </is>
-      </c>
-    </row>
-    <row r="1189">
-      <c r="A1189" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1189" t="n">
-        <v>3545</v>
-      </c>
-      <c r="C1189" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1189" t="inlineStr">
-        <is>
-          <t>просп Аерокосмічний (Гагаріна) 177</t>
-        </is>
-      </c>
-      <c r="E1189" t="inlineStr">
-        <is>
-          <t>Харків</t>
-        </is>
-      </c>
-      <c r="F1189" t="inlineStr">
-        <is>
-          <t>Харківська</t>
-        </is>
-      </c>
-      <c r="G1189" t="n">
-        <v>50.0169162</v>
-      </c>
-      <c r="H1189" t="n">
-        <v>36.2067146</v>
-      </c>
-      <c r="I1189" t="inlineStr">
-        <is>
-          <t>Пн: 09:00-18:00
-Вт: 09:00-18:00
-Ср: 09:00-18:00
-Чт: 09:00-18:00
-Пт: 09:00-18:00
-Сб: 09:00-17:00
-Нд: 09:00-17:00</t>
-        </is>
-      </c>
-      <c r="J1189" t="inlineStr">
-        <is>
-          <t>Харківська</t>
-        </is>
-      </c>
-    </row>
-    <row r="1190">
-      <c r="A1190" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1190" t="n">
-        <v>3547</v>
-      </c>
-      <c r="C1190" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1190" t="inlineStr">
-        <is>
-          <t>вул Олімпійська 75</t>
-        </is>
-      </c>
-      <c r="E1190" t="inlineStr">
-        <is>
-          <t>Хотин</t>
-        </is>
-      </c>
-      <c r="F1190" t="inlineStr">
-        <is>
-          <t>Чернівецька</t>
-        </is>
-      </c>
-      <c r="G1190" t="n">
-        <v>48.5043413</v>
-      </c>
-      <c r="H1190" t="n">
-        <v>26.490402</v>
-      </c>
-      <c r="I1190" t="inlineStr">
-        <is>
-          <t>Пн: 09:00-18:00
-Вт: 09:00-18:00
-Ср: 09:00-18:00
-Чт: 09:00-18:00
-Пт: 09:00-18:00
-Сб: 09:00-17:00
-Нд: 10:00-14:00</t>
-        </is>
-      </c>
-      <c r="J1190" t="inlineStr">
-        <is>
-          <t>Чернівецька</t>
-        </is>
-      </c>
-    </row>
-    <row r="1191">
-      <c r="A1191" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1191" t="n">
-        <v>3549</v>
-      </c>
-      <c r="C1191" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1191" t="inlineStr">
-        <is>
-          <t>вул Жовтнева 4-А</t>
-        </is>
-      </c>
-      <c r="E1191" t="inlineStr">
-        <is>
-          <t>Гребінка</t>
-        </is>
-      </c>
-      <c r="F1191" t="inlineStr">
-        <is>
-          <t>Полтавська</t>
-        </is>
-      </c>
-      <c r="G1191" t="n">
-        <v>50.1185138</v>
-      </c>
-      <c r="H1191" t="n">
-        <v>32.4391051</v>
-      </c>
-      <c r="I1191" t="inlineStr">
-        <is>
-          <t>Пн: 09:00-17:00
-Вт: 09:00-17:00
-Ср: 09:00-17:00
-Чт: 09:00-17:00
-Пт: 09:00-17:00
-Сб: 09:00-14:00
-Нд: 09:00-14:00</t>
-        </is>
-      </c>
-      <c r="J1191" t="inlineStr">
-        <is>
-          <t>Полтавська</t>
-        </is>
-      </c>
-    </row>
-    <row r="1192">
-      <c r="A1192" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1192" t="n">
-        <v>3554</v>
-      </c>
-      <c r="C1192" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1192" t="inlineStr">
-        <is>
-          <t>вул Городоцька 137</t>
-        </is>
-      </c>
-      <c r="E1192" t="inlineStr">
-        <is>
-          <t>Львів</t>
-        </is>
-      </c>
-      <c r="F1192" t="inlineStr">
-        <is>
-          <t>Львівська</t>
-        </is>
-      </c>
-      <c r="G1192" t="n">
-        <v>49.8367768</v>
-      </c>
-      <c r="H1192" t="n">
-        <v>24.0028087</v>
-      </c>
-      <c r="I1192" t="inlineStr">
-        <is>
-          <t>Пн: 09:00-19:00
-Вт: 09:00-19:00
-Ср: 09:00-19:00
-Чт: 09:00-19:00
-Пт: 09:00-19:00
-Сб: 09:00-18:00
-Нд: 10:00-18:00</t>
-        </is>
-      </c>
-      <c r="J1192" t="inlineStr">
-        <is>
-          <t>Львівська</t>
-        </is>
-      </c>
-    </row>
-    <row r="1193">
-      <c r="A1193" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1193" t="n">
-        <v>3555</v>
-      </c>
-      <c r="C1193" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1193" t="inlineStr">
-        <is>
-          <t>вул Здолбунівська 15</t>
-        </is>
-      </c>
-      <c r="E1193" t="inlineStr">
-        <is>
-          <t>Київ</t>
-        </is>
-      </c>
-      <c r="F1193" t="inlineStr">
-        <is>
-          <t>м. Київ</t>
-        </is>
-      </c>
-      <c r="G1193" t="n">
-        <v>50.4185123</v>
-      </c>
-      <c r="H1193" t="n">
-        <v>30.631541</v>
-      </c>
-      <c r="I1193" t="inlineStr">
-        <is>
-          <t>Пн: 10:00-20:00
-Вт: 10:00-20:00
-Ср: 10:00-20:00
-Чт: 10:00-20:00
-Пт: 10:00-20:00
-Сб: 10:00-20:00
-Нд: 10:00-20:00</t>
-        </is>
-      </c>
-      <c r="J1193" t="inlineStr">
-        <is>
-          <t>м. Київ</t>
-        </is>
-      </c>
-    </row>
-    <row r="1194">
-      <c r="A1194" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1194" t="n">
-        <v>3556</v>
-      </c>
-      <c r="C1194" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1194" t="inlineStr">
-        <is>
-          <t>вул Шевченка 42</t>
-        </is>
-      </c>
-      <c r="E1194" t="inlineStr">
-        <is>
-          <t>Овруч</t>
-        </is>
-      </c>
-      <c r="F1194" t="inlineStr">
-        <is>
-          <t>Житомирська</t>
-        </is>
-      </c>
-      <c r="G1194" t="n">
-        <v>51.3197441</v>
-      </c>
-      <c r="H1194" t="n">
-        <v>28.8004248</v>
-      </c>
-      <c r="I1194" t="inlineStr">
-        <is>
-          <t>Пн: 09:00-18:00
-Вт: 09:00-18:00
-Ср: 09:00-18:00
-Чт: 09:00-18:00
-Пт: 09:00-18:00
-Сб: 09:00-18:00
-Нд: 09:00-18:00</t>
-        </is>
-      </c>
-      <c r="J1194" t="inlineStr">
-        <is>
-          <t>Житомирська</t>
-        </is>
-      </c>
-    </row>
-    <row r="1195">
-      <c r="A1195" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1195" t="n">
-        <v>3558</v>
-      </c>
-      <c r="C1195" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1195" t="inlineStr">
-        <is>
-          <t>вул Київська 26</t>
-        </is>
-      </c>
-      <c r="E1195" t="inlineStr">
-        <is>
-          <t>Іванків</t>
-        </is>
-      </c>
-      <c r="F1195" t="inlineStr">
-        <is>
-          <t>Kiev</t>
-        </is>
-      </c>
-      <c r="G1195" t="n">
-        <v>50.9338356</v>
-      </c>
-      <c r="H1195" t="n">
-        <v>29.9031381</v>
-      </c>
-      <c r="I1195" t="inlineStr">
-        <is>
-          <t>Пн: 08:00-18:00
-Вт: 08:00-18:00
-Ср: 08:00-18:00
-Чт: 08:00-18:00
-Пт: 08:00-18:00
-Сб: 08:00-18:00
-Нд: 09:00-17:00</t>
-        </is>
-      </c>
-      <c r="J1195" t="inlineStr">
-        <is>
-          <t>Kiev</t>
-        </is>
-      </c>
-    </row>
-    <row r="1196">
-      <c r="A1196" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1196" t="n">
-        <v>3559</v>
-      </c>
-      <c r="C1196" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1196" t="inlineStr">
-        <is>
-          <t>просп Соборний 51</t>
-        </is>
-      </c>
-      <c r="E1196" t="inlineStr">
-        <is>
-          <t>Запоріжжя</t>
-        </is>
-      </c>
-      <c r="F1196" t="inlineStr">
-        <is>
-          <t>Zaporizhia</t>
-        </is>
-      </c>
-      <c r="G1196" t="n">
-        <v>47.8176164</v>
-      </c>
-      <c r="H1196" t="n">
-        <v>35.1753352</v>
-      </c>
-      <c r="I1196" t="inlineStr">
-        <is>
-          <t>Пн: 09:00-19:00
-Вт: 09:00-19:00
-Ср: 09:00-19:00
-Чт: 09:00-19:00
-Пт: 09:00-19:00
-Сб: 09:00-19:00
-Нд: 10:00-18:00</t>
-        </is>
-      </c>
-      <c r="J1196" t="inlineStr">
-        <is>
-          <t>Zaporizhia</t>
-        </is>
-      </c>
-    </row>
-    <row r="1197">
-      <c r="A1197" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1197" t="n">
-        <v>3560</v>
-      </c>
-      <c r="C1197" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1197" t="inlineStr">
-        <is>
-          <t>вул Палацова 9</t>
-        </is>
-      </c>
-      <c r="E1197" t="inlineStr">
-        <is>
-          <t>Краматорськ</t>
-        </is>
-      </c>
-      <c r="F1197" t="inlineStr">
-        <is>
-          <t>Донецька</t>
-        </is>
-      </c>
-      <c r="G1197" t="n">
-        <v>48.7366237</v>
-      </c>
-      <c r="H1197" t="n">
-        <v>37.5916381</v>
-      </c>
-      <c r="I1197" t="inlineStr">
-        <is>
-          <t>Пн: 09:00-17:00
-Вт: 09:00-17:00
-Ср: 09:00-17:00
-Чт: 09:00-17:00
-Пт: 09:00-17:00
-Сб: 09:00-17:00
-Нд: 09:00-17:00</t>
-        </is>
-      </c>
-      <c r="J1197" t="inlineStr">
-        <is>
-          <t>Донецька</t>
-        </is>
-      </c>
-    </row>
-    <row r="1198">
-      <c r="A1198" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1198" t="n">
-        <v>3561</v>
-      </c>
-      <c r="C1198" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1198" t="inlineStr">
-        <is>
-          <t>вул Ф. Караманець (Ватутіна) 29</t>
-        </is>
-      </c>
-      <c r="E1198" t="inlineStr">
-        <is>
-          <t>Кривий Ріг</t>
-        </is>
-      </c>
-      <c r="F1198" t="inlineStr">
-        <is>
-          <t>Дніпропетровська</t>
-        </is>
-      </c>
-      <c r="G1198" t="n">
-        <v>48.024687</v>
-      </c>
-      <c r="H1198" t="n">
-        <v>33.4709468</v>
-      </c>
-      <c r="I1198" t="inlineStr">
-        <is>
-          <t>Пн: 09:00-18:00
-Вт: 09:00-18:00
-Ср: 09:00-18:00
-Чт: 09:00-18:00
-Пт: 09:00-18:00
-Сб: Вихідний
-Нд: Вихідний</t>
-        </is>
-      </c>
-      <c r="J1198" t="inlineStr">
-        <is>
-          <t>Дніпропетровська</t>
-        </is>
-      </c>
-    </row>
-    <row r="1199">
-      <c r="A1199" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1199" t="n">
-        <v>3563</v>
-      </c>
-      <c r="C1199" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1199" t="inlineStr">
-        <is>
-          <t>вул Шевченка 116</t>
-        </is>
-      </c>
-      <c r="E1199" t="inlineStr">
-        <is>
-          <t>Дунаївці</t>
-        </is>
-      </c>
-      <c r="F1199" t="inlineStr">
-        <is>
-          <t>Хмельницька</t>
-        </is>
-      </c>
-      <c r="G1199" t="n">
-        <v>48.8922754</v>
-      </c>
-      <c r="H1199" t="n">
-        <v>26.8568241</v>
-      </c>
-      <c r="I1199" t="inlineStr">
-        <is>
-          <t>Пн: 09:00-18:00
-Вт: 09:00-18:00
-Ср: 09:00-18:00
-Чт: 09:00-18:00
-Пт: 09:00-18:00
-Сб: 09:00-14:00
-Нд: Вихідний</t>
-        </is>
-      </c>
-      <c r="J1199" t="inlineStr">
-        <is>
-          <t>Хмельницька</t>
-        </is>
-      </c>
-    </row>
-    <row r="1200">
-      <c r="A1200" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1200" t="n">
-        <v>3566</v>
-      </c>
-      <c r="C1200" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1200" t="inlineStr">
-        <is>
-          <t>вул Р. Шухевича 1а</t>
-        </is>
-      </c>
-      <c r="E1200" t="inlineStr">
-        <is>
-          <t>Хмельницький</t>
-        </is>
-      </c>
-      <c r="F1200" t="inlineStr">
-        <is>
-          <t>Хмельницька</t>
-        </is>
-      </c>
-      <c r="G1200" t="n">
-        <v>49.4360713</v>
-      </c>
-      <c r="H1200" t="n">
-        <v>26.9572295</v>
-      </c>
-      <c r="I1200" t="inlineStr">
-        <is>
-          <t>Пн: 09:00-19:00
-Вт: 09:00-19:00
-Ср: 09:00-19:00
-Чт: 09:00-19:00
-Пт: 09:00-19:00
-Сб: 10:00-18:00
-Нд: 10:00-18:00</t>
-        </is>
-      </c>
-      <c r="J1200" t="inlineStr">
-        <is>
-          <t>Хмельницька</t>
-        </is>
-      </c>
-    </row>
-    <row r="1201">
-      <c r="A1201" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1201" t="n">
-        <v>3567</v>
-      </c>
-      <c r="C1201" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1201" t="inlineStr">
-        <is>
-          <t>вул Макухи 1</t>
-        </is>
-      </c>
-      <c r="E1201" t="inlineStr">
-        <is>
-          <t>Тлумач</t>
-        </is>
-      </c>
-      <c r="F1201" t="inlineStr">
-        <is>
-          <t>Івано-Франківська</t>
-        </is>
-      </c>
-      <c r="G1201" t="n">
-        <v>48.8652727</v>
-      </c>
-      <c r="H1201" t="n">
-        <v>25.0043864</v>
-      </c>
-      <c r="I1201" t="inlineStr">
-        <is>
-          <t>Пн: 09:00-17:00
-Вт: 09:00-17:00
-Ср: 09:00-17:00
-Чт: 09:00-17:00
-Пт: 09:00-17:00
-Сб: Вихідний
-Нд: Вихідний</t>
-        </is>
-      </c>
-      <c r="J1201" t="inlineStr">
-        <is>
-          <t>Івано-Франківська</t>
-        </is>
-      </c>
-    </row>
-    <row r="1202">
-      <c r="A1202" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1202" t="n">
-        <v>3568</v>
-      </c>
-      <c r="C1202" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1202" t="inlineStr">
-        <is>
-          <t>вул Андріївська 5</t>
-        </is>
-      </c>
-      <c r="E1202" t="inlineStr">
-        <is>
-          <t>Березне</t>
-        </is>
-      </c>
-      <c r="F1202" t="inlineStr">
-        <is>
-          <t>Рівненська</t>
-        </is>
-      </c>
-      <c r="G1202" t="n">
-        <v>51.0019955</v>
-      </c>
-      <c r="H1202" t="n">
-        <v>26.7547284</v>
-      </c>
-      <c r="I1202" t="inlineStr">
-        <is>
-          <t>Пн: 09:00-18:00
-Вт: 09:00-18:00
-Ср: 09:00-18:00
-Чт: 09:00-18:00
-Пт: 09:00-18:00
-Сб: 09:00-16:00
-Нд: 09:00-16:00</t>
-        </is>
-      </c>
-      <c r="J1202" t="inlineStr">
-        <is>
-          <t>Рівненська</t>
-        </is>
-      </c>
-    </row>
-    <row r="1203">
-      <c r="A1203" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1203" t="n">
-        <v>3569</v>
-      </c>
-      <c r="C1203" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1203" t="inlineStr">
-        <is>
-          <t>вул Широка 37</t>
-        </is>
-      </c>
-      <c r="E1203" t="inlineStr">
-        <is>
-          <t>Сарни</t>
-        </is>
-      </c>
-      <c r="F1203" t="inlineStr">
-        <is>
-          <t>Рівненська</t>
-        </is>
-      </c>
-      <c r="G1203" t="n">
-        <v>51.3355537</v>
-      </c>
-      <c r="H1203" t="n">
-        <v>26.6158412</v>
-      </c>
-      <c r="I1203" t="inlineStr">
-        <is>
-          <t>Пн: 09:00-18:00
-Вт: 09:00-18:00
-Ср: 09:00-18:00
-Чт: 09:00-18:00
-Пт: 09:00-18:00
-Сб: 09:00-18:00
-Нд: 09:00-17:00</t>
-        </is>
-      </c>
-      <c r="J1203" t="inlineStr">
-        <is>
-          <t>Рівненська</t>
-        </is>
-      </c>
-    </row>
-    <row r="1204">
-      <c r="A1204" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1204" t="n">
-        <v>3570</v>
-      </c>
-      <c r="C1204" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1204" t="inlineStr">
-        <is>
-          <t>вул Січових Стрільців 33А</t>
-        </is>
-      </c>
-      <c r="E1204" t="inlineStr">
-        <is>
-          <t>Бурштин</t>
-        </is>
-      </c>
-      <c r="F1204" t="inlineStr">
-        <is>
-          <t>Івано-Франківська</t>
-        </is>
-      </c>
-      <c r="G1204" t="n">
-        <v>49.2511835</v>
-      </c>
-      <c r="H1204" t="n">
-        <v>24.6288295</v>
-      </c>
-      <c r="I1204" t="inlineStr">
-        <is>
-          <t>Пн: 09:00-18:00
-Вт: 09:00-18:00
-Ср: 09:00-18:00
-Чт: 09:00-18:00
-Пт: 09:00-18:00
-Сб: 09:00-17:00
-Нд: Вихідний</t>
-        </is>
-      </c>
-      <c r="J1204" t="inlineStr">
-        <is>
-          <t>Івано-Франківська</t>
-        </is>
-      </c>
-    </row>
-    <row r="1205">
-      <c r="A1205" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1205" t="n">
-        <v>3571</v>
-      </c>
-      <c r="C1205" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1205" t="inlineStr">
-        <is>
-          <t>вул Небесної Сотні 85</t>
-        </is>
-      </c>
-      <c r="E1205" t="inlineStr">
-        <is>
-          <t>Романів</t>
-        </is>
-      </c>
-      <c r="F1205" t="inlineStr">
-        <is>
-          <t>Житомирська</t>
-        </is>
-      </c>
-      <c r="G1205" t="n">
-        <v>50.141605</v>
-      </c>
-      <c r="H1205" t="n">
-        <v>27.934655</v>
-      </c>
-      <c r="I1205" t="inlineStr">
-        <is>
-          <t>Пн: 08:00-18:00
-Вт: 08:00-18:00
-Ср: 08:00-18:00
-Чт: 08:00-18:00
-Пт: 08:00-18:00
-Сб: 08:00-17:00
-Нд: 09:00-17:00</t>
-        </is>
-      </c>
-      <c r="J1205" t="inlineStr">
-        <is>
-          <t>Житомирська</t>
-        </is>
-      </c>
-    </row>
-    <row r="1206">
-      <c r="A1206" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1206" t="n">
-        <v>3573</v>
-      </c>
-      <c r="C1206" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1206" t="inlineStr">
-        <is>
-          <t>вул Велика Окружна 4</t>
-        </is>
-      </c>
-      <c r="E1206" t="inlineStr">
-        <is>
-          <t>Київ</t>
-        </is>
-      </c>
-      <c r="F1206" t="inlineStr">
-        <is>
-          <t>Kiev</t>
-        </is>
-      </c>
-      <c r="G1206" t="n">
-        <v>50.4295904</v>
-      </c>
-      <c r="H1206" t="n">
-        <v>30.3567847</v>
-      </c>
-      <c r="I1206" t="inlineStr">
-        <is>
-          <t>Пн: 10:00-21:00
-Вт: 10:00-21:00
-Ср: 10:00-21:00
-Чт: 10:00-21:00
-Пт: 10:00-21:00
-Сб: 10:00-21:00
-Нд: 10:00-21:00</t>
-        </is>
-      </c>
-      <c r="J1206" t="inlineStr">
-        <is>
-          <t>Kiev</t>
-        </is>
-      </c>
-    </row>
-    <row r="1207">
-      <c r="A1207" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1207" t="n">
-        <v>3574</v>
-      </c>
-      <c r="C1207" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1207" t="inlineStr">
-        <is>
-          <t>вул Шевченка 50</t>
-        </is>
-      </c>
-      <c r="E1207" t="inlineStr">
-        <is>
-          <t>Богородчани</t>
-        </is>
-      </c>
-      <c r="F1207" t="inlineStr">
-        <is>
-          <t>Івано-Франківська</t>
-        </is>
-      </c>
-      <c r="G1207" t="n">
-        <v>48.809756</v>
-      </c>
-      <c r="H1207" t="n">
-        <v>24.5400082</v>
-      </c>
-      <c r="I1207" t="inlineStr">
-        <is>
-          <t>Пн: 09:00-18:00
-Вт: 09:00-18:00
-Ср: 09:00-18:00
-Чт: 09:00-18:00
-Пт: 09:00-18:00
-Сб: 09:00-17:00
-Нд: 10:00-16:00</t>
-        </is>
-      </c>
-      <c r="J1207" t="inlineStr">
-        <is>
-          <t>Івано-Франківська</t>
-        </is>
-      </c>
-    </row>
-    <row r="1208">
-      <c r="A1208" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1208" t="n">
-        <v>3575</v>
-      </c>
-      <c r="C1208" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1208" t="inlineStr">
-        <is>
-          <t>просп Богдана Хмельницкого (Героїв Сталінграда) 118Д</t>
-        </is>
-      </c>
-      <c r="E1208" t="inlineStr">
-        <is>
-          <t>Дніпро</t>
-        </is>
-      </c>
-      <c r="F1208" t="inlineStr">
-        <is>
-          <t>Дніпропетровська</t>
-        </is>
-      </c>
-      <c r="G1208" t="n">
-        <v>48.4076054</v>
-      </c>
-      <c r="H1208" t="n">
-        <v>35.0004028</v>
-      </c>
-      <c r="I1208" t="inlineStr">
-        <is>
-          <t>Пн: 09:00-19:00
-Вт: 09:00-19:00
-Ср: 09:00-19:00
-Чт: 09:00-19:00
-Пт: 09:00-19:00
-Сб: 09:00-19:00
-Нд: 09:00-19:00</t>
-        </is>
-      </c>
-      <c r="J1208" t="inlineStr">
-        <is>
-          <t>Дніпропетровська</t>
-        </is>
-      </c>
-    </row>
-    <row r="1209">
-      <c r="A1209" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1209" t="n">
-        <v>3576</v>
-      </c>
-      <c r="C1209" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1209" t="inlineStr">
-        <is>
-          <t>вул Грушевського 41А</t>
-        </is>
-      </c>
-      <c r="E1209" t="inlineStr">
-        <is>
-          <t>Первомайськ</t>
-        </is>
-      </c>
-      <c r="F1209" t="inlineStr">
-        <is>
-          <t>Миколаївська</t>
-        </is>
-      </c>
-      <c r="G1209" t="n">
-        <v>48.0425652</v>
-      </c>
-      <c r="H1209" t="n">
-        <v>30.8444596</v>
-      </c>
-      <c r="I1209" t="inlineStr">
-        <is>
-          <t>Пн: 08:00-18:00
-Вт: 08:00-18:00
-Ср: Вихідний
-Чт: Вихідний
-Пт: 08:00-18:00
-Сб: 08:00-18:00
-Нд: 08:00-16:00</t>
-        </is>
-      </c>
-      <c r="J1209" t="inlineStr">
-        <is>
-          <t>Миколаївська</t>
         </is>
       </c>
     </row>

--- a/all_shops.xlsx
+++ b/all_shops.xlsx
@@ -52489,7 +52489,7 @@
         </is>
       </c>
       <c r="B1139" t="n">
-        <v>3414</v>
+        <v>3420</v>
       </c>
       <c r="C1139" t="inlineStr">
         <is>
@@ -52498,7 +52498,7 @@
       </c>
       <c r="D1139" t="inlineStr">
         <is>
-          <t>просп Адмиральський 37</t>
+          <t>вул Ушинського 10</t>
         </is>
       </c>
       <c r="E1139" t="inlineStr">
@@ -52512,12 +52512,324 @@
         </is>
       </c>
       <c r="G1139" t="n">
-        <v>46.43745</v>
+        <v>46.4845584</v>
       </c>
       <c r="H1139" t="n">
-        <v>30.72675</v>
+        <v>30.7208259</v>
       </c>
       <c r="I1139" t="inlineStr">
+        <is>
+          <t>Пн: 09:00-18:00
+Вт: 09:00-18:00
+Ср: 09:00-18:00
+Чт: 09:00-18:00
+Пт: 09:00-18:00
+Сб: 09:00-18:00
+Нд: Вихідний</t>
+        </is>
+      </c>
+      <c r="J1139" t="inlineStr">
+        <is>
+          <t>Odessa</t>
+        </is>
+      </c>
+    </row>
+    <row r="1140">
+      <c r="A1140" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1140" t="n">
+        <v>3422</v>
+      </c>
+      <c r="C1140" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1140" t="inlineStr">
+        <is>
+          <t>вул Європейська (Жовтнева) 31а</t>
+        </is>
+      </c>
+      <c r="E1140" t="inlineStr">
+        <is>
+          <t>Вишневе</t>
+        </is>
+      </c>
+      <c r="F1140" t="inlineStr">
+        <is>
+          <t>Kiev</t>
+        </is>
+      </c>
+      <c r="G1140" t="n">
+        <v>50.3919298</v>
+      </c>
+      <c r="H1140" t="n">
+        <v>30.3759122</v>
+      </c>
+      <c r="I1140" t="inlineStr">
+        <is>
+          <t>Пн: 10:00-19:00
+Вт: 10:00-19:00
+Ср: 10:00-19:00
+Чт: 10:00-19:00
+Пт: 10:00-19:00
+Сб: 10:00-19:00
+Нд: 10:00-18:00</t>
+        </is>
+      </c>
+      <c r="J1140" t="inlineStr">
+        <is>
+          <t>Kiev</t>
+        </is>
+      </c>
+    </row>
+    <row r="1141">
+      <c r="A1141" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1141" t="n">
+        <v>3424</v>
+      </c>
+      <c r="C1141" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1141" t="inlineStr">
+        <is>
+          <t>просп Свободи 47</t>
+        </is>
+      </c>
+      <c r="E1141" t="inlineStr">
+        <is>
+          <t>Кременчук</t>
+        </is>
+      </c>
+      <c r="F1141" t="inlineStr">
+        <is>
+          <t>Полтавська</t>
+        </is>
+      </c>
+      <c r="G1141" t="n">
+        <v>49.0886626</v>
+      </c>
+      <c r="H1141" t="n">
+        <v>33.4285175</v>
+      </c>
+      <c r="I1141" t="inlineStr">
+        <is>
+          <t>Пн: 09:00-19:00
+Вт: 09:00-19:00
+Ср: 09:00-19:00
+Чт: 09:00-19:00
+Пт: 09:00-19:00
+Сб: 09:00-18:00
+Нд: 09:00-17:00</t>
+        </is>
+      </c>
+      <c r="J1141" t="inlineStr">
+        <is>
+          <t>Полтавська</t>
+        </is>
+      </c>
+    </row>
+    <row r="1142">
+      <c r="A1142" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1142" t="n">
+        <v>3428</v>
+      </c>
+      <c r="C1142" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1142" t="inlineStr">
+        <is>
+          <t>пл Миру 11</t>
+        </is>
+      </c>
+      <c r="E1142" t="inlineStr">
+        <is>
+          <t>Гадяч</t>
+        </is>
+      </c>
+      <c r="F1142" t="inlineStr">
+        <is>
+          <t>Полтавська</t>
+        </is>
+      </c>
+      <c r="G1142" t="n">
+        <v>50.3739846</v>
+      </c>
+      <c r="H1142" t="n">
+        <v>33.9836438</v>
+      </c>
+      <c r="I1142" t="inlineStr">
+        <is>
+          <t>Пн: 09:00-17:00
+Вт: 09:00-17:00
+Ср: 09:00-17:00
+Чт: 09:00-17:00
+Пт: 09:00-17:00
+Сб: 09:00-17:00
+Нд: 09:00-17:00</t>
+        </is>
+      </c>
+      <c r="J1142" t="inlineStr">
+        <is>
+          <t>Полтавська</t>
+        </is>
+      </c>
+    </row>
+    <row r="1143">
+      <c r="A1143" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1143" t="n">
+        <v>3432</v>
+      </c>
+      <c r="C1143" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1143" t="inlineStr">
+        <is>
+          <t>бул Шевченка 385</t>
+        </is>
+      </c>
+      <c r="E1143" t="inlineStr">
+        <is>
+          <t>Черкаси</t>
+        </is>
+      </c>
+      <c r="F1143" t="inlineStr">
+        <is>
+          <t>Черкаська</t>
+        </is>
+      </c>
+      <c r="G1143" t="n">
+        <v>49.424669</v>
+      </c>
+      <c r="H1143" t="n">
+        <v>32.0953677</v>
+      </c>
+      <c r="I1143" t="inlineStr">
+        <is>
+          <t>Пн: 10:00-20:00
+Вт: 10:00-20:00
+Ср: 10:00-20:00
+Чт: 10:00-20:00
+Пт: 10:00-20:00
+Сб: 10:00-20:00
+Нд: 10:00-20:00</t>
+        </is>
+      </c>
+      <c r="J1143" t="inlineStr">
+        <is>
+          <t>Черкаська</t>
+        </is>
+      </c>
+    </row>
+    <row r="1144">
+      <c r="A1144" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1144" t="n">
+        <v>3435</v>
+      </c>
+      <c r="C1144" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1144" t="inlineStr">
+        <is>
+          <t>просп Науки 1/2</t>
+        </is>
+      </c>
+      <c r="E1144" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="F1144" t="inlineStr">
+        <is>
+          <t>м. Київ</t>
+        </is>
+      </c>
+      <c r="G1144" t="n">
+        <v>50.4064898</v>
+      </c>
+      <c r="H1144" t="n">
+        <v>30.519621</v>
+      </c>
+      <c r="I1144" t="inlineStr">
+        <is>
+          <t>Пн: 07:00-22:00
+Вт: 07:00-22:00
+Ср: 07:00-22:00
+Чт: 07:00-22:00
+Пт: 07:00-22:00
+Сб: 07:00-22:00
+Нд: 07:00-22:00</t>
+        </is>
+      </c>
+      <c r="J1144" t="inlineStr">
+        <is>
+          <t>м. Київ</t>
+        </is>
+      </c>
+    </row>
+    <row r="1145">
+      <c r="A1145" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1145" t="n">
+        <v>3437</v>
+      </c>
+      <c r="C1145" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1145" t="inlineStr">
+        <is>
+          <t>просп Богоявленський 338</t>
+        </is>
+      </c>
+      <c r="E1145" t="inlineStr">
+        <is>
+          <t>Миколаїв (Миколаївська)</t>
+        </is>
+      </c>
+      <c r="F1145" t="inlineStr">
+        <is>
+          <t>Миколаївська</t>
+        </is>
+      </c>
+      <c r="G1145" t="n">
+        <v>46.8557792</v>
+      </c>
+      <c r="H1145" t="n">
+        <v>32.0141945</v>
+      </c>
+      <c r="I1145" t="inlineStr">
         <is>
           <t>Пн: 09:00-18:00
 Вт: 09:00-18:00
@@ -52528,48 +52840,724 @@
 Нд: 09:00-18:00</t>
         </is>
       </c>
-      <c r="J1139" t="inlineStr">
-        <is>
-          <t>Odessa</t>
-        </is>
-      </c>
-    </row>
-    <row r="1140">
-      <c r="A1140" t="inlineStr">
+      <c r="J1145" t="inlineStr">
+        <is>
+          <t>Миколаївська</t>
+        </is>
+      </c>
+    </row>
+    <row r="1146">
+      <c r="A1146" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1140" t="n">
-        <v>3420</v>
-      </c>
-      <c r="C1140" t="inlineStr">
+      <c r="B1146" t="n">
+        <v>3441</v>
+      </c>
+      <c r="C1146" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1140" t="inlineStr">
-        <is>
-          <t>вул Ушинського 10</t>
-        </is>
-      </c>
-      <c r="E1140" t="inlineStr">
-        <is>
-          <t>Одеса</t>
-        </is>
-      </c>
-      <c r="F1140" t="inlineStr">
-        <is>
-          <t>Odessa</t>
-        </is>
-      </c>
-      <c r="G1140" t="n">
-        <v>46.4845584</v>
-      </c>
-      <c r="H1140" t="n">
-        <v>30.7208259</v>
-      </c>
-      <c r="I1140" t="inlineStr">
+      <c r="D1146" t="inlineStr">
+        <is>
+          <t>вул Українська 71а</t>
+        </is>
+      </c>
+      <c r="E1146" t="inlineStr">
+        <is>
+          <t>Путила</t>
+        </is>
+      </c>
+      <c r="F1146" t="inlineStr">
+        <is>
+          <t>Чернівецька</t>
+        </is>
+      </c>
+      <c r="G1146" t="n">
+        <v>47.998305</v>
+      </c>
+      <c r="H1146" t="n">
+        <v>25.0850933</v>
+      </c>
+      <c r="I1146" t="inlineStr">
+        <is>
+          <t>Пн: 09:00-18:00
+Вт: 09:00-18:00
+Ср: 09:00-18:00
+Чт: 09:00-18:00
+Пт: 09:00-18:00
+Сб: 09:00-17:00
+Нд: 10:00-16:00</t>
+        </is>
+      </c>
+      <c r="J1146" t="inlineStr">
+        <is>
+          <t>Чернівецька</t>
+        </is>
+      </c>
+    </row>
+    <row r="1147">
+      <c r="A1147" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1147" t="n">
+        <v>3445</v>
+      </c>
+      <c r="C1147" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1147" t="inlineStr">
+        <is>
+          <t>вул Шевченка 73</t>
+        </is>
+      </c>
+      <c r="E1147" t="inlineStr">
+        <is>
+          <t>Снятин</t>
+        </is>
+      </c>
+      <c r="F1147" t="inlineStr">
+        <is>
+          <t>Івано-Франківська</t>
+        </is>
+      </c>
+      <c r="G1147" t="n">
+        <v>48.4514483</v>
+      </c>
+      <c r="H1147" t="n">
+        <v>25.5551122</v>
+      </c>
+      <c r="I1147" t="inlineStr">
+        <is>
+          <t>Пн: 09:00-18:00
+Вт: 09:00-18:00
+Ср: 09:00-18:00
+Чт: 09:00-18:00
+Пт: 09:00-18:00
+Сб: 09:00-15:00
+Нд: Вихідний</t>
+        </is>
+      </c>
+      <c r="J1147" t="inlineStr">
+        <is>
+          <t>Івано-Франківська</t>
+        </is>
+      </c>
+    </row>
+    <row r="1148">
+      <c r="A1148" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1148" t="n">
+        <v>3454</v>
+      </c>
+      <c r="C1148" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1148" t="inlineStr">
+        <is>
+          <t>вул Зелена 1а</t>
+        </is>
+      </c>
+      <c r="E1148" t="inlineStr">
+        <is>
+          <t>Мостиська</t>
+        </is>
+      </c>
+      <c r="F1148" t="inlineStr">
+        <is>
+          <t>Львівська</t>
+        </is>
+      </c>
+      <c r="G1148" t="n">
+        <v>49.7913487</v>
+      </c>
+      <c r="H1148" t="n">
+        <v>23.1536667</v>
+      </c>
+      <c r="I1148" t="inlineStr">
+        <is>
+          <t>Пн: 09:00-19:00
+Вт: 09:00-19:00
+Ср: 09:00-19:00
+Чт: 09:00-19:00
+Пт: 09:00-19:00
+Сб: 09:00-18:00
+Нд: 10:00-17:00</t>
+        </is>
+      </c>
+      <c r="J1148" t="inlineStr">
+        <is>
+          <t>Львівська</t>
+        </is>
+      </c>
+    </row>
+    <row r="1149">
+      <c r="A1149" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1149" t="n">
+        <v>3464</v>
+      </c>
+      <c r="C1149" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1149" t="inlineStr">
+        <is>
+          <t>вул Огієнка 41</t>
+        </is>
+      </c>
+      <c r="E1149" t="inlineStr">
+        <is>
+          <t>Камянець-Подільский</t>
+        </is>
+      </c>
+      <c r="F1149" t="inlineStr">
+        <is>
+          <t>Хмельницька</t>
+        </is>
+      </c>
+      <c r="G1149" t="n">
+        <v>48.681053</v>
+      </c>
+      <c r="H1149" t="n">
+        <v>26.5871481</v>
+      </c>
+      <c r="I1149" t="inlineStr">
+        <is>
+          <t>Пн: 08:00-18:00
+Вт: 08:00-18:00
+Ср: 08:00-18:00
+Чт: 08:00-18:00
+Пт: 08:00-18:00
+Сб: 10:00-16:00
+Нд: 10:00-16:00</t>
+        </is>
+      </c>
+      <c r="J1149" t="inlineStr">
+        <is>
+          <t>Хмельницька</t>
+        </is>
+      </c>
+    </row>
+    <row r="1150">
+      <c r="A1150" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1150" t="n">
+        <v>3465</v>
+      </c>
+      <c r="C1150" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1150" t="inlineStr">
+        <is>
+          <t>вул Хмельницька 6</t>
+        </is>
+      </c>
+      <c r="E1150" t="inlineStr">
+        <is>
+          <t>Ярмолинці</t>
+        </is>
+      </c>
+      <c r="F1150" t="inlineStr">
+        <is>
+          <t>Хмельницька</t>
+        </is>
+      </c>
+      <c r="G1150" t="n">
+        <v>49.19112</v>
+      </c>
+      <c r="H1150" t="n">
+        <v>26.83537</v>
+      </c>
+      <c r="I1150" t="inlineStr">
+        <is>
+          <t>Пн: 09:00-18:00
+Вт: 09:00-18:00
+Ср: 09:00-18:00
+Чт: 09:00-18:00
+Пт: 09:00-18:00
+Сб: 09:00-14:00
+Нд: Вихідний</t>
+        </is>
+      </c>
+      <c r="J1150" t="inlineStr">
+        <is>
+          <t>Хмельницька</t>
+        </is>
+      </c>
+    </row>
+    <row r="1151">
+      <c r="A1151" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1151" t="n">
+        <v>3466</v>
+      </c>
+      <c r="C1151" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1151" t="inlineStr">
+        <is>
+          <t>просп Берестейський (Перемоги) 86а</t>
+        </is>
+      </c>
+      <c r="E1151" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="F1151" t="inlineStr">
+        <is>
+          <t>Kiev</t>
+        </is>
+      </c>
+      <c r="G1151" t="n">
+        <v>50.4588998</v>
+      </c>
+      <c r="H1151" t="n">
+        <v>30.4041254</v>
+      </c>
+      <c r="I1151" t="inlineStr">
+        <is>
+          <t>Пн: 10:00-21:00
+Вт: 10:00-21:00
+Ср: 10:00-21:00
+Чт: 10:00-21:00
+Пт: 10:00-21:00
+Сб: 10:00-21:00
+Нд: 10:00-21:00</t>
+        </is>
+      </c>
+      <c r="J1151" t="inlineStr">
+        <is>
+          <t>Kiev</t>
+        </is>
+      </c>
+    </row>
+    <row r="1152">
+      <c r="A1152" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1152" t="n">
+        <v>3470</v>
+      </c>
+      <c r="C1152" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1152" t="inlineStr">
+        <is>
+          <t>вул  Хрещатик 13</t>
+        </is>
+      </c>
+      <c r="E1152" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="F1152" t="inlineStr">
+        <is>
+          <t>м. Київ</t>
+        </is>
+      </c>
+      <c r="G1152" t="n">
+        <v>50.4487897</v>
+      </c>
+      <c r="H1152" t="n">
+        <v>30.5233361</v>
+      </c>
+      <c r="I1152" t="inlineStr">
+        <is>
+          <t>Пн: 10:00-20:00
+Вт: 10:00-20:00
+Ср: 10:00-20:00
+Чт: 10:00-20:00
+Пт: 10:00-20:00
+Сб: 10:00-20:00
+Нд: 10:00-20:00</t>
+        </is>
+      </c>
+      <c r="J1152" t="inlineStr">
+        <is>
+          <t>м. Київ</t>
+        </is>
+      </c>
+    </row>
+    <row r="1153">
+      <c r="A1153" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1153" t="n">
+        <v>3471</v>
+      </c>
+      <c r="C1153" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1153" t="inlineStr">
+        <is>
+          <t>вул Університетська 45</t>
+        </is>
+      </c>
+      <c r="E1153" t="inlineStr">
+        <is>
+          <t>Словянськ</t>
+        </is>
+      </c>
+      <c r="F1153" t="inlineStr">
+        <is>
+          <t>Дніпропетровська</t>
+        </is>
+      </c>
+      <c r="G1153" t="n">
+        <v>48.0008788</v>
+      </c>
+      <c r="H1153" t="n">
+        <v>33.4821954</v>
+      </c>
+      <c r="I1153" t="inlineStr">
+        <is>
+          <t>Пн: 10:00-17:00
+Вт: 10:00-17:00
+Ср: 10:00-17:00
+Чт: 10:00-17:00
+Пт: 10:00-17:00
+Сб: 10:00-16:00
+Нд: Вихідний</t>
+        </is>
+      </c>
+      <c r="J1153" t="inlineStr">
+        <is>
+          <t>Дніпропетровська</t>
+        </is>
+      </c>
+    </row>
+    <row r="1154">
+      <c r="A1154" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1154" t="n">
+        <v>3472</v>
+      </c>
+      <c r="C1154" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1154" t="inlineStr">
+        <is>
+          <t>вул Чернівецька 2Б</t>
+        </is>
+      </c>
+      <c r="E1154" t="inlineStr">
+        <is>
+          <t>Сторожинець</t>
+        </is>
+      </c>
+      <c r="F1154" t="inlineStr">
+        <is>
+          <t>Чернівецька</t>
+        </is>
+      </c>
+      <c r="G1154" t="n">
+        <v>48.1604917</v>
+      </c>
+      <c r="H1154" t="n">
+        <v>25.721244</v>
+      </c>
+      <c r="I1154" t="inlineStr">
+        <is>
+          <t>Пн: 09:00-18:00
+Вт: 09:00-18:00
+Ср: 09:00-18:00
+Чт: 09:00-18:00
+Пт: 09:00-18:00
+Сб: 09:00-15:00
+Нд: Вихідний</t>
+        </is>
+      </c>
+      <c r="J1154" t="inlineStr">
+        <is>
+          <t>Чернівецька</t>
+        </is>
+      </c>
+    </row>
+    <row r="1155">
+      <c r="A1155" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1155" t="n">
+        <v>3474</v>
+      </c>
+      <c r="C1155" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1155" t="inlineStr">
+        <is>
+          <t>вул Нескорених (Героїв Праці) 13</t>
+        </is>
+      </c>
+      <c r="E1155" t="inlineStr">
+        <is>
+          <t>Харків</t>
+        </is>
+      </c>
+      <c r="F1155" t="inlineStr">
+        <is>
+          <t>Харківська</t>
+        </is>
+      </c>
+      <c r="G1155" t="n">
+        <v>50.0254117</v>
+      </c>
+      <c r="H1155" t="n">
+        <v>36.3369339</v>
+      </c>
+      <c r="I1155" t="inlineStr">
+        <is>
+          <t>Пн: 09:00-18:00
+Вт: 09:00-18:00
+Ср: 09:00-18:00
+Чт: 09:00-18:00
+Пт: 09:00-18:00
+Сб: 09:00-17:00
+Нд: 09:00-17:00</t>
+        </is>
+      </c>
+      <c r="J1155" t="inlineStr">
+        <is>
+          <t>Харківська</t>
+        </is>
+      </c>
+    </row>
+    <row r="1156">
+      <c r="A1156" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1156" t="n">
+        <v>3478</v>
+      </c>
+      <c r="C1156" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1156" t="inlineStr">
+        <is>
+          <t>просп Європейського Союзу (Правди) 58</t>
+        </is>
+      </c>
+      <c r="E1156" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="F1156" t="inlineStr">
+        <is>
+          <t>Kiev</t>
+        </is>
+      </c>
+      <c r="G1156" t="n">
+        <v>50.5047315</v>
+      </c>
+      <c r="H1156" t="n">
+        <v>30.4374307</v>
+      </c>
+      <c r="I1156" t="inlineStr">
+        <is>
+          <t>Пн: 09:00-21:00
+Вт: 09:00-21:00
+Ср: 09:00-21:00
+Чт: 09:00-21:00
+Пт: 09:00-21:00
+Сб: 09:00-21:00
+Нд: 09:00-21:00</t>
+        </is>
+      </c>
+      <c r="J1156" t="inlineStr">
+        <is>
+          <t>Kiev</t>
+        </is>
+      </c>
+    </row>
+    <row r="1157">
+      <c r="A1157" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1157" t="n">
+        <v>3479</v>
+      </c>
+      <c r="C1157" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1157" t="inlineStr">
+        <is>
+          <t>вул Європейського Союзу (Правди) 47</t>
+        </is>
+      </c>
+      <c r="E1157" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="F1157" t="inlineStr">
+        <is>
+          <t>м. Київ</t>
+        </is>
+      </c>
+      <c r="G1157" t="n">
+        <v>50.5037667</v>
+      </c>
+      <c r="H1157" t="n">
+        <v>30.419093</v>
+      </c>
+      <c r="I1157" t="inlineStr">
+        <is>
+          <t>Пн: 10:00-22:00
+Вт: 10:00-22:00
+Ср: 10:00-22:00
+Чт: 10:00-22:00
+Пт: 10:00-22:00
+Сб: 10:00-22:00
+Нд: 10:00-22:00</t>
+        </is>
+      </c>
+      <c r="J1157" t="inlineStr">
+        <is>
+          <t>м. Київ</t>
+        </is>
+      </c>
+    </row>
+    <row r="1158">
+      <c r="A1158" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1158" t="n">
+        <v>3483</v>
+      </c>
+      <c r="C1158" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1158" t="inlineStr">
+        <is>
+          <t>просп Коцюбинського 19</t>
+        </is>
+      </c>
+      <c r="E1158" t="inlineStr">
+        <is>
+          <t>Вінниця</t>
+        </is>
+      </c>
+      <c r="F1158" t="inlineStr">
+        <is>
+          <t>Vinnyts'ka</t>
+        </is>
+      </c>
+      <c r="G1158" t="n">
+        <v>49.239071</v>
+      </c>
+      <c r="H1158" t="n">
+        <v>28.4981039</v>
+      </c>
+      <c r="I1158" t="inlineStr">
+        <is>
+          <t>Пн: 08:00-18:00
+Вт: 08:00-18:00
+Ср: 08:00-18:00
+Чт: 08:00-18:00
+Пт: 08:00-18:00
+Сб: 09:00-17:00
+Нд: 09:00-17:00</t>
+        </is>
+      </c>
+      <c r="J1158" t="inlineStr">
+        <is>
+          <t>Vinnyts'ka</t>
+        </is>
+      </c>
+    </row>
+    <row r="1159">
+      <c r="A1159" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1159" t="n">
+        <v>3485</v>
+      </c>
+      <c r="C1159" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1159" t="inlineStr">
+        <is>
+          <t>вул Котляра (був. Червоноармійська) 8/10</t>
+        </is>
+      </c>
+      <c r="E1159" t="inlineStr">
+        <is>
+          <t>Харків</t>
+        </is>
+      </c>
+      <c r="F1159" t="inlineStr">
+        <is>
+          <t>Харківська</t>
+        </is>
+      </c>
+      <c r="G1159" t="n">
+        <v>49.9892648</v>
+      </c>
+      <c r="H1159" t="n">
+        <v>36.2077698</v>
+      </c>
+      <c r="I1159" t="inlineStr">
         <is>
           <t>Пн: 09:00-18:00
 Вт: 09:00-18:00
@@ -52577,103 +53565,311 @@
 Чт: 09:00-18:00
 Пт: 09:00-18:00
 Сб: 09:00-18:00
-Нд: Вихідний</t>
-        </is>
-      </c>
-      <c r="J1140" t="inlineStr">
-        <is>
-          <t>Odessa</t>
-        </is>
-      </c>
-    </row>
-    <row r="1141">
-      <c r="A1141" t="inlineStr">
+Нд: 09:00-17:00</t>
+        </is>
+      </c>
+      <c r="J1159" t="inlineStr">
+        <is>
+          <t>Харківська</t>
+        </is>
+      </c>
+    </row>
+    <row r="1160">
+      <c r="A1160" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1141" t="n">
-        <v>3422</v>
-      </c>
-      <c r="C1141" t="inlineStr">
+      <c r="B1160" t="n">
+        <v>3491</v>
+      </c>
+      <c r="C1160" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1141" t="inlineStr">
-        <is>
-          <t>вул Європейська (Жовтнева) 31а</t>
-        </is>
-      </c>
-      <c r="E1141" t="inlineStr">
-        <is>
-          <t>Вишневе</t>
-        </is>
-      </c>
-      <c r="F1141" t="inlineStr">
+      <c r="D1160" t="inlineStr">
+        <is>
+          <t>вул Інститутська 10</t>
+        </is>
+      </c>
+      <c r="E1160" t="inlineStr">
+        <is>
+          <t>Хмельницький</t>
+        </is>
+      </c>
+      <c r="F1160" t="inlineStr">
+        <is>
+          <t>Хмельницька</t>
+        </is>
+      </c>
+      <c r="G1160" t="n">
+        <v>49.4098499</v>
+      </c>
+      <c r="H1160" t="n">
+        <v>26.9605436</v>
+      </c>
+      <c r="I1160" t="inlineStr">
+        <is>
+          <t>Пн: 09:00-19:00
+Вт: 09:00-19:00
+Ср: 09:00-19:00
+Чт: 09:00-19:00
+Пт: 09:00-19:00
+Сб: 10:00-18:00
+Нд: 10:00-18:00</t>
+        </is>
+      </c>
+      <c r="J1160" t="inlineStr">
+        <is>
+          <t>Хмельницька</t>
+        </is>
+      </c>
+    </row>
+    <row r="1161">
+      <c r="A1161" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1161" t="n">
+        <v>3494</v>
+      </c>
+      <c r="C1161" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1161" t="inlineStr">
+        <is>
+          <t>вул Шевченків Шлях 144-А</t>
+        </is>
+      </c>
+      <c r="E1161" t="inlineStr">
+        <is>
+          <t>Березань</t>
+        </is>
+      </c>
+      <c r="F1161" t="inlineStr">
         <is>
           <t>Kiev</t>
         </is>
       </c>
-      <c r="G1141" t="n">
-        <v>50.3919298</v>
-      </c>
-      <c r="H1141" t="n">
-        <v>30.3759122</v>
-      </c>
-      <c r="I1141" t="inlineStr">
-        <is>
-          <t>Пн: 10:00-19:00
-Вт: 10:00-19:00
-Ср: 10:00-19:00
-Чт: 10:00-19:00
-Пт: 10:00-19:00
-Сб: 10:00-19:00
-Нд: 10:00-18:00</t>
-        </is>
-      </c>
-      <c r="J1141" t="inlineStr">
+      <c r="G1161" t="n">
+        <v>50.3119113</v>
+      </c>
+      <c r="H1161" t="n">
+        <v>31.4678577</v>
+      </c>
+      <c r="I1161" t="inlineStr">
+        <is>
+          <t>Пн: 09:00-17:00
+Вт: 09:00-17:00
+Ср: 09:00-17:00
+Чт: 09:00-17:00
+Пт: 09:00-17:00
+Сб: 10:00-16:00
+Нд: 10:00-16:00</t>
+        </is>
+      </c>
+      <c r="J1161" t="inlineStr">
         <is>
           <t>Kiev</t>
         </is>
       </c>
     </row>
-    <row r="1142">
-      <c r="A1142" t="inlineStr">
+    <row r="1162">
+      <c r="A1162" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1142" t="n">
-        <v>3424</v>
-      </c>
-      <c r="C1142" t="inlineStr">
+      <c r="B1162" t="n">
+        <v>3495</v>
+      </c>
+      <c r="C1162" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1142" t="inlineStr">
-        <is>
-          <t>просп Свободи 47</t>
-        </is>
-      </c>
-      <c r="E1142" t="inlineStr">
-        <is>
-          <t>Кременчук</t>
-        </is>
-      </c>
-      <c r="F1142" t="inlineStr">
-        <is>
-          <t>Полтавська</t>
-        </is>
-      </c>
-      <c r="G1142" t="n">
-        <v>49.0886626</v>
-      </c>
-      <c r="H1142" t="n">
-        <v>33.4285175</v>
-      </c>
-      <c r="I1142" t="inlineStr">
+      <c r="D1162" t="inlineStr">
+        <is>
+          <t>вул Міцкевича 1</t>
+        </is>
+      </c>
+      <c r="E1162" t="inlineStr">
+        <is>
+          <t>Борислав</t>
+        </is>
+      </c>
+      <c r="F1162" t="inlineStr">
+        <is>
+          <t>Львівська</t>
+        </is>
+      </c>
+      <c r="G1162" t="n">
+        <v>49.287286</v>
+      </c>
+      <c r="H1162" t="n">
+        <v>23.4159004</v>
+      </c>
+      <c r="I1162" t="inlineStr">
+        <is>
+          <t>Пн: 09:00-18:00
+Вт: 09:00-18:00
+Ср: 09:00-18:00
+Чт: 09:00-18:00
+Пт: 09:00-18:00
+Сб: 09:00-17:00
+Нд: 10:00-17:00</t>
+        </is>
+      </c>
+      <c r="J1162" t="inlineStr">
+        <is>
+          <t>Львівська</t>
+        </is>
+      </c>
+    </row>
+    <row r="1163">
+      <c r="A1163" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1163" t="n">
+        <v>3496</v>
+      </c>
+      <c r="C1163" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1163" t="inlineStr">
+        <is>
+          <t>вул І.Франка 1</t>
+        </is>
+      </c>
+      <c r="E1163" t="inlineStr">
+        <is>
+          <t>Верховина</t>
+        </is>
+      </c>
+      <c r="F1163" t="inlineStr">
+        <is>
+          <t>Івано-Франківська</t>
+        </is>
+      </c>
+      <c r="G1163" t="n">
+        <v>48.1549768</v>
+      </c>
+      <c r="H1163" t="n">
+        <v>24.8291227</v>
+      </c>
+      <c r="I1163" t="inlineStr">
+        <is>
+          <t>Пн: 09:00-18:00
+Вт: 09:00-18:00
+Ср: 09:00-18:00
+Чт: 09:00-18:00
+Пт: 09:00-18:00
+Сб: 09:00-17:00
+Нд: 10:00-16:00</t>
+        </is>
+      </c>
+      <c r="J1163" t="inlineStr">
+        <is>
+          <t>Івано-Франківська</t>
+        </is>
+      </c>
+    </row>
+    <row r="1164">
+      <c r="A1164" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1164" t="n">
+        <v>3498</v>
+      </c>
+      <c r="C1164" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1164" t="inlineStr">
+        <is>
+          <t>просп Олександра Поля 1/9</t>
+        </is>
+      </c>
+      <c r="E1164" t="inlineStr">
+        <is>
+          <t>Дніпро</t>
+        </is>
+      </c>
+      <c r="F1164" t="inlineStr">
+        <is>
+          <t>Дніпропетровська</t>
+        </is>
+      </c>
+      <c r="G1164" t="n">
+        <v>48.4642698</v>
+      </c>
+      <c r="H1164" t="n">
+        <v>35.0290126</v>
+      </c>
+      <c r="I1164" t="inlineStr">
+        <is>
+          <t>Пн: 09:00-19:00
+Вт: 09:00-19:00
+Ср: 09:00-19:00
+Чт: 09:00-19:00
+Пт: 09:00-19:00
+Сб: 09:00-19:00
+Нд: 09:00-18:00</t>
+        </is>
+      </c>
+      <c r="J1164" t="inlineStr">
+        <is>
+          <t>Дніпропетровська</t>
+        </is>
+      </c>
+    </row>
+    <row r="1165">
+      <c r="A1165" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1165" t="n">
+        <v>3501</v>
+      </c>
+      <c r="C1165" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1165" t="inlineStr">
+        <is>
+          <t>просп Дмитра Яворницького (К.Маркса) 65</t>
+        </is>
+      </c>
+      <c r="E1165" t="inlineStr">
+        <is>
+          <t>Дніпро</t>
+        </is>
+      </c>
+      <c r="F1165" t="inlineStr">
+        <is>
+          <t>Дніпропетровська</t>
+        </is>
+      </c>
+      <c r="G1165" t="n">
+        <v>48.4647786</v>
+      </c>
+      <c r="H1165" t="n">
+        <v>35.0447223</v>
+      </c>
+      <c r="I1165" t="inlineStr">
         <is>
           <t>Пн: 09:00-19:00
 Вт: 09:00-19:00
@@ -52681,51 +53877,1351 @@
 Чт: 09:00-19:00
 Пт: 09:00-19:00
 Сб: 09:00-18:00
+Нд: 09:00-18:00</t>
+        </is>
+      </c>
+      <c r="J1165" t="inlineStr">
+        <is>
+          <t>Дніпропетровська</t>
+        </is>
+      </c>
+    </row>
+    <row r="1166">
+      <c r="A1166" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1166" t="n">
+        <v>3505</v>
+      </c>
+      <c r="C1166" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1166" t="inlineStr">
+        <is>
+          <t>пл Шевченка 26</t>
+        </is>
+      </c>
+      <c r="E1166" t="inlineStr">
+        <is>
+          <t>Коломия</t>
+        </is>
+      </c>
+      <c r="F1166" t="inlineStr">
+        <is>
+          <t>Івано-Франківська</t>
+        </is>
+      </c>
+      <c r="G1166" t="n">
+        <v>48.5249278</v>
+      </c>
+      <c r="H1166" t="n">
+        <v>25.0375409</v>
+      </c>
+      <c r="I1166" t="inlineStr">
+        <is>
+          <t>Пн: 09:00-18:00
+Вт: 09:00-18:00
+Ср: 09:00-18:00
+Чт: 09:00-18:00
+Пт: 09:00-18:00
+Сб: 09:00-18:00
+Нд: 10:00-17:00</t>
+        </is>
+      </c>
+      <c r="J1166" t="inlineStr">
+        <is>
+          <t>Івано-Франківська</t>
+        </is>
+      </c>
+    </row>
+    <row r="1167">
+      <c r="A1167" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1167" t="n">
+        <v>3506</v>
+      </c>
+      <c r="C1167" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1167" t="inlineStr">
+        <is>
+          <t>вул Медова 5</t>
+        </is>
+      </c>
+      <c r="E1167" t="inlineStr">
+        <is>
+          <t>Кремeнець</t>
+        </is>
+      </c>
+      <c r="F1167" t="inlineStr">
+        <is>
+          <t>Тернопільська</t>
+        </is>
+      </c>
+      <c r="G1167" t="n">
+        <v>50.095605</v>
+      </c>
+      <c r="H1167" t="n">
+        <v>25.7259463</v>
+      </c>
+      <c r="I1167" t="inlineStr">
+        <is>
+          <t>Пн: 09:00-19:00
+Вт: 09:00-19:00
+Ср: 09:00-19:00
+Чт: 09:00-19:00
+Пт: 09:00-19:00
+Сб: 10:00-16:00
+Нд: 10:00-16:00</t>
+        </is>
+      </c>
+      <c r="J1167" t="inlineStr">
+        <is>
+          <t>Тернопільська</t>
+        </is>
+      </c>
+    </row>
+    <row r="1168">
+      <c r="A1168" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1168" t="n">
+        <v>3508</v>
+      </c>
+      <c r="C1168" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1168" t="inlineStr">
+        <is>
+          <t>вул Шевченка 100</t>
+        </is>
+      </c>
+      <c r="E1168" t="inlineStr">
+        <is>
+          <t>Люботин</t>
+        </is>
+      </c>
+      <c r="F1168" t="inlineStr">
+        <is>
+          <t>Харківська</t>
+        </is>
+      </c>
+      <c r="G1168" t="n">
+        <v>49.9407992</v>
+      </c>
+      <c r="H1168" t="n">
+        <v>35.9262566</v>
+      </c>
+      <c r="I1168" t="inlineStr">
+        <is>
+          <t>Пн: 08:00-18:00
+Вт: 08:00-18:00
+Ср: 08:00-18:00
+Чт: 08:00-18:00
+Пт: 08:00-18:00
+Сб: 08:00-18:00
+Нд: 08:00-16:00</t>
+        </is>
+      </c>
+      <c r="J1168" t="inlineStr">
+        <is>
+          <t>Харківська</t>
+        </is>
+      </c>
+    </row>
+    <row r="1169">
+      <c r="A1169" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1169" t="n">
+        <v>3510</v>
+      </c>
+      <c r="C1169" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1169" t="inlineStr">
+        <is>
+          <t>вул Петропавлівська 49</t>
+        </is>
+      </c>
+      <c r="E1169" t="inlineStr">
+        <is>
+          <t>Суми</t>
+        </is>
+      </c>
+      <c r="F1169" t="inlineStr">
+        <is>
+          <t>Сумська</t>
+        </is>
+      </c>
+      <c r="G1169" t="n">
+        <v>50.9065729</v>
+      </c>
+      <c r="H1169" t="n">
+        <v>34.796901</v>
+      </c>
+      <c r="I1169" t="inlineStr">
+        <is>
+          <t>Пн: 09:00-18:00
+Вт: 09:00-18:00
+Ср: 09:00-18:00
+Чт: 09:00-18:00
+Пт: 09:00-18:00
+Сб: 09:00-18:00
+Нд: 09:00-18:00</t>
+        </is>
+      </c>
+      <c r="J1169" t="inlineStr">
+        <is>
+          <t>Сумська</t>
+        </is>
+      </c>
+    </row>
+    <row r="1170">
+      <c r="A1170" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1170" t="n">
+        <v>3512</v>
+      </c>
+      <c r="C1170" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1170" t="inlineStr">
+        <is>
+          <t>вул Валентинівська (Блюхера) 37/128</t>
+        </is>
+      </c>
+      <c r="E1170" t="inlineStr">
+        <is>
+          <t>Харків</t>
+        </is>
+      </c>
+      <c r="F1170" t="inlineStr">
+        <is>
+          <t>Харківська</t>
+        </is>
+      </c>
+      <c r="G1170" t="n">
+        <v>50.0098371</v>
+      </c>
+      <c r="H1170" t="n">
+        <v>36.3503577</v>
+      </c>
+      <c r="I1170" t="inlineStr">
+        <is>
+          <t>Пн: 09:00-19:00
+Вт: 09:00-19:00
+Ср: 09:00-19:00
+Чт: 09:00-19:00
+Пт: 09:00-19:00
+Сб: 09:00-18:00
+Нд: 09:00-18:00</t>
+        </is>
+      </c>
+      <c r="J1170" t="inlineStr">
+        <is>
+          <t>Харківська</t>
+        </is>
+      </c>
+    </row>
+    <row r="1171">
+      <c r="A1171" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1171" t="n">
+        <v>3514</v>
+      </c>
+      <c r="C1171" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1171" t="inlineStr">
+        <is>
+          <t>вул Центральна 32а</t>
+        </is>
+      </c>
+      <c r="E1171" t="inlineStr">
+        <is>
+          <t>Чемерівці</t>
+        </is>
+      </c>
+      <c r="F1171" t="inlineStr">
+        <is>
+          <t>Хмельницька</t>
+        </is>
+      </c>
+      <c r="G1171" t="n">
+        <v>49.011295</v>
+      </c>
+      <c r="H1171" t="n">
+        <v>26.340395</v>
+      </c>
+      <c r="I1171" t="inlineStr">
+        <is>
+          <t>Пн: 08:00-18:00
+Вт: 08:00-18:00
+Ср: 08:00-18:00
+Чт: 08:00-18:00
+Пт: 08:00-18:00
+Сб: 09:00-16:00
+Нд: 09:00-15:00</t>
+        </is>
+      </c>
+      <c r="J1171" t="inlineStr">
+        <is>
+          <t>Хмельницька</t>
+        </is>
+      </c>
+    </row>
+    <row r="1172">
+      <c r="A1172" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1172" t="n">
+        <v>3517</v>
+      </c>
+      <c r="C1172" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1172" t="inlineStr">
+        <is>
+          <t>просп Свободи (Леніна) 16Д</t>
+        </is>
+      </c>
+      <c r="E1172" t="inlineStr">
+        <is>
+          <t>Хмільник</t>
+        </is>
+      </c>
+      <c r="F1172" t="inlineStr">
+        <is>
+          <t>Vinnyts'ka</t>
+        </is>
+      </c>
+      <c r="G1172" t="n">
+        <v>49.5576747</v>
+      </c>
+      <c r="H1172" t="n">
+        <v>27.9528561</v>
+      </c>
+      <c r="I1172" t="inlineStr">
+        <is>
+          <t>Пн: 08:00-17:00
+Вт: 08:00-17:00
+Ср: 08:00-17:00
+Чт: 08:00-17:00
+Пт: 08:00-17:00
+Сб: 08:00-17:00
+Нд: Вихідний</t>
+        </is>
+      </c>
+      <c r="J1172" t="inlineStr">
+        <is>
+          <t>Vinnyts'ka</t>
+        </is>
+      </c>
+    </row>
+    <row r="1173">
+      <c r="A1173" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1173" t="n">
+        <v>3520</v>
+      </c>
+      <c r="C1173" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1173" t="inlineStr">
+        <is>
+          <t>пл Шевченка 6</t>
+        </is>
+      </c>
+      <c r="E1173" t="inlineStr">
+        <is>
+          <t>Славута</t>
+        </is>
+      </c>
+      <c r="F1173" t="inlineStr">
+        <is>
+          <t>Хмельницька</t>
+        </is>
+      </c>
+      <c r="G1173" t="n">
+        <v>50.2957898</v>
+      </c>
+      <c r="H1173" t="n">
+        <v>26.8570458</v>
+      </c>
+      <c r="I1173" t="inlineStr">
+        <is>
+          <t>Пн: 08:00-17:00
+Вт: 08:00-17:00
+Ср: 08:00-17:00
+Чт: 08:00-17:00
+Пт: 08:00-17:00
+Сб: 08:00-17:00
+Нд: 08:00-17:00</t>
+        </is>
+      </c>
+      <c r="J1173" t="inlineStr">
+        <is>
+          <t>Хмельницька</t>
+        </is>
+      </c>
+    </row>
+    <row r="1174">
+      <c r="A1174" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1174" t="n">
+        <v>3526</v>
+      </c>
+      <c r="C1174" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1174" t="inlineStr">
+        <is>
+          <t>вул Незалежності 65</t>
+        </is>
+      </c>
+      <c r="E1174" t="inlineStr">
+        <is>
+          <t>Камянка-Бузька</t>
+        </is>
+      </c>
+      <c r="F1174" t="inlineStr">
+        <is>
+          <t>Львівська</t>
+        </is>
+      </c>
+      <c r="G1174" t="n">
+        <v>50.107376</v>
+      </c>
+      <c r="H1174" t="n">
+        <v>24.3436341</v>
+      </c>
+      <c r="I1174" t="inlineStr">
+        <is>
+          <t>Пн: 09:00-18:00
+Вт: 09:00-18:00
+Ср: 09:00-18:00
+Чт: 09:00-18:00
+Пт: 09:00-18:00
+Сб: 09:00-16:00
+Нд: 09:00-16:00</t>
+        </is>
+      </c>
+      <c r="J1174" t="inlineStr">
+        <is>
+          <t>Львівська</t>
+        </is>
+      </c>
+    </row>
+    <row r="1175">
+      <c r="A1175" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1175" t="n">
+        <v>3530</v>
+      </c>
+      <c r="C1175" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1175" t="inlineStr">
+        <is>
+          <t>вул Савіцького 14</t>
+        </is>
+      </c>
+      <c r="E1175" t="inlineStr">
+        <is>
+          <t>Летичів</t>
+        </is>
+      </c>
+      <c r="F1175" t="inlineStr">
+        <is>
+          <t>Хмельницька</t>
+        </is>
+      </c>
+      <c r="G1175" t="n">
+        <v>49.3813788</v>
+      </c>
+      <c r="H1175" t="n">
+        <v>27.6197046</v>
+      </c>
+      <c r="I1175" t="inlineStr">
+        <is>
+          <t>Пн: 09:00-18:00
+Вт: 09:00-18:00
+Ср: 09:00-18:00
+Чт: 09:00-18:00
+Пт: 09:00-18:00
+Сб: 09:00-18:00
+Нд: 09:00-18:00</t>
+        </is>
+      </c>
+      <c r="J1175" t="inlineStr">
+        <is>
+          <t>Хмельницька</t>
+        </is>
+      </c>
+    </row>
+    <row r="1176">
+      <c r="A1176" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1176" t="n">
+        <v>3531</v>
+      </c>
+      <c r="C1176" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1176" t="inlineStr">
+        <is>
+          <t>вул Берестейський (Перемоги) 26</t>
+        </is>
+      </c>
+      <c r="E1176" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="F1176" t="inlineStr">
+        <is>
+          <t>м. Київ</t>
+        </is>
+      </c>
+      <c r="G1176" t="n">
+        <v>50.4515345</v>
+      </c>
+      <c r="H1176" t="n">
+        <v>30.4678476</v>
+      </c>
+      <c r="I1176" t="inlineStr">
+        <is>
+          <t>Пн: 10:00-21:00
+Вт: 10:00-21:00
+Ср: 10:00-21:00
+Чт: 10:00-21:00
+Пт: 10:00-21:00
+Сб: 10:00-21:00
+Нд: 10:00-21:00</t>
+        </is>
+      </c>
+      <c r="J1176" t="inlineStr">
+        <is>
+          <t>м. Київ</t>
+        </is>
+      </c>
+    </row>
+    <row r="1177">
+      <c r="A1177" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1177" t="n">
+        <v>3534</v>
+      </c>
+      <c r="C1177" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1177" t="inlineStr">
+        <is>
+          <t>вул Шевченка 74а</t>
+        </is>
+      </c>
+      <c r="E1177" t="inlineStr">
+        <is>
+          <t>Городенка</t>
+        </is>
+      </c>
+      <c r="F1177" t="inlineStr">
+        <is>
+          <t>Івано-Франківська</t>
+        </is>
+      </c>
+      <c r="G1177" t="n">
+        <v>48.66888903427731</v>
+      </c>
+      <c r="H1177" t="n">
+        <v>25.50435338169336</v>
+      </c>
+      <c r="I1177" t="inlineStr">
+        <is>
+          <t>Пн: 08:00-18:00
+Вт: 08:00-18:00
+Ср: 08:00-18:00
+Чт: 08:00-18:00
+Пт: 08:00-18:00
+Сб: 08:00-18:00
+Нд: 10:00-17:00</t>
+        </is>
+      </c>
+      <c r="J1177" t="inlineStr">
+        <is>
+          <t>Івано-Франківська</t>
+        </is>
+      </c>
+    </row>
+    <row r="1178">
+      <c r="A1178" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1178" t="n">
+        <v>3535</v>
+      </c>
+      <c r="C1178" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1178" t="inlineStr">
+        <is>
+          <t>вул Бекетова 21</t>
+        </is>
+      </c>
+      <c r="E1178" t="inlineStr">
+        <is>
+          <t>Харків</t>
+        </is>
+      </c>
+      <c r="F1178" t="inlineStr">
+        <is>
+          <t>Харківська</t>
+        </is>
+      </c>
+      <c r="G1178" t="n">
+        <v>49.9512627</v>
+      </c>
+      <c r="H1178" t="n">
+        <v>36.371922</v>
+      </c>
+      <c r="I1178" t="inlineStr">
+        <is>
+          <t>Пн: 09:00-17:00
+Вт: 09:00-17:00
+Ср: 09:00-17:00
+Чт: 09:00-17:00
+Пт: 09:00-17:00
+Сб: 09:00-17:00
+Нд: 09:00-16:00</t>
+        </is>
+      </c>
+      <c r="J1178" t="inlineStr">
+        <is>
+          <t>Харківська</t>
+        </is>
+      </c>
+    </row>
+    <row r="1179">
+      <c r="A1179" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1179" t="n">
+        <v>3541</v>
+      </c>
+      <c r="C1179" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1179" t="inlineStr">
+        <is>
+          <t>вул Одеська 121, А/1</t>
+        </is>
+      </c>
+      <c r="E1179" t="inlineStr">
+        <is>
+          <t>Первомайськ</t>
+        </is>
+      </c>
+      <c r="F1179" t="inlineStr">
+        <is>
+          <t>Миколаївська</t>
+        </is>
+      </c>
+      <c r="G1179" t="n">
+        <v>48.0228289</v>
+      </c>
+      <c r="H1179" t="n">
+        <v>30.8511121</v>
+      </c>
+      <c r="I1179" t="inlineStr">
+        <is>
+          <t>Пн: 09:00-18:00
+Вт: 09:00-18:00
+Ср: 09:00-18:00
+Чт: 09:00-18:00
+Пт: 09:00-18:00
+Сб: 09:00-18:00
+Нд: 09:00-18:00</t>
+        </is>
+      </c>
+      <c r="J1179" t="inlineStr">
+        <is>
+          <t>Миколаївська</t>
+        </is>
+      </c>
+    </row>
+    <row r="1180">
+      <c r="A1180" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1180" t="n">
+        <v>3542</v>
+      </c>
+      <c r="C1180" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1180" t="inlineStr">
+        <is>
+          <t>просп Героїв Харкова 274</t>
+        </is>
+      </c>
+      <c r="E1180" t="inlineStr">
+        <is>
+          <t>Харків</t>
+        </is>
+      </c>
+      <c r="F1180" t="inlineStr">
+        <is>
+          <t>Харківська</t>
+        </is>
+      </c>
+      <c r="G1180" t="n">
+        <v>49.9432342</v>
+      </c>
+      <c r="H1180" t="n">
+        <v>36.3984342</v>
+      </c>
+      <c r="I1180" t="inlineStr">
+        <is>
+          <t>Пн: 09:00-18:00
+Вт: 09:00-18:00
+Ср: 09:00-18:00
+Чт: 09:00-18:00
+Пт: 09:00-18:00
+Сб: 09:00-17:00
 Нд: 09:00-17:00</t>
         </is>
       </c>
-      <c r="J1142" t="inlineStr">
+      <c r="J1180" t="inlineStr">
+        <is>
+          <t>Харківська</t>
+        </is>
+      </c>
+    </row>
+    <row r="1181">
+      <c r="A1181" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1181" t="n">
+        <v>3543</v>
+      </c>
+      <c r="C1181" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1181" t="inlineStr">
+        <is>
+          <t>вул Салтівське шосе 147</t>
+        </is>
+      </c>
+      <c r="E1181" t="inlineStr">
+        <is>
+          <t>Харків</t>
+        </is>
+      </c>
+      <c r="F1181" t="inlineStr">
+        <is>
+          <t>Харківська</t>
+        </is>
+      </c>
+      <c r="G1181" t="n">
+        <v>49.9908024</v>
+      </c>
+      <c r="H1181" t="n">
+        <v>36.3585856</v>
+      </c>
+      <c r="I1181" t="inlineStr">
+        <is>
+          <t>Пн: 09:00-18:00
+Вт: 09:00-18:00
+Ср: 09:00-18:00
+Чт: 09:00-18:00
+Пт: 09:00-18:00
+Сб: 09:00-17:00
+Нд: 09:00-17:00</t>
+        </is>
+      </c>
+      <c r="J1181" t="inlineStr">
+        <is>
+          <t>Харківська</t>
+        </is>
+      </c>
+    </row>
+    <row r="1182">
+      <c r="A1182" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1182" t="n">
+        <v>3544</v>
+      </c>
+      <c r="C1182" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1182" t="inlineStr">
+        <is>
+          <t>просп Петра Григоренка 3</t>
+        </is>
+      </c>
+      <c r="E1182" t="inlineStr">
+        <is>
+          <t>Харків</t>
+        </is>
+      </c>
+      <c r="F1182" t="inlineStr">
+        <is>
+          <t>Харківська</t>
+        </is>
+      </c>
+      <c r="G1182" t="n">
+        <v>49.9650438</v>
+      </c>
+      <c r="H1182" t="n">
+        <v>36.3219614</v>
+      </c>
+      <c r="I1182" t="inlineStr">
+        <is>
+          <t>Пн: 09:00-18:00
+Вт: 09:00-18:00
+Ср: 09:00-18:00
+Чт: 09:00-18:00
+Пт: 09:00-18:00
+Сб: 09:00-17:00
+Нд: 09:00-17:00</t>
+        </is>
+      </c>
+      <c r="J1182" t="inlineStr">
+        <is>
+          <t>Харківська</t>
+        </is>
+      </c>
+    </row>
+    <row r="1183">
+      <c r="A1183" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1183" t="n">
+        <v>3545</v>
+      </c>
+      <c r="C1183" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1183" t="inlineStr">
+        <is>
+          <t>просп Аерокосмічний (Гагаріна) 177</t>
+        </is>
+      </c>
+      <c r="E1183" t="inlineStr">
+        <is>
+          <t>Харків</t>
+        </is>
+      </c>
+      <c r="F1183" t="inlineStr">
+        <is>
+          <t>Харківська</t>
+        </is>
+      </c>
+      <c r="G1183" t="n">
+        <v>50.0169162</v>
+      </c>
+      <c r="H1183" t="n">
+        <v>36.2067146</v>
+      </c>
+      <c r="I1183" t="inlineStr">
+        <is>
+          <t>Пн: 09:00-18:00
+Вт: 09:00-18:00
+Ср: 09:00-18:00
+Чт: 09:00-18:00
+Пт: 09:00-18:00
+Сб: 09:00-17:00
+Нд: 09:00-17:00</t>
+        </is>
+      </c>
+      <c r="J1183" t="inlineStr">
+        <is>
+          <t>Харківська</t>
+        </is>
+      </c>
+    </row>
+    <row r="1184">
+      <c r="A1184" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1184" t="n">
+        <v>3547</v>
+      </c>
+      <c r="C1184" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1184" t="inlineStr">
+        <is>
+          <t>вул Олімпійська 75</t>
+        </is>
+      </c>
+      <c r="E1184" t="inlineStr">
+        <is>
+          <t>Хотин</t>
+        </is>
+      </c>
+      <c r="F1184" t="inlineStr">
+        <is>
+          <t>Чернівецька</t>
+        </is>
+      </c>
+      <c r="G1184" t="n">
+        <v>48.5043413</v>
+      </c>
+      <c r="H1184" t="n">
+        <v>26.490402</v>
+      </c>
+      <c r="I1184" t="inlineStr">
+        <is>
+          <t>Пн: 09:00-18:00
+Вт: 09:00-18:00
+Ср: 09:00-18:00
+Чт: 09:00-18:00
+Пт: 09:00-18:00
+Сб: 09:00-17:00
+Нд: 10:00-14:00</t>
+        </is>
+      </c>
+      <c r="J1184" t="inlineStr">
+        <is>
+          <t>Чернівецька</t>
+        </is>
+      </c>
+    </row>
+    <row r="1185">
+      <c r="A1185" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1185" t="n">
+        <v>3549</v>
+      </c>
+      <c r="C1185" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1185" t="inlineStr">
+        <is>
+          <t>вул Жовтнева 4-А</t>
+        </is>
+      </c>
+      <c r="E1185" t="inlineStr">
+        <is>
+          <t>Гребінка</t>
+        </is>
+      </c>
+      <c r="F1185" t="inlineStr">
         <is>
           <t>Полтавська</t>
         </is>
       </c>
-    </row>
-    <row r="1143">
-      <c r="A1143" t="inlineStr">
+      <c r="G1185" t="n">
+        <v>50.1185138</v>
+      </c>
+      <c r="H1185" t="n">
+        <v>32.4391051</v>
+      </c>
+      <c r="I1185" t="inlineStr">
+        <is>
+          <t>Пн: 09:00-17:00
+Вт: 09:00-17:00
+Ср: 09:00-17:00
+Чт: 09:00-17:00
+Пт: 09:00-17:00
+Сб: 09:00-14:00
+Нд: 09:00-14:00</t>
+        </is>
+      </c>
+      <c r="J1185" t="inlineStr">
+        <is>
+          <t>Полтавська</t>
+        </is>
+      </c>
+    </row>
+    <row r="1186">
+      <c r="A1186" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1143" t="n">
-        <v>3428</v>
-      </c>
-      <c r="C1143" t="inlineStr">
+      <c r="B1186" t="n">
+        <v>3554</v>
+      </c>
+      <c r="C1186" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1143" t="inlineStr">
-        <is>
-          <t>пл Миру 11</t>
-        </is>
-      </c>
-      <c r="E1143" t="inlineStr">
-        <is>
-          <t>Гадяч</t>
-        </is>
-      </c>
-      <c r="F1143" t="inlineStr">
-        <is>
-          <t>Полтавська</t>
-        </is>
-      </c>
-      <c r="G1143" t="n">
-        <v>50.3739846</v>
-      </c>
-      <c r="H1143" t="n">
-        <v>33.9836438</v>
-      </c>
-      <c r="I1143" t="inlineStr">
+      <c r="D1186" t="inlineStr">
+        <is>
+          <t>вул Городоцька 137</t>
+        </is>
+      </c>
+      <c r="E1186" t="inlineStr">
+        <is>
+          <t>Львів</t>
+        </is>
+      </c>
+      <c r="F1186" t="inlineStr">
+        <is>
+          <t>Львівська</t>
+        </is>
+      </c>
+      <c r="G1186" t="n">
+        <v>49.8367768</v>
+      </c>
+      <c r="H1186" t="n">
+        <v>24.0028087</v>
+      </c>
+      <c r="I1186" t="inlineStr">
+        <is>
+          <t>Пн: 09:00-19:00
+Вт: 09:00-19:00
+Ср: 09:00-19:00
+Чт: 09:00-19:00
+Пт: 09:00-19:00
+Сб: 09:00-18:00
+Нд: 10:00-18:00</t>
+        </is>
+      </c>
+      <c r="J1186" t="inlineStr">
+        <is>
+          <t>Львівська</t>
+        </is>
+      </c>
+    </row>
+    <row r="1187">
+      <c r="A1187" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1187" t="n">
+        <v>3555</v>
+      </c>
+      <c r="C1187" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1187" t="inlineStr">
+        <is>
+          <t>вул Здолбунівська 15</t>
+        </is>
+      </c>
+      <c r="E1187" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="F1187" t="inlineStr">
+        <is>
+          <t>м. Київ</t>
+        </is>
+      </c>
+      <c r="G1187" t="n">
+        <v>50.4185123</v>
+      </c>
+      <c r="H1187" t="n">
+        <v>30.631541</v>
+      </c>
+      <c r="I1187" t="inlineStr">
+        <is>
+          <t>Пн: 10:00-20:00
+Вт: 10:00-20:00
+Ср: 10:00-20:00
+Чт: 10:00-20:00
+Пт: 10:00-20:00
+Сб: 10:00-20:00
+Нд: 10:00-20:00</t>
+        </is>
+      </c>
+      <c r="J1187" t="inlineStr">
+        <is>
+          <t>м. Київ</t>
+        </is>
+      </c>
+    </row>
+    <row r="1188">
+      <c r="A1188" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1188" t="n">
+        <v>3556</v>
+      </c>
+      <c r="C1188" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1188" t="inlineStr">
+        <is>
+          <t>вул Шевченка 42</t>
+        </is>
+      </c>
+      <c r="E1188" t="inlineStr">
+        <is>
+          <t>Овруч</t>
+        </is>
+      </c>
+      <c r="F1188" t="inlineStr">
+        <is>
+          <t>Житомирська</t>
+        </is>
+      </c>
+      <c r="G1188" t="n">
+        <v>51.3197441</v>
+      </c>
+      <c r="H1188" t="n">
+        <v>28.8004248</v>
+      </c>
+      <c r="I1188" t="inlineStr">
+        <is>
+          <t>Пн: 09:00-18:00
+Вт: 09:00-18:00
+Ср: 09:00-18:00
+Чт: 09:00-18:00
+Пт: 09:00-18:00
+Сб: 09:00-18:00
+Нд: 09:00-18:00</t>
+        </is>
+      </c>
+      <c r="J1188" t="inlineStr">
+        <is>
+          <t>Житомирська</t>
+        </is>
+      </c>
+    </row>
+    <row r="1189">
+      <c r="A1189" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1189" t="n">
+        <v>3558</v>
+      </c>
+      <c r="C1189" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1189" t="inlineStr">
+        <is>
+          <t>вул Київська 26</t>
+        </is>
+      </c>
+      <c r="E1189" t="inlineStr">
+        <is>
+          <t>Іванків</t>
+        </is>
+      </c>
+      <c r="F1189" t="inlineStr">
+        <is>
+          <t>Kiev</t>
+        </is>
+      </c>
+      <c r="G1189" t="n">
+        <v>50.9338356</v>
+      </c>
+      <c r="H1189" t="n">
+        <v>29.9031381</v>
+      </c>
+      <c r="I1189" t="inlineStr">
+        <is>
+          <t>Пн: 08:00-18:00
+Вт: 08:00-18:00
+Ср: 08:00-18:00
+Чт: 08:00-18:00
+Пт: 08:00-18:00
+Сб: 08:00-18:00
+Нд: 09:00-17:00</t>
+        </is>
+      </c>
+      <c r="J1189" t="inlineStr">
+        <is>
+          <t>Kiev</t>
+        </is>
+      </c>
+    </row>
+    <row r="1190">
+      <c r="A1190" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1190" t="n">
+        <v>3559</v>
+      </c>
+      <c r="C1190" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1190" t="inlineStr">
+        <is>
+          <t>просп Соборний 51</t>
+        </is>
+      </c>
+      <c r="E1190" t="inlineStr">
+        <is>
+          <t>Запоріжжя</t>
+        </is>
+      </c>
+      <c r="F1190" t="inlineStr">
+        <is>
+          <t>Zaporizhia</t>
+        </is>
+      </c>
+      <c r="G1190" t="n">
+        <v>47.8176164</v>
+      </c>
+      <c r="H1190" t="n">
+        <v>35.1753352</v>
+      </c>
+      <c r="I1190" t="inlineStr">
+        <is>
+          <t>Пн: 09:00-19:00
+Вт: 09:00-19:00
+Ср: 09:00-19:00
+Чт: 09:00-19:00
+Пт: 09:00-19:00
+Сб: 09:00-19:00
+Нд: 10:00-18:00</t>
+        </is>
+      </c>
+      <c r="J1190" t="inlineStr">
+        <is>
+          <t>Zaporizhia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1191">
+      <c r="A1191" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1191" t="n">
+        <v>3560</v>
+      </c>
+      <c r="C1191" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1191" t="inlineStr">
+        <is>
+          <t>вул Палацова 9</t>
+        </is>
+      </c>
+      <c r="E1191" t="inlineStr">
+        <is>
+          <t>Краматорськ</t>
+        </is>
+      </c>
+      <c r="F1191" t="inlineStr">
+        <is>
+          <t>Донецька</t>
+        </is>
+      </c>
+      <c r="G1191" t="n">
+        <v>48.7366237</v>
+      </c>
+      <c r="H1191" t="n">
+        <v>37.5916381</v>
+      </c>
+      <c r="I1191" t="inlineStr">
         <is>
           <t>Пн: 09:00-17:00
 Вт: 09:00-17:00
@@ -52736,152 +55232,308 @@
 Нд: 09:00-17:00</t>
         </is>
       </c>
-      <c r="J1143" t="inlineStr">
-        <is>
-          <t>Полтавська</t>
-        </is>
-      </c>
-    </row>
-    <row r="1144">
-      <c r="A1144" t="inlineStr">
+      <c r="J1191" t="inlineStr">
+        <is>
+          <t>Донецька</t>
+        </is>
+      </c>
+    </row>
+    <row r="1192">
+      <c r="A1192" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1144" t="n">
-        <v>3432</v>
-      </c>
-      <c r="C1144" t="inlineStr">
+      <c r="B1192" t="n">
+        <v>3561</v>
+      </c>
+      <c r="C1192" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1144" t="inlineStr">
-        <is>
-          <t>бул Шевченка 385</t>
-        </is>
-      </c>
-      <c r="E1144" t="inlineStr">
-        <is>
-          <t>Черкаси</t>
-        </is>
-      </c>
-      <c r="F1144" t="inlineStr">
-        <is>
-          <t>Черкаська</t>
-        </is>
-      </c>
-      <c r="G1144" t="n">
-        <v>49.424669</v>
-      </c>
-      <c r="H1144" t="n">
-        <v>32.0953677</v>
-      </c>
-      <c r="I1144" t="inlineStr">
-        <is>
-          <t>Пн: 10:00-20:00
-Вт: 10:00-20:00
-Ср: 10:00-20:00
-Чт: 10:00-20:00
-Пт: 10:00-20:00
-Сб: 10:00-20:00
-Нд: 10:00-20:00</t>
-        </is>
-      </c>
-      <c r="J1144" t="inlineStr">
-        <is>
-          <t>Черкаська</t>
-        </is>
-      </c>
-    </row>
-    <row r="1145">
-      <c r="A1145" t="inlineStr">
+      <c r="D1192" t="inlineStr">
+        <is>
+          <t>вул Ф. Караманець (Ватутіна) 29</t>
+        </is>
+      </c>
+      <c r="E1192" t="inlineStr">
+        <is>
+          <t>Кривий Ріг</t>
+        </is>
+      </c>
+      <c r="F1192" t="inlineStr">
+        <is>
+          <t>Дніпропетровська</t>
+        </is>
+      </c>
+      <c r="G1192" t="n">
+        <v>48.024687</v>
+      </c>
+      <c r="H1192" t="n">
+        <v>33.4709468</v>
+      </c>
+      <c r="I1192" t="inlineStr">
+        <is>
+          <t>Пн: 09:00-18:00
+Вт: 09:00-18:00
+Ср: 09:00-18:00
+Чт: 09:00-18:00
+Пт: 09:00-18:00
+Сб: Вихідний
+Нд: Вихідний</t>
+        </is>
+      </c>
+      <c r="J1192" t="inlineStr">
+        <is>
+          <t>Дніпропетровська</t>
+        </is>
+      </c>
+    </row>
+    <row r="1193">
+      <c r="A1193" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1145" t="n">
-        <v>3435</v>
-      </c>
-      <c r="C1145" t="inlineStr">
+      <c r="B1193" t="n">
+        <v>3563</v>
+      </c>
+      <c r="C1193" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1145" t="inlineStr">
-        <is>
-          <t>просп Науки 1/2</t>
-        </is>
-      </c>
-      <c r="E1145" t="inlineStr">
-        <is>
-          <t>Київ</t>
-        </is>
-      </c>
-      <c r="F1145" t="inlineStr">
-        <is>
-          <t>м. Київ</t>
-        </is>
-      </c>
-      <c r="G1145" t="n">
-        <v>50.4064898</v>
-      </c>
-      <c r="H1145" t="n">
-        <v>30.519621</v>
-      </c>
-      <c r="I1145" t="inlineStr">
-        <is>
-          <t>Пн: 07:00-22:00
-Вт: 07:00-22:00
-Ср: 07:00-22:00
-Чт: 07:00-22:00
-Пт: 07:00-22:00
-Сб: 07:00-22:00
-Нд: 07:00-22:00</t>
-        </is>
-      </c>
-      <c r="J1145" t="inlineStr">
-        <is>
-          <t>м. Київ</t>
-        </is>
-      </c>
-    </row>
-    <row r="1146">
-      <c r="A1146" t="inlineStr">
+      <c r="D1193" t="inlineStr">
+        <is>
+          <t>вул Шевченка 116</t>
+        </is>
+      </c>
+      <c r="E1193" t="inlineStr">
+        <is>
+          <t>Дунаївці</t>
+        </is>
+      </c>
+      <c r="F1193" t="inlineStr">
+        <is>
+          <t>Хмельницька</t>
+        </is>
+      </c>
+      <c r="G1193" t="n">
+        <v>48.8922754</v>
+      </c>
+      <c r="H1193" t="n">
+        <v>26.8568241</v>
+      </c>
+      <c r="I1193" t="inlineStr">
+        <is>
+          <t>Пн: 09:00-18:00
+Вт: 09:00-18:00
+Ср: 09:00-18:00
+Чт: 09:00-18:00
+Пт: 09:00-18:00
+Сб: 09:00-14:00
+Нд: Вихідний</t>
+        </is>
+      </c>
+      <c r="J1193" t="inlineStr">
+        <is>
+          <t>Хмельницька</t>
+        </is>
+      </c>
+    </row>
+    <row r="1194">
+      <c r="A1194" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1146" t="n">
-        <v>3437</v>
-      </c>
-      <c r="C1146" t="inlineStr">
+      <c r="B1194" t="n">
+        <v>3566</v>
+      </c>
+      <c r="C1194" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1146" t="inlineStr">
-        <is>
-          <t>просп Богоявленський 338</t>
-        </is>
-      </c>
-      <c r="E1146" t="inlineStr">
-        <is>
-          <t>Миколаїв (Миколаївська)</t>
-        </is>
-      </c>
-      <c r="F1146" t="inlineStr">
-        <is>
-          <t>Миколаївська</t>
-        </is>
-      </c>
-      <c r="G1146" t="n">
-        <v>46.8557792</v>
-      </c>
-      <c r="H1146" t="n">
-        <v>32.0141945</v>
-      </c>
-      <c r="I1146" t="inlineStr">
+      <c r="D1194" t="inlineStr">
+        <is>
+          <t>вул Р. Шухевича 1а</t>
+        </is>
+      </c>
+      <c r="E1194" t="inlineStr">
+        <is>
+          <t>Хмельницький</t>
+        </is>
+      </c>
+      <c r="F1194" t="inlineStr">
+        <is>
+          <t>Хмельницька</t>
+        </is>
+      </c>
+      <c r="G1194" t="n">
+        <v>49.4360713</v>
+      </c>
+      <c r="H1194" t="n">
+        <v>26.9572295</v>
+      </c>
+      <c r="I1194" t="inlineStr">
+        <is>
+          <t>Пн: 09:00-19:00
+Вт: 09:00-19:00
+Ср: 09:00-19:00
+Чт: 09:00-19:00
+Пт: 09:00-19:00
+Сб: 10:00-18:00
+Нд: 10:00-18:00</t>
+        </is>
+      </c>
+      <c r="J1194" t="inlineStr">
+        <is>
+          <t>Хмельницька</t>
+        </is>
+      </c>
+    </row>
+    <row r="1195">
+      <c r="A1195" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1195" t="n">
+        <v>3567</v>
+      </c>
+      <c r="C1195" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1195" t="inlineStr">
+        <is>
+          <t>вул Макухи 1</t>
+        </is>
+      </c>
+      <c r="E1195" t="inlineStr">
+        <is>
+          <t>Тлумач</t>
+        </is>
+      </c>
+      <c r="F1195" t="inlineStr">
+        <is>
+          <t>Івано-Франківська</t>
+        </is>
+      </c>
+      <c r="G1195" t="n">
+        <v>48.8652727</v>
+      </c>
+      <c r="H1195" t="n">
+        <v>25.0043864</v>
+      </c>
+      <c r="I1195" t="inlineStr">
+        <is>
+          <t>Пн: 09:00-17:00
+Вт: 09:00-17:00
+Ср: 09:00-17:00
+Чт: 09:00-17:00
+Пт: 09:00-17:00
+Сб: Вихідний
+Нд: Вихідний</t>
+        </is>
+      </c>
+      <c r="J1195" t="inlineStr">
+        <is>
+          <t>Івано-Франківська</t>
+        </is>
+      </c>
+    </row>
+    <row r="1196">
+      <c r="A1196" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1196" t="n">
+        <v>3568</v>
+      </c>
+      <c r="C1196" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1196" t="inlineStr">
+        <is>
+          <t>вул Андріївська 5</t>
+        </is>
+      </c>
+      <c r="E1196" t="inlineStr">
+        <is>
+          <t>Березне</t>
+        </is>
+      </c>
+      <c r="F1196" t="inlineStr">
+        <is>
+          <t>Рівненська</t>
+        </is>
+      </c>
+      <c r="G1196" t="n">
+        <v>51.0019955</v>
+      </c>
+      <c r="H1196" t="n">
+        <v>26.7547284</v>
+      </c>
+      <c r="I1196" t="inlineStr">
+        <is>
+          <t>Пн: 09:00-18:00
+Вт: 09:00-18:00
+Ср: 09:00-18:00
+Чт: 09:00-18:00
+Пт: 09:00-18:00
+Сб: 09:00-16:00
+Нд: 09:00-16:00</t>
+        </is>
+      </c>
+      <c r="J1196" t="inlineStr">
+        <is>
+          <t>Рівненська</t>
+        </is>
+      </c>
+    </row>
+    <row r="1197">
+      <c r="A1197" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1197" t="n">
+        <v>3569</v>
+      </c>
+      <c r="C1197" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1197" t="inlineStr">
+        <is>
+          <t>вул Широка 37</t>
+        </is>
+      </c>
+      <c r="E1197" t="inlineStr">
+        <is>
+          <t>Сарни</t>
+        </is>
+      </c>
+      <c r="F1197" t="inlineStr">
+        <is>
+          <t>Рівненська</t>
+        </is>
+      </c>
+      <c r="G1197" t="n">
+        <v>51.3355537</v>
+      </c>
+      <c r="H1197" t="n">
+        <v>26.6158412</v>
+      </c>
+      <c r="I1197" t="inlineStr">
         <is>
           <t>Пн: 09:00-18:00
 Вт: 09:00-18:00
@@ -52889,51 +55541,207 @@
 Чт: 09:00-18:00
 Пт: 09:00-18:00
 Сб: 09:00-18:00
-Нд: 09:00-18:00</t>
-        </is>
-      </c>
-      <c r="J1146" t="inlineStr">
-        <is>
-          <t>Миколаївська</t>
-        </is>
-      </c>
-    </row>
-    <row r="1147">
-      <c r="A1147" t="inlineStr">
+Нд: 09:00-17:00</t>
+        </is>
+      </c>
+      <c r="J1197" t="inlineStr">
+        <is>
+          <t>Рівненська</t>
+        </is>
+      </c>
+    </row>
+    <row r="1198">
+      <c r="A1198" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1147" t="n">
-        <v>3441</v>
-      </c>
-      <c r="C1147" t="inlineStr">
+      <c r="B1198" t="n">
+        <v>3570</v>
+      </c>
+      <c r="C1198" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1147" t="inlineStr">
-        <is>
-          <t>вул Українська 71а</t>
-        </is>
-      </c>
-      <c r="E1147" t="inlineStr">
-        <is>
-          <t>Путила</t>
-        </is>
-      </c>
-      <c r="F1147" t="inlineStr">
-        <is>
-          <t>Чернівецька</t>
-        </is>
-      </c>
-      <c r="G1147" t="n">
-        <v>47.998305</v>
-      </c>
-      <c r="H1147" t="n">
-        <v>25.0850933</v>
-      </c>
-      <c r="I1147" t="inlineStr">
+      <c r="D1198" t="inlineStr">
+        <is>
+          <t>вул Січових Стрільців 33А</t>
+        </is>
+      </c>
+      <c r="E1198" t="inlineStr">
+        <is>
+          <t>Бурштин</t>
+        </is>
+      </c>
+      <c r="F1198" t="inlineStr">
+        <is>
+          <t>Івано-Франківська</t>
+        </is>
+      </c>
+      <c r="G1198" t="n">
+        <v>49.2511835</v>
+      </c>
+      <c r="H1198" t="n">
+        <v>24.6288295</v>
+      </c>
+      <c r="I1198" t="inlineStr">
+        <is>
+          <t>Пн: 09:00-18:00
+Вт: 09:00-18:00
+Ср: 09:00-18:00
+Чт: 09:00-18:00
+Пт: 09:00-18:00
+Сб: 09:00-17:00
+Нд: Вихідний</t>
+        </is>
+      </c>
+      <c r="J1198" t="inlineStr">
+        <is>
+          <t>Івано-Франківська</t>
+        </is>
+      </c>
+    </row>
+    <row r="1199">
+      <c r="A1199" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1199" t="n">
+        <v>3571</v>
+      </c>
+      <c r="C1199" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1199" t="inlineStr">
+        <is>
+          <t>вул Небесної Сотні 85</t>
+        </is>
+      </c>
+      <c r="E1199" t="inlineStr">
+        <is>
+          <t>Романів</t>
+        </is>
+      </c>
+      <c r="F1199" t="inlineStr">
+        <is>
+          <t>Житомирська</t>
+        </is>
+      </c>
+      <c r="G1199" t="n">
+        <v>50.141605</v>
+      </c>
+      <c r="H1199" t="n">
+        <v>27.934655</v>
+      </c>
+      <c r="I1199" t="inlineStr">
+        <is>
+          <t>Пн: 08:00-18:00
+Вт: 08:00-18:00
+Ср: 08:00-18:00
+Чт: 08:00-18:00
+Пт: 08:00-18:00
+Сб: 08:00-17:00
+Нд: 09:00-17:00</t>
+        </is>
+      </c>
+      <c r="J1199" t="inlineStr">
+        <is>
+          <t>Житомирська</t>
+        </is>
+      </c>
+    </row>
+    <row r="1200">
+      <c r="A1200" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1200" t="n">
+        <v>3573</v>
+      </c>
+      <c r="C1200" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1200" t="inlineStr">
+        <is>
+          <t>вул Велика Окружна 4</t>
+        </is>
+      </c>
+      <c r="E1200" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="F1200" t="inlineStr">
+        <is>
+          <t>Kiev</t>
+        </is>
+      </c>
+      <c r="G1200" t="n">
+        <v>50.4295904</v>
+      </c>
+      <c r="H1200" t="n">
+        <v>30.3567847</v>
+      </c>
+      <c r="I1200" t="inlineStr">
+        <is>
+          <t>Пн: 10:00-21:00
+Вт: 10:00-21:00
+Ср: 10:00-21:00
+Чт: 10:00-21:00
+Пт: 10:00-21:00
+Сб: 10:00-21:00
+Нд: 10:00-21:00</t>
+        </is>
+      </c>
+      <c r="J1200" t="inlineStr">
+        <is>
+          <t>Kiev</t>
+        </is>
+      </c>
+    </row>
+    <row r="1201">
+      <c r="A1201" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1201" t="n">
+        <v>3574</v>
+      </c>
+      <c r="C1201" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1201" t="inlineStr">
+        <is>
+          <t>вул Шевченка 50</t>
+        </is>
+      </c>
+      <c r="E1201" t="inlineStr">
+        <is>
+          <t>Богородчани</t>
+        </is>
+      </c>
+      <c r="F1201" t="inlineStr">
+        <is>
+          <t>Івано-Франківська</t>
+        </is>
+      </c>
+      <c r="G1201" t="n">
+        <v>48.809756</v>
+      </c>
+      <c r="H1201" t="n">
+        <v>24.5400082</v>
+      </c>
+      <c r="I1201" t="inlineStr">
         <is>
           <t>Пн: 09:00-18:00
 Вт: 09:00-18:00
@@ -52944,464 +55752,360 @@
 Нд: 10:00-16:00</t>
         </is>
       </c>
-      <c r="J1147" t="inlineStr">
-        <is>
-          <t>Чернівецька</t>
-        </is>
-      </c>
-    </row>
-    <row r="1148">
-      <c r="A1148" t="inlineStr">
+      <c r="J1201" t="inlineStr">
+        <is>
+          <t>Івано-Франківська</t>
+        </is>
+      </c>
+    </row>
+    <row r="1202">
+      <c r="A1202" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1148" t="n">
-        <v>3445</v>
-      </c>
-      <c r="C1148" t="inlineStr">
+      <c r="B1202" t="n">
+        <v>3575</v>
+      </c>
+      <c r="C1202" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1148" t="inlineStr">
-        <is>
-          <t>вул Шевченка 73</t>
-        </is>
-      </c>
-      <c r="E1148" t="inlineStr">
-        <is>
-          <t>Снятин</t>
-        </is>
-      </c>
-      <c r="F1148" t="inlineStr">
-        <is>
-          <t>Івано-Франківська</t>
-        </is>
-      </c>
-      <c r="G1148" t="n">
-        <v>48.4514483</v>
-      </c>
-      <c r="H1148" t="n">
-        <v>25.5551122</v>
-      </c>
-      <c r="I1148" t="inlineStr">
+      <c r="D1202" t="inlineStr">
+        <is>
+          <t>просп Богдана Хмельницкого (Героїв Сталінграда) 118Д</t>
+        </is>
+      </c>
+      <c r="E1202" t="inlineStr">
+        <is>
+          <t>Дніпро</t>
+        </is>
+      </c>
+      <c r="F1202" t="inlineStr">
+        <is>
+          <t>Дніпропетровська</t>
+        </is>
+      </c>
+      <c r="G1202" t="n">
+        <v>48.4076054</v>
+      </c>
+      <c r="H1202" t="n">
+        <v>35.0004028</v>
+      </c>
+      <c r="I1202" t="inlineStr">
+        <is>
+          <t>Пн: 09:00-19:00
+Вт: 09:00-19:00
+Ср: 09:00-19:00
+Чт: 09:00-19:00
+Пт: 09:00-19:00
+Сб: 09:00-19:00
+Нд: 09:00-19:00</t>
+        </is>
+      </c>
+      <c r="J1202" t="inlineStr">
+        <is>
+          <t>Дніпропетровська</t>
+        </is>
+      </c>
+    </row>
+    <row r="1203">
+      <c r="A1203" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1203" t="n">
+        <v>3577</v>
+      </c>
+      <c r="C1203" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1203" t="inlineStr">
+        <is>
+          <t>вул Харківська 2/2</t>
+        </is>
+      </c>
+      <c r="E1203" t="inlineStr">
+        <is>
+          <t>Суми</t>
+        </is>
+      </c>
+      <c r="F1203" t="inlineStr">
+        <is>
+          <t>Сумська</t>
+        </is>
+      </c>
+      <c r="G1203" t="n">
+        <v>50.9041752</v>
+      </c>
+      <c r="H1203" t="n">
+        <v>34.8048057</v>
+      </c>
+      <c r="I1203" t="inlineStr">
+        <is>
+          <t>Пн: 10:00-19:00
+Вт: 10:00-19:00
+Ср: 10:00-19:00
+Чт: 10:00-19:00
+Пт: 10:00-19:00
+Сб: 10:00-19:00
+Нд: 10:00-19:00</t>
+        </is>
+      </c>
+      <c r="J1203" t="inlineStr">
+        <is>
+          <t>Сумська</t>
+        </is>
+      </c>
+    </row>
+    <row r="1204">
+      <c r="A1204" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1204" t="n">
+        <v>3579</v>
+      </c>
+      <c r="C1204" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1204" t="inlineStr">
+        <is>
+          <t>вул Грушевського 41А</t>
+        </is>
+      </c>
+      <c r="E1204" t="inlineStr">
+        <is>
+          <t>Первомайськ</t>
+        </is>
+      </c>
+      <c r="F1204" t="inlineStr">
+        <is>
+          <t>Миколаївська</t>
+        </is>
+      </c>
+      <c r="G1204" t="n">
+        <v>48.0425652</v>
+      </c>
+      <c r="H1204" t="n">
+        <v>30.8444596</v>
+      </c>
+      <c r="I1204" t="inlineStr">
+        <is>
+          <t>Пн: 08:00-18:00
+Вт: 08:00-18:00
+Ср: 08:00-18:00
+Чт: 08:00-18:00
+Пт: 08:00-18:00
+Сб: 10:00-17:00
+Нд: Вихідний</t>
+        </is>
+      </c>
+      <c r="J1204" t="inlineStr">
+        <is>
+          <t>Миколаївська</t>
+        </is>
+      </c>
+    </row>
+    <row r="1205">
+      <c r="A1205" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1205" t="n">
+        <v>3581</v>
+      </c>
+      <c r="C1205" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1205" t="inlineStr">
+        <is>
+          <t>вул Петровського, павільйон №8 2</t>
+        </is>
+      </c>
+      <c r="E1205" t="inlineStr">
+        <is>
+          <t>Городня</t>
+        </is>
+      </c>
+      <c r="F1205" t="inlineStr">
+        <is>
+          <t>Чернігівська</t>
+        </is>
+      </c>
+      <c r="G1205" t="n">
+        <v>51.8859534</v>
+      </c>
+      <c r="H1205" t="n">
+        <v>31.6026785</v>
+      </c>
+      <c r="I1205" t="inlineStr">
+        <is>
+          <t>Пн: 09:00-17:00
+Вт: 09:00-17:00
+Ср: 09:00-17:00
+Чт: 09:00-17:00
+Пт: Вихідний
+Сб: 09:00-14:00
+Нд: 09:00-14:00</t>
+        </is>
+      </c>
+      <c r="J1205" t="inlineStr">
+        <is>
+          <t>Чернігівська</t>
+        </is>
+      </c>
+    </row>
+    <row r="1206">
+      <c r="A1206" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1206" t="n">
+        <v>3582</v>
+      </c>
+      <c r="C1206" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1206" t="inlineStr">
+        <is>
+          <t>вул Святоюріївська 10/2</t>
+        </is>
+      </c>
+      <c r="E1206" t="inlineStr">
+        <is>
+          <t>Вишневе</t>
+        </is>
+      </c>
+      <c r="F1206" t="inlineStr">
+        <is>
+          <t>Kiev</t>
+        </is>
+      </c>
+      <c r="G1206" t="n">
+        <v>50.3833741</v>
+      </c>
+      <c r="H1206" t="n">
+        <v>30.3731464</v>
+      </c>
+      <c r="I1206" t="inlineStr">
+        <is>
+          <t>Пн: 09:00-19:00
+Вт: Вихідний
+Ср: 09:00-19:00
+Чт: 09:00-19:00
+Пт: Вихідний
+Сб: 09:00-19:00
+Нд: 09:00-19:00</t>
+        </is>
+      </c>
+      <c r="J1206" t="inlineStr">
+        <is>
+          <t>Kiev</t>
+        </is>
+      </c>
+    </row>
+    <row r="1207">
+      <c r="A1207" t="inlineStr">
+        <is>
+          <t>kyivstar</t>
+        </is>
+      </c>
+      <c r="B1207" t="n">
+        <v>3583</v>
+      </c>
+      <c r="C1207" t="inlineStr">
+        <is>
+          <t>Kyivstar</t>
+        </is>
+      </c>
+      <c r="D1207" t="inlineStr">
+        <is>
+          <t>просп Відрадний 69/1</t>
+        </is>
+      </c>
+      <c r="E1207" t="inlineStr">
+        <is>
+          <t>Київ</t>
+        </is>
+      </c>
+      <c r="F1207" t="inlineStr">
+        <is>
+          <t>Kiev</t>
+        </is>
+      </c>
+      <c r="G1207" t="n">
+        <v>50.428885</v>
+      </c>
+      <c r="H1207" t="n">
+        <v>30.4309396</v>
+      </c>
+      <c r="I1207" t="inlineStr">
         <is>
           <t>Пн: 09:00-18:00
 Вт: 09:00-18:00
 Ср: 09:00-18:00
 Чт: 09:00-18:00
 Пт: 09:00-18:00
-Сб: 09:00-15:00
+Сб: 10:00-17:00
 Нд: Вихідний</t>
         </is>
       </c>
-      <c r="J1148" t="inlineStr">
-        <is>
-          <t>Івано-Франківська</t>
-        </is>
-      </c>
-    </row>
-    <row r="1149">
-      <c r="A1149" t="inlineStr">
+      <c r="J1207" t="inlineStr">
+        <is>
+          <t>Kiev</t>
+        </is>
+      </c>
+    </row>
+    <row r="1208">
+      <c r="A1208" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1149" t="n">
-        <v>3454</v>
-      </c>
-      <c r="C1149" t="inlineStr">
+      <c r="B1208" t="n">
+        <v>3585</v>
+      </c>
+      <c r="C1208" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1149" t="inlineStr">
-        <is>
-          <t>вул Зелена 1а</t>
-        </is>
-      </c>
-      <c r="E1149" t="inlineStr">
-        <is>
-          <t>Мостиська</t>
-        </is>
-      </c>
-      <c r="F1149" t="inlineStr">
-        <is>
-          <t>Львівська</t>
-        </is>
-      </c>
-      <c r="G1149" t="n">
-        <v>49.7913487</v>
-      </c>
-      <c r="H1149" t="n">
-        <v>23.1536667</v>
-      </c>
-      <c r="I1149" t="inlineStr">
-        <is>
-          <t>Пн: 09:00-19:00
-Вт: 09:00-19:00
-Ср: 09:00-19:00
-Чт: 09:00-19:00
-Пт: 09:00-19:00
-Сб: 09:00-18:00
-Нд: 10:00-17:00</t>
-        </is>
-      </c>
-      <c r="J1149" t="inlineStr">
-        <is>
-          <t>Львівська</t>
-        </is>
-      </c>
-    </row>
-    <row r="1150">
-      <c r="A1150" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1150" t="n">
-        <v>3464</v>
-      </c>
-      <c r="C1150" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1150" t="inlineStr">
-        <is>
-          <t>вул Огієнка 41</t>
-        </is>
-      </c>
-      <c r="E1150" t="inlineStr">
-        <is>
-          <t>Камянець-Подільский</t>
-        </is>
-      </c>
-      <c r="F1150" t="inlineStr">
-        <is>
-          <t>Хмельницька</t>
-        </is>
-      </c>
-      <c r="G1150" t="n">
-        <v>48.681053</v>
-      </c>
-      <c r="H1150" t="n">
-        <v>26.5871481</v>
-      </c>
-      <c r="I1150" t="inlineStr">
-        <is>
-          <t>Пн: 08:00-18:00
-Вт: 08:00-18:00
-Ср: 08:00-18:00
-Чт: 08:00-18:00
-Пт: 08:00-18:00
-Сб: 10:00-16:00
-Нд: 10:00-16:00</t>
-        </is>
-      </c>
-      <c r="J1150" t="inlineStr">
-        <is>
-          <t>Хмельницька</t>
-        </is>
-      </c>
-    </row>
-    <row r="1151">
-      <c r="A1151" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1151" t="n">
-        <v>3465</v>
-      </c>
-      <c r="C1151" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1151" t="inlineStr">
-        <is>
-          <t>вул Хмельницька 6</t>
-        </is>
-      </c>
-      <c r="E1151" t="inlineStr">
-        <is>
-          <t>Ярмолинці</t>
-        </is>
-      </c>
-      <c r="F1151" t="inlineStr">
-        <is>
-          <t>Хмельницька</t>
-        </is>
-      </c>
-      <c r="G1151" t="n">
-        <v>49.19112</v>
-      </c>
-      <c r="H1151" t="n">
-        <v>26.83537</v>
-      </c>
-      <c r="I1151" t="inlineStr">
-        <is>
-          <t>Пн: 09:00-18:00
-Вт: 09:00-18:00
-Ср: 09:00-18:00
-Чт: 09:00-18:00
-Пт: 09:00-18:00
-Сб: 09:00-14:00
-Нд: Вихідний</t>
-        </is>
-      </c>
-      <c r="J1151" t="inlineStr">
-        <is>
-          <t>Хмельницька</t>
-        </is>
-      </c>
-    </row>
-    <row r="1152">
-      <c r="A1152" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1152" t="n">
-        <v>3466</v>
-      </c>
-      <c r="C1152" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1152" t="inlineStr">
-        <is>
-          <t>просп Берестейський (Перемоги) 86а</t>
-        </is>
-      </c>
-      <c r="E1152" t="inlineStr">
+      <c r="D1208" t="inlineStr">
+        <is>
+          <t>вул Бориспільська 1</t>
+        </is>
+      </c>
+      <c r="E1208" t="inlineStr">
         <is>
           <t>Київ</t>
         </is>
       </c>
-      <c r="F1152" t="inlineStr">
+      <c r="F1208" t="inlineStr">
         <is>
           <t>Kiev</t>
         </is>
       </c>
-      <c r="G1152" t="n">
-        <v>50.4588998</v>
-      </c>
-      <c r="H1152" t="n">
-        <v>30.4041254</v>
-      </c>
-      <c r="I1152" t="inlineStr">
-        <is>
-          <t>Пн: 10:00-21:00
-Вт: 10:00-21:00
-Ср: 10:00-21:00
-Чт: 10:00-21:00
-Пт: 10:00-21:00
-Сб: 10:00-21:00
-Нд: 10:00-21:00</t>
-        </is>
-      </c>
-      <c r="J1152" t="inlineStr">
-        <is>
-          <t>Kiev</t>
-        </is>
-      </c>
-    </row>
-    <row r="1153">
-      <c r="A1153" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1153" t="n">
-        <v>3470</v>
-      </c>
-      <c r="C1153" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1153" t="inlineStr">
-        <is>
-          <t>вул  Хрещатик 13</t>
-        </is>
-      </c>
-      <c r="E1153" t="inlineStr">
-        <is>
-          <t>Київ</t>
-        </is>
-      </c>
-      <c r="F1153" t="inlineStr">
-        <is>
-          <t>м. Київ</t>
-        </is>
-      </c>
-      <c r="G1153" t="n">
-        <v>50.4487897</v>
-      </c>
-      <c r="H1153" t="n">
-        <v>30.5233361</v>
-      </c>
-      <c r="I1153" t="inlineStr">
-        <is>
-          <t>Пн: 10:00-20:00
-Вт: 10:00-20:00
-Ср: 10:00-20:00
-Чт: 10:00-20:00
-Пт: 10:00-20:00
-Сб: 10:00-20:00
-Нд: 10:00-20:00</t>
-        </is>
-      </c>
-      <c r="J1153" t="inlineStr">
-        <is>
-          <t>м. Київ</t>
-        </is>
-      </c>
-    </row>
-    <row r="1154">
-      <c r="A1154" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1154" t="n">
-        <v>3471</v>
-      </c>
-      <c r="C1154" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1154" t="inlineStr">
-        <is>
-          <t>вул Університетська 45</t>
-        </is>
-      </c>
-      <c r="E1154" t="inlineStr">
-        <is>
-          <t>Словянськ</t>
-        </is>
-      </c>
-      <c r="F1154" t="inlineStr">
-        <is>
-          <t>Дніпропетровська</t>
-        </is>
-      </c>
-      <c r="G1154" t="n">
-        <v>48.0008788</v>
-      </c>
-      <c r="H1154" t="n">
-        <v>33.4821954</v>
-      </c>
-      <c r="I1154" t="inlineStr">
-        <is>
-          <t>Пн: 10:00-17:00
-Вт: 10:00-17:00
-Ср: 10:00-17:00
-Чт: 10:00-17:00
-Пт: 10:00-17:00
-Сб: 10:00-16:00
-Нд: Вихідний</t>
-        </is>
-      </c>
-      <c r="J1154" t="inlineStr">
-        <is>
-          <t>Дніпропетровська</t>
-        </is>
-      </c>
-    </row>
-    <row r="1155">
-      <c r="A1155" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1155" t="n">
-        <v>3472</v>
-      </c>
-      <c r="C1155" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1155" t="inlineStr">
-        <is>
-          <t>вул Чернівецька 2Б</t>
-        </is>
-      </c>
-      <c r="E1155" t="inlineStr">
-        <is>
-          <t>Сторожинець</t>
-        </is>
-      </c>
-      <c r="F1155" t="inlineStr">
-        <is>
-          <t>Чернівецька</t>
-        </is>
-      </c>
-      <c r="G1155" t="n">
-        <v>48.1604917</v>
-      </c>
-      <c r="H1155" t="n">
-        <v>25.721244</v>
-      </c>
-      <c r="I1155" t="inlineStr">
-        <is>
-          <t>Пн: 09:00-18:00
-Вт: 09:00-18:00
-Ср: 09:00-18:00
-Чт: 09:00-18:00
-Пт: 09:00-18:00
-Сб: 09:00-15:00
-Нд: Вихідний</t>
-        </is>
-      </c>
-      <c r="J1155" t="inlineStr">
-        <is>
-          <t>Чернівецька</t>
-        </is>
-      </c>
-    </row>
-    <row r="1156">
-      <c r="A1156" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1156" t="n">
-        <v>3474</v>
-      </c>
-      <c r="C1156" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1156" t="inlineStr">
-        <is>
-          <t>вул Нескорених (Героїв Праці) 13</t>
-        </is>
-      </c>
-      <c r="E1156" t="inlineStr">
-        <is>
-          <t>Харків</t>
-        </is>
-      </c>
-      <c r="F1156" t="inlineStr">
-        <is>
-          <t>Харківська</t>
-        </is>
-      </c>
-      <c r="G1156" t="n">
-        <v>50.0254117</v>
-      </c>
-      <c r="H1156" t="n">
-        <v>36.3369339</v>
-      </c>
-      <c r="I1156" t="inlineStr">
+      <c r="G1208" t="n">
+        <v>50.4313257</v>
+      </c>
+      <c r="H1208" t="n">
+        <v>30.6494712</v>
+      </c>
+      <c r="I1208" t="inlineStr">
         <is>
           <t>Пн: 09:00-18:00
 Вт: 09:00-18:00
@@ -53412,1920 +56116,48 @@
 Нд: 09:00-17:00</t>
         </is>
       </c>
-      <c r="J1156" t="inlineStr">
-        <is>
-          <t>Харківська</t>
-        </is>
-      </c>
-    </row>
-    <row r="1157">
-      <c r="A1157" t="inlineStr">
+      <c r="J1208" t="inlineStr">
+        <is>
+          <t>Kiev</t>
+        </is>
+      </c>
+    </row>
+    <row r="1209">
+      <c r="A1209" t="inlineStr">
         <is>
           <t>kyivstar</t>
         </is>
       </c>
-      <c r="B1157" t="n">
-        <v>3478</v>
-      </c>
-      <c r="C1157" t="inlineStr">
+      <c r="B1209" t="n">
+        <v>3586</v>
+      </c>
+      <c r="C1209" t="inlineStr">
         <is>
           <t>Kyivstar</t>
         </is>
       </c>
-      <c r="D1157" t="inlineStr">
-        <is>
-          <t>просп Європейського Союзу (Правди) 58</t>
-        </is>
-      </c>
-      <c r="E1157" t="inlineStr">
-        <is>
-          <t>Київ</t>
-        </is>
-      </c>
-      <c r="F1157" t="inlineStr">
-        <is>
-          <t>Kiev</t>
-        </is>
-      </c>
-      <c r="G1157" t="n">
-        <v>50.5047315</v>
-      </c>
-      <c r="H1157" t="n">
-        <v>30.4374307</v>
-      </c>
-      <c r="I1157" t="inlineStr">
-        <is>
-          <t>Пн: 09:00-21:00
-Вт: 09:00-21:00
-Ср: 09:00-21:00
-Чт: 09:00-21:00
-Пт: 09:00-21:00
-Сб: 09:00-21:00
-Нд: 09:00-21:00</t>
-        </is>
-      </c>
-      <c r="J1157" t="inlineStr">
-        <is>
-          <t>Kiev</t>
-        </is>
-      </c>
-    </row>
-    <row r="1158">
-      <c r="A1158" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1158" t="n">
-        <v>3479</v>
-      </c>
-      <c r="C1158" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1158" t="inlineStr">
-        <is>
-          <t>вул Європейського Союзу (Правди) 47</t>
-        </is>
-      </c>
-      <c r="E1158" t="inlineStr">
-        <is>
-          <t>Київ</t>
-        </is>
-      </c>
-      <c r="F1158" t="inlineStr">
-        <is>
-          <t>м. Київ</t>
-        </is>
-      </c>
-      <c r="G1158" t="n">
-        <v>50.5037667</v>
-      </c>
-      <c r="H1158" t="n">
-        <v>30.419093</v>
-      </c>
-      <c r="I1158" t="inlineStr">
-        <is>
-          <t>Пн: 10:00-22:00
-Вт: 10:00-22:00
-Ср: 10:00-22:00
-Чт: 10:00-22:00
-Пт: 10:00-22:00
-Сб: 10:00-22:00
-Нд: 10:00-22:00</t>
-        </is>
-      </c>
-      <c r="J1158" t="inlineStr">
-        <is>
-          <t>м. Київ</t>
-        </is>
-      </c>
-    </row>
-    <row r="1159">
-      <c r="A1159" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1159" t="n">
-        <v>3483</v>
-      </c>
-      <c r="C1159" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1159" t="inlineStr">
-        <is>
-          <t>просп Коцюбинського 19</t>
-        </is>
-      </c>
-      <c r="E1159" t="inlineStr">
-        <is>
-          <t>Вінниця</t>
-        </is>
-      </c>
-      <c r="F1159" t="inlineStr">
-        <is>
-          <t>Vinnyts'ka</t>
-        </is>
-      </c>
-      <c r="G1159" t="n">
-        <v>49.239071</v>
-      </c>
-      <c r="H1159" t="n">
-        <v>28.4981039</v>
-      </c>
-      <c r="I1159" t="inlineStr">
-        <is>
-          <t>Пн: 08:00-18:00
-Вт: 08:00-18:00
-Ср: 08:00-18:00
-Чт: 08:00-18:00
-Пт: 08:00-18:00
-Сб: 09:00-17:00
-Нд: 09:00-17:00</t>
-        </is>
-      </c>
-      <c r="J1159" t="inlineStr">
-        <is>
-          <t>Vinnyts'ka</t>
-        </is>
-      </c>
-    </row>
-    <row r="1160">
-      <c r="A1160" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1160" t="n">
-        <v>3485</v>
-      </c>
-      <c r="C1160" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1160" t="inlineStr">
-        <is>
-          <t>вул Котляра (був. Червоноармійська) 8/10</t>
-        </is>
-      </c>
-      <c r="E1160" t="inlineStr">
-        <is>
-          <t>Харків</t>
-        </is>
-      </c>
-      <c r="F1160" t="inlineStr">
-        <is>
-          <t>Харківська</t>
-        </is>
-      </c>
-      <c r="G1160" t="n">
-        <v>49.9892648</v>
-      </c>
-      <c r="H1160" t="n">
-        <v>36.2077698</v>
-      </c>
-      <c r="I1160" t="inlineStr">
-        <is>
-          <t>Пн: 09:00-18:00
-Вт: 09:00-18:00
-Ср: 09:00-18:00
-Чт: 09:00-18:00
-Пт: 09:00-18:00
-Сб: 09:00-18:00
-Нд: 09:00-17:00</t>
-        </is>
-      </c>
-      <c r="J1160" t="inlineStr">
-        <is>
-          <t>Харківська</t>
-        </is>
-      </c>
-    </row>
-    <row r="1161">
-      <c r="A1161" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1161" t="n">
-        <v>3491</v>
-      </c>
-      <c r="C1161" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1161" t="inlineStr">
-        <is>
-          <t>вул Інститутська 10</t>
-        </is>
-      </c>
-      <c r="E1161" t="inlineStr">
-        <is>
-          <t>Хмельницький</t>
-        </is>
-      </c>
-      <c r="F1161" t="inlineStr">
-        <is>
-          <t>Хмельницька</t>
-        </is>
-      </c>
-      <c r="G1161" t="n">
-        <v>49.4098499</v>
-      </c>
-      <c r="H1161" t="n">
-        <v>26.9605436</v>
-      </c>
-      <c r="I1161" t="inlineStr">
-        <is>
-          <t>Пн: 09:00-19:00
-Вт: 09:00-19:00
-Ср: 09:00-19:00
-Чт: 09:00-19:00
-Пт: 09:00-19:00
-Сб: 10:00-18:00
-Нд: 10:00-18:00</t>
-        </is>
-      </c>
-      <c r="J1161" t="inlineStr">
-        <is>
-          <t>Хмельницька</t>
-        </is>
-      </c>
-    </row>
-    <row r="1162">
-      <c r="A1162" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1162" t="n">
-        <v>3494</v>
-      </c>
-      <c r="C1162" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1162" t="inlineStr">
-        <is>
-          <t>вул Шевченків Шлях 144-А</t>
-        </is>
-      </c>
-      <c r="E1162" t="inlineStr">
-        <is>
-          <t>Березань</t>
-        </is>
-      </c>
-      <c r="F1162" t="inlineStr">
-        <is>
-          <t>Kiev</t>
-        </is>
-      </c>
-      <c r="G1162" t="n">
-        <v>50.3119113</v>
-      </c>
-      <c r="H1162" t="n">
-        <v>31.4678577</v>
-      </c>
-      <c r="I1162" t="inlineStr">
-        <is>
-          <t>Пн: 09:00-17:00
-Вт: 09:00-17:00
-Ср: 09:00-17:00
-Чт: 09:00-17:00
-Пт: 09:00-17:00
-Сб: 10:00-16:00
-Нд: 10:00-16:00</t>
-        </is>
-      </c>
-      <c r="J1162" t="inlineStr">
-        <is>
-          <t>Kiev</t>
-        </is>
-      </c>
-    </row>
-    <row r="1163">
-      <c r="A1163" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1163" t="n">
-        <v>3495</v>
-      </c>
-      <c r="C1163" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1163" t="inlineStr">
-        <is>
-          <t>вул Міцкевича 1</t>
-        </is>
-      </c>
-      <c r="E1163" t="inlineStr">
-        <is>
-          <t>Борислав</t>
-        </is>
-      </c>
-      <c r="F1163" t="inlineStr">
-        <is>
-          <t>Львівська</t>
-        </is>
-      </c>
-      <c r="G1163" t="n">
-        <v>49.287286</v>
-      </c>
-      <c r="H1163" t="n">
-        <v>23.4159004</v>
-      </c>
-      <c r="I1163" t="inlineStr">
-        <is>
-          <t>Пн: 09:00-18:00
-Вт: 09:00-18:00
-Ср: 09:00-18:00
-Чт: 09:00-18:00
-Пт: 09:00-18:00
-Сб: 09:00-17:00
-Нд: 10:00-17:00</t>
-        </is>
-      </c>
-      <c r="J1163" t="inlineStr">
-        <is>
-          <t>Львівська</t>
-        </is>
-      </c>
-    </row>
-    <row r="1164">
-      <c r="A1164" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1164" t="n">
-        <v>3496</v>
-      </c>
-      <c r="C1164" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1164" t="inlineStr">
-        <is>
-          <t>вул І.Франка 1</t>
-        </is>
-      </c>
-      <c r="E1164" t="inlineStr">
-        <is>
-          <t>Верховина</t>
-        </is>
-      </c>
-      <c r="F1164" t="inlineStr">
-        <is>
-          <t>Івано-Франківська</t>
-        </is>
-      </c>
-      <c r="G1164" t="n">
-        <v>48.1549768</v>
-      </c>
-      <c r="H1164" t="n">
-        <v>24.8291227</v>
-      </c>
-      <c r="I1164" t="inlineStr">
-        <is>
-          <t>Пн: 09:00-18:00
-Вт: 09:00-18:00
-Ср: 09:00-18:00
-Чт: 09:00-18:00
-Пт: 09:00-18:00
-Сб: 09:00-17:00
-Нд: 10:00-16:00</t>
-        </is>
-      </c>
-      <c r="J1164" t="inlineStr">
-        <is>
-          <t>Івано-Франківська</t>
-        </is>
-      </c>
-    </row>
-    <row r="1165">
-      <c r="A1165" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1165" t="n">
-        <v>3498</v>
-      </c>
-      <c r="C1165" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1165" t="inlineStr">
-        <is>
-          <t>просп Олександра Поля 1/9</t>
-        </is>
-      </c>
-      <c r="E1165" t="inlineStr">
-        <is>
-          <t>Дніпро</t>
-        </is>
-      </c>
-      <c r="F1165" t="inlineStr">
-        <is>
-          <t>Дніпропетровська</t>
-        </is>
-      </c>
-      <c r="G1165" t="n">
-        <v>48.4642698</v>
-      </c>
-      <c r="H1165" t="n">
-        <v>35.0290126</v>
-      </c>
-      <c r="I1165" t="inlineStr">
-        <is>
-          <t>Пн: 09:00-19:00
-Вт: 09:00-19:00
-Ср: 09:00-19:00
-Чт: 09:00-19:00
-Пт: 09:00-19:00
-Сб: 09:00-19:00
-Нд: 09:00-18:00</t>
-        </is>
-      </c>
-      <c r="J1165" t="inlineStr">
-        <is>
-          <t>Дніпропетровська</t>
-        </is>
-      </c>
-    </row>
-    <row r="1166">
-      <c r="A1166" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1166" t="n">
-        <v>3501</v>
-      </c>
-      <c r="C1166" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1166" t="inlineStr">
-        <is>
-          <t>просп Дмитра Яворницького (К.Маркса) 65</t>
-        </is>
-      </c>
-      <c r="E1166" t="inlineStr">
-        <is>
-          <t>Дніпро</t>
-        </is>
-      </c>
-      <c r="F1166" t="inlineStr">
-        <is>
-          <t>Дніпропетровська</t>
-        </is>
-      </c>
-      <c r="G1166" t="n">
-        <v>48.4647786</v>
-      </c>
-      <c r="H1166" t="n">
-        <v>35.0447223</v>
-      </c>
-      <c r="I1166" t="inlineStr">
-        <is>
-          <t>Пн: 09:00-19:00
-Вт: 09:00-19:00
-Ср: 09:00-19:00
-Чт: 09:00-19:00
-Пт: 09:00-19:00
-Сб: 09:00-18:00
-Нд: 09:00-18:00</t>
-        </is>
-      </c>
-      <c r="J1166" t="inlineStr">
-        <is>
-          <t>Дніпропетровська</t>
-        </is>
-      </c>
-    </row>
-    <row r="1167">
-      <c r="A1167" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1167" t="n">
-        <v>3505</v>
-      </c>
-      <c r="C1167" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1167" t="inlineStr">
-        <is>
-          <t>пл Шевченка 26</t>
-        </is>
-      </c>
-      <c r="E1167" t="inlineStr">
-        <is>
-          <t>Коломия</t>
-        </is>
-      </c>
-      <c r="F1167" t="inlineStr">
-        <is>
-          <t>Івано-Франківська</t>
-        </is>
-      </c>
-      <c r="G1167" t="n">
-        <v>48.5249278</v>
-      </c>
-      <c r="H1167" t="n">
-        <v>25.0375409</v>
-      </c>
-      <c r="I1167" t="inlineStr">
-        <is>
-          <t>Пн: 09:00-18:00
-Вт: 09:00-18:00
-Ср: 09:00-18:00
-Чт: 09:00-18:00
-Пт: 09:00-18:00
-Сб: 09:00-18:00
-Нд: 10:00-17:00</t>
-        </is>
-      </c>
-      <c r="J1167" t="inlineStr">
-        <is>
-          <t>Івано-Франківська</t>
-        </is>
-      </c>
-    </row>
-    <row r="1168">
-      <c r="A1168" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1168" t="n">
-        <v>3506</v>
-      </c>
-      <c r="C1168" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1168" t="inlineStr">
-        <is>
-          <t>вул Медова 5</t>
-        </is>
-      </c>
-      <c r="E1168" t="inlineStr">
-        <is>
-          <t>Кремeнець</t>
-        </is>
-      </c>
-      <c r="F1168" t="inlineStr">
-        <is>
-          <t>Тернопільська</t>
-        </is>
-      </c>
-      <c r="G1168" t="n">
-        <v>50.095605</v>
-      </c>
-      <c r="H1168" t="n">
-        <v>25.7259463</v>
-      </c>
-      <c r="I1168" t="inlineStr">
-        <is>
-          <t>Пн: 09:00-19:00
-Вт: 09:00-19:00
-Ср: 09:00-19:00
-Чт: 09:00-19:00
-Пт: 09:00-19:00
-Сб: 10:00-16:00
-Нд: 10:00-16:00</t>
-        </is>
-      </c>
-      <c r="J1168" t="inlineStr">
-        <is>
-          <t>Тернопільська</t>
-        </is>
-      </c>
-    </row>
-    <row r="1169">
-      <c r="A1169" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1169" t="n">
-        <v>3508</v>
-      </c>
-      <c r="C1169" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1169" t="inlineStr">
-        <is>
-          <t>вул Шевченка 100</t>
-        </is>
-      </c>
-      <c r="E1169" t="inlineStr">
-        <is>
-          <t>Люботин</t>
-        </is>
-      </c>
-      <c r="F1169" t="inlineStr">
-        <is>
-          <t>Харківська</t>
-        </is>
-      </c>
-      <c r="G1169" t="n">
-        <v>49.9407992</v>
-      </c>
-      <c r="H1169" t="n">
-        <v>35.9262566</v>
-      </c>
-      <c r="I1169" t="inlineStr">
-        <is>
-          <t>Пн: 08:00-18:00
-Вт: 08:00-18:00
-Ср: 08:00-18:00
-Чт: 08:00-18:00
-Пт: 08:00-18:00
-Сб: 08:00-18:00
-Нд: 08:00-16:00</t>
-        </is>
-      </c>
-      <c r="J1169" t="inlineStr">
-        <is>
-          <t>Харківська</t>
-        </is>
-      </c>
-    </row>
-    <row r="1170">
-      <c r="A1170" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1170" t="n">
-        <v>3510</v>
-      </c>
-      <c r="C1170" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1170" t="inlineStr">
-        <is>
-          <t>вул Петропавлівська 49</t>
-        </is>
-      </c>
-      <c r="E1170" t="inlineStr">
-        <is>
-          <t>Суми</t>
-        </is>
-      </c>
-      <c r="F1170" t="inlineStr">
-        <is>
-          <t>Сумська</t>
-        </is>
-      </c>
-      <c r="G1170" t="n">
-        <v>50.9065729</v>
-      </c>
-      <c r="H1170" t="n">
-        <v>34.796901</v>
-      </c>
-      <c r="I1170" t="inlineStr">
-        <is>
-          <t>Пн: 09:00-18:00
-Вт: 09:00-18:00
-Ср: 09:00-18:00
-Чт: 09:00-18:00
-Пт: 09:00-18:00
-Сб: 09:00-18:00
-Нд: 09:00-18:00</t>
-        </is>
-      </c>
-      <c r="J1170" t="inlineStr">
-        <is>
-          <t>Сумська</t>
-        </is>
-      </c>
-    </row>
-    <row r="1171">
-      <c r="A1171" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1171" t="n">
-        <v>3512</v>
-      </c>
-      <c r="C1171" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1171" t="inlineStr">
-        <is>
-          <t>вул Валентинівська (Блюхера) 37/128</t>
-        </is>
-      </c>
-      <c r="E1171" t="inlineStr">
-        <is>
-          <t>Харків</t>
-        </is>
-      </c>
-      <c r="F1171" t="inlineStr">
-        <is>
-          <t>Харківська</t>
-        </is>
-      </c>
-      <c r="G1171" t="n">
-        <v>50.0098371</v>
-      </c>
-      <c r="H1171" t="n">
-        <v>36.3503577</v>
-      </c>
-      <c r="I1171" t="inlineStr">
-        <is>
-          <t>Пн: 09:00-19:00
-Вт: 09:00-19:00
-Ср: 09:00-19:00
-Чт: 09:00-19:00
-Пт: 09:00-19:00
-Сб: 09:00-18:00
-Нд: 09:00-18:00</t>
-        </is>
-      </c>
-      <c r="J1171" t="inlineStr">
-        <is>
-          <t>Харківська</t>
-        </is>
-      </c>
-    </row>
-    <row r="1172">
-      <c r="A1172" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1172" t="n">
-        <v>3514</v>
-      </c>
-      <c r="C1172" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1172" t="inlineStr">
-        <is>
-          <t>вул Центральна 32а</t>
-        </is>
-      </c>
-      <c r="E1172" t="inlineStr">
-        <is>
-          <t>Чемерівці</t>
-        </is>
-      </c>
-      <c r="F1172" t="inlineStr">
-        <is>
-          <t>Хмельницька</t>
-        </is>
-      </c>
-      <c r="G1172" t="n">
-        <v>49.011295</v>
-      </c>
-      <c r="H1172" t="n">
-        <v>26.340395</v>
-      </c>
-      <c r="I1172" t="inlineStr">
-        <is>
-          <t>Пн: 08:00-18:00
-Вт: 08:00-18:00
-Ср: 08:00-18:00
-Чт: 08:00-18:00
-Пт: 08:00-18:00
-Сб: 09:00-16:00
-Нд: 09:00-15:00</t>
-        </is>
-      </c>
-      <c r="J1172" t="inlineStr">
-        <is>
-          <t>Хмельницька</t>
-        </is>
-      </c>
-    </row>
-    <row r="1173">
-      <c r="A1173" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1173" t="n">
-        <v>3517</v>
-      </c>
-      <c r="C1173" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1173" t="inlineStr">
-        <is>
-          <t>просп Свободи (Леніна) 16Д</t>
-        </is>
-      </c>
-      <c r="E1173" t="inlineStr">
-        <is>
-          <t>Хмільник</t>
-        </is>
-      </c>
-      <c r="F1173" t="inlineStr">
-        <is>
-          <t>Vinnyts'ka</t>
-        </is>
-      </c>
-      <c r="G1173" t="n">
-        <v>49.5576747</v>
-      </c>
-      <c r="H1173" t="n">
-        <v>27.9528561</v>
-      </c>
-      <c r="I1173" t="inlineStr">
-        <is>
-          <t>Пн: 08:00-17:00
-Вт: 08:00-17:00
-Ср: 08:00-17:00
-Чт: 08:00-17:00
-Пт: 08:00-17:00
-Сб: 08:00-17:00
-Нд: Вихідний</t>
-        </is>
-      </c>
-      <c r="J1173" t="inlineStr">
-        <is>
-          <t>Vinnyts'ka</t>
-        </is>
-      </c>
-    </row>
-    <row r="1174">
-      <c r="A1174" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1174" t="n">
-        <v>3520</v>
-      </c>
-      <c r="C1174" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1174" t="inlineStr">
-        <is>
-          <t>пл Шевченка 6</t>
-        </is>
-      </c>
-      <c r="E1174" t="inlineStr">
-        <is>
-          <t>Славута</t>
-        </is>
-      </c>
-      <c r="F1174" t="inlineStr">
-        <is>
-          <t>Хмельницька</t>
-        </is>
-      </c>
-      <c r="G1174" t="n">
-        <v>50.2957898</v>
-      </c>
-      <c r="H1174" t="n">
-        <v>26.8570458</v>
-      </c>
-      <c r="I1174" t="inlineStr">
-        <is>
-          <t>Пн: 08:00-17:00
-Вт: 08:00-17:00
-Ср: 08:00-17:00
-Чт: 08:00-17:00
-Пт: 08:00-17:00
-Сб: 08:00-17:00
-Нд: 08:00-17:00</t>
-        </is>
-      </c>
-      <c r="J1174" t="inlineStr">
-        <is>
-          <t>Хмельницька</t>
-        </is>
-      </c>
-    </row>
-    <row r="1175">
-      <c r="A1175" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1175" t="n">
-        <v>3526</v>
-      </c>
-      <c r="C1175" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1175" t="inlineStr">
-        <is>
-          <t>вул Незалежності 65</t>
-        </is>
-      </c>
-      <c r="E1175" t="inlineStr">
-        <is>
-          <t>Камянка-Бузька</t>
-        </is>
-      </c>
-      <c r="F1175" t="inlineStr">
-        <is>
-          <t>Львівська</t>
-        </is>
-      </c>
-      <c r="G1175" t="n">
-        <v>50.107376</v>
-      </c>
-      <c r="H1175" t="n">
-        <v>24.3436341</v>
-      </c>
-      <c r="I1175" t="inlineStr">
-        <is>
-          <t>Пн: 09:00-18:00
-Вт: 09:00-18:00
-Ср: 09:00-18:00
-Чт: 09:00-18:00
-Пт: 09:00-18:00
-Сб: 09:00-16:00
-Нд: 09:00-16:00</t>
-        </is>
-      </c>
-      <c r="J1175" t="inlineStr">
-        <is>
-          <t>Львівська</t>
-        </is>
-      </c>
-    </row>
-    <row r="1176">
-      <c r="A1176" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1176" t="n">
-        <v>3530</v>
-      </c>
-      <c r="C1176" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1176" t="inlineStr">
-        <is>
-          <t>вул Савіцького 14</t>
-        </is>
-      </c>
-      <c r="E1176" t="inlineStr">
-        <is>
-          <t>Летичів</t>
-        </is>
-      </c>
-      <c r="F1176" t="inlineStr">
-        <is>
-          <t>Хмельницька</t>
-        </is>
-      </c>
-      <c r="G1176" t="n">
-        <v>49.3813788</v>
-      </c>
-      <c r="H1176" t="n">
-        <v>27.6197046</v>
-      </c>
-      <c r="I1176" t="inlineStr">
-        <is>
-          <t>Пн: 09:00-18:00
-Вт: 09:00-18:00
-Ср: 09:00-18:00
-Чт: 09:00-18:00
-Пт: 09:00-18:00
-Сб: 09:00-18:00
-Нд: 09:00-18:00</t>
-        </is>
-      </c>
-      <c r="J1176" t="inlineStr">
-        <is>
-          <t>Хмельницька</t>
-        </is>
-      </c>
-    </row>
-    <row r="1177">
-      <c r="A1177" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1177" t="n">
-        <v>3531</v>
-      </c>
-      <c r="C1177" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1177" t="inlineStr">
-        <is>
-          <t>вул Берестейський (Перемоги) 26</t>
-        </is>
-      </c>
-      <c r="E1177" t="inlineStr">
-        <is>
-          <t>Київ</t>
-        </is>
-      </c>
-      <c r="F1177" t="inlineStr">
-        <is>
-          <t>м. Київ</t>
-        </is>
-      </c>
-      <c r="G1177" t="n">
-        <v>50.4515345</v>
-      </c>
-      <c r="H1177" t="n">
-        <v>30.4678476</v>
-      </c>
-      <c r="I1177" t="inlineStr">
-        <is>
-          <t>Пн: 10:00-21:00
-Вт: 10:00-21:00
-Ср: 10:00-21:00
-Чт: 10:00-21:00
-Пт: 10:00-21:00
-Сб: 10:00-21:00
-Нд: 10:00-21:00</t>
-        </is>
-      </c>
-      <c r="J1177" t="inlineStr">
-        <is>
-          <t>м. Київ</t>
-        </is>
-      </c>
-    </row>
-    <row r="1178">
-      <c r="A1178" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1178" t="n">
-        <v>3534</v>
-      </c>
-      <c r="C1178" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1178" t="inlineStr">
-        <is>
-          <t>вул Шевченка 74а</t>
-        </is>
-      </c>
-      <c r="E1178" t="inlineStr">
-        <is>
-          <t>Городенка</t>
-        </is>
-      </c>
-      <c r="F1178" t="inlineStr">
-        <is>
-          <t>Івано-Франківська</t>
-        </is>
-      </c>
-      <c r="G1178" t="n">
-        <v>48.66888903427731</v>
-      </c>
-      <c r="H1178" t="n">
-        <v>25.50435338169336</v>
-      </c>
-      <c r="I1178" t="inlineStr">
-        <is>
-          <t>Пн: 08:00-18:00
-Вт: 08:00-18:00
-Ср: 08:00-18:00
-Чт: 08:00-18:00
-Пт: 08:00-18:00
-Сб: 08:00-18:00
-Нд: 10:00-17:00</t>
-        </is>
-      </c>
-      <c r="J1178" t="inlineStr">
-        <is>
-          <t>Івано-Франківська</t>
-        </is>
-      </c>
-    </row>
-    <row r="1179">
-      <c r="A1179" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1179" t="n">
-        <v>3535</v>
-      </c>
-      <c r="C1179" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1179" t="inlineStr">
-        <is>
-          <t>вул Бекетова 21</t>
-        </is>
-      </c>
-      <c r="E1179" t="inlineStr">
-        <is>
-          <t>Харків</t>
-        </is>
-      </c>
-      <c r="F1179" t="inlineStr">
-        <is>
-          <t>Харківська</t>
-        </is>
-      </c>
-      <c r="G1179" t="n">
-        <v>49.9512627</v>
-      </c>
-      <c r="H1179" t="n">
-        <v>36.371922</v>
-      </c>
-      <c r="I1179" t="inlineStr">
-        <is>
-          <t>Пн: 09:00-17:00
-Вт: 09:00-17:00
-Ср: 09:00-17:00
-Чт: 09:00-17:00
-Пт: 09:00-17:00
-Сб: 09:00-17:00
-Нд: 09:00-16:00</t>
-        </is>
-      </c>
-      <c r="J1179" t="inlineStr">
-        <is>
-          <t>Харківська</t>
-        </is>
-      </c>
-    </row>
-    <row r="1180">
-      <c r="A1180" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1180" t="n">
-        <v>3541</v>
-      </c>
-      <c r="C1180" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1180" t="inlineStr">
-        <is>
-          <t>вул Одеська 121, А/1</t>
-        </is>
-      </c>
-      <c r="E1180" t="inlineStr">
-        <is>
-          <t>Первомайськ</t>
-        </is>
-      </c>
-      <c r="F1180" t="inlineStr">
-        <is>
-          <t>Миколаївська</t>
-        </is>
-      </c>
-      <c r="G1180" t="n">
-        <v>48.0228289</v>
-      </c>
-      <c r="H1180" t="n">
-        <v>30.8511121</v>
-      </c>
-      <c r="I1180" t="inlineStr">
-        <is>
-          <t>Пн: 09:00-18:00
-Вт: 09:00-18:00
-Ср: 09:00-18:00
-Чт: 09:00-18:00
-Пт: 09:00-18:00
-Сб: 09:00-18:00
-Нд: 09:00-18:00</t>
-        </is>
-      </c>
-      <c r="J1180" t="inlineStr">
-        <is>
-          <t>Миколаївська</t>
-        </is>
-      </c>
-    </row>
-    <row r="1181">
-      <c r="A1181" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1181" t="n">
-        <v>3542</v>
-      </c>
-      <c r="C1181" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1181" t="inlineStr">
-        <is>
-          <t>просп Героїв Харкова 274</t>
-        </is>
-      </c>
-      <c r="E1181" t="inlineStr">
-        <is>
-          <t>Харків</t>
-        </is>
-      </c>
-      <c r="F1181" t="inlineStr">
-        <is>
-          <t>Харківська</t>
-        </is>
-      </c>
-      <c r="G1181" t="n">
-        <v>49.9432342</v>
-      </c>
-      <c r="H1181" t="n">
-        <v>36.3984342</v>
-      </c>
-      <c r="I1181" t="inlineStr">
-        <is>
-          <t>Пн: 09:00-18:00
-Вт: 09:00-18:00
-Ср: 09:00-18:00
-Чт: 09:00-18:00
-Пт: 09:00-18:00
-Сб: 09:00-17:00
-Нд: 09:00-17:00</t>
-        </is>
-      </c>
-      <c r="J1181" t="inlineStr">
-        <is>
-          <t>Харківська</t>
-        </is>
-      </c>
-    </row>
-    <row r="1182">
-      <c r="A1182" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1182" t="n">
-        <v>3543</v>
-      </c>
-      <c r="C1182" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1182" t="inlineStr">
-        <is>
-          <t>вул Салтівське шосе 147</t>
-        </is>
-      </c>
-      <c r="E1182" t="inlineStr">
-        <is>
-          <t>Харків</t>
-        </is>
-      </c>
-      <c r="F1182" t="inlineStr">
-        <is>
-          <t>Харківська</t>
-        </is>
-      </c>
-      <c r="G1182" t="n">
-        <v>49.9908024</v>
-      </c>
-      <c r="H1182" t="n">
-        <v>36.3585856</v>
-      </c>
-      <c r="I1182" t="inlineStr">
-        <is>
-          <t>Пн: 09:00-18:00
-Вт: 09:00-18:00
-Ср: 09:00-18:00
-Чт: 09:00-18:00
-Пт: 09:00-18:00
-Сб: 09:00-17:00
-Нд: 09:00-17:00</t>
-        </is>
-      </c>
-      <c r="J1182" t="inlineStr">
-        <is>
-          <t>Харківська</t>
-        </is>
-      </c>
-    </row>
-    <row r="1183">
-      <c r="A1183" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1183" t="n">
-        <v>3544</v>
-      </c>
-      <c r="C1183" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1183" t="inlineStr">
-        <is>
-          <t>просп Петра Григоренка 3</t>
-        </is>
-      </c>
-      <c r="E1183" t="inlineStr">
-        <is>
-          <t>Харків</t>
-        </is>
-      </c>
-      <c r="F1183" t="inlineStr">
-        <is>
-          <t>Харківська</t>
-        </is>
-      </c>
-      <c r="G1183" t="n">
-        <v>49.9650438</v>
-      </c>
-      <c r="H1183" t="n">
-        <v>36.3219614</v>
-      </c>
-      <c r="I1183" t="inlineStr">
-        <is>
-          <t>Пн: 09:00-18:00
-Вт: 09:00-18:00
-Ср: 09:00-18:00
-Чт: 09:00-18:00
-Пт: 09:00-18:00
-Сб: 09:00-17:00
-Нд: 09:00-17:00</t>
-        </is>
-      </c>
-      <c r="J1183" t="inlineStr">
-        <is>
-          <t>Харківська</t>
-        </is>
-      </c>
-    </row>
-    <row r="1184">
-      <c r="A1184" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1184" t="n">
-        <v>3545</v>
-      </c>
-      <c r="C1184" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1184" t="inlineStr">
-        <is>
-          <t>просп Аерокосмічний (Гагаріна) 177</t>
-        </is>
-      </c>
-      <c r="E1184" t="inlineStr">
-        <is>
-          <t>Харків</t>
-        </is>
-      </c>
-      <c r="F1184" t="inlineStr">
-        <is>
-          <t>Харківська</t>
-        </is>
-      </c>
-      <c r="G1184" t="n">
-        <v>50.0169162</v>
-      </c>
-      <c r="H1184" t="n">
-        <v>36.2067146</v>
-      </c>
-      <c r="I1184" t="inlineStr">
-        <is>
-          <t>Пн: 09:00-18:00
-Вт: 09:00-18:00
-Ср: 09:00-18:00
-Чт: 09:00-18:00
-Пт: 09:00-18:00
-Сб: 09:00-17:00
-Нд: 09:00-17:00</t>
-        </is>
-      </c>
-      <c r="J1184" t="inlineStr">
-        <is>
-          <t>Харківська</t>
-        </is>
-      </c>
-    </row>
-    <row r="1185">
-      <c r="A1185" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1185" t="n">
-        <v>3547</v>
-      </c>
-      <c r="C1185" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1185" t="inlineStr">
-        <is>
-          <t>вул Олімпійська 75</t>
-        </is>
-      </c>
-      <c r="E1185" t="inlineStr">
-        <is>
-          <t>Хотин</t>
-        </is>
-      </c>
-      <c r="F1185" t="inlineStr">
-        <is>
-          <t>Чернівецька</t>
-        </is>
-      </c>
-      <c r="G1185" t="n">
-        <v>48.5043413</v>
-      </c>
-      <c r="H1185" t="n">
-        <v>26.490402</v>
-      </c>
-      <c r="I1185" t="inlineStr">
-        <is>
-          <t>Пн: 09:00-18:00
-Вт: 09:00-18:00
-Ср: 09:00-18:00
-Чт: 09:00-18:00
-Пт: 09:00-18:00
-Сб: 09:00-17:00
-Нд: 10:00-14:00</t>
-        </is>
-      </c>
-      <c r="J1185" t="inlineStr">
-        <is>
-          <t>Чернівецька</t>
-        </is>
-      </c>
-    </row>
-    <row r="1186">
-      <c r="A1186" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1186" t="n">
-        <v>3549</v>
-      </c>
-      <c r="C1186" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1186" t="inlineStr">
-        <is>
-          <t>вул Жовтнева 4-А</t>
-        </is>
-      </c>
-      <c r="E1186" t="inlineStr">
-        <is>
-          <t>Гребінка</t>
-        </is>
-      </c>
-      <c r="F1186" t="inlineStr">
-        <is>
-          <t>Полтавська</t>
-        </is>
-      </c>
-      <c r="G1186" t="n">
-        <v>50.1185138</v>
-      </c>
-      <c r="H1186" t="n">
-        <v>32.4391051</v>
-      </c>
-      <c r="I1186" t="inlineStr">
-        <is>
-          <t>Пн: 09:00-17:00
-Вт: 09:00-17:00
-Ср: 09:00-17:00
-Чт: 09:00-17:00
-Пт: 09:00-17:00
-Сб: 09:00-14:00
-Нд: 09:00-14:00</t>
-        </is>
-      </c>
-      <c r="J1186" t="inlineStr">
-        <is>
-          <t>Полтавська</t>
-        </is>
-      </c>
-    </row>
-    <row r="1187">
-      <c r="A1187" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1187" t="n">
-        <v>3554</v>
-      </c>
-      <c r="C1187" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1187" t="inlineStr">
-        <is>
-          <t>вул Городоцька 137</t>
-        </is>
-      </c>
-      <c r="E1187" t="inlineStr">
-        <is>
-          <t>Львів</t>
-        </is>
-      </c>
-      <c r="F1187" t="inlineStr">
-        <is>
-          <t>Львівська</t>
-        </is>
-      </c>
-      <c r="G1187" t="n">
-        <v>49.8367768</v>
-      </c>
-      <c r="H1187" t="n">
-        <v>24.0028087</v>
-      </c>
-      <c r="I1187" t="inlineStr">
-        <is>
-          <t>Пн: 09:00-19:00
-Вт: 09:00-19:00
-Ср: 09:00-19:00
-Чт: 09:00-19:00
-Пт: 09:00-19:00
-Сб: 09:00-18:00
-Нд: 10:00-18:00</t>
-        </is>
-      </c>
-      <c r="J1187" t="inlineStr">
-        <is>
-          <t>Львівська</t>
-        </is>
-      </c>
-    </row>
-    <row r="1188">
-      <c r="A1188" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1188" t="n">
-        <v>3555</v>
-      </c>
-      <c r="C1188" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1188" t="inlineStr">
-        <is>
-          <t>вул Здолбунівська 15</t>
-        </is>
-      </c>
-      <c r="E1188" t="inlineStr">
-        <is>
-          <t>Київ</t>
-        </is>
-      </c>
-      <c r="F1188" t="inlineStr">
-        <is>
-          <t>м. Київ</t>
-        </is>
-      </c>
-      <c r="G1188" t="n">
-        <v>50.4185123</v>
-      </c>
-      <c r="H1188" t="n">
-        <v>30.631541</v>
-      </c>
-      <c r="I1188" t="inlineStr">
-        <is>
-          <t>Пн: 10:00-20:00
-Вт: 10:00-20:00
-Ср: 10:00-20:00
-Чт: 10:00-20:00
-Пт: 10:00-20:00
-Сб: 10:00-20:00
-Нд: 10:00-20:00</t>
-        </is>
-      </c>
-      <c r="J1188" t="inlineStr">
-        <is>
-          <t>м. Київ</t>
-        </is>
-      </c>
-    </row>
-    <row r="1189">
-      <c r="A1189" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1189" t="n">
-        <v>3556</v>
-      </c>
-      <c r="C1189" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1189" t="inlineStr">
-        <is>
-          <t>вул Шевченка 42</t>
-        </is>
-      </c>
-      <c r="E1189" t="inlineStr">
-        <is>
-          <t>Овруч</t>
-        </is>
-      </c>
-      <c r="F1189" t="inlineStr">
-        <is>
-          <t>Житомирська</t>
-        </is>
-      </c>
-      <c r="G1189" t="n">
-        <v>51.3197441</v>
-      </c>
-      <c r="H1189" t="n">
-        <v>28.8004248</v>
-      </c>
-      <c r="I1189" t="inlineStr">
-        <is>
-          <t>Пн: 09:00-18:00
-Вт: 09:00-18:00
-Ср: 09:00-18:00
-Чт: 09:00-18:00
-Пт: 09:00-18:00
-Сб: 09:00-18:00
-Нд: 09:00-18:00</t>
-        </is>
-      </c>
-      <c r="J1189" t="inlineStr">
-        <is>
-          <t>Житомирська</t>
-        </is>
-      </c>
-    </row>
-    <row r="1190">
-      <c r="A1190" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1190" t="n">
-        <v>3558</v>
-      </c>
-      <c r="C1190" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1190" t="inlineStr">
-        <is>
-          <t>вул Київська 26</t>
-        </is>
-      </c>
-      <c r="E1190" t="inlineStr">
-        <is>
-          <t>Іванків</t>
-        </is>
-      </c>
-      <c r="F1190" t="inlineStr">
-        <is>
-          <t>Kiev</t>
-        </is>
-      </c>
-      <c r="G1190" t="n">
-        <v>50.9338356</v>
-      </c>
-      <c r="H1190" t="n">
-        <v>29.9031381</v>
-      </c>
-      <c r="I1190" t="inlineStr">
-        <is>
-          <t>Пн: 08:00-18:00
-Вт: 08:00-18:00
-Ср: 08:00-18:00
-Чт: 08:00-18:00
-Пт: 08:00-18:00
-Сб: 08:00-18:00
-Нд: 09:00-17:00</t>
-        </is>
-      </c>
-      <c r="J1190" t="inlineStr">
-        <is>
-          <t>Kiev</t>
-        </is>
-      </c>
-    </row>
-    <row r="1191">
-      <c r="A1191" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1191" t="n">
-        <v>3559</v>
-      </c>
-      <c r="C1191" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1191" t="inlineStr">
-        <is>
-          <t>просп Соборний 51</t>
-        </is>
-      </c>
-      <c r="E1191" t="inlineStr">
-        <is>
-          <t>Запоріжжя</t>
-        </is>
-      </c>
-      <c r="F1191" t="inlineStr">
-        <is>
-          <t>Zaporizhia</t>
-        </is>
-      </c>
-      <c r="G1191" t="n">
-        <v>47.8176164</v>
-      </c>
-      <c r="H1191" t="n">
-        <v>35.1753352</v>
-      </c>
-      <c r="I1191" t="inlineStr">
-        <is>
-          <t>Пн: 09:00-19:00
-Вт: 09:00-19:00
-Ср: 09:00-19:00
-Чт: 09:00-19:00
-Пт: 09:00-19:00
-Сб: 09:00-19:00
-Нд: 10:00-18:00</t>
-        </is>
-      </c>
-      <c r="J1191" t="inlineStr">
-        <is>
-          <t>Zaporizhia</t>
-        </is>
-      </c>
-    </row>
-    <row r="1192">
-      <c r="A1192" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1192" t="n">
-        <v>3560</v>
-      </c>
-      <c r="C1192" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1192" t="inlineStr">
-        <is>
-          <t>вул Палацова 9</t>
-        </is>
-      </c>
-      <c r="E1192" t="inlineStr">
-        <is>
-          <t>Краматорськ</t>
-        </is>
-      </c>
-      <c r="F1192" t="inlineStr">
-        <is>
-          <t>Донецька</t>
-        </is>
-      </c>
-      <c r="G1192" t="n">
-        <v>48.7366237</v>
-      </c>
-      <c r="H1192" t="n">
-        <v>37.5916381</v>
-      </c>
-      <c r="I1192" t="inlineStr">
-        <is>
-          <t>Пн: 09:00-17:00
-Вт: 09:00-17:00
-Ср: 09:00-17:00
-Чт: 09:00-17:00
-Пт: 09:00-17:00
-Сб: 09:00-17:00
-Нд: 09:00-17:00</t>
-        </is>
-      </c>
-      <c r="J1192" t="inlineStr">
-        <is>
-          <t>Донецька</t>
-        </is>
-      </c>
-    </row>
-    <row r="1193">
-      <c r="A1193" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1193" t="n">
-        <v>3561</v>
-      </c>
-      <c r="C1193" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1193" t="inlineStr">
-        <is>
-          <t>вул Ф. Караманець (Ватутіна) 29</t>
-        </is>
-      </c>
-      <c r="E1193" t="inlineStr">
-        <is>
-          <t>Кривий Ріг</t>
-        </is>
-      </c>
-      <c r="F1193" t="inlineStr">
-        <is>
-          <t>Дніпропетровська</t>
-        </is>
-      </c>
-      <c r="G1193" t="n">
-        <v>48.024687</v>
-      </c>
-      <c r="H1193" t="n">
-        <v>33.4709468</v>
-      </c>
-      <c r="I1193" t="inlineStr">
+      <c r="D1209" t="inlineStr">
+        <is>
+          <t>просп Адмиральський 37</t>
+        </is>
+      </c>
+      <c r="E1209" t="inlineStr">
+        <is>
+          <t>Одеса</t>
+        </is>
+      </c>
+      <c r="F1209" t="inlineStr">
+        <is>
+          <t>Odessa</t>
+        </is>
+      </c>
+      <c r="G1209" t="n">
+        <v>46.43745</v>
+      </c>
+      <c r="H1209" t="n">
+        <v>30.72675</v>
+      </c>
+      <c r="I1209" t="inlineStr">
         <is>
           <t>Пн: 09:00-18:00
 Вт: 09:00-18:00
@@ -55336,841 +56168,9 @@
 Нд: Вихідний</t>
         </is>
       </c>
-      <c r="J1193" t="inlineStr">
-        <is>
-          <t>Дніпропетровська</t>
-        </is>
-      </c>
-    </row>
-    <row r="1194">
-      <c r="A1194" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1194" t="n">
-        <v>3563</v>
-      </c>
-      <c r="C1194" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1194" t="inlineStr">
-        <is>
-          <t>вул Шевченка 116</t>
-        </is>
-      </c>
-      <c r="E1194" t="inlineStr">
-        <is>
-          <t>Дунаївці</t>
-        </is>
-      </c>
-      <c r="F1194" t="inlineStr">
-        <is>
-          <t>Хмельницька</t>
-        </is>
-      </c>
-      <c r="G1194" t="n">
-        <v>48.8922754</v>
-      </c>
-      <c r="H1194" t="n">
-        <v>26.8568241</v>
-      </c>
-      <c r="I1194" t="inlineStr">
-        <is>
-          <t>Пн: 09:00-18:00
-Вт: 09:00-18:00
-Ср: 09:00-18:00
-Чт: 09:00-18:00
-Пт: 09:00-18:00
-Сб: 09:00-14:00
-Нд: Вихідний</t>
-        </is>
-      </c>
-      <c r="J1194" t="inlineStr">
-        <is>
-          <t>Хмельницька</t>
-        </is>
-      </c>
-    </row>
-    <row r="1195">
-      <c r="A1195" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1195" t="n">
-        <v>3566</v>
-      </c>
-      <c r="C1195" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1195" t="inlineStr">
-        <is>
-          <t>вул Р. Шухевича 1а</t>
-        </is>
-      </c>
-      <c r="E1195" t="inlineStr">
-        <is>
-          <t>Хмельницький</t>
-        </is>
-      </c>
-      <c r="F1195" t="inlineStr">
-        <is>
-          <t>Хмельницька</t>
-        </is>
-      </c>
-      <c r="G1195" t="n">
-        <v>49.4360713</v>
-      </c>
-      <c r="H1195" t="n">
-        <v>26.9572295</v>
-      </c>
-      <c r="I1195" t="inlineStr">
-        <is>
-          <t>Пн: 09:00-19:00
-Вт: 09:00-19:00
-Ср: 09:00-19:00
-Чт: 09:00-19:00
-Пт: 09:00-19:00
-Сб: 10:00-18:00
-Нд: 10:00-18:00</t>
-        </is>
-      </c>
-      <c r="J1195" t="inlineStr">
-        <is>
-          <t>Хмельницька</t>
-        </is>
-      </c>
-    </row>
-    <row r="1196">
-      <c r="A1196" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1196" t="n">
-        <v>3567</v>
-      </c>
-      <c r="C1196" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1196" t="inlineStr">
-        <is>
-          <t>вул Макухи 1</t>
-        </is>
-      </c>
-      <c r="E1196" t="inlineStr">
-        <is>
-          <t>Тлумач</t>
-        </is>
-      </c>
-      <c r="F1196" t="inlineStr">
-        <is>
-          <t>Івано-Франківська</t>
-        </is>
-      </c>
-      <c r="G1196" t="n">
-        <v>48.8652727</v>
-      </c>
-      <c r="H1196" t="n">
-        <v>25.0043864</v>
-      </c>
-      <c r="I1196" t="inlineStr">
-        <is>
-          <t>Пн: 09:00-17:00
-Вт: 09:00-17:00
-Ср: 09:00-17:00
-Чт: 09:00-17:00
-Пт: 09:00-17:00
-Сб: Вихідний
-Нд: Вихідний</t>
-        </is>
-      </c>
-      <c r="J1196" t="inlineStr">
-        <is>
-          <t>Івано-Франківська</t>
-        </is>
-      </c>
-    </row>
-    <row r="1197">
-      <c r="A1197" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1197" t="n">
-        <v>3568</v>
-      </c>
-      <c r="C1197" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1197" t="inlineStr">
-        <is>
-          <t>вул Андріївська 5</t>
-        </is>
-      </c>
-      <c r="E1197" t="inlineStr">
-        <is>
-          <t>Березне</t>
-        </is>
-      </c>
-      <c r="F1197" t="inlineStr">
-        <is>
-          <t>Рівненська</t>
-        </is>
-      </c>
-      <c r="G1197" t="n">
-        <v>51.0019955</v>
-      </c>
-      <c r="H1197" t="n">
-        <v>26.7547284</v>
-      </c>
-      <c r="I1197" t="inlineStr">
-        <is>
-          <t>Пн: 09:00-18:00
-Вт: 09:00-18:00
-Ср: 09:00-18:00
-Чт: 09:00-18:00
-Пт: 09:00-18:00
-Сб: 09:00-16:00
-Нд: 09:00-16:00</t>
-        </is>
-      </c>
-      <c r="J1197" t="inlineStr">
-        <is>
-          <t>Рівненська</t>
-        </is>
-      </c>
-    </row>
-    <row r="1198">
-      <c r="A1198" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1198" t="n">
-        <v>3569</v>
-      </c>
-      <c r="C1198" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1198" t="inlineStr">
-        <is>
-          <t>вул Широка 37</t>
-        </is>
-      </c>
-      <c r="E1198" t="inlineStr">
-        <is>
-          <t>Сарни</t>
-        </is>
-      </c>
-      <c r="F1198" t="inlineStr">
-        <is>
-          <t>Рівненська</t>
-        </is>
-      </c>
-      <c r="G1198" t="n">
-        <v>51.3355537</v>
-      </c>
-      <c r="H1198" t="n">
-        <v>26.6158412</v>
-      </c>
-      <c r="I1198" t="inlineStr">
-        <is>
-          <t>Пн: 09:00-18:00
-Вт: 09:00-18:00
-Ср: 09:00-18:00
-Чт: 09:00-18:00
-Пт: 09:00-18:00
-Сб: 09:00-18:00
-Нд: 09:00-17:00</t>
-        </is>
-      </c>
-      <c r="J1198" t="inlineStr">
-        <is>
-          <t>Рівненська</t>
-        </is>
-      </c>
-    </row>
-    <row r="1199">
-      <c r="A1199" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1199" t="n">
-        <v>3570</v>
-      </c>
-      <c r="C1199" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1199" t="inlineStr">
-        <is>
-          <t>вул Січових Стрільців 33А</t>
-        </is>
-      </c>
-      <c r="E1199" t="inlineStr">
-        <is>
-          <t>Бурштин</t>
-        </is>
-      </c>
-      <c r="F1199" t="inlineStr">
-        <is>
-          <t>Івано-Франківська</t>
-        </is>
-      </c>
-      <c r="G1199" t="n">
-        <v>49.2511835</v>
-      </c>
-      <c r="H1199" t="n">
-        <v>24.6288295</v>
-      </c>
-      <c r="I1199" t="inlineStr">
-        <is>
-          <t>Пн: 09:00-18:00
-Вт: 09:00-18:00
-Ср: 09:00-18:00
-Чт: 09:00-18:00
-Пт: 09:00-18:00
-Сб: 09:00-17:00
-Нд: Вихідний</t>
-        </is>
-      </c>
-      <c r="J1199" t="inlineStr">
-        <is>
-          <t>Івано-Франківська</t>
-        </is>
-      </c>
-    </row>
-    <row r="1200">
-      <c r="A1200" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1200" t="n">
-        <v>3571</v>
-      </c>
-      <c r="C1200" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1200" t="inlineStr">
-        <is>
-          <t>вул Небесної Сотні 85</t>
-        </is>
-      </c>
-      <c r="E1200" t="inlineStr">
-        <is>
-          <t>Романів</t>
-        </is>
-      </c>
-      <c r="F1200" t="inlineStr">
-        <is>
-          <t>Житомирська</t>
-        </is>
-      </c>
-      <c r="G1200" t="n">
-        <v>50.141605</v>
-      </c>
-      <c r="H1200" t="n">
-        <v>27.934655</v>
-      </c>
-      <c r="I1200" t="inlineStr">
-        <is>
-          <t>Пн: 08:00-18:00
-Вт: 08:00-18:00
-Ср: 08:00-18:00
-Чт: 08:00-18:00
-Пт: 08:00-18:00
-Сб: 08:00-17:00
-Нд: 09:00-17:00</t>
-        </is>
-      </c>
-      <c r="J1200" t="inlineStr">
-        <is>
-          <t>Житомирська</t>
-        </is>
-      </c>
-    </row>
-    <row r="1201">
-      <c r="A1201" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1201" t="n">
-        <v>3573</v>
-      </c>
-      <c r="C1201" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1201" t="inlineStr">
-        <is>
-          <t>вул Велика Окружна 4</t>
-        </is>
-      </c>
-      <c r="E1201" t="inlineStr">
-        <is>
-          <t>Київ</t>
-        </is>
-      </c>
-      <c r="F1201" t="inlineStr">
-        <is>
-          <t>Kiev</t>
-        </is>
-      </c>
-      <c r="G1201" t="n">
-        <v>50.4295904</v>
-      </c>
-      <c r="H1201" t="n">
-        <v>30.3567847</v>
-      </c>
-      <c r="I1201" t="inlineStr">
-        <is>
-          <t>Пн: 10:00-21:00
-Вт: 10:00-21:00
-Ср: 10:00-21:00
-Чт: 10:00-21:00
-Пт: 10:00-21:00
-Сб: 10:00-21:00
-Нд: 10:00-21:00</t>
-        </is>
-      </c>
-      <c r="J1201" t="inlineStr">
-        <is>
-          <t>Kiev</t>
-        </is>
-      </c>
-    </row>
-    <row r="1202">
-      <c r="A1202" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1202" t="n">
-        <v>3574</v>
-      </c>
-      <c r="C1202" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1202" t="inlineStr">
-        <is>
-          <t>вул Шевченка 50</t>
-        </is>
-      </c>
-      <c r="E1202" t="inlineStr">
-        <is>
-          <t>Богородчани</t>
-        </is>
-      </c>
-      <c r="F1202" t="inlineStr">
-        <is>
-          <t>Івано-Франківська</t>
-        </is>
-      </c>
-      <c r="G1202" t="n">
-        <v>48.809756</v>
-      </c>
-      <c r="H1202" t="n">
-        <v>24.5400082</v>
-      </c>
-      <c r="I1202" t="inlineStr">
-        <is>
-          <t>Пн: 09:00-18:00
-Вт: 09:00-18:00
-Ср: 09:00-18:00
-Чт: 09:00-18:00
-Пт: 09:00-18:00
-Сб: 09:00-17:00
-Нд: 10:00-16:00</t>
-        </is>
-      </c>
-      <c r="J1202" t="inlineStr">
-        <is>
-          <t>Івано-Франківська</t>
-        </is>
-      </c>
-    </row>
-    <row r="1203">
-      <c r="A1203" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1203" t="n">
-        <v>3575</v>
-      </c>
-      <c r="C1203" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1203" t="inlineStr">
-        <is>
-          <t>просп Богдана Хмельницкого (Героїв Сталінграда) 118Д</t>
-        </is>
-      </c>
-      <c r="E1203" t="inlineStr">
-        <is>
-          <t>Дніпро</t>
-        </is>
-      </c>
-      <c r="F1203" t="inlineStr">
-        <is>
-          <t>Дніпропетровська</t>
-        </is>
-      </c>
-      <c r="G1203" t="n">
-        <v>48.4076054</v>
-      </c>
-      <c r="H1203" t="n">
-        <v>35.0004028</v>
-      </c>
-      <c r="I1203" t="inlineStr">
-        <is>
-          <t>Пн: 09:00-19:00
-Вт: 09:00-19:00
-Ср: 09:00-19:00
-Чт: 09:00-19:00
-Пт: 09:00-19:00
-Сб: 09:00-19:00
-Нд: 09:00-19:00</t>
-        </is>
-      </c>
-      <c r="J1203" t="inlineStr">
-        <is>
-          <t>Дніпропетровська</t>
-        </is>
-      </c>
-    </row>
-    <row r="1204">
-      <c r="A1204" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1204" t="n">
-        <v>3577</v>
-      </c>
-      <c r="C1204" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1204" t="inlineStr">
-        <is>
-          <t>вул Харківська 2/2</t>
-        </is>
-      </c>
-      <c r="E1204" t="inlineStr">
-        <is>
-          <t>Суми</t>
-        </is>
-      </c>
-      <c r="F1204" t="inlineStr">
-        <is>
-          <t>Сумська</t>
-        </is>
-      </c>
-      <c r="G1204" t="n">
-        <v>50.9041752</v>
-      </c>
-      <c r="H1204" t="n">
-        <v>34.8048057</v>
-      </c>
-      <c r="I1204" t="inlineStr">
-        <is>
-          <t>Пн: 10:00-19:00
-Вт: 10:00-19:00
-Ср: 10:00-19:00
-Чт: 10:00-19:00
-Пт: 10:00-19:00
-Сб: 10:00-19:00
-Нд: 10:00-19:00</t>
-        </is>
-      </c>
-      <c r="J1204" t="inlineStr">
-        <is>
-          <t>Сумська</t>
-        </is>
-      </c>
-    </row>
-    <row r="1205">
-      <c r="A1205" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1205" t="n">
-        <v>3579</v>
-      </c>
-      <c r="C1205" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1205" t="inlineStr">
-        <is>
-          <t>вул Грушевського 41А</t>
-        </is>
-      </c>
-      <c r="E1205" t="inlineStr">
-        <is>
-          <t>Первомайськ</t>
-        </is>
-      </c>
-      <c r="F1205" t="inlineStr">
-        <is>
-          <t>Миколаївська</t>
-        </is>
-      </c>
-      <c r="G1205" t="n">
-        <v>48.0425652</v>
-      </c>
-      <c r="H1205" t="n">
-        <v>30.8444596</v>
-      </c>
-      <c r="I1205" t="inlineStr">
-        <is>
-          <t>Пн: 08:00-18:00
-Вт: 08:00-18:00
-Ср: 08:00-18:00
-Чт: 08:00-18:00
-Пт: 08:00-18:00
-Сб: 10:00-17:00
-Нд: Вихідний</t>
-        </is>
-      </c>
-      <c r="J1205" t="inlineStr">
-        <is>
-          <t>Миколаївська</t>
-        </is>
-      </c>
-    </row>
-    <row r="1206">
-      <c r="A1206" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1206" t="n">
-        <v>3581</v>
-      </c>
-      <c r="C1206" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1206" t="inlineStr">
-        <is>
-          <t>вул Петровського, павільйон №8 2</t>
-        </is>
-      </c>
-      <c r="E1206" t="inlineStr">
-        <is>
-          <t>Городня</t>
-        </is>
-      </c>
-      <c r="F1206" t="inlineStr">
-        <is>
-          <t>Чернігівська</t>
-        </is>
-      </c>
-      <c r="G1206" t="n">
-        <v>51.8859534</v>
-      </c>
-      <c r="H1206" t="n">
-        <v>31.6026785</v>
-      </c>
-      <c r="I1206" t="inlineStr">
-        <is>
-          <t>Пн: 09:00-17:00
-Вт: 09:00-17:00
-Ср: 09:00-17:00
-Чт: 09:00-17:00
-Пт: Вихідний
-Сб: 09:00-14:00
-Нд: 09:00-14:00</t>
-        </is>
-      </c>
-      <c r="J1206" t="inlineStr">
-        <is>
-          <t>Чернігівська</t>
-        </is>
-      </c>
-    </row>
-    <row r="1207">
-      <c r="A1207" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1207" t="n">
-        <v>3582</v>
-      </c>
-      <c r="C1207" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1207" t="inlineStr">
-        <is>
-          <t>вул Святоюріївська 10/2</t>
-        </is>
-      </c>
-      <c r="E1207" t="inlineStr">
-        <is>
-          <t>Вишневе</t>
-        </is>
-      </c>
-      <c r="F1207" t="inlineStr">
-        <is>
-          <t>Kiev</t>
-        </is>
-      </c>
-      <c r="G1207" t="n">
-        <v>50.3833741</v>
-      </c>
-      <c r="H1207" t="n">
-        <v>30.3731464</v>
-      </c>
-      <c r="I1207" t="inlineStr">
-        <is>
-          <t>Пн: 09:00-19:00
-Вт: Вихідний
-Ср: 09:00-19:00
-Чт: 09:00-19:00
-Пт: Вихідний
-Сб: 09:00-19:00
-Нд: 09:00-19:00</t>
-        </is>
-      </c>
-      <c r="J1207" t="inlineStr">
-        <is>
-          <t>Kiev</t>
-        </is>
-      </c>
-    </row>
-    <row r="1208">
-      <c r="A1208" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1208" t="n">
-        <v>3583</v>
-      </c>
-      <c r="C1208" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1208" t="inlineStr">
-        <is>
-          <t>просп Відрадний 69/1</t>
-        </is>
-      </c>
-      <c r="E1208" t="inlineStr">
-        <is>
-          <t>Київ</t>
-        </is>
-      </c>
-      <c r="F1208" t="inlineStr">
-        <is>
-          <t>Kiev</t>
-        </is>
-      </c>
-      <c r="G1208" t="n">
-        <v>50.428885</v>
-      </c>
-      <c r="H1208" t="n">
-        <v>30.4309396</v>
-      </c>
-      <c r="I1208" t="inlineStr">
-        <is>
-          <t>Пн: 09:00-18:00
-Вт: 09:00-18:00
-Ср: 09:00-18:00
-Чт: 09:00-18:00
-Пт: 09:00-18:00
-Сб: 10:00-17:00
-Нд: Вихідний</t>
-        </is>
-      </c>
-      <c r="J1208" t="inlineStr">
-        <is>
-          <t>Kiev</t>
-        </is>
-      </c>
-    </row>
-    <row r="1209">
-      <c r="A1209" t="inlineStr">
-        <is>
-          <t>kyivstar</t>
-        </is>
-      </c>
-      <c r="B1209" t="n">
-        <v>3585</v>
-      </c>
-      <c r="C1209" t="inlineStr">
-        <is>
-          <t>Kyivstar</t>
-        </is>
-      </c>
-      <c r="D1209" t="inlineStr">
-        <is>
-          <t>вул Бориспільська 1</t>
-        </is>
-      </c>
-      <c r="E1209" t="inlineStr">
-        <is>
-          <t>Київ</t>
-        </is>
-      </c>
-      <c r="F1209" t="inlineStr">
-        <is>
-          <t>Kiev</t>
-        </is>
-      </c>
-      <c r="G1209" t="n">
-        <v>50.4313257</v>
-      </c>
-      <c r="H1209" t="n">
-        <v>30.6494712</v>
-      </c>
-      <c r="I1209" t="inlineStr">
-        <is>
-          <t>Пн: 09:00-18:00
-Вт: 09:00-18:00
-Ср: 09:00-18:00
-Чт: 09:00-18:00
-Пт: 09:00-18:00
-Сб: 09:00-17:00
-Нд: 09:00-17:00</t>
-        </is>
-      </c>
       <c r="J1209" t="inlineStr">
         <is>
-          <t>Kiev</t>
+          <t>Odessa</t>
         </is>
       </c>
     </row>
